--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>185100.03</v>
+        <v>338131.31</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>71.21069433</v>
+        <v>83.15975802</v>
       </c>
       <c r="E2" t="n">
-        <v>205</v>
+        <v>216</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,97 +509,118 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>50871.54</v>
+        <v>28370.02</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>19.571027</v>
+        <v>6.97730121</v>
       </c>
       <c r="E3" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Business/Economy</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>18435.53</v>
+        <v>26854.86</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>7.09241858</v>
+        <v>6.60466391</v>
       </c>
       <c r="E4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Business/Economy</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>3303.59</v>
+        <v>12206.22</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1.27093949</v>
+        <v>3.00198849</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>2222.22</v>
+        <v>554.28</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.8549206</v>
+        <v>0.1363192</v>
       </c>
       <c r="E6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>487.8</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0.11996916</v>
+      </c>
+      <c r="E7" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
-        <v>259932.91</v>
-      </c>
-      <c r="D7" s="6" t="n">
+      <c r="C8" s="5" t="n">
+        <v>406604.49</v>
+      </c>
+      <c r="D8" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E7" s="4" t="n">
-        <v>259</v>
+      <c r="E8" s="4" t="n">
+        <v>269</v>
       </c>
     </row>
   </sheetData>
@@ -613,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E268"/>
+  <dimension ref="A1:E274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6257,6 +6278,132 @@
         <v>205</v>
       </c>
     </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="n">
+        <v>26854.86</v>
+      </c>
+      <c r="D269" s="3" t="n">
+        <v>6.60466391</v>
+      </c>
+      <c r="E269" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="n">
+        <v>554.28</v>
+      </c>
+      <c r="D270" s="3" t="n">
+        <v>0.1363192</v>
+      </c>
+      <c r="E270" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="n">
+        <v>487.8</v>
+      </c>
+      <c r="D271" s="3" t="n">
+        <v>0.11996916</v>
+      </c>
+      <c r="E271" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="n">
+        <v>12206.22</v>
+      </c>
+      <c r="D272" s="3" t="n">
+        <v>3.00198849</v>
+      </c>
+      <c r="E272" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="n">
+        <v>28370.02</v>
+      </c>
+      <c r="D273" s="3" t="n">
+        <v>6.97730121</v>
+      </c>
+      <c r="E273" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="n">
+        <v>338131.31</v>
+      </c>
+      <c r="D274" s="3" t="n">
+        <v>83.15975802</v>
+      </c>
+      <c r="E274" t="n">
+        <v>216</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>338131.31</v>
+        <v>173578.47</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>83.15975802</v>
+        <v>69.22476868</v>
       </c>
       <c r="E2" t="n">
-        <v>216</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>28370.02</v>
+        <v>50514.02</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>6.97730121</v>
+        <v>20.14547858</v>
       </c>
       <c r="E3" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>26854.86</v>
+        <v>19985.78</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>6.60466391</v>
+        <v>7.97052191</v>
       </c>
       <c r="E4" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>12206.22</v>
+        <v>4445.7</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>3.00198849</v>
+        <v>1.77298806</v>
       </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,55 +572,34 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>554.28</v>
+        <v>2222.22</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.1363192</v>
+        <v>0.88624278</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Culture</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>487.8</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>0.11996916</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n">
-        <v>406604.49</v>
-      </c>
-      <c r="D8" s="6" t="n">
+      <c r="C7" s="5" t="n">
+        <v>250746.19</v>
+      </c>
+      <c r="D7" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E8" s="4" t="n">
-        <v>269</v>
+      <c r="E7" s="4" t="n">
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E274"/>
+  <dimension ref="A1:E279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6404,6 +6383,111 @@
         <v>216</v>
       </c>
     </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C275" s="2" t="n">
+        <v>19985.78</v>
+      </c>
+      <c r="D275" s="3" t="n">
+        <v>7.97052191</v>
+      </c>
+      <c r="E275" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C276" s="2" t="n">
+        <v>2222.22</v>
+      </c>
+      <c r="D276" s="3" t="n">
+        <v>0.88624278</v>
+      </c>
+      <c r="E276" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C277" s="2" t="n">
+        <v>4445.7</v>
+      </c>
+      <c r="D277" s="3" t="n">
+        <v>1.77298806</v>
+      </c>
+      <c r="E277" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C278" s="2" t="n">
+        <v>50514.02</v>
+      </c>
+      <c r="D278" s="3" t="n">
+        <v>20.14547858</v>
+      </c>
+      <c r="E278" t="n">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C279" s="2" t="n">
+        <v>173578.47</v>
+      </c>
+      <c r="D279" s="3" t="n">
+        <v>69.22476868</v>
+      </c>
+      <c r="E279" t="n">
+        <v>156</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,61 +488,61 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>173578.47</v>
+        <v>386921.44</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>69.22476868</v>
+        <v>82.46548108</v>
       </c>
       <c r="E2" t="n">
-        <v>156</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tech &amp; Science</t>
+          <t>Business/Economy</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>50514.02</v>
+        <v>40560.99</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>20.14547858</v>
+        <v>8.644859670000001</v>
       </c>
       <c r="E3" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Business/Economy</t>
+          <t>Tech &amp; Science</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>19985.78</v>
+        <v>34873.15</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>7.97052191</v>
+        <v>7.43259689</v>
       </c>
       <c r="E4" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,55 +551,34 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>4445.7</v>
+        <v>6836.42</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1.77298806</v>
+        <v>1.45706235</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Crypto</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>2222.22</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0.88624278</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
-        <v>250746.19</v>
-      </c>
-      <c r="D7" s="6" t="n">
+      <c r="C6" s="5" t="n">
+        <v>469192</v>
+      </c>
+      <c r="D6" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E7" s="4" t="n">
-        <v>208</v>
+      <c r="E6" s="4" t="n">
+        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -613,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E279"/>
+  <dimension ref="A1:E283"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6488,6 +6467,90 @@
         <v>156</v>
       </c>
     </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C280" s="2" t="n">
+        <v>40560.99</v>
+      </c>
+      <c r="D280" s="3" t="n">
+        <v>8.644859670000001</v>
+      </c>
+      <c r="E280" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C281" s="2" t="n">
+        <v>6836.42</v>
+      </c>
+      <c r="D281" s="3" t="n">
+        <v>1.45706235</v>
+      </c>
+      <c r="E281" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C282" s="2" t="n">
+        <v>34873.15</v>
+      </c>
+      <c r="D282" s="3" t="n">
+        <v>7.43259689</v>
+      </c>
+      <c r="E282" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C283" s="2" t="n">
+        <v>386921.44</v>
+      </c>
+      <c r="D283" s="3" t="n">
+        <v>82.46548108</v>
+      </c>
+      <c r="E283" t="n">
+        <v>179</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,97 +488,118 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>386921.44</v>
+        <v>152493.34</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>82.46548108</v>
+        <v>50.17144579</v>
       </c>
       <c r="E2" t="n">
-        <v>179</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Business/Economy</t>
+          <t>Tech &amp; Science</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>40560.99</v>
+        <v>82048.36</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>8.644859670000001</v>
+        <v>26.99452216</v>
       </c>
       <c r="E3" t="n">
-        <v>24</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tech &amp; Science</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>34873.15</v>
+        <v>67302.87</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>7.43259689</v>
+        <v>22.14314601</v>
       </c>
       <c r="E4" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>6836.42</v>
+        <v>2062.08</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1.45706235</v>
+        <v>0.67843969</v>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>37.83</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0.01244635</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n">
-        <v>469192</v>
-      </c>
-      <c r="D6" s="6" t="n">
+      <c r="C7" s="5" t="n">
+        <v>303944.48</v>
+      </c>
+      <c r="D7" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>242</v>
+      <c r="E7" s="4" t="n">
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -592,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E283"/>
+  <dimension ref="A1:E288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6551,6 +6572,111 @@
         <v>179</v>
       </c>
     </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C284" s="2" t="n">
+        <v>2062.08</v>
+      </c>
+      <c r="D284" s="3" t="n">
+        <v>0.67843969</v>
+      </c>
+      <c r="E284" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C285" s="2" t="n">
+        <v>67302.87</v>
+      </c>
+      <c r="D285" s="3" t="n">
+        <v>22.14314601</v>
+      </c>
+      <c r="E285" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C286" s="2" t="n">
+        <v>37.83</v>
+      </c>
+      <c r="D286" s="3" t="n">
+        <v>0.01244635</v>
+      </c>
+      <c r="E286" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C287" s="2" t="n">
+        <v>82048.36</v>
+      </c>
+      <c r="D287" s="3" t="n">
+        <v>26.99452216</v>
+      </c>
+      <c r="E287" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C288" s="2" t="n">
+        <v>152493.34</v>
+      </c>
+      <c r="D288" s="3" t="n">
+        <v>50.17144579</v>
+      </c>
+      <c r="E288" t="n">
+        <v>182</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,82 +488,82 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>152493.34</v>
+        <v>181053.97</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>50.17144579</v>
+        <v>89.78272215</v>
       </c>
       <c r="E2" t="n">
-        <v>182</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tech &amp; Science</t>
+          <t>Business/Economy</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>82048.36</v>
+        <v>16850.05</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>26.99452216</v>
+        <v>8.3557591</v>
       </c>
       <c r="E3" t="n">
-        <v>72</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Tech &amp; Science</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>67302.87</v>
+        <v>1989.87</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>22.14314601</v>
+        <v>0.98675519</v>
       </c>
       <c r="E4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2062.08</v>
+        <v>1221.31</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.67843969</v>
+        <v>0.60563453</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>37.83</v>
+        <v>542.72</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.01244635</v>
+        <v>0.26912903</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>303944.48</v>
+        <v>201657.92</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>266</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -613,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E288"/>
+  <dimension ref="A1:E293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6677,6 +6677,111 @@
         <v>182</v>
       </c>
     </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C289" s="2" t="n">
+        <v>16850.05</v>
+      </c>
+      <c r="D289" s="3" t="n">
+        <v>8.3557591</v>
+      </c>
+      <c r="E289" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C290" s="2" t="n">
+        <v>1221.31</v>
+      </c>
+      <c r="D290" s="3" t="n">
+        <v>0.60563453</v>
+      </c>
+      <c r="E290" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C291" s="2" t="n">
+        <v>542.72</v>
+      </c>
+      <c r="D291" s="3" t="n">
+        <v>0.26912903</v>
+      </c>
+      <c r="E291" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C292" s="2" t="n">
+        <v>1989.87</v>
+      </c>
+      <c r="D292" s="3" t="n">
+        <v>0.98675519</v>
+      </c>
+      <c r="E292" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C293" s="2" t="n">
+        <v>181053.97</v>
+      </c>
+      <c r="D293" s="3" t="n">
+        <v>89.78272215</v>
+      </c>
+      <c r="E293" t="n">
+        <v>162</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,118 +488,97 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>181053.97</v>
+        <v>120566.81</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>89.78272215</v>
+        <v>70.03621393</v>
       </c>
       <c r="E2" t="n">
-        <v>162</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Business/Economy</t>
+          <t>Tech &amp; Science</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>16850.05</v>
+        <v>42038.15</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>8.3557591</v>
+        <v>24.41959662</v>
       </c>
       <c r="E3" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tech &amp; Science</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1989.87</v>
+        <v>6752.82</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.98675519</v>
+        <v>3.92265455</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Business/Economy</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1221.31</v>
+        <v>2791.46</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.60563453</v>
+        <v>1.6215349</v>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Sports</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>542.72</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0.26912903</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
-        <v>201657.92</v>
-      </c>
-      <c r="D7" s="6" t="n">
+      <c r="C6" s="5" t="n">
+        <v>172149.24</v>
+      </c>
+      <c r="D6" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E7" s="4" t="n">
-        <v>181</v>
+      <c r="E6" s="4" t="n">
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -613,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E293"/>
+  <dimension ref="A1:E297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6782,6 +6761,90 @@
         <v>162</v>
       </c>
     </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C294" s="2" t="n">
+        <v>2791.46</v>
+      </c>
+      <c r="D294" s="3" t="n">
+        <v>1.6215349</v>
+      </c>
+      <c r="E294" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C295" s="2" t="n">
+        <v>6752.82</v>
+      </c>
+      <c r="D295" s="3" t="n">
+        <v>3.92265455</v>
+      </c>
+      <c r="E295" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C296" s="2" t="n">
+        <v>42038.15</v>
+      </c>
+      <c r="D296" s="3" t="n">
+        <v>24.41959662</v>
+      </c>
+      <c r="E296" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C297" s="2" t="n">
+        <v>120566.81</v>
+      </c>
+      <c r="D297" s="3" t="n">
+        <v>70.03621393</v>
+      </c>
+      <c r="E297" t="n">
+        <v>130</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,61 +488,61 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>120566.81</v>
+        <v>246387.68</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>70.03621393</v>
+        <v>94.44021005</v>
       </c>
       <c r="E2" t="n">
-        <v>130</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tech &amp; Science</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>42038.15</v>
+        <v>9364.209999999999</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>24.41959662</v>
+        <v>3.58929456</v>
       </c>
       <c r="E3" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Tech &amp; Science</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>6752.82</v>
+        <v>4780.88</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>3.92265455</v>
+        <v>1.83250766</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2791.46</v>
+        <v>360</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1.6215349</v>
+        <v>0.13798773</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -572,13 +572,13 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>172149.24</v>
+        <v>260892.77</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>154</v>
+        <v>226</v>
       </c>
     </row>
   </sheetData>
@@ -592,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E297"/>
+  <dimension ref="A1:E301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6845,6 +6845,90 @@
         <v>130</v>
       </c>
     </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C298" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="D298" s="3" t="n">
+        <v>0.13798773</v>
+      </c>
+      <c r="E298" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C299" s="2" t="n">
+        <v>9364.209999999999</v>
+      </c>
+      <c r="D299" s="3" t="n">
+        <v>3.58929456</v>
+      </c>
+      <c r="E299" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C300" s="2" t="n">
+        <v>4780.88</v>
+      </c>
+      <c r="D300" s="3" t="n">
+        <v>1.83250766</v>
+      </c>
+      <c r="E300" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C301" s="2" t="n">
+        <v>246387.68</v>
+      </c>
+      <c r="D301" s="3" t="n">
+        <v>94.44021005</v>
+      </c>
+      <c r="E301" t="n">
+        <v>208</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,97 +488,76 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>246387.68</v>
+        <v>204355.28</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>94.44021005</v>
+        <v>78.8469589</v>
       </c>
       <c r="E2" t="n">
-        <v>208</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Tech &amp; Science</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>9364.209999999999</v>
+        <v>48766.63</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>3.58929456</v>
+        <v>18.81576278</v>
       </c>
       <c r="E3" t="n">
-        <v>8</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tech &amp; Science</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>4780.88</v>
+        <v>6057.75</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1.83250766</v>
+        <v>2.33727832</v>
       </c>
       <c r="E4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Business/Economy</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>360</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>0.13798773</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n">
-        <v>260892.77</v>
-      </c>
-      <c r="D6" s="6" t="n">
+      <c r="C5" s="5" t="n">
+        <v>259179.66</v>
+      </c>
+      <c r="D5" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>226</v>
+      <c r="E5" s="4" t="n">
+        <v>336</v>
       </c>
     </row>
   </sheetData>
@@ -592,7 +571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E301"/>
+  <dimension ref="A1:E304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6929,6 +6908,69 @@
         <v>208</v>
       </c>
     </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C302" s="2" t="n">
+        <v>6057.75</v>
+      </c>
+      <c r="D302" s="3" t="n">
+        <v>2.33727832</v>
+      </c>
+      <c r="E302" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C303" s="2" t="n">
+        <v>48766.63</v>
+      </c>
+      <c r="D303" s="3" t="n">
+        <v>18.81576278</v>
+      </c>
+      <c r="E303" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C304" s="2" t="n">
+        <v>204355.28</v>
+      </c>
+      <c r="D304" s="3" t="n">
+        <v>78.8469589</v>
+      </c>
+      <c r="E304" t="n">
+        <v>260</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,76 +488,160 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>204355.28</v>
+        <v>195571.31</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>78.8469589</v>
+        <v>73.22160434</v>
       </c>
       <c r="E2" t="n">
-        <v>260</v>
+        <v>205</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tech &amp; Science</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>48766.63</v>
+        <v>22548.18</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>18.81576278</v>
+        <v>8.44200468</v>
       </c>
       <c r="E3" t="n">
-        <v>72</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Culture</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>6057.75</v>
+        <v>19175.48</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2.33727832</v>
+        <v>7.17927087</v>
       </c>
       <c r="E4" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>16523.23</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>6.18627246</v>
+      </c>
+      <c r="E5" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>9171.51</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>3.43379955</v>
+      </c>
+      <c r="E6" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>3105.38</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>1.1626496</v>
+      </c>
+      <c r="E7" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0.3743985</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n">
-        <v>259179.66</v>
-      </c>
-      <c r="D5" s="6" t="n">
+      <c r="C9" s="5" t="n">
+        <v>267095.09</v>
+      </c>
+      <c r="D9" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E5" s="4" t="n">
-        <v>336</v>
+      <c r="E9" s="4" t="n">
+        <v>277</v>
       </c>
     </row>
   </sheetData>
@@ -571,7 +655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E304"/>
+  <dimension ref="A1:E311"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6971,6 +7055,153 @@
         <v>260</v>
       </c>
     </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C305" s="2" t="n">
+        <v>16523.23</v>
+      </c>
+      <c r="D305" s="3" t="n">
+        <v>6.18627246</v>
+      </c>
+      <c r="E305" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C306" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D306" s="3" t="n">
+        <v>0.3743985</v>
+      </c>
+      <c r="E306" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C307" s="2" t="n">
+        <v>19175.48</v>
+      </c>
+      <c r="D307" s="3" t="n">
+        <v>7.17927087</v>
+      </c>
+      <c r="E307" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C308" s="2" t="n">
+        <v>22548.18</v>
+      </c>
+      <c r="D308" s="3" t="n">
+        <v>8.44200468</v>
+      </c>
+      <c r="E308" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C309" s="2" t="n">
+        <v>3105.38</v>
+      </c>
+      <c r="D309" s="3" t="n">
+        <v>1.1626496</v>
+      </c>
+      <c r="E309" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C310" s="2" t="n">
+        <v>9171.51</v>
+      </c>
+      <c r="D310" s="3" t="n">
+        <v>3.43379955</v>
+      </c>
+      <c r="E310" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C311" s="2" t="n">
+        <v>195571.31</v>
+      </c>
+      <c r="D311" s="3" t="n">
+        <v>73.22160434</v>
+      </c>
+      <c r="E311" t="n">
+        <v>205</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,160 +488,97 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>195571.31</v>
+        <v>199428.62</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>73.22160434</v>
+        <v>71.60172292</v>
       </c>
       <c r="E2" t="n">
-        <v>205</v>
+        <v>216</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Tech &amp; Science</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>22548.18</v>
+        <v>30092.08</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>8.44200468</v>
+        <v>10.80409008</v>
       </c>
       <c r="E3" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Culture</t>
+          <t>Business/Economy</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>19175.48</v>
+        <v>27350.51</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>7.17927087</v>
+        <v>9.8197723</v>
       </c>
       <c r="E4" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Business/Economy</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>16523.23</v>
+        <v>21653.68</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>6.18627246</v>
+        <v>7.7744147</v>
       </c>
       <c r="E5" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Tech &amp; Science</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>9171.51</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>3.43379955</v>
-      </c>
-      <c r="E6" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Sports</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>3105.38</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>1.1626496</v>
-      </c>
-      <c r="E7" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Crypto</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>0.3743985</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C9" s="5" t="n">
-        <v>267095.09</v>
-      </c>
-      <c r="D9" s="6" t="n">
+      <c r="C6" s="5" t="n">
+        <v>278524.89</v>
+      </c>
+      <c r="D6" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E9" s="4" t="n">
-        <v>277</v>
+      <c r="E6" s="4" t="n">
+        <v>262</v>
       </c>
     </row>
   </sheetData>
@@ -655,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E311"/>
+  <dimension ref="A1:E315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7202,6 +7139,90 @@
         <v>205</v>
       </c>
     </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C312" s="2" t="n">
+        <v>27350.51</v>
+      </c>
+      <c r="D312" s="3" t="n">
+        <v>9.8197723</v>
+      </c>
+      <c r="E312" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C313" s="2" t="n">
+        <v>21653.68</v>
+      </c>
+      <c r="D313" s="3" t="n">
+        <v>7.7744147</v>
+      </c>
+      <c r="E313" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C314" s="2" t="n">
+        <v>30092.08</v>
+      </c>
+      <c r="D314" s="3" t="n">
+        <v>10.80409008</v>
+      </c>
+      <c r="E314" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C315" s="2" t="n">
+        <v>199428.62</v>
+      </c>
+      <c r="D315" s="3" t="n">
+        <v>71.60172292</v>
+      </c>
+      <c r="E315" t="n">
+        <v>216</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,97 +488,139 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>199428.62</v>
+        <v>194181.54</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>71.60172292</v>
+        <v>62.78325757</v>
       </c>
       <c r="E2" t="n">
-        <v>216</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tech &amp; Science</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>30092.08</v>
+        <v>72445.86</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>10.80409008</v>
+        <v>23.4233753</v>
       </c>
       <c r="E3" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Business/Economy</t>
+          <t>Tech &amp; Science</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>27350.51</v>
+        <v>23146.75</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>9.8197723</v>
+        <v>7.48386467</v>
       </c>
       <c r="E4" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Business/Economy</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>21653.68</v>
+        <v>18403.89</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>7.7744147</v>
+        <v>5.9503914</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>1021.81</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0.33037415</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>88.88</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0.0287369</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n">
-        <v>278524.89</v>
-      </c>
-      <c r="D6" s="6" t="n">
+      <c r="C8" s="5" t="n">
+        <v>309288.73</v>
+      </c>
+      <c r="D8" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>262</v>
+      <c r="E8" s="4" t="n">
+        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -592,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E315"/>
+  <dimension ref="A1:E321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7223,6 +7265,132 @@
         <v>216</v>
       </c>
     </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C316" s="2" t="n">
+        <v>18403.89</v>
+      </c>
+      <c r="D316" s="3" t="n">
+        <v>5.9503914</v>
+      </c>
+      <c r="E316" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C317" s="2" t="n">
+        <v>88.88</v>
+      </c>
+      <c r="D317" s="3" t="n">
+        <v>0.0287369</v>
+      </c>
+      <c r="E317" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C318" s="2" t="n">
+        <v>72445.86</v>
+      </c>
+      <c r="D318" s="3" t="n">
+        <v>23.4233753</v>
+      </c>
+      <c r="E318" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C319" s="2" t="n">
+        <v>1021.81</v>
+      </c>
+      <c r="D319" s="3" t="n">
+        <v>0.33037415</v>
+      </c>
+      <c r="E319" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C320" s="2" t="n">
+        <v>23146.75</v>
+      </c>
+      <c r="D320" s="3" t="n">
+        <v>7.48386467</v>
+      </c>
+      <c r="E320" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C321" s="2" t="n">
+        <v>194181.54</v>
+      </c>
+      <c r="D321" s="3" t="n">
+        <v>62.78325757</v>
+      </c>
+      <c r="E321" t="n">
+        <v>190</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,61 +488,61 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>194181.54</v>
+        <v>209907.32</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>62.78325757</v>
+        <v>71.66787662</v>
       </c>
       <c r="E2" t="n">
-        <v>190</v>
+        <v>243</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Tech &amp; Science</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>72445.86</v>
+        <v>59465.09</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>23.4233753</v>
+        <v>20.30294481</v>
       </c>
       <c r="E3" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tech &amp; Science</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>23146.75</v>
+        <v>19747.53</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>7.48386467</v>
+        <v>6.74232582</v>
       </c>
       <c r="E4" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>18403.89</v>
+        <v>3620.25</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>5.9503914</v>
+        <v>1.23604851</v>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,55 +572,34 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1021.81</v>
+        <v>148.8</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.33037415</v>
+        <v>0.05080423</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Culture</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>88.88</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>0.0287369</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n">
-        <v>309288.73</v>
-      </c>
-      <c r="D8" s="6" t="n">
+      <c r="C7" s="5" t="n">
+        <v>292888.99</v>
+      </c>
+      <c r="D7" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E8" s="4" t="n">
-        <v>249</v>
+      <c r="E7" s="4" t="n">
+        <v>285</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E321"/>
+  <dimension ref="A1:E326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7391,6 +7370,111 @@
         <v>190</v>
       </c>
     </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C322" s="2" t="n">
+        <v>3620.25</v>
+      </c>
+      <c r="D322" s="3" t="n">
+        <v>1.23604851</v>
+      </c>
+      <c r="E322" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C323" s="2" t="n">
+        <v>19747.53</v>
+      </c>
+      <c r="D323" s="3" t="n">
+        <v>6.74232582</v>
+      </c>
+      <c r="E323" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C324" s="2" t="n">
+        <v>148.8</v>
+      </c>
+      <c r="D324" s="3" t="n">
+        <v>0.05080423</v>
+      </c>
+      <c r="E324" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C325" s="2" t="n">
+        <v>59465.09</v>
+      </c>
+      <c r="D325" s="3" t="n">
+        <v>20.30294481</v>
+      </c>
+      <c r="E325" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C326" s="2" t="n">
+        <v>209907.32</v>
+      </c>
+      <c r="D326" s="3" t="n">
+        <v>71.66787662</v>
+      </c>
+      <c r="E326" t="n">
+        <v>243</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>209907.32</v>
+        <v>236819.16</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>71.66787662</v>
+        <v>80.4669396</v>
       </c>
       <c r="E2" t="n">
-        <v>243</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,61 +509,61 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>59465.09</v>
+        <v>48724.48</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>20.30294481</v>
+        <v>16.55571192</v>
       </c>
       <c r="E3" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Business/Economy</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>19747.53</v>
+        <v>6884.07</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>6.74232582</v>
+        <v>2.33908458</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Business/Economy</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>3620.25</v>
+        <v>1851.18</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1.23604851</v>
+        <v>0.62899805</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,10 +572,10 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>148.8</v>
+        <v>27.27</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.05080423</v>
+        <v>0.009265860000000001</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>292888.99</v>
+        <v>294306.16</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>285</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -613,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E326"/>
+  <dimension ref="A1:E331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7475,6 +7475,111 @@
         <v>243</v>
       </c>
     </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C327" s="2" t="n">
+        <v>6884.07</v>
+      </c>
+      <c r="D327" s="3" t="n">
+        <v>2.33908458</v>
+      </c>
+      <c r="E327" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C328" s="2" t="n">
+        <v>1851.18</v>
+      </c>
+      <c r="D328" s="3" t="n">
+        <v>0.62899805</v>
+      </c>
+      <c r="E328" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C329" s="2" t="n">
+        <v>27.27</v>
+      </c>
+      <c r="D329" s="3" t="n">
+        <v>0.009265860000000001</v>
+      </c>
+      <c r="E329" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C330" s="2" t="n">
+        <v>48724.48</v>
+      </c>
+      <c r="D330" s="3" t="n">
+        <v>16.55571192</v>
+      </c>
+      <c r="E330" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C331" s="2" t="n">
+        <v>236819.16</v>
+      </c>
+      <c r="D331" s="3" t="n">
+        <v>80.4669396</v>
+      </c>
+      <c r="E331" t="n">
+        <v>190</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>236819.16</v>
+        <v>212632.81</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>80.4669396</v>
+        <v>69.30793795</v>
       </c>
       <c r="E2" t="n">
-        <v>190</v>
+        <v>206</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,61 +509,61 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>48724.48</v>
+        <v>47810.16</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>16.55571192</v>
+        <v>15.58378315</v>
       </c>
       <c r="E3" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Business/Economy</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>6884.07</v>
+        <v>44200.33</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2.33908458</v>
+        <v>14.40715442</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Business/Economy</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1851.18</v>
+        <v>1121.22</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.62899805</v>
+        <v>0.3654631</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>27.27</v>
+        <v>1029.79</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.009265860000000001</v>
+        <v>0.33566138</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>294306.16</v>
+        <v>306794.31</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>230</v>
+        <v>259</v>
       </c>
     </row>
   </sheetData>
@@ -613,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E331"/>
+  <dimension ref="A1:E336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7580,6 +7580,111 @@
         <v>190</v>
       </c>
     </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C332" s="2" t="n">
+        <v>1121.22</v>
+      </c>
+      <c r="D332" s="3" t="n">
+        <v>0.3654631</v>
+      </c>
+      <c r="E332" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C333" s="2" t="n">
+        <v>44200.33</v>
+      </c>
+      <c r="D333" s="3" t="n">
+        <v>14.40715442</v>
+      </c>
+      <c r="E333" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C334" s="2" t="n">
+        <v>1029.79</v>
+      </c>
+      <c r="D334" s="3" t="n">
+        <v>0.33566138</v>
+      </c>
+      <c r="E334" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C335" s="2" t="n">
+        <v>47810.16</v>
+      </c>
+      <c r="D335" s="3" t="n">
+        <v>15.58378315</v>
+      </c>
+      <c r="E335" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C336" s="2" t="n">
+        <v>212632.81</v>
+      </c>
+      <c r="D336" s="3" t="n">
+        <v>69.30793795</v>
+      </c>
+      <c r="E336" t="n">
+        <v>206</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>212632.81</v>
+        <v>152961.82</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>69.30793795</v>
+        <v>54.89389036</v>
       </c>
       <c r="E2" t="n">
-        <v>206</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>47810.16</v>
+        <v>77569.86</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>15.58378315</v>
+        <v>27.8377401</v>
       </c>
       <c r="E3" t="n">
-        <v>31</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>44200.33</v>
+        <v>41944.2</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>14.40715442</v>
+        <v>15.05264723</v>
       </c>
       <c r="E4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,55 +551,34 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1121.22</v>
+        <v>6174.11</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.3654631</v>
+        <v>2.21572231</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Sports</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>1029.79</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0.33566138</v>
-      </c>
-      <c r="E6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
-        <v>306794.31</v>
-      </c>
-      <c r="D7" s="6" t="n">
+      <c r="C6" s="5" t="n">
+        <v>278649.99</v>
+      </c>
+      <c r="D6" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E7" s="4" t="n">
-        <v>259</v>
+      <c r="E6" s="4" t="n">
+        <v>270</v>
       </c>
     </row>
   </sheetData>
@@ -613,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E336"/>
+  <dimension ref="A1:E340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7685,6 +7664,90 @@
         <v>206</v>
       </c>
     </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C337" s="2" t="n">
+        <v>6174.11</v>
+      </c>
+      <c r="D337" s="3" t="n">
+        <v>2.21572231</v>
+      </c>
+      <c r="E337" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C338" s="2" t="n">
+        <v>41944.2</v>
+      </c>
+      <c r="D338" s="3" t="n">
+        <v>15.05264723</v>
+      </c>
+      <c r="E338" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C339" s="2" t="n">
+        <v>77569.86</v>
+      </c>
+      <c r="D339" s="3" t="n">
+        <v>27.8377401</v>
+      </c>
+      <c r="E339" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C340" s="2" t="n">
+        <v>152961.82</v>
+      </c>
+      <c r="D340" s="3" t="n">
+        <v>54.89389036</v>
+      </c>
+      <c r="E340" t="n">
+        <v>166</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,49 +479,49 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Unclassified</t>
+          <t>Tech &amp; Science</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>152961.82</v>
+        <v>164042.55</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>54.89389036</v>
+        <v>45.92230724</v>
       </c>
       <c r="E2" t="n">
-        <v>166</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tech &amp; Science</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>77569.86</v>
+        <v>102446.97</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>27.8377401</v>
+        <v>28.67915204</v>
       </c>
       <c r="E3" t="n">
-        <v>81</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,55 +530,76 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>41944.2</v>
+        <v>57985.61</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>15.05264723</v>
+        <v>16.23257501</v>
       </c>
       <c r="E4" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>28414.86</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>7.95449675</v>
+      </c>
+      <c r="E5" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
-        <v>6174.11</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>2.21572231</v>
-      </c>
-      <c r="E5" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="C6" s="2" t="n">
+        <v>4327.58</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>1.21146897</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n">
-        <v>278649.99</v>
-      </c>
-      <c r="D6" s="6" t="n">
+      <c r="C7" s="5" t="n">
+        <v>357217.57</v>
+      </c>
+      <c r="D7" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>270</v>
+      <c r="E7" s="4" t="n">
+        <v>272</v>
       </c>
     </row>
   </sheetData>
@@ -592,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E340"/>
+  <dimension ref="A1:E345"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7748,6 +7769,111 @@
         <v>166</v>
       </c>
     </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C341" s="2" t="n">
+        <v>4327.58</v>
+      </c>
+      <c r="D341" s="3" t="n">
+        <v>1.21146897</v>
+      </c>
+      <c r="E341" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Culture</t>
+        </is>
+      </c>
+      <c r="C342" s="2" t="n">
+        <v>28414.86</v>
+      </c>
+      <c r="D342" s="3" t="n">
+        <v>7.95449675</v>
+      </c>
+      <c r="E342" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C343" s="2" t="n">
+        <v>57985.61</v>
+      </c>
+      <c r="D343" s="3" t="n">
+        <v>16.23257501</v>
+      </c>
+      <c r="E343" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C344" s="2" t="n">
+        <v>164042.55</v>
+      </c>
+      <c r="D344" s="3" t="n">
+        <v>45.92230724</v>
+      </c>
+      <c r="E344" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C345" s="2" t="n">
+        <v>102446.97</v>
+      </c>
+      <c r="D345" s="3" t="n">
+        <v>28.67915204</v>
+      </c>
+      <c r="E345" t="n">
+        <v>134</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,49 +479,49 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tech &amp; Science</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>164042.55</v>
+        <v>271430.81</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>45.92230724</v>
+        <v>56.60643722</v>
       </c>
       <c r="E2" t="n">
-        <v>58</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Unclassified</t>
+          <t>Tech &amp; Science</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>102446.97</v>
+        <v>131512.85</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>28.67915204</v>
+        <v>27.42678286</v>
       </c>
       <c r="E3" t="n">
-        <v>134</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,76 +530,55 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>57985.61</v>
+        <v>70012.2</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>16.23257501</v>
+        <v>14.60092612</v>
       </c>
       <c r="E4" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Culture</t>
+          <t>Business/Economy</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>28414.86</v>
+        <v>6549.34</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>7.95449675</v>
+        <v>1.3658538</v>
       </c>
       <c r="E5" t="n">
-        <v>47</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Business/Economy</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>4327.58</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>1.21146897</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
-        <v>357217.57</v>
-      </c>
-      <c r="D7" s="6" t="n">
+      <c r="C6" s="5" t="n">
+        <v>479505.2</v>
+      </c>
+      <c r="D6" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E7" s="4" t="n">
-        <v>272</v>
+      <c r="E6" s="4" t="n">
+        <v>253</v>
       </c>
     </row>
   </sheetData>
@@ -613,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E345"/>
+  <dimension ref="A1:E349"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -7874,6 +7853,90 @@
         <v>134</v>
       </c>
     </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C346" s="2" t="n">
+        <v>6549.34</v>
+      </c>
+      <c r="D346" s="3" t="n">
+        <v>1.3658538</v>
+      </c>
+      <c r="E346" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C347" s="2" t="n">
+        <v>70012.2</v>
+      </c>
+      <c r="D347" s="3" t="n">
+        <v>14.60092612</v>
+      </c>
+      <c r="E347" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C348" s="2" t="n">
+        <v>131512.85</v>
+      </c>
+      <c r="D348" s="3" t="n">
+        <v>27.42678286</v>
+      </c>
+      <c r="E348" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C349" s="2" t="n">
+        <v>271430.81</v>
+      </c>
+      <c r="D349" s="3" t="n">
+        <v>56.60643722</v>
+      </c>
+      <c r="E349" t="n">
+        <v>153</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -69,11 +69,11 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -477,108 +477,24 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Unclassified</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>271430.81</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>56.60643722</v>
-      </c>
-      <c r="E2" t="n">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Tech &amp; Science</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>131512.85</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>27.42678286</v>
-      </c>
-      <c r="E3" t="n">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Geopolitics</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>70012.2</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>14.60092612</v>
-      </c>
-      <c r="E4" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Business/Economy</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>6549.34</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>1.3658538</v>
-      </c>
-      <c r="E5" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n">
-        <v>479505.2</v>
-      </c>
-      <c r="D6" s="6" t="n">
+      <c r="C2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>253</v>
+      <c r="E2" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -640,10 +556,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="5" t="n">
         <v>948.86</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="6" t="n">
         <v>0.19126904</v>
       </c>
       <c r="E2" t="n">
@@ -661,10 +577,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="5" t="n">
         <v>461123.2</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="6" t="n">
         <v>92.95216732</v>
       </c>
       <c r="E3" t="n">
@@ -682,10 +598,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" s="5" t="n">
         <v>333</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="6" t="n">
         <v>0.06712538</v>
       </c>
       <c r="E4" t="n">
@@ -703,10 +619,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" s="5" t="n">
         <v>33681.49</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="6" t="n">
         <v>6.78943825</v>
       </c>
       <c r="E5" t="n">
@@ -724,10 +640,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" s="5" t="n">
         <v>3947.95</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="6" t="n">
         <v>0.94921987</v>
       </c>
       <c r="E6" t="n">
@@ -745,10 +661,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" s="5" t="n">
         <v>316928.34</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="6" t="n">
         <v>76.20022474</v>
       </c>
       <c r="E7" t="n">
@@ -766,10 +682,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="C8" s="5" t="n">
         <v>28879.81</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="6" t="n">
         <v>6.94367696</v>
       </c>
       <c r="E8" t="n">
@@ -787,10 +703,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n">
+      <c r="C9" s="5" t="n">
         <v>66159.13</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" s="6" t="n">
         <v>15.90687843</v>
       </c>
       <c r="E9" t="n">
@@ -808,10 +724,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n">
+      <c r="C10" s="5" t="n">
         <v>672.72</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D10" s="6" t="n">
         <v>0.12167625</v>
       </c>
       <c r="E10" t="n">
@@ -829,10 +745,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n">
+      <c r="C11" s="5" t="n">
         <v>506109.58</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="D11" s="6" t="n">
         <v>91.54108388</v>
       </c>
       <c r="E11" t="n">
@@ -850,10 +766,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n">
+      <c r="C12" s="5" t="n">
         <v>13144.61</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" s="6" t="n">
         <v>2.37749273</v>
       </c>
       <c r="E12" t="n">
@@ -871,10 +787,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n">
+      <c r="C13" s="5" t="n">
         <v>32950.07</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" s="6" t="n">
         <v>5.95974714</v>
       </c>
       <c r="E13" t="n">
@@ -892,10 +808,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
+      <c r="C14" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D14" s="6" t="n">
         <v>0.00340356</v>
       </c>
       <c r="E14" t="n">
@@ -913,10 +829,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n">
+      <c r="C15" s="5" t="n">
         <v>3803.45</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="D15" s="6" t="n">
         <v>1.43836189</v>
       </c>
       <c r="E15" t="n">
@@ -934,10 +850,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n">
+      <c r="C16" s="5" t="n">
         <v>229609.87</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D16" s="6" t="n">
         <v>86.83224112000001</v>
       </c>
       <c r="E16" t="n">
@@ -955,10 +871,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C17" s="2" t="n">
+      <c r="C17" s="5" t="n">
         <v>884.04</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="D17" s="6" t="n">
         <v>0.33432001</v>
       </c>
       <c r="E17" t="n">
@@ -976,10 +892,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C18" s="2" t="n">
+      <c r="C18" s="5" t="n">
         <v>30122.92</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="D18" s="6" t="n">
         <v>11.39167342</v>
       </c>
       <c r="E18" t="n">
@@ -997,10 +913,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C19" s="2" t="n">
+      <c r="C19" s="5" t="n">
         <v>23268.18</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="D19" s="6" t="n">
         <v>4.17124226</v>
       </c>
       <c r="E19" t="n">
@@ -1018,10 +934,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C20" s="2" t="n">
+      <c r="C20" s="5" t="n">
         <v>451338.15</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="D20" s="6" t="n">
         <v>80.91052954</v>
       </c>
       <c r="E20" t="n">
@@ -1039,10 +955,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C21" s="2" t="n">
+      <c r="C21" s="5" t="n">
         <v>20229.42</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="D21" s="6" t="n">
         <v>3.62648955</v>
       </c>
       <c r="E21" t="n">
@@ -1060,10 +976,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C22" s="2" t="n">
+      <c r="C22" s="5" t="n">
         <v>62988</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="D22" s="6" t="n">
         <v>11.29173865</v>
       </c>
       <c r="E22" t="n">
@@ -1081,10 +997,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C23" s="2" t="n">
+      <c r="C23" s="5" t="n">
         <v>103.09</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="D23" s="6" t="n">
         <v>0.02902112</v>
       </c>
       <c r="E23" t="n">
@@ -1102,10 +1018,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C24" s="2" t="n">
+      <c r="C24" s="5" t="n">
         <v>283.13</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="D24" s="6" t="n">
         <v>0.07970463</v>
       </c>
       <c r="E24" t="n">
@@ -1123,10 +1039,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n">
+      <c r="C25" s="5" t="n">
         <v>341584.75</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="D25" s="6" t="n">
         <v>96.16036696</v>
       </c>
       <c r="E25" t="n">
@@ -1144,10 +1060,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C26" s="2" t="n">
+      <c r="C26" s="5" t="n">
         <v>13253.08</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="D26" s="6" t="n">
         <v>3.7309073</v>
       </c>
       <c r="E26" t="n">
@@ -1165,10 +1081,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C27" s="2" t="n">
+      <c r="C27" s="5" t="n">
         <v>366675.1</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="D27" s="6" t="n">
         <v>88.88052623</v>
       </c>
       <c r="E27" t="n">
@@ -1186,10 +1102,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C28" s="2" t="n">
+      <c r="C28" s="5" t="n">
         <v>10967.83</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="D28" s="6" t="n">
         <v>2.65855659</v>
       </c>
       <c r="E28" t="n">
@@ -1207,10 +1123,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C29" s="2" t="n">
+      <c r="C29" s="5" t="n">
         <v>34905.37</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="D29" s="6" t="n">
         <v>8.460917179999999</v>
       </c>
       <c r="E29" t="n">
@@ -1228,10 +1144,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C30" s="2" t="n">
+      <c r="C30" s="5" t="n">
         <v>431085.81</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="D30" s="6" t="n">
         <v>81.83421629999999</v>
       </c>
       <c r="E30" t="n">
@@ -1249,10 +1165,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C31" s="2" t="n">
+      <c r="C31" s="5" t="n">
         <v>1633.45</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="D31" s="6" t="n">
         <v>0.31008235</v>
       </c>
       <c r="E31" t="n">
@@ -1270,10 +1186,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C32" s="2" t="n">
+      <c r="C32" s="5" t="n">
         <v>94060.16</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="D32" s="6" t="n">
         <v>17.85570135</v>
       </c>
       <c r="E32" t="n">
@@ -1291,10 +1207,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C33" s="2" t="n">
+      <c r="C33" s="5" t="n">
         <v>321805.16</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="D33" s="6" t="n">
         <v>78.53984421</v>
       </c>
       <c r="E33" t="n">
@@ -1312,10 +1228,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C34" s="2" t="n">
+      <c r="C34" s="5" t="n">
         <v>81063.48</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="D34" s="6" t="n">
         <v>19.78437229</v>
       </c>
       <c r="E34" t="n">
@@ -1333,10 +1249,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C35" s="2" t="n">
+      <c r="C35" s="5" t="n">
         <v>6866.27</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="D35" s="6" t="n">
         <v>1.6757835</v>
       </c>
       <c r="E35" t="n">
@@ -1354,10 +1270,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C36" s="2" t="n">
+      <c r="C36" s="5" t="n">
         <v>352851.14</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="D36" s="6" t="n">
         <v>94.15474251000001</v>
       </c>
       <c r="E36" t="n">
@@ -1375,10 +1291,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C37" s="2" t="n">
+      <c r="C37" s="5" t="n">
         <v>576.49</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="D37" s="6" t="n">
         <v>0.1538305</v>
       </c>
       <c r="E37" t="n">
@@ -1396,10 +1312,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C38" s="2" t="n">
+      <c r="C38" s="5" t="n">
         <v>21329</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="D38" s="6" t="n">
         <v>5.69142699</v>
       </c>
       <c r="E38" t="n">
@@ -1417,10 +1333,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C39" s="2" t="n">
+      <c r="C39" s="5" t="n">
         <v>83.52</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="D39" s="6" t="n">
         <v>0.01466719</v>
       </c>
       <c r="E39" t="n">
@@ -1438,10 +1354,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C40" s="2" t="n">
+      <c r="C40" s="5" t="n">
         <v>509873.13</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="D40" s="6" t="n">
         <v>89.54027855</v>
       </c>
       <c r="E40" t="n">
@@ -1459,10 +1375,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C41" s="2" t="n">
+      <c r="C41" s="5" t="n">
         <v>8520.23</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="D41" s="6" t="n">
         <v>1.49626196</v>
       </c>
       <c r="E41" t="n">
@@ -1480,10 +1396,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C42" s="2" t="n">
+      <c r="C42" s="5" t="n">
         <v>50957.5</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="D42" s="6" t="n">
         <v>8.94879231</v>
       </c>
       <c r="E42" t="n">
@@ -1501,10 +1417,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C43" s="2" t="n">
+      <c r="C43" s="5" t="n">
         <v>9326.15</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="D43" s="6" t="n">
         <v>1.62650962</v>
       </c>
       <c r="E43" t="n">
@@ -1522,10 +1438,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C44" s="2" t="n">
+      <c r="C44" s="5" t="n">
         <v>510341.61</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="D44" s="6" t="n">
         <v>89.00516713</v>
       </c>
       <c r="E44" t="n">
@@ -1543,10 +1459,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C45" s="2" t="n">
+      <c r="C45" s="5" t="n">
         <v>2517.04</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="D45" s="6" t="n">
         <v>0.43897962</v>
       </c>
       <c r="E45" t="n">
@@ -1564,10 +1480,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C46" s="2" t="n">
+      <c r="C46" s="5" t="n">
         <v>51199.45</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="D46" s="6" t="n">
         <v>8.92934363</v>
       </c>
       <c r="E46" t="n">
@@ -1585,10 +1501,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="C47" s="2" t="n">
+      <c r="C47" s="5" t="n">
         <v>850</v>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="D47" s="6" t="n">
         <v>0.25302704</v>
       </c>
       <c r="E47" t="n">
@@ -1606,10 +1522,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C48" s="2" t="n">
+      <c r="C48" s="5" t="n">
         <v>1223.36</v>
       </c>
-      <c r="D48" s="3" t="n">
+      <c r="D48" s="6" t="n">
         <v>0.36416843</v>
       </c>
       <c r="E48" t="n">
@@ -1627,10 +1543,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C49" s="2" t="n">
+      <c r="C49" s="5" t="n">
         <v>270843.56</v>
       </c>
-      <c r="D49" s="3" t="n">
+      <c r="D49" s="6" t="n">
         <v>80.62440645</v>
       </c>
       <c r="E49" t="n">
@@ -1648,10 +1564,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C50" s="2" t="n">
+      <c r="C50" s="5" t="n">
         <v>612.64</v>
       </c>
-      <c r="D50" s="3" t="n">
+      <c r="D50" s="6" t="n">
         <v>0.18236999</v>
       </c>
       <c r="E50" t="n">
@@ -1669,10 +1585,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C51" s="2" t="n">
+      <c r="C51" s="5" t="n">
         <v>62402.91</v>
       </c>
-      <c r="D51" s="3" t="n">
+      <c r="D51" s="6" t="n">
         <v>18.57602809</v>
       </c>
       <c r="E51" t="n">
@@ -1690,10 +1606,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C52" s="2" t="n">
+      <c r="C52" s="5" t="n">
         <v>555930.41</v>
       </c>
-      <c r="D52" s="3" t="n">
+      <c r="D52" s="6" t="n">
         <v>91.1452503</v>
       </c>
       <c r="E52" t="n">
@@ -1711,10 +1627,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C53" s="2" t="n">
+      <c r="C53" s="5" t="n">
         <v>1590.9</v>
       </c>
-      <c r="D53" s="3" t="n">
+      <c r="D53" s="6" t="n">
         <v>0.26082937</v>
       </c>
       <c r="E53" t="n">
@@ -1732,10 +1648,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C54" s="2" t="n">
+      <c r="C54" s="5" t="n">
         <v>52417.67</v>
       </c>
-      <c r="D54" s="3" t="n">
+      <c r="D54" s="6" t="n">
         <v>8.59392033</v>
       </c>
       <c r="E54" t="n">
@@ -1753,10 +1669,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C55" s="2" t="n">
+      <c r="C55" s="5" t="n">
         <v>10.55</v>
       </c>
-      <c r="D55" s="3" t="n">
+      <c r="D55" s="6" t="n">
         <v>0.00287103</v>
       </c>
       <c r="E55" t="n">
@@ -1774,10 +1690,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C56" s="2" t="n">
+      <c r="C56" s="5" t="n">
         <v>319888.32</v>
       </c>
-      <c r="D56" s="3" t="n">
+      <c r="D56" s="6" t="n">
         <v>87.05305848</v>
       </c>
       <c r="E56" t="n">
@@ -1795,10 +1711,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C57" s="2" t="n">
+      <c r="C57" s="5" t="n">
         <v>1278.17</v>
       </c>
-      <c r="D57" s="3" t="n">
+      <c r="D57" s="6" t="n">
         <v>0.34783579</v>
       </c>
       <c r="E57" t="n">
@@ -1816,10 +1732,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C58" s="2" t="n">
+      <c r="C58" s="5" t="n">
         <v>46286.58</v>
       </c>
-      <c r="D58" s="3" t="n">
+      <c r="D58" s="6" t="n">
         <v>12.5962347</v>
       </c>
       <c r="E58" t="n">
@@ -1837,10 +1753,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C59" s="2" t="n">
+      <c r="C59" s="5" t="n">
         <v>354.29</v>
       </c>
-      <c r="D59" s="3" t="n">
+      <c r="D59" s="6" t="n">
         <v>0.1171275</v>
       </c>
       <c r="E59" t="n">
@@ -1858,10 +1774,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C60" s="2" t="n">
+      <c r="C60" s="5" t="n">
         <v>121.49</v>
       </c>
-      <c r="D60" s="3" t="n">
+      <c r="D60" s="6" t="n">
         <v>0.04016433</v>
       </c>
       <c r="E60" t="n">
@@ -1879,10 +1795,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C61" s="2" t="n">
+      <c r="C61" s="5" t="n">
         <v>264522.3</v>
       </c>
-      <c r="D61" s="3" t="n">
+      <c r="D61" s="6" t="n">
         <v>87.4504938</v>
       </c>
       <c r="E61" t="n">
@@ -1900,10 +1816,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C62" s="2" t="n">
+      <c r="C62" s="5" t="n">
         <v>1149.77</v>
       </c>
-      <c r="D62" s="3" t="n">
+      <c r="D62" s="6" t="n">
         <v>0.38011145</v>
       </c>
       <c r="E62" t="n">
@@ -1921,10 +1837,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C63" s="2" t="n">
+      <c r="C63" s="5" t="n">
         <v>36334.49</v>
       </c>
-      <c r="D63" s="3" t="n">
+      <c r="D63" s="6" t="n">
         <v>12.01210292</v>
       </c>
       <c r="E63" t="n">
@@ -1942,10 +1858,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C64" s="2" t="n">
+      <c r="C64" s="5" t="n">
         <v>4545.45</v>
       </c>
-      <c r="D64" s="3" t="n">
+      <c r="D64" s="6" t="n">
         <v>1.24043036</v>
       </c>
       <c r="E64" t="n">
@@ -1963,10 +1879,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C65" s="2" t="n">
+      <c r="C65" s="5" t="n">
         <v>874</v>
       </c>
-      <c r="D65" s="3" t="n">
+      <c r="D65" s="6" t="n">
         <v>0.23851019</v>
       </c>
       <c r="E65" t="n">
@@ -1984,10 +1900,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C66" s="2" t="n">
+      <c r="C66" s="5" t="n">
         <v>284866.12</v>
       </c>
-      <c r="D66" s="3" t="n">
+      <c r="D66" s="6" t="n">
         <v>77.73852608</v>
       </c>
       <c r="E66" t="n">
@@ -2005,10 +1921,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C67" s="2" t="n">
+      <c r="C67" s="5" t="n">
         <v>1590.95</v>
       </c>
-      <c r="D67" s="3" t="n">
+      <c r="D67" s="6" t="n">
         <v>0.43416222</v>
       </c>
       <c r="E67" t="n">
@@ -2026,10 +1942,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C68" s="2" t="n">
+      <c r="C68" s="5" t="n">
         <v>74564.85000000001</v>
       </c>
-      <c r="D68" s="3" t="n">
+      <c r="D68" s="6" t="n">
         <v>20.34837115</v>
       </c>
       <c r="E68" t="n">
@@ -2047,10 +1963,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C69" s="2" t="n">
+      <c r="C69" s="5" t="n">
         <v>442814.15</v>
       </c>
-      <c r="D69" s="3" t="n">
+      <c r="D69" s="6" t="n">
         <v>80.48822254</v>
       </c>
       <c r="E69" t="n">
@@ -2068,10 +1984,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C70" s="2" t="n">
+      <c r="C70" s="5" t="n">
         <v>914.39</v>
       </c>
-      <c r="D70" s="3" t="n">
+      <c r="D70" s="6" t="n">
         <v>0.16620432</v>
       </c>
       <c r="E70" t="n">
@@ -2089,10 +2005,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C71" s="2" t="n">
+      <c r="C71" s="5" t="n">
         <v>106431.64</v>
       </c>
-      <c r="D71" s="3" t="n">
+      <c r="D71" s="6" t="n">
         <v>19.34557314</v>
       </c>
       <c r="E71" t="n">
@@ -2110,10 +2026,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C72" s="2" t="n">
+      <c r="C72" s="5" t="n">
         <v>166</v>
       </c>
-      <c r="D72" s="3" t="n">
+      <c r="D72" s="6" t="n">
         <v>0.02878159</v>
       </c>
       <c r="E72" t="n">
@@ -2131,10 +2047,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C73" s="2" t="n">
+      <c r="C73" s="5" t="n">
         <v>81.83</v>
       </c>
-      <c r="D73" s="3" t="n">
+      <c r="D73" s="6" t="n">
         <v>0.01418794</v>
       </c>
       <c r="E73" t="n">
@@ -2152,10 +2068,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C74" s="2" t="n">
+      <c r="C74" s="5" t="n">
         <v>528120.33</v>
       </c>
-      <c r="D74" s="3" t="n">
+      <c r="D74" s="6" t="n">
         <v>91.56712743999999</v>
       </c>
       <c r="E74" t="n">
@@ -2173,10 +2089,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C75" s="2" t="n">
+      <c r="C75" s="5" t="n">
         <v>567.3200000000001</v>
       </c>
-      <c r="D75" s="3" t="n">
+      <c r="D75" s="6" t="n">
         <v>0.09836369</v>
       </c>
       <c r="E75" t="n">
@@ -2194,10 +2110,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C76" s="2" t="n">
+      <c r="C76" s="5" t="n">
         <v>47822.08</v>
       </c>
-      <c r="D76" s="3" t="n">
+      <c r="D76" s="6" t="n">
         <v>8.29153934</v>
       </c>
       <c r="E76" t="n">
@@ -2215,10 +2131,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C77" s="2" t="n">
+      <c r="C77" s="5" t="n">
         <v>2157.29</v>
       </c>
-      <c r="D77" s="3" t="n">
+      <c r="D77" s="6" t="n">
         <v>1.00708473</v>
       </c>
       <c r="E77" t="n">
@@ -2236,10 +2152,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C78" s="2" t="n">
+      <c r="C78" s="5" t="n">
         <v>177127.26</v>
       </c>
-      <c r="D78" s="3" t="n">
+      <c r="D78" s="6" t="n">
         <v>82.68807579999999</v>
       </c>
       <c r="E78" t="n">
@@ -2257,10 +2173,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C79" s="2" t="n">
+      <c r="C79" s="5" t="n">
         <v>826.1799999999999</v>
       </c>
-      <c r="D79" s="3" t="n">
+      <c r="D79" s="6" t="n">
         <v>0.38568448</v>
       </c>
       <c r="E79" t="n">
@@ -2278,10 +2194,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C80" s="2" t="n">
+      <c r="C80" s="5" t="n">
         <v>34100.64</v>
       </c>
-      <c r="D80" s="3" t="n">
+      <c r="D80" s="6" t="n">
         <v>15.91915499</v>
       </c>
       <c r="E80" t="n">
@@ -2299,10 +2215,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C81" s="2" t="n">
+      <c r="C81" s="5" t="n">
         <v>54.12</v>
       </c>
-      <c r="D81" s="3" t="n">
+      <c r="D81" s="6" t="n">
         <v>0.01747125</v>
       </c>
       <c r="E81" t="n">
@@ -2320,10 +2236,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C82" s="2" t="n">
+      <c r="C82" s="5" t="n">
         <v>66</v>
       </c>
-      <c r="D82" s="3" t="n">
+      <c r="D82" s="6" t="n">
         <v>0.0213064</v>
       </c>
       <c r="E82" t="n">
@@ -2341,10 +2257,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C83" s="2" t="n">
+      <c r="C83" s="5" t="n">
         <v>21771.31</v>
       </c>
-      <c r="D83" s="3" t="n">
+      <c r="D83" s="6" t="n">
         <v>7.02830778</v>
       </c>
       <c r="E83" t="n">
@@ -2362,10 +2278,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C84" s="2" t="n">
+      <c r="C84" s="5" t="n">
         <v>214416.2</v>
       </c>
-      <c r="D84" s="3" t="n">
+      <c r="D84" s="6" t="n">
         <v>69.21875842999999</v>
       </c>
       <c r="E84" t="n">
@@ -2383,10 +2299,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C85" s="2" t="n">
+      <c r="C85" s="5" t="n">
         <v>9060.450000000001</v>
       </c>
-      <c r="D85" s="3" t="n">
+      <c r="D85" s="6" t="n">
         <v>2.92493338</v>
       </c>
       <c r="E85" t="n">
@@ -2404,10 +2320,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C86" s="2" t="n">
+      <c r="C86" s="5" t="n">
         <v>64397.95</v>
       </c>
-      <c r="D86" s="3" t="n">
+      <c r="D86" s="6" t="n">
         <v>20.78922276</v>
       </c>
       <c r="E86" t="n">
@@ -2425,10 +2341,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C87" s="2" t="n">
+      <c r="C87" s="5" t="n">
         <v>1067.9</v>
       </c>
-      <c r="D87" s="3" t="n">
+      <c r="D87" s="6" t="n">
         <v>0.29681338</v>
       </c>
       <c r="E87" t="n">
@@ -2446,10 +2362,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C88" s="2" t="n">
+      <c r="C88" s="5" t="n">
         <v>260988.37</v>
       </c>
-      <c r="D88" s="3" t="n">
+      <c r="D88" s="6" t="n">
         <v>72.53941456</v>
       </c>
       <c r="E88" t="n">
@@ -2467,10 +2383,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C89" s="2" t="n">
+      <c r="C89" s="5" t="n">
         <v>7522.28</v>
       </c>
-      <c r="D89" s="3" t="n">
+      <c r="D89" s="6" t="n">
         <v>2.09075135</v>
       </c>
       <c r="E89" t="n">
@@ -2488,10 +2404,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C90" s="2" t="n">
+      <c r="C90" s="5" t="n">
         <v>90209.81</v>
       </c>
-      <c r="D90" s="3" t="n">
+      <c r="D90" s="6" t="n">
         <v>25.07302071</v>
       </c>
       <c r="E90" t="n">
@@ -2509,10 +2425,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C91" s="2" t="n">
+      <c r="C91" s="5" t="n">
         <v>11124.49</v>
       </c>
-      <c r="D91" s="3" t="n">
+      <c r="D91" s="6" t="n">
         <v>3.35098295</v>
       </c>
       <c r="E91" t="n">
@@ -2530,10 +2446,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C92" s="2" t="n">
+      <c r="C92" s="5" t="n">
         <v>201888.41</v>
       </c>
-      <c r="D92" s="3" t="n">
+      <c r="D92" s="6" t="n">
         <v>60.81398972</v>
       </c>
       <c r="E92" t="n">
@@ -2551,10 +2467,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C93" s="2" t="n">
+      <c r="C93" s="5" t="n">
         <v>15503.87</v>
       </c>
-      <c r="D93" s="3" t="n">
+      <c r="D93" s="6" t="n">
         <v>4.67016502</v>
       </c>
       <c r="E93" t="n">
@@ -2572,10 +2488,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C94" s="2" t="n">
+      <c r="C94" s="5" t="n">
         <v>103460.15</v>
       </c>
-      <c r="D94" s="3" t="n">
+      <c r="D94" s="6" t="n">
         <v>31.1648623</v>
       </c>
       <c r="E94" t="n">
@@ -2593,10 +2509,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C95" s="2" t="n">
+      <c r="C95" s="5" t="n">
         <v>1029.41</v>
       </c>
-      <c r="D95" s="3" t="n">
+      <c r="D95" s="6" t="n">
         <v>0.31513536</v>
       </c>
       <c r="E95" t="n">
@@ -2614,10 +2530,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C96" s="2" t="n">
+      <c r="C96" s="5" t="n">
         <v>1848</v>
       </c>
-      <c r="D96" s="3" t="n">
+      <c r="D96" s="6" t="n">
         <v>0.56573196</v>
       </c>
       <c r="E96" t="n">
@@ -2635,10 +2551,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C97" s="2" t="n">
+      <c r="C97" s="5" t="n">
         <v>126297.98</v>
       </c>
-      <c r="D97" s="3" t="n">
+      <c r="D97" s="6" t="n">
         <v>38.66385499</v>
       </c>
       <c r="E97" t="n">
@@ -2656,10 +2572,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C98" s="2" t="n">
+      <c r="C98" s="5" t="n">
         <v>23680.09</v>
       </c>
-      <c r="D98" s="3" t="n">
+      <c r="D98" s="6" t="n">
         <v>7.24923364</v>
       </c>
       <c r="E98" t="n">
@@ -2677,10 +2593,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C99" s="2" t="n">
+      <c r="C99" s="5" t="n">
         <v>173800.98</v>
       </c>
-      <c r="D99" s="3" t="n">
+      <c r="D99" s="6" t="n">
         <v>53.20604405</v>
       </c>
       <c r="E99" t="n">
@@ -2698,10 +2614,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C100" s="2" t="n">
+      <c r="C100" s="5" t="n">
         <v>856.11</v>
       </c>
-      <c r="D100" s="3" t="n">
+      <c r="D100" s="6" t="n">
         <v>0.22747196</v>
       </c>
       <c r="E100" t="n">
@@ -2719,10 +2635,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C101" s="2" t="n">
+      <c r="C101" s="5" t="n">
         <v>9.68</v>
       </c>
-      <c r="D101" s="3" t="n">
+      <c r="D101" s="6" t="n">
         <v>0.00257202</v>
       </c>
       <c r="E101" t="n">
@@ -2740,10 +2656,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C102" s="2" t="n">
+      <c r="C102" s="5" t="n">
         <v>296012.79</v>
       </c>
-      <c r="D102" s="3" t="n">
+      <c r="D102" s="6" t="n">
         <v>78.65181887</v>
       </c>
       <c r="E102" t="n">
@@ -2761,10 +2677,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C103" s="2" t="n">
+      <c r="C103" s="5" t="n">
         <v>3709.15</v>
       </c>
-      <c r="D103" s="3" t="n">
+      <c r="D103" s="6" t="n">
         <v>0.98553645</v>
       </c>
       <c r="E103" t="n">
@@ -2782,10 +2698,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C104" s="2" t="n">
+      <c r="C104" s="5" t="n">
         <v>75770.75</v>
       </c>
-      <c r="D104" s="3" t="n">
+      <c r="D104" s="6" t="n">
         <v>20.13260071</v>
       </c>
       <c r="E104" t="n">
@@ -2803,10 +2719,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C105" s="2" t="n">
+      <c r="C105" s="5" t="n">
         <v>363.62</v>
       </c>
-      <c r="D105" s="3" t="n">
+      <c r="D105" s="6" t="n">
         <v>0.09792976</v>
       </c>
       <c r="E105" t="n">
@@ -2824,10 +2740,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C106" s="2" t="n">
+      <c r="C106" s="5" t="n">
         <v>303265.05</v>
       </c>
-      <c r="D106" s="3" t="n">
+      <c r="D106" s="6" t="n">
         <v>81.67502655</v>
       </c>
       <c r="E106" t="n">
@@ -2845,10 +2761,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C107" s="2" t="n">
+      <c r="C107" s="5" t="n">
         <v>829.42</v>
       </c>
-      <c r="D107" s="3" t="n">
+      <c r="D107" s="6" t="n">
         <v>0.22337853</v>
       </c>
       <c r="E107" t="n">
@@ -2866,10 +2782,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C108" s="2" t="n">
+      <c r="C108" s="5" t="n">
         <v>66848.86</v>
       </c>
-      <c r="D108" s="3" t="n">
+      <c r="D108" s="6" t="n">
         <v>18.00366516</v>
       </c>
       <c r="E108" t="n">
@@ -2887,10 +2803,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C109" s="2" t="n">
+      <c r="C109" s="5" t="n">
         <v>174192.16</v>
       </c>
-      <c r="D109" s="3" t="n">
+      <c r="D109" s="6" t="n">
         <v>66.86566559000001</v>
       </c>
       <c r="E109" t="n">
@@ -2908,10 +2824,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C110" s="2" t="n">
+      <c r="C110" s="5" t="n">
         <v>19438.25</v>
       </c>
-      <c r="D110" s="3" t="n">
+      <c r="D110" s="6" t="n">
         <v>7.461596</v>
       </c>
       <c r="E110" t="n">
@@ -2929,10 +2845,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C111" s="2" t="n">
+      <c r="C111" s="5" t="n">
         <v>66880.21000000001</v>
       </c>
-      <c r="D111" s="3" t="n">
+      <c r="D111" s="6" t="n">
         <v>25.67273841</v>
       </c>
       <c r="E111" t="n">
@@ -2950,10 +2866,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C112" s="2" t="n">
+      <c r="C112" s="5" t="n">
         <v>1885.29</v>
       </c>
-      <c r="D112" s="3" t="n">
+      <c r="D112" s="6" t="n">
         <v>0.5105483200000001</v>
       </c>
       <c r="E112" t="n">
@@ -2971,10 +2887,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C113" s="2" t="n">
+      <c r="C113" s="5" t="n">
         <v>642.63</v>
       </c>
-      <c r="D113" s="3" t="n">
+      <c r="D113" s="6" t="n">
         <v>0.17402822</v>
       </c>
       <c r="E113" t="n">
@@ -2992,10 +2908,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C114" s="2" t="n">
+      <c r="C114" s="5" t="n">
         <v>2177.75</v>
       </c>
-      <c r="D114" s="3" t="n">
+      <c r="D114" s="6" t="n">
         <v>0.58974832</v>
       </c>
       <c r="E114" t="n">
@@ -3013,10 +2929,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C115" s="2" t="n">
+      <c r="C115" s="5" t="n">
         <v>202289.9</v>
       </c>
-      <c r="D115" s="3" t="n">
+      <c r="D115" s="6" t="n">
         <v>54.78137012</v>
       </c>
       <c r="E115" t="n">
@@ -3034,10 +2950,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C116" s="2" t="n">
+      <c r="C116" s="5" t="n">
         <v>30328.46</v>
       </c>
-      <c r="D116" s="3" t="n">
+      <c r="D116" s="6" t="n">
         <v>8.213136649999999</v>
       </c>
       <c r="E116" t="n">
@@ -3055,10 +2971,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C117" s="2" t="n">
+      <c r="C117" s="5" t="n">
         <v>131943.66</v>
       </c>
-      <c r="D117" s="3" t="n">
+      <c r="D117" s="6" t="n">
         <v>35.73116836</v>
       </c>
       <c r="E117" t="n">
@@ -3076,10 +2992,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C118" s="2" t="n">
+      <c r="C118" s="5" t="n">
         <v>101.72</v>
       </c>
-      <c r="D118" s="3" t="n">
+      <c r="D118" s="6" t="n">
         <v>0.03804713</v>
       </c>
       <c r="E118" t="n">
@@ -3097,10 +3013,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C119" s="2" t="n">
+      <c r="C119" s="5" t="n">
         <v>58</v>
       </c>
-      <c r="D119" s="3" t="n">
+      <c r="D119" s="6" t="n">
         <v>0.02169419</v>
       </c>
       <c r="E119" t="n">
@@ -3118,10 +3034,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C120" s="2" t="n">
+      <c r="C120" s="5" t="n">
         <v>167439.3</v>
       </c>
-      <c r="D120" s="3" t="n">
+      <c r="D120" s="6" t="n">
         <v>62.62863161</v>
       </c>
       <c r="E120" t="n">
@@ -3139,10 +3055,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C121" s="2" t="n">
+      <c r="C121" s="5" t="n">
         <v>7300.3</v>
       </c>
-      <c r="D121" s="3" t="n">
+      <c r="D121" s="6" t="n">
         <v>2.73058833</v>
       </c>
       <c r="E121" t="n">
@@ -3160,10 +3076,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C122" s="2" t="n">
+      <c r="C122" s="5" t="n">
         <v>92453.32000000001</v>
       </c>
-      <c r="D122" s="3" t="n">
+      <c r="D122" s="6" t="n">
         <v>34.58103874</v>
       </c>
       <c r="E122" t="n">
@@ -3181,10 +3097,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C123" s="2" t="n">
+      <c r="C123" s="5" t="n">
         <v>1475.74</v>
       </c>
-      <c r="D123" s="3" t="n">
+      <c r="D123" s="6" t="n">
         <v>0.33417908</v>
       </c>
       <c r="E123" t="n">
@@ -3202,10 +3118,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C124" s="2" t="n">
+      <c r="C124" s="5" t="n">
         <v>2209.05</v>
       </c>
-      <c r="D124" s="3" t="n">
+      <c r="D124" s="6" t="n">
         <v>0.50023602</v>
       </c>
       <c r="E124" t="n">
@@ -3223,10 +3139,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C125" s="2" t="n">
+      <c r="C125" s="5" t="n">
         <v>232354.93</v>
       </c>
-      <c r="D125" s="3" t="n">
+      <c r="D125" s="6" t="n">
         <v>52.61642084</v>
       </c>
       <c r="E125" t="n">
@@ -3244,10 +3160,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C126" s="2" t="n">
+      <c r="C126" s="5" t="n">
         <v>11084.31</v>
       </c>
-      <c r="D126" s="3" t="n">
+      <c r="D126" s="6" t="n">
         <v>2.51002516</v>
       </c>
       <c r="E126" t="n">
@@ -3265,10 +3181,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C127" s="2" t="n">
+      <c r="C127" s="5" t="n">
         <v>194477.52</v>
       </c>
-      <c r="D127" s="3" t="n">
+      <c r="D127" s="6" t="n">
         <v>44.0391389</v>
       </c>
       <c r="E127" t="n">
@@ -3286,10 +3202,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C128" s="2" t="n">
+      <c r="C128" s="5" t="n">
         <v>2990.78</v>
       </c>
-      <c r="D128" s="3" t="n">
+      <c r="D128" s="6" t="n">
         <v>0.63513389</v>
       </c>
       <c r="E128" t="n">
@@ -3307,10 +3223,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C129" s="2" t="n">
+      <c r="C129" s="5" t="n">
         <v>847.45</v>
       </c>
-      <c r="D129" s="3" t="n">
+      <c r="D129" s="6" t="n">
         <v>0.17996784</v>
       </c>
       <c r="E129" t="n">
@@ -3328,10 +3244,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C130" s="2" t="n">
+      <c r="C130" s="5" t="n">
         <v>211.86</v>
       </c>
-      <c r="D130" s="3" t="n">
+      <c r="D130" s="6" t="n">
         <v>0.04499143</v>
       </c>
       <c r="E130" t="n">
@@ -3349,10 +3265,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C131" s="2" t="n">
+      <c r="C131" s="5" t="n">
         <v>222684.94</v>
       </c>
-      <c r="D131" s="3" t="n">
+      <c r="D131" s="6" t="n">
         <v>47.29025603</v>
       </c>
       <c r="E131" t="n">
@@ -3370,10 +3286,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C132" s="2" t="n">
+      <c r="C132" s="5" t="n">
         <v>10642.51</v>
       </c>
-      <c r="D132" s="3" t="n">
+      <c r="D132" s="6" t="n">
         <v>2.26008558</v>
       </c>
       <c r="E132" t="n">
@@ -3391,10 +3307,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C133" s="2" t="n">
+      <c r="C133" s="5" t="n">
         <v>233512.15</v>
       </c>
-      <c r="D133" s="3" t="n">
+      <c r="D133" s="6" t="n">
         <v>49.58956523</v>
       </c>
       <c r="E133" t="n">
@@ -3412,10 +3328,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C134" s="2" t="n">
+      <c r="C134" s="5" t="n">
         <v>2894.67</v>
       </c>
-      <c r="D134" s="3" t="n">
+      <c r="D134" s="6" t="n">
         <v>0.84868485</v>
       </c>
       <c r="E134" t="n">
@@ -3433,10 +3349,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C135" s="2" t="n">
+      <c r="C135" s="5" t="n">
         <v>2112.75</v>
       </c>
-      <c r="D135" s="3" t="n">
+      <c r="D135" s="6" t="n">
         <v>0.61943465</v>
       </c>
       <c r="E135" t="n">
@@ -3454,10 +3370,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C136" s="2" t="n">
+      <c r="C136" s="5" t="n">
         <v>133738.48</v>
       </c>
-      <c r="D136" s="3" t="n">
+      <c r="D136" s="6" t="n">
         <v>39.21062549</v>
       </c>
       <c r="E136" t="n">
@@ -3475,10 +3391,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C137" s="2" t="n">
+      <c r="C137" s="5" t="n">
         <v>9278.84</v>
       </c>
-      <c r="D137" s="3" t="n">
+      <c r="D137" s="6" t="n">
         <v>2.72045204</v>
       </c>
       <c r="E137" t="n">
@@ -3496,10 +3412,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C138" s="2" t="n">
+      <c r="C138" s="5" t="n">
         <v>193052.4</v>
       </c>
-      <c r="D138" s="3" t="n">
+      <c r="D138" s="6" t="n">
         <v>56.60080297</v>
       </c>
       <c r="E138" t="n">
@@ -3517,10 +3433,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C139" s="2" t="n">
+      <c r="C139" s="5" t="n">
         <v>138.16</v>
       </c>
-      <c r="D139" s="3" t="n">
+      <c r="D139" s="6" t="n">
         <v>0.04037037</v>
       </c>
       <c r="E139" t="n">
@@ -3538,10 +3454,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C140" s="2" t="n">
+      <c r="C140" s="5" t="n">
         <v>165616.96</v>
       </c>
-      <c r="D140" s="3" t="n">
+      <c r="D140" s="6" t="n">
         <v>48.39329811</v>
       </c>
       <c r="E140" t="n">
@@ -3559,10 +3475,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C141" s="2" t="n">
+      <c r="C141" s="5" t="n">
         <v>14589.85</v>
       </c>
-      <c r="D141" s="3" t="n">
+      <c r="D141" s="6" t="n">
         <v>4.26315614</v>
       </c>
       <c r="E141" t="n">
@@ -3580,10 +3496,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C142" s="2" t="n">
+      <c r="C142" s="5" t="n">
         <v>161886.22</v>
       </c>
-      <c r="D142" s="3" t="n">
+      <c r="D142" s="6" t="n">
         <v>47.30317538</v>
       </c>
       <c r="E142" t="n">
@@ -3601,10 +3517,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C143" s="2" t="n">
+      <c r="C143" s="5" t="n">
         <v>39179.97</v>
       </c>
-      <c r="D143" s="3" t="n">
+      <c r="D143" s="6" t="n">
         <v>6.57522763</v>
       </c>
       <c r="E143" t="n">
@@ -3622,10 +3538,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C144" s="2" t="n">
+      <c r="C144" s="5" t="n">
         <v>142325.87</v>
       </c>
-      <c r="D144" s="3" t="n">
+      <c r="D144" s="6" t="n">
         <v>23.88529122</v>
       </c>
       <c r="E144" t="n">
@@ -3643,10 +3559,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C145" s="2" t="n">
+      <c r="C145" s="5" t="n">
         <v>16620.71</v>
       </c>
-      <c r="D145" s="3" t="n">
+      <c r="D145" s="6" t="n">
         <v>2.78930667</v>
       </c>
       <c r="E145" t="n">
@@ -3664,10 +3580,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C146" s="2" t="n">
+      <c r="C146" s="5" t="n">
         <v>397745.9</v>
       </c>
-      <c r="D146" s="3" t="n">
+      <c r="D146" s="6" t="n">
         <v>66.75017447</v>
       </c>
       <c r="E146" t="n">
@@ -3685,10 +3601,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C147" s="2" t="n">
+      <c r="C147" s="5" t="n">
         <v>1244.23</v>
       </c>
-      <c r="D147" s="3" t="n">
+      <c r="D147" s="6" t="n">
         <v>0.42616348</v>
       </c>
       <c r="E147" t="n">
@@ -3706,10 +3622,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C148" s="2" t="n">
+      <c r="C148" s="5" t="n">
         <v>4545.45</v>
       </c>
-      <c r="D148" s="3" t="n">
+      <c r="D148" s="6" t="n">
         <v>1.55687034</v>
       </c>
       <c r="E148" t="n">
@@ -3727,10 +3643,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C149" s="2" t="n">
+      <c r="C149" s="5" t="n">
         <v>54421.47</v>
       </c>
-      <c r="D149" s="3" t="n">
+      <c r="D149" s="6" t="n">
         <v>18.63999655</v>
       </c>
       <c r="E149" t="n">
@@ -3748,10 +3664,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C150" s="2" t="n">
+      <c r="C150" s="5" t="n">
         <v>231749.58</v>
       </c>
-      <c r="D150" s="3" t="n">
+      <c r="D150" s="6" t="n">
         <v>79.37696964</v>
       </c>
       <c r="E150" t="n">
@@ -3769,10 +3685,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C151" s="2" t="n">
+      <c r="C151" s="5" t="n">
         <v>29.6</v>
       </c>
-      <c r="D151" s="3" t="n">
+      <c r="D151" s="6" t="n">
         <v>0.00689719</v>
       </c>
       <c r="E151" t="n">
@@ -3790,10 +3706,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C152" s="2" t="n">
+      <c r="C152" s="5" t="n">
         <v>309.27</v>
       </c>
-      <c r="D152" s="3" t="n">
+      <c r="D152" s="6" t="n">
         <v>0.07206398</v>
       </c>
       <c r="E152" t="n">
@@ -3811,10 +3727,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C153" s="2" t="n">
+      <c r="C153" s="5" t="n">
         <v>3725.16</v>
       </c>
-      <c r="D153" s="3" t="n">
+      <c r="D153" s="6" t="n">
         <v>0.8680113</v>
       </c>
       <c r="E153" t="n">
@@ -3832,10 +3748,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C154" s="2" t="n">
+      <c r="C154" s="5" t="n">
         <v>8.109999999999999</v>
       </c>
-      <c r="D154" s="3" t="n">
+      <c r="D154" s="6" t="n">
         <v>0.00188974</v>
       </c>
       <c r="E154" t="n">
@@ -3853,10 +3769,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C155" s="2" t="n">
+      <c r="C155" s="5" t="n">
         <v>163136.27</v>
       </c>
-      <c r="D155" s="3" t="n">
+      <c r="D155" s="6" t="n">
         <v>38.01289779</v>
       </c>
       <c r="E155" t="n">
@@ -3874,10 +3790,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C156" s="2" t="n">
+      <c r="C156" s="5" t="n">
         <v>261951.9</v>
       </c>
-      <c r="D156" s="3" t="n">
+      <c r="D156" s="6" t="n">
         <v>61.03824</v>
       </c>
       <c r="E156" t="n">
@@ -3895,10 +3811,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C157" s="2" t="n">
+      <c r="C157" s="5" t="n">
         <v>55.55</v>
       </c>
-      <c r="D157" s="3" t="n">
+      <c r="D157" s="6" t="n">
         <v>0.01644298</v>
       </c>
       <c r="E157" t="n">
@@ -3916,10 +3832,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C158" s="2" t="n">
+      <c r="C158" s="5" t="n">
         <v>91.41</v>
       </c>
-      <c r="D158" s="3" t="n">
+      <c r="D158" s="6" t="n">
         <v>0.02705766</v>
       </c>
       <c r="E158" t="n">
@@ -3937,10 +3853,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C159" s="2" t="n">
+      <c r="C159" s="5" t="n">
         <v>5382.13</v>
       </c>
-      <c r="D159" s="3" t="n">
+      <c r="D159" s="6" t="n">
         <v>1.59312834</v>
       </c>
       <c r="E159" t="n">
@@ -3958,10 +3874,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C160" s="2" t="n">
+      <c r="C160" s="5" t="n">
         <v>909.09</v>
       </c>
-      <c r="D160" s="3" t="n">
+      <c r="D160" s="6" t="n">
         <v>0.26909366</v>
       </c>
       <c r="E160" t="n">
@@ -3979,10 +3895,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C161" s="2" t="n">
+      <c r="C161" s="5" t="n">
         <v>32670.17</v>
       </c>
-      <c r="D161" s="3" t="n">
+      <c r="D161" s="6" t="n">
         <v>9.670478749999999</v>
       </c>
       <c r="E161" t="n">
@@ -4000,10 +3916,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C162" s="2" t="n">
+      <c r="C162" s="5" t="n">
         <v>298725.7</v>
       </c>
-      <c r="D162" s="3" t="n">
+      <c r="D162" s="6" t="n">
         <v>88.42379861000001</v>
       </c>
       <c r="E162" t="n">
@@ -4021,10 +3937,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C163" s="2" t="n">
+      <c r="C163" s="5" t="n">
         <v>287.66</v>
       </c>
-      <c r="D163" s="3" t="n">
+      <c r="D163" s="6" t="n">
         <v>0.08204844999999999</v>
       </c>
       <c r="E163" t="n">
@@ -4042,10 +3958,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C164" s="2" t="n">
+      <c r="C164" s="5" t="n">
         <v>9919.66</v>
       </c>
-      <c r="D164" s="3" t="n">
+      <c r="D164" s="6" t="n">
         <v>2.82935676</v>
       </c>
       <c r="E164" t="n">
@@ -4063,10 +3979,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C165" s="2" t="n">
+      <c r="C165" s="5" t="n">
         <v>1385.01</v>
       </c>
-      <c r="D165" s="3" t="n">
+      <c r="D165" s="6" t="n">
         <v>0.39504251</v>
       </c>
       <c r="E165" t="n">
@@ -4084,10 +4000,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C166" s="2" t="n">
+      <c r="C166" s="5" t="n">
         <v>69940.2</v>
       </c>
-      <c r="D166" s="3" t="n">
+      <c r="D166" s="6" t="n">
         <v>19.94884679</v>
       </c>
       <c r="E166" t="n">
@@ -4105,10 +4021,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C167" s="2" t="n">
+      <c r="C167" s="5" t="n">
         <v>269065.18</v>
       </c>
-      <c r="D167" s="3" t="n">
+      <c r="D167" s="6" t="n">
         <v>76.74470549</v>
       </c>
       <c r="E167" t="n">
@@ -4126,10 +4042,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C168" s="2" t="n">
+      <c r="C168" s="5" t="n">
         <v>580.2</v>
       </c>
-      <c r="D168" s="3" t="n">
+      <c r="D168" s="6" t="n">
         <v>0.1561468</v>
       </c>
       <c r="E168" t="n">
@@ -4147,10 +4063,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C169" s="2" t="n">
+      <c r="C169" s="5" t="n">
         <v>98.44</v>
       </c>
-      <c r="D169" s="3" t="n">
+      <c r="D169" s="6" t="n">
         <v>0.02649275</v>
       </c>
       <c r="E169" t="n">
@@ -4168,10 +4084,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C170" s="2" t="n">
+      <c r="C170" s="5" t="n">
         <v>172.72</v>
       </c>
-      <c r="D170" s="3" t="n">
+      <c r="D170" s="6" t="n">
         <v>0.04648341</v>
       </c>
       <c r="E170" t="n">
@@ -4189,10 +4105,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C171" s="2" t="n">
+      <c r="C171" s="5" t="n">
         <v>3342.15</v>
       </c>
-      <c r="D171" s="3" t="n">
+      <c r="D171" s="6" t="n">
         <v>0.89945887</v>
       </c>
       <c r="E171" t="n">
@@ -4210,10 +4126,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C172" s="2" t="n">
+      <c r="C172" s="5" t="n">
         <v>7627.33</v>
       </c>
-      <c r="D172" s="3" t="n">
+      <c r="D172" s="6" t="n">
         <v>2.05271147</v>
       </c>
       <c r="E172" t="n">
@@ -4231,10 +4147,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C173" s="2" t="n">
+      <c r="C173" s="5" t="n">
         <v>359752.57</v>
       </c>
-      <c r="D173" s="3" t="n">
+      <c r="D173" s="6" t="n">
         <v>96.81870670000001</v>
       </c>
       <c r="E173" t="n">
@@ -4252,10 +4168,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C174" s="2" t="n">
+      <c r="C174" s="5" t="n">
         <v>61.94</v>
       </c>
-      <c r="D174" s="3" t="n">
+      <c r="D174" s="6" t="n">
         <v>0.02167129</v>
       </c>
       <c r="E174" t="n">
@@ -4273,10 +4189,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C175" s="2" t="n">
+      <c r="C175" s="5" t="n">
         <v>222</v>
       </c>
-      <c r="D175" s="3" t="n">
+      <c r="D175" s="6" t="n">
         <v>0.07767236</v>
       </c>
       <c r="E175" t="n">
@@ -4294,10 +4210,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C176" s="2" t="n">
+      <c r="C176" s="5" t="n">
         <v>10426.45</v>
       </c>
-      <c r="D176" s="3" t="n">
+      <c r="D176" s="6" t="n">
         <v>3.64795946</v>
       </c>
       <c r="E176" t="n">
@@ -4315,10 +4231,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C177" s="2" t="n">
+      <c r="C177" s="5" t="n">
         <v>36051.27</v>
       </c>
-      <c r="D177" s="3" t="n">
+      <c r="D177" s="6" t="n">
         <v>12.61345632</v>
       </c>
       <c r="E177" t="n">
@@ -4336,10 +4252,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C178" s="2" t="n">
+      <c r="C178" s="5" t="n">
         <v>239054.29</v>
       </c>
-      <c r="D178" s="3" t="n">
+      <c r="D178" s="6" t="n">
         <v>83.63924057</v>
       </c>
       <c r="E178" t="n">
@@ -4357,10 +4273,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C179" s="2" t="n">
+      <c r="C179" s="5" t="n">
         <v>1971.96</v>
       </c>
-      <c r="D179" s="3" t="n">
+      <c r="D179" s="6" t="n">
         <v>0.29536296</v>
       </c>
       <c r="E179" t="n">
@@ -4378,10 +4294,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C180" s="2" t="n">
+      <c r="C180" s="5" t="n">
         <v>970.1799999999999</v>
       </c>
-      <c r="D180" s="3" t="n">
+      <c r="D180" s="6" t="n">
         <v>0.14531493</v>
       </c>
       <c r="E180" t="n">
@@ -4399,10 +4315,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C181" s="2" t="n">
+      <c r="C181" s="5" t="n">
         <v>23400.38</v>
       </c>
-      <c r="D181" s="3" t="n">
+      <c r="D181" s="6" t="n">
         <v>3.50494199</v>
       </c>
       <c r="E181" t="n">
@@ -4420,10 +4336,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C182" s="2" t="n">
+      <c r="C182" s="5" t="n">
         <v>158698.51</v>
       </c>
-      <c r="D182" s="3" t="n">
+      <c r="D182" s="6" t="n">
         <v>23.77008715</v>
       </c>
       <c r="E182" t="n">
@@ -4441,10 +4357,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C183" s="2" t="n">
+      <c r="C183" s="5" t="n">
         <v>482598.55</v>
       </c>
-      <c r="D183" s="3" t="n">
+      <c r="D183" s="6" t="n">
         <v>72.28429297</v>
       </c>
       <c r="E183" t="n">
@@ -4462,10 +4378,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C184" s="2" t="n">
+      <c r="C184" s="5" t="n">
         <v>349.42</v>
       </c>
-      <c r="D184" s="3" t="n">
+      <c r="D184" s="6" t="n">
         <v>0.0757804</v>
       </c>
       <c r="E184" t="n">
@@ -4483,10 +4399,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C185" s="2" t="n">
+      <c r="C185" s="5" t="n">
         <v>5203.15</v>
       </c>
-      <c r="D185" s="3" t="n">
+      <c r="D185" s="6" t="n">
         <v>1.12843225</v>
       </c>
       <c r="E185" t="n">
@@ -4504,10 +4420,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C186" s="2" t="n">
+      <c r="C186" s="5" t="n">
         <v>43002.78</v>
       </c>
-      <c r="D186" s="3" t="n">
+      <c r="D186" s="6" t="n">
         <v>9.326220449999999</v>
       </c>
       <c r="E186" t="n">
@@ -4525,10 +4441,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C187" s="2" t="n">
+      <c r="C187" s="5" t="n">
         <v>412540.12</v>
       </c>
-      <c r="D187" s="3" t="n">
+      <c r="D187" s="6" t="n">
         <v>89.4695669</v>
       </c>
       <c r="E187" t="n">
@@ -4546,10 +4462,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C188" s="2" t="n">
+      <c r="C188" s="5" t="n">
         <v>1231.47</v>
       </c>
-      <c r="D188" s="3" t="n">
+      <c r="D188" s="6" t="n">
         <v>0.34199572</v>
       </c>
       <c r="E188" t="n">
@@ -4567,10 +4483,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C189" s="2" t="n">
+      <c r="C189" s="5" t="n">
         <v>484.18</v>
       </c>
-      <c r="D189" s="3" t="n">
+      <c r="D189" s="6" t="n">
         <v>0.13446328</v>
       </c>
       <c r="E189" t="n">
@@ -4588,10 +4504,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C190" s="2" t="n">
+      <c r="C190" s="5" t="n">
         <v>29461.66</v>
       </c>
-      <c r="D190" s="3" t="n">
+      <c r="D190" s="6" t="n">
         <v>8.18189784</v>
       </c>
       <c r="E190" t="n">
@@ -4609,10 +4525,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C191" s="2" t="n">
+      <c r="C191" s="5" t="n">
         <v>328906.14</v>
       </c>
-      <c r="D191" s="3" t="n">
+      <c r="D191" s="6" t="n">
         <v>91.34164317</v>
       </c>
       <c r="E191" t="n">
@@ -4630,10 +4546,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C192" s="2" t="n">
+      <c r="C192" s="5" t="n">
         <v>23.47</v>
       </c>
-      <c r="D192" s="3" t="n">
+      <c r="D192" s="6" t="n">
         <v>0.00471838</v>
       </c>
       <c r="E192" t="n">
@@ -4651,10 +4567,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C193" s="2" t="n">
+      <c r="C193" s="5" t="n">
         <v>13128.29</v>
       </c>
-      <c r="D193" s="3" t="n">
+      <c r="D193" s="6" t="n">
         <v>2.63929312</v>
       </c>
       <c r="E193" t="n">
@@ -4672,10 +4588,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C194" s="2" t="n">
+      <c r="C194" s="5" t="n">
         <v>42522.52</v>
       </c>
-      <c r="D194" s="3" t="n">
+      <c r="D194" s="6" t="n">
         <v>8.548668129999999</v>
       </c>
       <c r="E194" t="n">
@@ -4693,10 +4609,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C195" s="2" t="n">
+      <c r="C195" s="5" t="n">
         <v>441742.62</v>
       </c>
-      <c r="D195" s="3" t="n">
+      <c r="D195" s="6" t="n">
         <v>88.80732037999999</v>
       </c>
       <c r="E195" t="n">
@@ -4714,10 +4630,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C196" s="2" t="n">
+      <c r="C196" s="5" t="n">
         <v>14510.35</v>
       </c>
-      <c r="D196" s="3" t="n">
+      <c r="D196" s="6" t="n">
         <v>2.82318771</v>
       </c>
       <c r="E196" t="n">
@@ -4735,10 +4651,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C197" s="2" t="n">
+      <c r="C197" s="5" t="n">
         <v>29796.3</v>
       </c>
-      <c r="D197" s="3" t="n">
+      <c r="D197" s="6" t="n">
         <v>5.79727904</v>
       </c>
       <c r="E197" t="n">
@@ -4756,10 +4672,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C198" s="2" t="n">
+      <c r="C198" s="5" t="n">
         <v>489.48</v>
       </c>
-      <c r="D198" s="3" t="n">
+      <c r="D198" s="6" t="n">
         <v>0.09523505</v>
       </c>
       <c r="E198" t="n">
@@ -4777,10 +4693,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C199" s="2" t="n">
+      <c r="C199" s="5" t="n">
         <v>45623.94</v>
       </c>
-      <c r="D199" s="3" t="n">
+      <c r="D199" s="6" t="n">
         <v>8.876763589999999</v>
       </c>
       <c r="E199" t="n">
@@ -4798,10 +4714,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C200" s="2" t="n">
+      <c r="C200" s="5" t="n">
         <v>423550.36</v>
       </c>
-      <c r="D200" s="3" t="n">
+      <c r="D200" s="6" t="n">
         <v>82.40753461</v>
       </c>
       <c r="E200" t="n">
@@ -4819,10 +4735,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C201" s="2" t="n">
+      <c r="C201" s="5" t="n">
         <v>2894.83</v>
       </c>
-      <c r="D201" s="3" t="n">
+      <c r="D201" s="6" t="n">
         <v>0.57425271</v>
       </c>
       <c r="E201" t="n">
@@ -4840,10 +4756,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C202" s="2" t="n">
+      <c r="C202" s="5" t="n">
         <v>19389.84</v>
       </c>
-      <c r="D202" s="3" t="n">
+      <c r="D202" s="6" t="n">
         <v>3.84639792</v>
       </c>
       <c r="E202" t="n">
@@ -4861,10 +4777,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C203" s="2" t="n">
+      <c r="C203" s="5" t="n">
         <v>7103.09</v>
       </c>
-      <c r="D203" s="3" t="n">
+      <c r="D203" s="6" t="n">
         <v>1.40905292</v>
       </c>
       <c r="E203" t="n">
@@ -4882,10 +4798,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C204" s="2" t="n">
+      <c r="C204" s="5" t="n">
         <v>71555.96000000001</v>
       </c>
-      <c r="D204" s="3" t="n">
+      <c r="D204" s="6" t="n">
         <v>14.19468627</v>
       </c>
       <c r="E204" t="n">
@@ -4903,10 +4819,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C205" s="2" t="n">
+      <c r="C205" s="5" t="n">
         <v>403160.13</v>
       </c>
-      <c r="D205" s="3" t="n">
+      <c r="D205" s="6" t="n">
         <v>79.97561018</v>
       </c>
       <c r="E205" t="n">
@@ -4924,10 +4840,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C206" s="2" t="n">
+      <c r="C206" s="5" t="n">
         <v>13873.76</v>
       </c>
-      <c r="D206" s="3" t="n">
+      <c r="D206" s="6" t="n">
         <v>4.61749343</v>
       </c>
       <c r="E206" t="n">
@@ -4945,10 +4861,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C207" s="2" t="n">
+      <c r="C207" s="5" t="n">
         <v>5637.21</v>
       </c>
-      <c r="D207" s="3" t="n">
+      <c r="D207" s="6" t="n">
         <v>1.87618786</v>
       </c>
       <c r="E207" t="n">
@@ -4966,10 +4882,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C208" s="2" t="n">
+      <c r="C208" s="5" t="n">
         <v>1363.63</v>
       </c>
-      <c r="D208" s="3" t="n">
+      <c r="D208" s="6" t="n">
         <v>0.45384615</v>
       </c>
       <c r="E208" t="n">
@@ -4987,10 +4903,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C209" s="2" t="n">
+      <c r="C209" s="5" t="n">
         <v>35429.67</v>
       </c>
-      <c r="D209" s="3" t="n">
+      <c r="D209" s="6" t="n">
         <v>11.79177587</v>
       </c>
       <c r="E209" t="n">
@@ -5008,10 +4924,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C210" s="2" t="n">
+      <c r="C210" s="5" t="n">
         <v>244156.58</v>
       </c>
-      <c r="D210" s="3" t="n">
+      <c r="D210" s="6" t="n">
         <v>81.26069669</v>
       </c>
       <c r="E210" t="n">
@@ -5029,10 +4945,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C211" s="2" t="n">
+      <c r="C211" s="5" t="n">
         <v>3194.31</v>
       </c>
-      <c r="D211" s="3" t="n">
+      <c r="D211" s="6" t="n">
         <v>0.86754762</v>
       </c>
       <c r="E211" t="n">
@@ -5050,10 +4966,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C212" s="2" t="n">
+      <c r="C212" s="5" t="n">
         <v>53332.81</v>
       </c>
-      <c r="D212" s="3" t="n">
+      <c r="D212" s="6" t="n">
         <v>14.48474085</v>
       </c>
       <c r="E212" t="n">
@@ -5071,10 +4987,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C213" s="2" t="n">
+      <c r="C213" s="5" t="n">
         <v>5480.02</v>
       </c>
-      <c r="D213" s="3" t="n">
+      <c r="D213" s="6" t="n">
         <v>1.48832716</v>
       </c>
       <c r="E213" t="n">
@@ -5092,10 +5008,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C214" s="2" t="n">
+      <c r="C214" s="5" t="n">
         <v>54619.67</v>
       </c>
-      <c r="D214" s="3" t="n">
+      <c r="D214" s="6" t="n">
         <v>14.83424116</v>
       </c>
       <c r="E214" t="n">
@@ -5113,10 +5029,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C215" s="2" t="n">
+      <c r="C215" s="5" t="n">
         <v>251573.15</v>
       </c>
-      <c r="D215" s="3" t="n">
+      <c r="D215" s="6" t="n">
         <v>68.32514322</v>
       </c>
       <c r="E215" t="n">
@@ -5134,10 +5050,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C216" s="2" t="n">
+      <c r="C216" s="5" t="n">
         <v>892</v>
       </c>
-      <c r="D216" s="3" t="n">
+      <c r="D216" s="6" t="n">
         <v>0.30548187</v>
       </c>
       <c r="E216" t="n">
@@ -5155,10 +5071,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C217" s="2" t="n">
+      <c r="C217" s="5" t="n">
         <v>7918.09</v>
       </c>
-      <c r="D217" s="3" t="n">
+      <c r="D217" s="6" t="n">
         <v>2.71169611</v>
       </c>
       <c r="E217" t="n">
@@ -5176,10 +5092,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C218" s="2" t="n">
+      <c r="C218" s="5" t="n">
         <v>37.66</v>
       </c>
-      <c r="D218" s="3" t="n">
+      <c r="D218" s="6" t="n">
         <v>0.01289736</v>
       </c>
       <c r="E218" t="n">
@@ -5197,10 +5113,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C219" s="2" t="n">
+      <c r="C219" s="5" t="n">
         <v>14209.15</v>
       </c>
-      <c r="D219" s="3" t="n">
+      <c r="D219" s="6" t="n">
         <v>4.86618576</v>
       </c>
       <c r="E219" t="n">
@@ -5218,10 +5134,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C220" s="2" t="n">
+      <c r="C220" s="5" t="n">
         <v>268940.79</v>
       </c>
-      <c r="D220" s="3" t="n">
+      <c r="D220" s="6" t="n">
         <v>92.1037389</v>
       </c>
       <c r="E220" t="n">
@@ -5239,10 +5155,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C221" s="2" t="n">
+      <c r="C221" s="5" t="n">
         <v>287</v>
       </c>
-      <c r="D221" s="3" t="n">
+      <c r="D221" s="6" t="n">
         <v>0.07919683</v>
       </c>
       <c r="E221" t="n">
@@ -5260,10 +5176,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C222" s="2" t="n">
+      <c r="C222" s="5" t="n">
         <v>17982.75</v>
       </c>
-      <c r="D222" s="3" t="n">
+      <c r="D222" s="6" t="n">
         <v>4.96228879</v>
       </c>
       <c r="E222" t="n">
@@ -5281,10 +5197,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C223" s="2" t="n">
+      <c r="C223" s="5" t="n">
         <v>2603.68</v>
       </c>
-      <c r="D223" s="3" t="n">
+      <c r="D223" s="6" t="n">
         <v>0.7184781</v>
       </c>
       <c r="E223" t="n">
@@ -5302,10 +5218,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C224" s="2" t="n">
+      <c r="C224" s="5" t="n">
         <v>34911.64</v>
       </c>
-      <c r="D224" s="3" t="n">
+      <c r="D224" s="6" t="n">
         <v>9.6337679</v>
       </c>
       <c r="E224" t="n">
@@ -5323,10 +5239,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C225" s="2" t="n">
+      <c r="C225" s="5" t="n">
         <v>306603.15</v>
       </c>
-      <c r="D225" s="3" t="n">
+      <c r="D225" s="6" t="n">
         <v>84.60626838</v>
       </c>
       <c r="E225" t="n">
@@ -5344,10 +5260,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C226" s="2" t="n">
+      <c r="C226" s="5" t="n">
         <v>1099.13</v>
       </c>
-      <c r="D226" s="3" t="n">
+      <c r="D226" s="6" t="n">
         <v>0.35003695</v>
       </c>
       <c r="E226" t="n">
@@ -5365,10 +5281,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C227" s="2" t="n">
+      <c r="C227" s="5" t="n">
         <v>1908.13</v>
       </c>
-      <c r="D227" s="3" t="n">
+      <c r="D227" s="6" t="n">
         <v>0.60767699</v>
       </c>
       <c r="E227" t="n">
@@ -5386,10 +5302,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C228" s="2" t="n">
+      <c r="C228" s="5" t="n">
         <v>1788.1</v>
       </c>
-      <c r="D228" s="3" t="n">
+      <c r="D228" s="6" t="n">
         <v>0.56945136</v>
       </c>
       <c r="E228" t="n">
@@ -5407,10 +5323,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C229" s="2" t="n">
+      <c r="C229" s="5" t="n">
         <v>54065.52</v>
       </c>
-      <c r="D229" s="3" t="n">
+      <c r="D229" s="6" t="n">
         <v>17.21809968</v>
       </c>
       <c r="E229" t="n">
@@ -5428,10 +5344,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C230" s="2" t="n">
+      <c r="C230" s="5" t="n">
         <v>255143.11</v>
       </c>
-      <c r="D230" s="3" t="n">
+      <c r="D230" s="6" t="n">
         <v>81.25473501</v>
       </c>
       <c r="E230" t="n">
@@ -5449,10 +5365,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C231" s="2" t="n">
+      <c r="C231" s="5" t="n">
         <v>2988.23</v>
       </c>
-      <c r="D231" s="3" t="n">
+      <c r="D231" s="6" t="n">
         <v>1.09502707</v>
       </c>
       <c r="E231" t="n">
@@ -5470,10 +5386,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C232" s="2" t="n">
+      <c r="C232" s="5" t="n">
         <v>89030.31</v>
       </c>
-      <c r="D232" s="3" t="n">
+      <c r="D232" s="6" t="n">
         <v>32.62486479</v>
       </c>
       <c r="E232" t="n">
@@ -5491,10 +5407,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C233" s="2" t="n">
+      <c r="C233" s="5" t="n">
         <v>180872.43</v>
       </c>
-      <c r="D233" s="3" t="n">
+      <c r="D233" s="6" t="n">
         <v>66.28010813</v>
       </c>
       <c r="E233" t="n">
@@ -5512,10 +5428,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C234" s="2" t="n">
+      <c r="C234" s="5" t="n">
         <v>232.92</v>
       </c>
-      <c r="D234" s="3" t="n">
+      <c r="D234" s="6" t="n">
         <v>0.10614272</v>
       </c>
       <c r="E234" t="n">
@@ -5533,10 +5449,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C235" s="2" t="n">
+      <c r="C235" s="5" t="n">
         <v>27443.48</v>
       </c>
-      <c r="D235" s="3" t="n">
+      <c r="D235" s="6" t="n">
         <v>12.50612011</v>
       </c>
       <c r="E235" t="n">
@@ -5554,10 +5470,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C236" s="2" t="n">
+      <c r="C236" s="5" t="n">
         <v>66453.41</v>
       </c>
-      <c r="D236" s="3" t="n">
+      <c r="D236" s="6" t="n">
         <v>30.28312471</v>
       </c>
       <c r="E236" t="n">
@@ -5575,10 +5491,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C237" s="2" t="n">
+      <c r="C237" s="5" t="n">
         <v>125310.59</v>
       </c>
-      <c r="D237" s="3" t="n">
+      <c r="D237" s="6" t="n">
         <v>57.10461246</v>
       </c>
       <c r="E237" t="n">
@@ -5596,10 +5512,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C238" s="2" t="n">
+      <c r="C238" s="5" t="n">
         <v>12206.63</v>
       </c>
-      <c r="D238" s="3" t="n">
+      <c r="D238" s="6" t="n">
         <v>2.80910278</v>
       </c>
       <c r="E238" t="n">
@@ -5617,10 +5533,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C239" s="2" t="n">
+      <c r="C239" s="5" t="n">
         <v>14439.81</v>
       </c>
-      <c r="D239" s="3" t="n">
+      <c r="D239" s="6" t="n">
         <v>3.32302285</v>
       </c>
       <c r="E239" t="n">
@@ -5638,10 +5554,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C240" s="2" t="n">
+      <c r="C240" s="5" t="n">
         <v>73404.17</v>
       </c>
-      <c r="D240" s="3" t="n">
+      <c r="D240" s="6" t="n">
         <v>16.89244764</v>
       </c>
       <c r="E240" t="n">
@@ -5659,10 +5575,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C241" s="2" t="n">
+      <c r="C241" s="5" t="n">
         <v>334487.78</v>
       </c>
-      <c r="D241" s="3" t="n">
+      <c r="D241" s="6" t="n">
         <v>76.97542673</v>
       </c>
       <c r="E241" t="n">
@@ -5680,10 +5596,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C242" s="2" t="n">
+      <c r="C242" s="5" t="n">
         <v>4414.12</v>
       </c>
-      <c r="D242" s="3" t="n">
+      <c r="D242" s="6" t="n">
         <v>2.02734127</v>
       </c>
       <c r="E242" t="n">
@@ -5701,10 +5617,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C243" s="2" t="n">
+      <c r="C243" s="5" t="n">
         <v>206.75</v>
       </c>
-      <c r="D243" s="3" t="n">
+      <c r="D243" s="6" t="n">
         <v>0.09495727</v>
       </c>
       <c r="E243" t="n">
@@ -5722,10 +5638,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C244" s="2" t="n">
+      <c r="C244" s="5" t="n">
         <v>6938.86</v>
       </c>
-      <c r="D244" s="3" t="n">
+      <c r="D244" s="6" t="n">
         <v>3.18691771</v>
       </c>
       <c r="E244" t="n">
@@ -5743,10 +5659,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C245" s="2" t="n">
+      <c r="C245" s="5" t="n">
         <v>206169.77</v>
       </c>
-      <c r="D245" s="3" t="n">
+      <c r="D245" s="6" t="n">
         <v>94.69078374999999</v>
       </c>
       <c r="E245" t="n">
@@ -5764,10 +5680,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C246" s="2" t="n">
+      <c r="C246" s="5" t="n">
         <v>45195.76</v>
       </c>
-      <c r="D246" s="3" t="n">
+      <c r="D246" s="6" t="n">
         <v>10.41762819</v>
       </c>
       <c r="E246" t="n">
@@ -5785,10 +5701,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C247" s="2" t="n">
+      <c r="C247" s="5" t="n">
         <v>9882.6</v>
       </c>
-      <c r="D247" s="3" t="n">
+      <c r="D247" s="6" t="n">
         <v>2.2779405</v>
       </c>
       <c r="E247" t="n">
@@ -5806,10 +5722,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C248" s="2" t="n">
+      <c r="C248" s="5" t="n">
         <v>305.19</v>
       </c>
-      <c r="D248" s="3" t="n">
+      <c r="D248" s="6" t="n">
         <v>0.07034633</v>
       </c>
       <c r="E248" t="n">
@@ -5827,10 +5743,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C249" s="2" t="n">
+      <c r="C249" s="5" t="n">
         <v>9384.76</v>
       </c>
-      <c r="D249" s="3" t="n">
+      <c r="D249" s="6" t="n">
         <v>2.16318832</v>
       </c>
       <c r="E249" t="n">
@@ -5848,10 +5764,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C250" s="2" t="n">
+      <c r="C250" s="5" t="n">
         <v>369070.94</v>
       </c>
-      <c r="D250" s="3" t="n">
+      <c r="D250" s="6" t="n">
         <v>85.07089664999999</v>
       </c>
       <c r="E250" t="n">
@@ -5869,10 +5785,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C251" s="2" t="n">
+      <c r="C251" s="5" t="n">
         <v>387.59</v>
       </c>
-      <c r="D251" s="3" t="n">
+      <c r="D251" s="6" t="n">
         <v>0.10977502</v>
       </c>
       <c r="E251" t="n">
@@ -5890,10 +5806,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C252" s="2" t="n">
+      <c r="C252" s="5" t="n">
         <v>3000</v>
       </c>
-      <c r="D252" s="3" t="n">
+      <c r="D252" s="6" t="n">
         <v>0.84967379</v>
       </c>
       <c r="E252" t="n">
@@ -5911,10 +5827,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C253" s="2" t="n">
+      <c r="C253" s="5" t="n">
         <v>114879.27</v>
       </c>
-      <c r="D253" s="3" t="n">
+      <c r="D253" s="6" t="n">
         <v>32.53663482</v>
       </c>
       <c r="E253" t="n">
@@ -5932,10 +5848,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C254" s="2" t="n">
+      <c r="C254" s="5" t="n">
         <v>234809.82</v>
       </c>
-      <c r="D254" s="3" t="n">
+      <c r="D254" s="6" t="n">
         <v>66.50391637</v>
       </c>
       <c r="E254" t="n">
@@ -5953,10 +5869,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C255" s="2" t="n">
+      <c r="C255" s="5" t="n">
         <v>8859.66</v>
       </c>
-      <c r="D255" s="3" t="n">
+      <c r="D255" s="6" t="n">
         <v>5.34081687</v>
       </c>
       <c r="E255" t="n">
@@ -5974,10 +5890,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C256" s="2" t="n">
+      <c r="C256" s="5" t="n">
         <v>1006.9</v>
       </c>
-      <c r="D256" s="3" t="n">
+      <c r="D256" s="6" t="n">
         <v>0.6069836199999999</v>
       </c>
       <c r="E256" t="n">
@@ -5995,10 +5911,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C257" s="2" t="n">
+      <c r="C257" s="5" t="n">
         <v>1000</v>
       </c>
-      <c r="D257" s="3" t="n">
+      <c r="D257" s="6" t="n">
         <v>0.60282413</v>
       </c>
       <c r="E257" t="n">
@@ -6016,10 +5932,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C258" s="2" t="n">
+      <c r="C258" s="5" t="n">
         <v>51121.7</v>
       </c>
-      <c r="D258" s="3" t="n">
+      <c r="D258" s="6" t="n">
         <v>30.81739456</v>
       </c>
       <c r="E258" t="n">
@@ -6037,10 +5953,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C259" s="2" t="n">
+      <c r="C259" s="5" t="n">
         <v>103897.6</v>
       </c>
-      <c r="D259" s="3" t="n">
+      <c r="D259" s="6" t="n">
         <v>62.63198081</v>
       </c>
       <c r="E259" t="n">
@@ -6058,10 +5974,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C260" s="2" t="n">
+      <c r="C260" s="5" t="n">
         <v>7692.3</v>
       </c>
-      <c r="D260" s="3" t="n">
+      <c r="D260" s="6" t="n">
         <v>6.29078176</v>
       </c>
       <c r="E260" t="n">
@@ -6079,10 +5995,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C261" s="2" t="n">
+      <c r="C261" s="5" t="n">
         <v>1882.73</v>
       </c>
-      <c r="D261" s="3" t="n">
+      <c r="D261" s="6" t="n">
         <v>1.5397012</v>
       </c>
       <c r="E261" t="n">
@@ -6100,10 +6016,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C262" s="2" t="n">
+      <c r="C262" s="5" t="n">
         <v>14869.63</v>
       </c>
-      <c r="D262" s="3" t="n">
+      <c r="D262" s="6" t="n">
         <v>12.1604198</v>
       </c>
       <c r="E262" t="n">
@@ -6121,10 +6037,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C263" s="2" t="n">
+      <c r="C263" s="5" t="n">
         <v>97834.25999999999</v>
       </c>
-      <c r="D263" s="3" t="n">
+      <c r="D263" s="6" t="n">
         <v>80.00909722999999</v>
       </c>
       <c r="E263" t="n">
@@ -6142,10 +6058,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C264" s="2" t="n">
+      <c r="C264" s="5" t="n">
         <v>3303.59</v>
       </c>
-      <c r="D264" s="3" t="n">
+      <c r="D264" s="6" t="n">
         <v>1.27093949</v>
       </c>
       <c r="E264" t="n">
@@ -6163,10 +6079,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C265" s="2" t="n">
+      <c r="C265" s="5" t="n">
         <v>18435.53</v>
       </c>
-      <c r="D265" s="3" t="n">
+      <c r="D265" s="6" t="n">
         <v>7.09241858</v>
       </c>
       <c r="E265" t="n">
@@ -6184,10 +6100,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C266" s="2" t="n">
+      <c r="C266" s="5" t="n">
         <v>2222.22</v>
       </c>
-      <c r="D266" s="3" t="n">
+      <c r="D266" s="6" t="n">
         <v>0.8549206</v>
       </c>
       <c r="E266" t="n">
@@ -6205,10 +6121,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C267" s="2" t="n">
+      <c r="C267" s="5" t="n">
         <v>50871.54</v>
       </c>
-      <c r="D267" s="3" t="n">
+      <c r="D267" s="6" t="n">
         <v>19.571027</v>
       </c>
       <c r="E267" t="n">
@@ -6226,10 +6142,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C268" s="2" t="n">
+      <c r="C268" s="5" t="n">
         <v>185100.03</v>
       </c>
-      <c r="D268" s="3" t="n">
+      <c r="D268" s="6" t="n">
         <v>71.21069433</v>
       </c>
       <c r="E268" t="n">
@@ -6247,10 +6163,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C269" s="2" t="n">
+      <c r="C269" s="5" t="n">
         <v>26854.86</v>
       </c>
-      <c r="D269" s="3" t="n">
+      <c r="D269" s="6" t="n">
         <v>6.60466391</v>
       </c>
       <c r="E269" t="n">
@@ -6268,10 +6184,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="C270" s="2" t="n">
+      <c r="C270" s="5" t="n">
         <v>554.28</v>
       </c>
-      <c r="D270" s="3" t="n">
+      <c r="D270" s="6" t="n">
         <v>0.1363192</v>
       </c>
       <c r="E270" t="n">
@@ -6289,10 +6205,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C271" s="2" t="n">
+      <c r="C271" s="5" t="n">
         <v>487.8</v>
       </c>
-      <c r="D271" s="3" t="n">
+      <c r="D271" s="6" t="n">
         <v>0.11996916</v>
       </c>
       <c r="E271" t="n">
@@ -6310,10 +6226,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C272" s="2" t="n">
+      <c r="C272" s="5" t="n">
         <v>12206.22</v>
       </c>
-      <c r="D272" s="3" t="n">
+      <c r="D272" s="6" t="n">
         <v>3.00198849</v>
       </c>
       <c r="E272" t="n">
@@ -6331,10 +6247,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C273" s="2" t="n">
+      <c r="C273" s="5" t="n">
         <v>28370.02</v>
       </c>
-      <c r="D273" s="3" t="n">
+      <c r="D273" s="6" t="n">
         <v>6.97730121</v>
       </c>
       <c r="E273" t="n">
@@ -6352,10 +6268,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C274" s="2" t="n">
+      <c r="C274" s="5" t="n">
         <v>338131.31</v>
       </c>
-      <c r="D274" s="3" t="n">
+      <c r="D274" s="6" t="n">
         <v>83.15975802</v>
       </c>
       <c r="E274" t="n">
@@ -6373,10 +6289,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C275" s="2" t="n">
+      <c r="C275" s="5" t="n">
         <v>19985.78</v>
       </c>
-      <c r="D275" s="3" t="n">
+      <c r="D275" s="6" t="n">
         <v>7.97052191</v>
       </c>
       <c r="E275" t="n">
@@ -6394,10 +6310,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="C276" s="2" t="n">
+      <c r="C276" s="5" t="n">
         <v>2222.22</v>
       </c>
-      <c r="D276" s="3" t="n">
+      <c r="D276" s="6" t="n">
         <v>0.88624278</v>
       </c>
       <c r="E276" t="n">
@@ -6415,10 +6331,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C277" s="2" t="n">
+      <c r="C277" s="5" t="n">
         <v>4445.7</v>
       </c>
-      <c r="D277" s="3" t="n">
+      <c r="D277" s="6" t="n">
         <v>1.77298806</v>
       </c>
       <c r="E277" t="n">
@@ -6436,10 +6352,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C278" s="2" t="n">
+      <c r="C278" s="5" t="n">
         <v>50514.02</v>
       </c>
-      <c r="D278" s="3" t="n">
+      <c r="D278" s="6" t="n">
         <v>20.14547858</v>
       </c>
       <c r="E278" t="n">
@@ -6457,10 +6373,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C279" s="2" t="n">
+      <c r="C279" s="5" t="n">
         <v>173578.47</v>
       </c>
-      <c r="D279" s="3" t="n">
+      <c r="D279" s="6" t="n">
         <v>69.22476868</v>
       </c>
       <c r="E279" t="n">
@@ -6478,10 +6394,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C280" s="2" t="n">
+      <c r="C280" s="5" t="n">
         <v>40560.99</v>
       </c>
-      <c r="D280" s="3" t="n">
+      <c r="D280" s="6" t="n">
         <v>8.644859670000001</v>
       </c>
       <c r="E280" t="n">
@@ -6499,10 +6415,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C281" s="2" t="n">
+      <c r="C281" s="5" t="n">
         <v>6836.42</v>
       </c>
-      <c r="D281" s="3" t="n">
+      <c r="D281" s="6" t="n">
         <v>1.45706235</v>
       </c>
       <c r="E281" t="n">
@@ -6520,10 +6436,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C282" s="2" t="n">
+      <c r="C282" s="5" t="n">
         <v>34873.15</v>
       </c>
-      <c r="D282" s="3" t="n">
+      <c r="D282" s="6" t="n">
         <v>7.43259689</v>
       </c>
       <c r="E282" t="n">
@@ -6541,10 +6457,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C283" s="2" t="n">
+      <c r="C283" s="5" t="n">
         <v>386921.44</v>
       </c>
-      <c r="D283" s="3" t="n">
+      <c r="D283" s="6" t="n">
         <v>82.46548108</v>
       </c>
       <c r="E283" t="n">
@@ -6562,10 +6478,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="C284" s="2" t="n">
+      <c r="C284" s="5" t="n">
         <v>2062.08</v>
       </c>
-      <c r="D284" s="3" t="n">
+      <c r="D284" s="6" t="n">
         <v>0.67843969</v>
       </c>
       <c r="E284" t="n">
@@ -6583,10 +6499,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C285" s="2" t="n">
+      <c r="C285" s="5" t="n">
         <v>67302.87</v>
       </c>
-      <c r="D285" s="3" t="n">
+      <c r="D285" s="6" t="n">
         <v>22.14314601</v>
       </c>
       <c r="E285" t="n">
@@ -6604,10 +6520,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C286" s="2" t="n">
+      <c r="C286" s="5" t="n">
         <v>37.83</v>
       </c>
-      <c r="D286" s="3" t="n">
+      <c r="D286" s="6" t="n">
         <v>0.01244635</v>
       </c>
       <c r="E286" t="n">
@@ -6625,10 +6541,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C287" s="2" t="n">
+      <c r="C287" s="5" t="n">
         <v>82048.36</v>
       </c>
-      <c r="D287" s="3" t="n">
+      <c r="D287" s="6" t="n">
         <v>26.99452216</v>
       </c>
       <c r="E287" t="n">
@@ -6646,10 +6562,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C288" s="2" t="n">
+      <c r="C288" s="5" t="n">
         <v>152493.34</v>
       </c>
-      <c r="D288" s="3" t="n">
+      <c r="D288" s="6" t="n">
         <v>50.17144579</v>
       </c>
       <c r="E288" t="n">
@@ -6667,10 +6583,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C289" s="2" t="n">
+      <c r="C289" s="5" t="n">
         <v>16850.05</v>
       </c>
-      <c r="D289" s="3" t="n">
+      <c r="D289" s="6" t="n">
         <v>8.3557591</v>
       </c>
       <c r="E289" t="n">
@@ -6688,10 +6604,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C290" s="2" t="n">
+      <c r="C290" s="5" t="n">
         <v>1221.31</v>
       </c>
-      <c r="D290" s="3" t="n">
+      <c r="D290" s="6" t="n">
         <v>0.60563453</v>
       </c>
       <c r="E290" t="n">
@@ -6709,10 +6625,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C291" s="2" t="n">
+      <c r="C291" s="5" t="n">
         <v>542.72</v>
       </c>
-      <c r="D291" s="3" t="n">
+      <c r="D291" s="6" t="n">
         <v>0.26912903</v>
       </c>
       <c r="E291" t="n">
@@ -6730,10 +6646,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C292" s="2" t="n">
+      <c r="C292" s="5" t="n">
         <v>1989.87</v>
       </c>
-      <c r="D292" s="3" t="n">
+      <c r="D292" s="6" t="n">
         <v>0.98675519</v>
       </c>
       <c r="E292" t="n">
@@ -6751,10 +6667,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C293" s="2" t="n">
+      <c r="C293" s="5" t="n">
         <v>181053.97</v>
       </c>
-      <c r="D293" s="3" t="n">
+      <c r="D293" s="6" t="n">
         <v>89.78272215</v>
       </c>
       <c r="E293" t="n">
@@ -6772,10 +6688,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C294" s="2" t="n">
+      <c r="C294" s="5" t="n">
         <v>2791.46</v>
       </c>
-      <c r="D294" s="3" t="n">
+      <c r="D294" s="6" t="n">
         <v>1.6215349</v>
       </c>
       <c r="E294" t="n">
@@ -6793,10 +6709,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C295" s="2" t="n">
+      <c r="C295" s="5" t="n">
         <v>6752.82</v>
       </c>
-      <c r="D295" s="3" t="n">
+      <c r="D295" s="6" t="n">
         <v>3.92265455</v>
       </c>
       <c r="E295" t="n">
@@ -6814,10 +6730,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C296" s="2" t="n">
+      <c r="C296" s="5" t="n">
         <v>42038.15</v>
       </c>
-      <c r="D296" s="3" t="n">
+      <c r="D296" s="6" t="n">
         <v>24.41959662</v>
       </c>
       <c r="E296" t="n">
@@ -6835,10 +6751,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C297" s="2" t="n">
+      <c r="C297" s="5" t="n">
         <v>120566.81</v>
       </c>
-      <c r="D297" s="3" t="n">
+      <c r="D297" s="6" t="n">
         <v>70.03621393</v>
       </c>
       <c r="E297" t="n">
@@ -6856,10 +6772,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C298" s="2" t="n">
+      <c r="C298" s="5" t="n">
         <v>360</v>
       </c>
-      <c r="D298" s="3" t="n">
+      <c r="D298" s="6" t="n">
         <v>0.13798773</v>
       </c>
       <c r="E298" t="n">
@@ -6877,10 +6793,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C299" s="2" t="n">
+      <c r="C299" s="5" t="n">
         <v>9364.209999999999</v>
       </c>
-      <c r="D299" s="3" t="n">
+      <c r="D299" s="6" t="n">
         <v>3.58929456</v>
       </c>
       <c r="E299" t="n">
@@ -6898,10 +6814,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C300" s="2" t="n">
+      <c r="C300" s="5" t="n">
         <v>4780.88</v>
       </c>
-      <c r="D300" s="3" t="n">
+      <c r="D300" s="6" t="n">
         <v>1.83250766</v>
       </c>
       <c r="E300" t="n">
@@ -6919,10 +6835,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C301" s="2" t="n">
+      <c r="C301" s="5" t="n">
         <v>246387.68</v>
       </c>
-      <c r="D301" s="3" t="n">
+      <c r="D301" s="6" t="n">
         <v>94.44021005</v>
       </c>
       <c r="E301" t="n">
@@ -6940,10 +6856,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C302" s="2" t="n">
+      <c r="C302" s="5" t="n">
         <v>6057.75</v>
       </c>
-      <c r="D302" s="3" t="n">
+      <c r="D302" s="6" t="n">
         <v>2.33727832</v>
       </c>
       <c r="E302" t="n">
@@ -6961,10 +6877,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C303" s="2" t="n">
+      <c r="C303" s="5" t="n">
         <v>48766.63</v>
       </c>
-      <c r="D303" s="3" t="n">
+      <c r="D303" s="6" t="n">
         <v>18.81576278</v>
       </c>
       <c r="E303" t="n">
@@ -6982,10 +6898,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C304" s="2" t="n">
+      <c r="C304" s="5" t="n">
         <v>204355.28</v>
       </c>
-      <c r="D304" s="3" t="n">
+      <c r="D304" s="6" t="n">
         <v>78.8469589</v>
       </c>
       <c r="E304" t="n">
@@ -7003,10 +6919,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C305" s="2" t="n">
+      <c r="C305" s="5" t="n">
         <v>16523.23</v>
       </c>
-      <c r="D305" s="3" t="n">
+      <c r="D305" s="6" t="n">
         <v>6.18627246</v>
       </c>
       <c r="E305" t="n">
@@ -7024,10 +6940,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="C306" s="2" t="n">
+      <c r="C306" s="5" t="n">
         <v>1000</v>
       </c>
-      <c r="D306" s="3" t="n">
+      <c r="D306" s="6" t="n">
         <v>0.3743985</v>
       </c>
       <c r="E306" t="n">
@@ -7045,10 +6961,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C307" s="2" t="n">
+      <c r="C307" s="5" t="n">
         <v>19175.48</v>
       </c>
-      <c r="D307" s="3" t="n">
+      <c r="D307" s="6" t="n">
         <v>7.17927087</v>
       </c>
       <c r="E307" t="n">
@@ -7066,10 +6982,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C308" s="2" t="n">
+      <c r="C308" s="5" t="n">
         <v>22548.18</v>
       </c>
-      <c r="D308" s="3" t="n">
+      <c r="D308" s="6" t="n">
         <v>8.44200468</v>
       </c>
       <c r="E308" t="n">
@@ -7087,10 +7003,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C309" s="2" t="n">
+      <c r="C309" s="5" t="n">
         <v>3105.38</v>
       </c>
-      <c r="D309" s="3" t="n">
+      <c r="D309" s="6" t="n">
         <v>1.1626496</v>
       </c>
       <c r="E309" t="n">
@@ -7108,10 +7024,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C310" s="2" t="n">
+      <c r="C310" s="5" t="n">
         <v>9171.51</v>
       </c>
-      <c r="D310" s="3" t="n">
+      <c r="D310" s="6" t="n">
         <v>3.43379955</v>
       </c>
       <c r="E310" t="n">
@@ -7129,10 +7045,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C311" s="2" t="n">
+      <c r="C311" s="5" t="n">
         <v>195571.31</v>
       </c>
-      <c r="D311" s="3" t="n">
+      <c r="D311" s="6" t="n">
         <v>73.22160434</v>
       </c>
       <c r="E311" t="n">
@@ -7150,10 +7066,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C312" s="2" t="n">
+      <c r="C312" s="5" t="n">
         <v>27350.51</v>
       </c>
-      <c r="D312" s="3" t="n">
+      <c r="D312" s="6" t="n">
         <v>9.8197723</v>
       </c>
       <c r="E312" t="n">
@@ -7171,10 +7087,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C313" s="2" t="n">
+      <c r="C313" s="5" t="n">
         <v>21653.68</v>
       </c>
-      <c r="D313" s="3" t="n">
+      <c r="D313" s="6" t="n">
         <v>7.7744147</v>
       </c>
       <c r="E313" t="n">
@@ -7192,10 +7108,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C314" s="2" t="n">
+      <c r="C314" s="5" t="n">
         <v>30092.08</v>
       </c>
-      <c r="D314" s="3" t="n">
+      <c r="D314" s="6" t="n">
         <v>10.80409008</v>
       </c>
       <c r="E314" t="n">
@@ -7213,10 +7129,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C315" s="2" t="n">
+      <c r="C315" s="5" t="n">
         <v>199428.62</v>
       </c>
-      <c r="D315" s="3" t="n">
+      <c r="D315" s="6" t="n">
         <v>71.60172292</v>
       </c>
       <c r="E315" t="n">
@@ -7234,10 +7150,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C316" s="2" t="n">
+      <c r="C316" s="5" t="n">
         <v>18403.89</v>
       </c>
-      <c r="D316" s="3" t="n">
+      <c r="D316" s="6" t="n">
         <v>5.9503914</v>
       </c>
       <c r="E316" t="n">
@@ -7255,10 +7171,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C317" s="2" t="n">
+      <c r="C317" s="5" t="n">
         <v>88.88</v>
       </c>
-      <c r="D317" s="3" t="n">
+      <c r="D317" s="6" t="n">
         <v>0.0287369</v>
       </c>
       <c r="E317" t="n">
@@ -7276,10 +7192,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C318" s="2" t="n">
+      <c r="C318" s="5" t="n">
         <v>72445.86</v>
       </c>
-      <c r="D318" s="3" t="n">
+      <c r="D318" s="6" t="n">
         <v>23.4233753</v>
       </c>
       <c r="E318" t="n">
@@ -7297,10 +7213,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C319" s="2" t="n">
+      <c r="C319" s="5" t="n">
         <v>1021.81</v>
       </c>
-      <c r="D319" s="3" t="n">
+      <c r="D319" s="6" t="n">
         <v>0.33037415</v>
       </c>
       <c r="E319" t="n">
@@ -7318,10 +7234,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C320" s="2" t="n">
+      <c r="C320" s="5" t="n">
         <v>23146.75</v>
       </c>
-      <c r="D320" s="3" t="n">
+      <c r="D320" s="6" t="n">
         <v>7.48386467</v>
       </c>
       <c r="E320" t="n">
@@ -7339,10 +7255,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C321" s="2" t="n">
+      <c r="C321" s="5" t="n">
         <v>194181.54</v>
       </c>
-      <c r="D321" s="3" t="n">
+      <c r="D321" s="6" t="n">
         <v>62.78325757</v>
       </c>
       <c r="E321" t="n">
@@ -7360,10 +7276,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C322" s="2" t="n">
+      <c r="C322" s="5" t="n">
         <v>3620.25</v>
       </c>
-      <c r="D322" s="3" t="n">
+      <c r="D322" s="6" t="n">
         <v>1.23604851</v>
       </c>
       <c r="E322" t="n">
@@ -7381,10 +7297,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C323" s="2" t="n">
+      <c r="C323" s="5" t="n">
         <v>19747.53</v>
       </c>
-      <c r="D323" s="3" t="n">
+      <c r="D323" s="6" t="n">
         <v>6.74232582</v>
       </c>
       <c r="E323" t="n">
@@ -7402,10 +7318,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C324" s="2" t="n">
+      <c r="C324" s="5" t="n">
         <v>148.8</v>
       </c>
-      <c r="D324" s="3" t="n">
+      <c r="D324" s="6" t="n">
         <v>0.05080423</v>
       </c>
       <c r="E324" t="n">
@@ -7423,10 +7339,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C325" s="2" t="n">
+      <c r="C325" s="5" t="n">
         <v>59465.09</v>
       </c>
-      <c r="D325" s="3" t="n">
+      <c r="D325" s="6" t="n">
         <v>20.30294481</v>
       </c>
       <c r="E325" t="n">
@@ -7444,10 +7360,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C326" s="2" t="n">
+      <c r="C326" s="5" t="n">
         <v>209907.32</v>
       </c>
-      <c r="D326" s="3" t="n">
+      <c r="D326" s="6" t="n">
         <v>71.66787662</v>
       </c>
       <c r="E326" t="n">
@@ -7465,10 +7381,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C327" s="2" t="n">
+      <c r="C327" s="5" t="n">
         <v>6884.07</v>
       </c>
-      <c r="D327" s="3" t="n">
+      <c r="D327" s="6" t="n">
         <v>2.33908458</v>
       </c>
       <c r="E327" t="n">
@@ -7486,10 +7402,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C328" s="2" t="n">
+      <c r="C328" s="5" t="n">
         <v>1851.18</v>
       </c>
-      <c r="D328" s="3" t="n">
+      <c r="D328" s="6" t="n">
         <v>0.62899805</v>
       </c>
       <c r="E328" t="n">
@@ -7507,10 +7423,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C329" s="2" t="n">
+      <c r="C329" s="5" t="n">
         <v>27.27</v>
       </c>
-      <c r="D329" s="3" t="n">
+      <c r="D329" s="6" t="n">
         <v>0.009265860000000001</v>
       </c>
       <c r="E329" t="n">
@@ -7528,10 +7444,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C330" s="2" t="n">
+      <c r="C330" s="5" t="n">
         <v>48724.48</v>
       </c>
-      <c r="D330" s="3" t="n">
+      <c r="D330" s="6" t="n">
         <v>16.55571192</v>
       </c>
       <c r="E330" t="n">
@@ -7549,10 +7465,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C331" s="2" t="n">
+      <c r="C331" s="5" t="n">
         <v>236819.16</v>
       </c>
-      <c r="D331" s="3" t="n">
+      <c r="D331" s="6" t="n">
         <v>80.4669396</v>
       </c>
       <c r="E331" t="n">
@@ -7570,10 +7486,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C332" s="2" t="n">
+      <c r="C332" s="5" t="n">
         <v>1121.22</v>
       </c>
-      <c r="D332" s="3" t="n">
+      <c r="D332" s="6" t="n">
         <v>0.3654631</v>
       </c>
       <c r="E332" t="n">
@@ -7591,10 +7507,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C333" s="2" t="n">
+      <c r="C333" s="5" t="n">
         <v>44200.33</v>
       </c>
-      <c r="D333" s="3" t="n">
+      <c r="D333" s="6" t="n">
         <v>14.40715442</v>
       </c>
       <c r="E333" t="n">
@@ -7612,10 +7528,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C334" s="2" t="n">
+      <c r="C334" s="5" t="n">
         <v>1029.79</v>
       </c>
-      <c r="D334" s="3" t="n">
+      <c r="D334" s="6" t="n">
         <v>0.33566138</v>
       </c>
       <c r="E334" t="n">
@@ -7633,10 +7549,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C335" s="2" t="n">
+      <c r="C335" s="5" t="n">
         <v>47810.16</v>
       </c>
-      <c r="D335" s="3" t="n">
+      <c r="D335" s="6" t="n">
         <v>15.58378315</v>
       </c>
       <c r="E335" t="n">
@@ -7654,10 +7570,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C336" s="2" t="n">
+      <c r="C336" s="5" t="n">
         <v>212632.81</v>
       </c>
-      <c r="D336" s="3" t="n">
+      <c r="D336" s="6" t="n">
         <v>69.30793795</v>
       </c>
       <c r="E336" t="n">
@@ -7675,10 +7591,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C337" s="2" t="n">
+      <c r="C337" s="5" t="n">
         <v>6174.11</v>
       </c>
-      <c r="D337" s="3" t="n">
+      <c r="D337" s="6" t="n">
         <v>2.21572231</v>
       </c>
       <c r="E337" t="n">
@@ -7696,10 +7612,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C338" s="2" t="n">
+      <c r="C338" s="5" t="n">
         <v>41944.2</v>
       </c>
-      <c r="D338" s="3" t="n">
+      <c r="D338" s="6" t="n">
         <v>15.05264723</v>
       </c>
       <c r="E338" t="n">
@@ -7717,10 +7633,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C339" s="2" t="n">
+      <c r="C339" s="5" t="n">
         <v>77569.86</v>
       </c>
-      <c r="D339" s="3" t="n">
+      <c r="D339" s="6" t="n">
         <v>27.8377401</v>
       </c>
       <c r="E339" t="n">
@@ -7738,10 +7654,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C340" s="2" t="n">
+      <c r="C340" s="5" t="n">
         <v>152961.82</v>
       </c>
-      <c r="D340" s="3" t="n">
+      <c r="D340" s="6" t="n">
         <v>54.89389036</v>
       </c>
       <c r="E340" t="n">
@@ -7759,10 +7675,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C341" s="2" t="n">
+      <c r="C341" s="5" t="n">
         <v>4327.58</v>
       </c>
-      <c r="D341" s="3" t="n">
+      <c r="D341" s="6" t="n">
         <v>1.21146897</v>
       </c>
       <c r="E341" t="n">
@@ -7780,10 +7696,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C342" s="2" t="n">
+      <c r="C342" s="5" t="n">
         <v>28414.86</v>
       </c>
-      <c r="D342" s="3" t="n">
+      <c r="D342" s="6" t="n">
         <v>7.95449675</v>
       </c>
       <c r="E342" t="n">
@@ -7801,10 +7717,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C343" s="2" t="n">
+      <c r="C343" s="5" t="n">
         <v>57985.61</v>
       </c>
-      <c r="D343" s="3" t="n">
+      <c r="D343" s="6" t="n">
         <v>16.23257501</v>
       </c>
       <c r="E343" t="n">
@@ -7822,10 +7738,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C344" s="2" t="n">
+      <c r="C344" s="5" t="n">
         <v>164042.55</v>
       </c>
-      <c r="D344" s="3" t="n">
+      <c r="D344" s="6" t="n">
         <v>45.92230724</v>
       </c>
       <c r="E344" t="n">
@@ -7843,10 +7759,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C345" s="2" t="n">
+      <c r="C345" s="5" t="n">
         <v>102446.97</v>
       </c>
-      <c r="D345" s="3" t="n">
+      <c r="D345" s="6" t="n">
         <v>28.67915204</v>
       </c>
       <c r="E345" t="n">
@@ -7864,10 +7780,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C346" s="2" t="n">
+      <c r="C346" s="5" t="n">
         <v>6549.34</v>
       </c>
-      <c r="D346" s="3" t="n">
+      <c r="D346" s="6" t="n">
         <v>1.3658538</v>
       </c>
       <c r="E346" t="n">
@@ -7885,10 +7801,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C347" s="2" t="n">
+      <c r="C347" s="5" t="n">
         <v>70012.2</v>
       </c>
-      <c r="D347" s="3" t="n">
+      <c r="D347" s="6" t="n">
         <v>14.60092612</v>
       </c>
       <c r="E347" t="n">
@@ -7906,10 +7822,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C348" s="2" t="n">
+      <c r="C348" s="5" t="n">
         <v>131512.85</v>
       </c>
-      <c r="D348" s="3" t="n">
+      <c r="D348" s="6" t="n">
         <v>27.42678286</v>
       </c>
       <c r="E348" t="n">
@@ -7927,10 +7843,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C349" s="2" t="n">
+      <c r="C349" s="5" t="n">
         <v>271430.81</v>
       </c>
-      <c r="D349" s="3" t="n">
+      <c r="D349" s="6" t="n">
         <v>56.60643722</v>
       </c>
       <c r="E349" t="n">

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -69,11 +69,11 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -477,24 +477,129 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>213080.31</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>63.28378952</v>
+      </c>
+      <c r="E2" t="n">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>75899.28</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>22.54170768</v>
+      </c>
+      <c r="E3" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>24900.55</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>7.39533918</v>
+      </c>
+      <c r="E4" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>15339.66</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>4.55580253</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>7486.19</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>2.2233611</v>
+      </c>
+      <c r="E6" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="4" t="n">
+      <c r="C7" s="5" t="n">
+        <v>336705.99</v>
+      </c>
+      <c r="D7" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>0</v>
+      <c r="E7" s="4" t="n">
+        <v>275</v>
       </c>
     </row>
   </sheetData>
@@ -508,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E349"/>
+  <dimension ref="A1:E354"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -556,10 +661,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C2" s="5" t="n">
+      <c r="C2" s="2" t="n">
         <v>948.86</v>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="D2" s="3" t="n">
         <v>0.19126904</v>
       </c>
       <c r="E2" t="n">
@@ -577,10 +682,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" s="2" t="n">
         <v>461123.2</v>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="3" t="n">
         <v>92.95216732</v>
       </c>
       <c r="E3" t="n">
@@ -598,10 +703,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="2" t="n">
         <v>333</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="3" t="n">
         <v>0.06712538</v>
       </c>
       <c r="E4" t="n">
@@ -619,10 +724,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="2" t="n">
         <v>33681.49</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="3" t="n">
         <v>6.78943825</v>
       </c>
       <c r="E5" t="n">
@@ -640,10 +745,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="2" t="n">
         <v>3947.95</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="3" t="n">
         <v>0.94921987</v>
       </c>
       <c r="E6" t="n">
@@ -661,10 +766,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="2" t="n">
         <v>316928.34</v>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="3" t="n">
         <v>76.20022474</v>
       </c>
       <c r="E7" t="n">
@@ -682,10 +787,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="2" t="n">
         <v>28879.81</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="3" t="n">
         <v>6.94367696</v>
       </c>
       <c r="E8" t="n">
@@ -703,10 +808,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="2" t="n">
         <v>66159.13</v>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="3" t="n">
         <v>15.90687843</v>
       </c>
       <c r="E9" t="n">
@@ -724,10 +829,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="2" t="n">
         <v>672.72</v>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="3" t="n">
         <v>0.12167625</v>
       </c>
       <c r="E10" t="n">
@@ -745,10 +850,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="2" t="n">
         <v>506109.58</v>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="3" t="n">
         <v>91.54108388</v>
       </c>
       <c r="E11" t="n">
@@ -766,10 +871,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C12" s="2" t="n">
         <v>13144.61</v>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="3" t="n">
         <v>2.37749273</v>
       </c>
       <c r="E12" t="n">
@@ -787,10 +892,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C13" s="2" t="n">
         <v>32950.07</v>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="3" t="n">
         <v>5.95974714</v>
       </c>
       <c r="E13" t="n">
@@ -808,10 +913,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C14" s="5" t="n">
+      <c r="C14" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="3" t="n">
         <v>0.00340356</v>
       </c>
       <c r="E14" t="n">
@@ -829,10 +934,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C15" s="2" t="n">
         <v>3803.45</v>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="3" t="n">
         <v>1.43836189</v>
       </c>
       <c r="E15" t="n">
@@ -850,10 +955,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C16" s="5" t="n">
+      <c r="C16" s="2" t="n">
         <v>229609.87</v>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D16" s="3" t="n">
         <v>86.83224112000001</v>
       </c>
       <c r="E16" t="n">
@@ -871,10 +976,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C17" s="5" t="n">
+      <c r="C17" s="2" t="n">
         <v>884.04</v>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="D17" s="3" t="n">
         <v>0.33432001</v>
       </c>
       <c r="E17" t="n">
@@ -892,10 +997,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C18" s="5" t="n">
+      <c r="C18" s="2" t="n">
         <v>30122.92</v>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D18" s="3" t="n">
         <v>11.39167342</v>
       </c>
       <c r="E18" t="n">
@@ -913,10 +1018,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C19" s="5" t="n">
+      <c r="C19" s="2" t="n">
         <v>23268.18</v>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D19" s="3" t="n">
         <v>4.17124226</v>
       </c>
       <c r="E19" t="n">
@@ -934,10 +1039,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C20" s="5" t="n">
+      <c r="C20" s="2" t="n">
         <v>451338.15</v>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="D20" s="3" t="n">
         <v>80.91052954</v>
       </c>
       <c r="E20" t="n">
@@ -955,10 +1060,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C21" s="5" t="n">
+      <c r="C21" s="2" t="n">
         <v>20229.42</v>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D21" s="3" t="n">
         <v>3.62648955</v>
       </c>
       <c r="E21" t="n">
@@ -976,10 +1081,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C22" s="5" t="n">
+      <c r="C22" s="2" t="n">
         <v>62988</v>
       </c>
-      <c r="D22" s="6" t="n">
+      <c r="D22" s="3" t="n">
         <v>11.29173865</v>
       </c>
       <c r="E22" t="n">
@@ -997,10 +1102,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C23" s="5" t="n">
+      <c r="C23" s="2" t="n">
         <v>103.09</v>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="D23" s="3" t="n">
         <v>0.02902112</v>
       </c>
       <c r="E23" t="n">
@@ -1018,10 +1123,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C24" s="5" t="n">
+      <c r="C24" s="2" t="n">
         <v>283.13</v>
       </c>
-      <c r="D24" s="6" t="n">
+      <c r="D24" s="3" t="n">
         <v>0.07970463</v>
       </c>
       <c r="E24" t="n">
@@ -1039,10 +1144,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C25" s="5" t="n">
+      <c r="C25" s="2" t="n">
         <v>341584.75</v>
       </c>
-      <c r="D25" s="6" t="n">
+      <c r="D25" s="3" t="n">
         <v>96.16036696</v>
       </c>
       <c r="E25" t="n">
@@ -1060,10 +1165,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C26" s="5" t="n">
+      <c r="C26" s="2" t="n">
         <v>13253.08</v>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="D26" s="3" t="n">
         <v>3.7309073</v>
       </c>
       <c r="E26" t="n">
@@ -1081,10 +1186,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C27" s="5" t="n">
+      <c r="C27" s="2" t="n">
         <v>366675.1</v>
       </c>
-      <c r="D27" s="6" t="n">
+      <c r="D27" s="3" t="n">
         <v>88.88052623</v>
       </c>
       <c r="E27" t="n">
@@ -1102,10 +1207,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C28" s="5" t="n">
+      <c r="C28" s="2" t="n">
         <v>10967.83</v>
       </c>
-      <c r="D28" s="6" t="n">
+      <c r="D28" s="3" t="n">
         <v>2.65855659</v>
       </c>
       <c r="E28" t="n">
@@ -1123,10 +1228,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C29" s="5" t="n">
+      <c r="C29" s="2" t="n">
         <v>34905.37</v>
       </c>
-      <c r="D29" s="6" t="n">
+      <c r="D29" s="3" t="n">
         <v>8.460917179999999</v>
       </c>
       <c r="E29" t="n">
@@ -1144,10 +1249,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C30" s="5" t="n">
+      <c r="C30" s="2" t="n">
         <v>431085.81</v>
       </c>
-      <c r="D30" s="6" t="n">
+      <c r="D30" s="3" t="n">
         <v>81.83421629999999</v>
       </c>
       <c r="E30" t="n">
@@ -1165,10 +1270,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C31" s="5" t="n">
+      <c r="C31" s="2" t="n">
         <v>1633.45</v>
       </c>
-      <c r="D31" s="6" t="n">
+      <c r="D31" s="3" t="n">
         <v>0.31008235</v>
       </c>
       <c r="E31" t="n">
@@ -1186,10 +1291,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C32" s="5" t="n">
+      <c r="C32" s="2" t="n">
         <v>94060.16</v>
       </c>
-      <c r="D32" s="6" t="n">
+      <c r="D32" s="3" t="n">
         <v>17.85570135</v>
       </c>
       <c r="E32" t="n">
@@ -1207,10 +1312,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C33" s="5" t="n">
+      <c r="C33" s="2" t="n">
         <v>321805.16</v>
       </c>
-      <c r="D33" s="6" t="n">
+      <c r="D33" s="3" t="n">
         <v>78.53984421</v>
       </c>
       <c r="E33" t="n">
@@ -1228,10 +1333,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C34" s="5" t="n">
+      <c r="C34" s="2" t="n">
         <v>81063.48</v>
       </c>
-      <c r="D34" s="6" t="n">
+      <c r="D34" s="3" t="n">
         <v>19.78437229</v>
       </c>
       <c r="E34" t="n">
@@ -1249,10 +1354,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C35" s="5" t="n">
+      <c r="C35" s="2" t="n">
         <v>6866.27</v>
       </c>
-      <c r="D35" s="6" t="n">
+      <c r="D35" s="3" t="n">
         <v>1.6757835</v>
       </c>
       <c r="E35" t="n">
@@ -1270,10 +1375,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C36" s="5" t="n">
+      <c r="C36" s="2" t="n">
         <v>352851.14</v>
       </c>
-      <c r="D36" s="6" t="n">
+      <c r="D36" s="3" t="n">
         <v>94.15474251000001</v>
       </c>
       <c r="E36" t="n">
@@ -1291,10 +1396,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C37" s="5" t="n">
+      <c r="C37" s="2" t="n">
         <v>576.49</v>
       </c>
-      <c r="D37" s="6" t="n">
+      <c r="D37" s="3" t="n">
         <v>0.1538305</v>
       </c>
       <c r="E37" t="n">
@@ -1312,10 +1417,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C38" s="5" t="n">
+      <c r="C38" s="2" t="n">
         <v>21329</v>
       </c>
-      <c r="D38" s="6" t="n">
+      <c r="D38" s="3" t="n">
         <v>5.69142699</v>
       </c>
       <c r="E38" t="n">
@@ -1333,10 +1438,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C39" s="5" t="n">
+      <c r="C39" s="2" t="n">
         <v>83.52</v>
       </c>
-      <c r="D39" s="6" t="n">
+      <c r="D39" s="3" t="n">
         <v>0.01466719</v>
       </c>
       <c r="E39" t="n">
@@ -1354,10 +1459,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C40" s="5" t="n">
+      <c r="C40" s="2" t="n">
         <v>509873.13</v>
       </c>
-      <c r="D40" s="6" t="n">
+      <c r="D40" s="3" t="n">
         <v>89.54027855</v>
       </c>
       <c r="E40" t="n">
@@ -1375,10 +1480,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C41" s="5" t="n">
+      <c r="C41" s="2" t="n">
         <v>8520.23</v>
       </c>
-      <c r="D41" s="6" t="n">
+      <c r="D41" s="3" t="n">
         <v>1.49626196</v>
       </c>
       <c r="E41" t="n">
@@ -1396,10 +1501,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C42" s="5" t="n">
+      <c r="C42" s="2" t="n">
         <v>50957.5</v>
       </c>
-      <c r="D42" s="6" t="n">
+      <c r="D42" s="3" t="n">
         <v>8.94879231</v>
       </c>
       <c r="E42" t="n">
@@ -1417,10 +1522,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C43" s="5" t="n">
+      <c r="C43" s="2" t="n">
         <v>9326.15</v>
       </c>
-      <c r="D43" s="6" t="n">
+      <c r="D43" s="3" t="n">
         <v>1.62650962</v>
       </c>
       <c r="E43" t="n">
@@ -1438,10 +1543,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C44" s="5" t="n">
+      <c r="C44" s="2" t="n">
         <v>510341.61</v>
       </c>
-      <c r="D44" s="6" t="n">
+      <c r="D44" s="3" t="n">
         <v>89.00516713</v>
       </c>
       <c r="E44" t="n">
@@ -1459,10 +1564,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C45" s="5" t="n">
+      <c r="C45" s="2" t="n">
         <v>2517.04</v>
       </c>
-      <c r="D45" s="6" t="n">
+      <c r="D45" s="3" t="n">
         <v>0.43897962</v>
       </c>
       <c r="E45" t="n">
@@ -1480,10 +1585,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C46" s="5" t="n">
+      <c r="C46" s="2" t="n">
         <v>51199.45</v>
       </c>
-      <c r="D46" s="6" t="n">
+      <c r="D46" s="3" t="n">
         <v>8.92934363</v>
       </c>
       <c r="E46" t="n">
@@ -1501,10 +1606,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="C47" s="5" t="n">
+      <c r="C47" s="2" t="n">
         <v>850</v>
       </c>
-      <c r="D47" s="6" t="n">
+      <c r="D47" s="3" t="n">
         <v>0.25302704</v>
       </c>
       <c r="E47" t="n">
@@ -1522,10 +1627,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C48" s="5" t="n">
+      <c r="C48" s="2" t="n">
         <v>1223.36</v>
       </c>
-      <c r="D48" s="6" t="n">
+      <c r="D48" s="3" t="n">
         <v>0.36416843</v>
       </c>
       <c r="E48" t="n">
@@ -1543,10 +1648,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C49" s="5" t="n">
+      <c r="C49" s="2" t="n">
         <v>270843.56</v>
       </c>
-      <c r="D49" s="6" t="n">
+      <c r="D49" s="3" t="n">
         <v>80.62440645</v>
       </c>
       <c r="E49" t="n">
@@ -1564,10 +1669,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C50" s="5" t="n">
+      <c r="C50" s="2" t="n">
         <v>612.64</v>
       </c>
-      <c r="D50" s="6" t="n">
+      <c r="D50" s="3" t="n">
         <v>0.18236999</v>
       </c>
       <c r="E50" t="n">
@@ -1585,10 +1690,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C51" s="5" t="n">
+      <c r="C51" s="2" t="n">
         <v>62402.91</v>
       </c>
-      <c r="D51" s="6" t="n">
+      <c r="D51" s="3" t="n">
         <v>18.57602809</v>
       </c>
       <c r="E51" t="n">
@@ -1606,10 +1711,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C52" s="5" t="n">
+      <c r="C52" s="2" t="n">
         <v>555930.41</v>
       </c>
-      <c r="D52" s="6" t="n">
+      <c r="D52" s="3" t="n">
         <v>91.1452503</v>
       </c>
       <c r="E52" t="n">
@@ -1627,10 +1732,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C53" s="5" t="n">
+      <c r="C53" s="2" t="n">
         <v>1590.9</v>
       </c>
-      <c r="D53" s="6" t="n">
+      <c r="D53" s="3" t="n">
         <v>0.26082937</v>
       </c>
       <c r="E53" t="n">
@@ -1648,10 +1753,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C54" s="5" t="n">
+      <c r="C54" s="2" t="n">
         <v>52417.67</v>
       </c>
-      <c r="D54" s="6" t="n">
+      <c r="D54" s="3" t="n">
         <v>8.59392033</v>
       </c>
       <c r="E54" t="n">
@@ -1669,10 +1774,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C55" s="5" t="n">
+      <c r="C55" s="2" t="n">
         <v>10.55</v>
       </c>
-      <c r="D55" s="6" t="n">
+      <c r="D55" s="3" t="n">
         <v>0.00287103</v>
       </c>
       <c r="E55" t="n">
@@ -1690,10 +1795,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C56" s="5" t="n">
+      <c r="C56" s="2" t="n">
         <v>319888.32</v>
       </c>
-      <c r="D56" s="6" t="n">
+      <c r="D56" s="3" t="n">
         <v>87.05305848</v>
       </c>
       <c r="E56" t="n">
@@ -1711,10 +1816,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C57" s="5" t="n">
+      <c r="C57" s="2" t="n">
         <v>1278.17</v>
       </c>
-      <c r="D57" s="6" t="n">
+      <c r="D57" s="3" t="n">
         <v>0.34783579</v>
       </c>
       <c r="E57" t="n">
@@ -1732,10 +1837,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C58" s="5" t="n">
+      <c r="C58" s="2" t="n">
         <v>46286.58</v>
       </c>
-      <c r="D58" s="6" t="n">
+      <c r="D58" s="3" t="n">
         <v>12.5962347</v>
       </c>
       <c r="E58" t="n">
@@ -1753,10 +1858,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C59" s="5" t="n">
+      <c r="C59" s="2" t="n">
         <v>354.29</v>
       </c>
-      <c r="D59" s="6" t="n">
+      <c r="D59" s="3" t="n">
         <v>0.1171275</v>
       </c>
       <c r="E59" t="n">
@@ -1774,10 +1879,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C60" s="5" t="n">
+      <c r="C60" s="2" t="n">
         <v>121.49</v>
       </c>
-      <c r="D60" s="6" t="n">
+      <c r="D60" s="3" t="n">
         <v>0.04016433</v>
       </c>
       <c r="E60" t="n">
@@ -1795,10 +1900,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C61" s="5" t="n">
+      <c r="C61" s="2" t="n">
         <v>264522.3</v>
       </c>
-      <c r="D61" s="6" t="n">
+      <c r="D61" s="3" t="n">
         <v>87.4504938</v>
       </c>
       <c r="E61" t="n">
@@ -1816,10 +1921,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C62" s="5" t="n">
+      <c r="C62" s="2" t="n">
         <v>1149.77</v>
       </c>
-      <c r="D62" s="6" t="n">
+      <c r="D62" s="3" t="n">
         <v>0.38011145</v>
       </c>
       <c r="E62" t="n">
@@ -1837,10 +1942,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C63" s="5" t="n">
+      <c r="C63" s="2" t="n">
         <v>36334.49</v>
       </c>
-      <c r="D63" s="6" t="n">
+      <c r="D63" s="3" t="n">
         <v>12.01210292</v>
       </c>
       <c r="E63" t="n">
@@ -1858,10 +1963,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C64" s="5" t="n">
+      <c r="C64" s="2" t="n">
         <v>4545.45</v>
       </c>
-      <c r="D64" s="6" t="n">
+      <c r="D64" s="3" t="n">
         <v>1.24043036</v>
       </c>
       <c r="E64" t="n">
@@ -1879,10 +1984,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C65" s="5" t="n">
+      <c r="C65" s="2" t="n">
         <v>874</v>
       </c>
-      <c r="D65" s="6" t="n">
+      <c r="D65" s="3" t="n">
         <v>0.23851019</v>
       </c>
       <c r="E65" t="n">
@@ -1900,10 +2005,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C66" s="5" t="n">
+      <c r="C66" s="2" t="n">
         <v>284866.12</v>
       </c>
-      <c r="D66" s="6" t="n">
+      <c r="D66" s="3" t="n">
         <v>77.73852608</v>
       </c>
       <c r="E66" t="n">
@@ -1921,10 +2026,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C67" s="5" t="n">
+      <c r="C67" s="2" t="n">
         <v>1590.95</v>
       </c>
-      <c r="D67" s="6" t="n">
+      <c r="D67" s="3" t="n">
         <v>0.43416222</v>
       </c>
       <c r="E67" t="n">
@@ -1942,10 +2047,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C68" s="5" t="n">
+      <c r="C68" s="2" t="n">
         <v>74564.85000000001</v>
       </c>
-      <c r="D68" s="6" t="n">
+      <c r="D68" s="3" t="n">
         <v>20.34837115</v>
       </c>
       <c r="E68" t="n">
@@ -1963,10 +2068,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C69" s="5" t="n">
+      <c r="C69" s="2" t="n">
         <v>442814.15</v>
       </c>
-      <c r="D69" s="6" t="n">
+      <c r="D69" s="3" t="n">
         <v>80.48822254</v>
       </c>
       <c r="E69" t="n">
@@ -1984,10 +2089,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C70" s="5" t="n">
+      <c r="C70" s="2" t="n">
         <v>914.39</v>
       </c>
-      <c r="D70" s="6" t="n">
+      <c r="D70" s="3" t="n">
         <v>0.16620432</v>
       </c>
       <c r="E70" t="n">
@@ -2005,10 +2110,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C71" s="5" t="n">
+      <c r="C71" s="2" t="n">
         <v>106431.64</v>
       </c>
-      <c r="D71" s="6" t="n">
+      <c r="D71" s="3" t="n">
         <v>19.34557314</v>
       </c>
       <c r="E71" t="n">
@@ -2026,10 +2131,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C72" s="5" t="n">
+      <c r="C72" s="2" t="n">
         <v>166</v>
       </c>
-      <c r="D72" s="6" t="n">
+      <c r="D72" s="3" t="n">
         <v>0.02878159</v>
       </c>
       <c r="E72" t="n">
@@ -2047,10 +2152,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C73" s="5" t="n">
+      <c r="C73" s="2" t="n">
         <v>81.83</v>
       </c>
-      <c r="D73" s="6" t="n">
+      <c r="D73" s="3" t="n">
         <v>0.01418794</v>
       </c>
       <c r="E73" t="n">
@@ -2068,10 +2173,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C74" s="5" t="n">
+      <c r="C74" s="2" t="n">
         <v>528120.33</v>
       </c>
-      <c r="D74" s="6" t="n">
+      <c r="D74" s="3" t="n">
         <v>91.56712743999999</v>
       </c>
       <c r="E74" t="n">
@@ -2089,10 +2194,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C75" s="5" t="n">
+      <c r="C75" s="2" t="n">
         <v>567.3200000000001</v>
       </c>
-      <c r="D75" s="6" t="n">
+      <c r="D75" s="3" t="n">
         <v>0.09836369</v>
       </c>
       <c r="E75" t="n">
@@ -2110,10 +2215,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C76" s="5" t="n">
+      <c r="C76" s="2" t="n">
         <v>47822.08</v>
       </c>
-      <c r="D76" s="6" t="n">
+      <c r="D76" s="3" t="n">
         <v>8.29153934</v>
       </c>
       <c r="E76" t="n">
@@ -2131,10 +2236,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C77" s="5" t="n">
+      <c r="C77" s="2" t="n">
         <v>2157.29</v>
       </c>
-      <c r="D77" s="6" t="n">
+      <c r="D77" s="3" t="n">
         <v>1.00708473</v>
       </c>
       <c r="E77" t="n">
@@ -2152,10 +2257,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C78" s="5" t="n">
+      <c r="C78" s="2" t="n">
         <v>177127.26</v>
       </c>
-      <c r="D78" s="6" t="n">
+      <c r="D78" s="3" t="n">
         <v>82.68807579999999</v>
       </c>
       <c r="E78" t="n">
@@ -2173,10 +2278,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C79" s="5" t="n">
+      <c r="C79" s="2" t="n">
         <v>826.1799999999999</v>
       </c>
-      <c r="D79" s="6" t="n">
+      <c r="D79" s="3" t="n">
         <v>0.38568448</v>
       </c>
       <c r="E79" t="n">
@@ -2194,10 +2299,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C80" s="5" t="n">
+      <c r="C80" s="2" t="n">
         <v>34100.64</v>
       </c>
-      <c r="D80" s="6" t="n">
+      <c r="D80" s="3" t="n">
         <v>15.91915499</v>
       </c>
       <c r="E80" t="n">
@@ -2215,10 +2320,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C81" s="5" t="n">
+      <c r="C81" s="2" t="n">
         <v>54.12</v>
       </c>
-      <c r="D81" s="6" t="n">
+      <c r="D81" s="3" t="n">
         <v>0.01747125</v>
       </c>
       <c r="E81" t="n">
@@ -2236,10 +2341,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C82" s="5" t="n">
+      <c r="C82" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="D82" s="6" t="n">
+      <c r="D82" s="3" t="n">
         <v>0.0213064</v>
       </c>
       <c r="E82" t="n">
@@ -2257,10 +2362,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C83" s="5" t="n">
+      <c r="C83" s="2" t="n">
         <v>21771.31</v>
       </c>
-      <c r="D83" s="6" t="n">
+      <c r="D83" s="3" t="n">
         <v>7.02830778</v>
       </c>
       <c r="E83" t="n">
@@ -2278,10 +2383,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C84" s="5" t="n">
+      <c r="C84" s="2" t="n">
         <v>214416.2</v>
       </c>
-      <c r="D84" s="6" t="n">
+      <c r="D84" s="3" t="n">
         <v>69.21875842999999</v>
       </c>
       <c r="E84" t="n">
@@ -2299,10 +2404,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C85" s="5" t="n">
+      <c r="C85" s="2" t="n">
         <v>9060.450000000001</v>
       </c>
-      <c r="D85" s="6" t="n">
+      <c r="D85" s="3" t="n">
         <v>2.92493338</v>
       </c>
       <c r="E85" t="n">
@@ -2320,10 +2425,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C86" s="5" t="n">
+      <c r="C86" s="2" t="n">
         <v>64397.95</v>
       </c>
-      <c r="D86" s="6" t="n">
+      <c r="D86" s="3" t="n">
         <v>20.78922276</v>
       </c>
       <c r="E86" t="n">
@@ -2341,10 +2446,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C87" s="5" t="n">
+      <c r="C87" s="2" t="n">
         <v>1067.9</v>
       </c>
-      <c r="D87" s="6" t="n">
+      <c r="D87" s="3" t="n">
         <v>0.29681338</v>
       </c>
       <c r="E87" t="n">
@@ -2362,10 +2467,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C88" s="5" t="n">
+      <c r="C88" s="2" t="n">
         <v>260988.37</v>
       </c>
-      <c r="D88" s="6" t="n">
+      <c r="D88" s="3" t="n">
         <v>72.53941456</v>
       </c>
       <c r="E88" t="n">
@@ -2383,10 +2488,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C89" s="5" t="n">
+      <c r="C89" s="2" t="n">
         <v>7522.28</v>
       </c>
-      <c r="D89" s="6" t="n">
+      <c r="D89" s="3" t="n">
         <v>2.09075135</v>
       </c>
       <c r="E89" t="n">
@@ -2404,10 +2509,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C90" s="5" t="n">
+      <c r="C90" s="2" t="n">
         <v>90209.81</v>
       </c>
-      <c r="D90" s="6" t="n">
+      <c r="D90" s="3" t="n">
         <v>25.07302071</v>
       </c>
       <c r="E90" t="n">
@@ -2425,10 +2530,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C91" s="5" t="n">
+      <c r="C91" s="2" t="n">
         <v>11124.49</v>
       </c>
-      <c r="D91" s="6" t="n">
+      <c r="D91" s="3" t="n">
         <v>3.35098295</v>
       </c>
       <c r="E91" t="n">
@@ -2446,10 +2551,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C92" s="5" t="n">
+      <c r="C92" s="2" t="n">
         <v>201888.41</v>
       </c>
-      <c r="D92" s="6" t="n">
+      <c r="D92" s="3" t="n">
         <v>60.81398972</v>
       </c>
       <c r="E92" t="n">
@@ -2467,10 +2572,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C93" s="5" t="n">
+      <c r="C93" s="2" t="n">
         <v>15503.87</v>
       </c>
-      <c r="D93" s="6" t="n">
+      <c r="D93" s="3" t="n">
         <v>4.67016502</v>
       </c>
       <c r="E93" t="n">
@@ -2488,10 +2593,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C94" s="5" t="n">
+      <c r="C94" s="2" t="n">
         <v>103460.15</v>
       </c>
-      <c r="D94" s="6" t="n">
+      <c r="D94" s="3" t="n">
         <v>31.1648623</v>
       </c>
       <c r="E94" t="n">
@@ -2509,10 +2614,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C95" s="5" t="n">
+      <c r="C95" s="2" t="n">
         <v>1029.41</v>
       </c>
-      <c r="D95" s="6" t="n">
+      <c r="D95" s="3" t="n">
         <v>0.31513536</v>
       </c>
       <c r="E95" t="n">
@@ -2530,10 +2635,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C96" s="5" t="n">
+      <c r="C96" s="2" t="n">
         <v>1848</v>
       </c>
-      <c r="D96" s="6" t="n">
+      <c r="D96" s="3" t="n">
         <v>0.56573196</v>
       </c>
       <c r="E96" t="n">
@@ -2551,10 +2656,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C97" s="5" t="n">
+      <c r="C97" s="2" t="n">
         <v>126297.98</v>
       </c>
-      <c r="D97" s="6" t="n">
+      <c r="D97" s="3" t="n">
         <v>38.66385499</v>
       </c>
       <c r="E97" t="n">
@@ -2572,10 +2677,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C98" s="5" t="n">
+      <c r="C98" s="2" t="n">
         <v>23680.09</v>
       </c>
-      <c r="D98" s="6" t="n">
+      <c r="D98" s="3" t="n">
         <v>7.24923364</v>
       </c>
       <c r="E98" t="n">
@@ -2593,10 +2698,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C99" s="5" t="n">
+      <c r="C99" s="2" t="n">
         <v>173800.98</v>
       </c>
-      <c r="D99" s="6" t="n">
+      <c r="D99" s="3" t="n">
         <v>53.20604405</v>
       </c>
       <c r="E99" t="n">
@@ -2614,10 +2719,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C100" s="5" t="n">
+      <c r="C100" s="2" t="n">
         <v>856.11</v>
       </c>
-      <c r="D100" s="6" t="n">
+      <c r="D100" s="3" t="n">
         <v>0.22747196</v>
       </c>
       <c r="E100" t="n">
@@ -2635,10 +2740,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C101" s="5" t="n">
+      <c r="C101" s="2" t="n">
         <v>9.68</v>
       </c>
-      <c r="D101" s="6" t="n">
+      <c r="D101" s="3" t="n">
         <v>0.00257202</v>
       </c>
       <c r="E101" t="n">
@@ -2656,10 +2761,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C102" s="5" t="n">
+      <c r="C102" s="2" t="n">
         <v>296012.79</v>
       </c>
-      <c r="D102" s="6" t="n">
+      <c r="D102" s="3" t="n">
         <v>78.65181887</v>
       </c>
       <c r="E102" t="n">
@@ -2677,10 +2782,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C103" s="5" t="n">
+      <c r="C103" s="2" t="n">
         <v>3709.15</v>
       </c>
-      <c r="D103" s="6" t="n">
+      <c r="D103" s="3" t="n">
         <v>0.98553645</v>
       </c>
       <c r="E103" t="n">
@@ -2698,10 +2803,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C104" s="5" t="n">
+      <c r="C104" s="2" t="n">
         <v>75770.75</v>
       </c>
-      <c r="D104" s="6" t="n">
+      <c r="D104" s="3" t="n">
         <v>20.13260071</v>
       </c>
       <c r="E104" t="n">
@@ -2719,10 +2824,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C105" s="5" t="n">
+      <c r="C105" s="2" t="n">
         <v>363.62</v>
       </c>
-      <c r="D105" s="6" t="n">
+      <c r="D105" s="3" t="n">
         <v>0.09792976</v>
       </c>
       <c r="E105" t="n">
@@ -2740,10 +2845,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C106" s="5" t="n">
+      <c r="C106" s="2" t="n">
         <v>303265.05</v>
       </c>
-      <c r="D106" s="6" t="n">
+      <c r="D106" s="3" t="n">
         <v>81.67502655</v>
       </c>
       <c r="E106" t="n">
@@ -2761,10 +2866,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C107" s="5" t="n">
+      <c r="C107" s="2" t="n">
         <v>829.42</v>
       </c>
-      <c r="D107" s="6" t="n">
+      <c r="D107" s="3" t="n">
         <v>0.22337853</v>
       </c>
       <c r="E107" t="n">
@@ -2782,10 +2887,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C108" s="5" t="n">
+      <c r="C108" s="2" t="n">
         <v>66848.86</v>
       </c>
-      <c r="D108" s="6" t="n">
+      <c r="D108" s="3" t="n">
         <v>18.00366516</v>
       </c>
       <c r="E108" t="n">
@@ -2803,10 +2908,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C109" s="5" t="n">
+      <c r="C109" s="2" t="n">
         <v>174192.16</v>
       </c>
-      <c r="D109" s="6" t="n">
+      <c r="D109" s="3" t="n">
         <v>66.86566559000001</v>
       </c>
       <c r="E109" t="n">
@@ -2824,10 +2929,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C110" s="5" t="n">
+      <c r="C110" s="2" t="n">
         <v>19438.25</v>
       </c>
-      <c r="D110" s="6" t="n">
+      <c r="D110" s="3" t="n">
         <v>7.461596</v>
       </c>
       <c r="E110" t="n">
@@ -2845,10 +2950,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C111" s="5" t="n">
+      <c r="C111" s="2" t="n">
         <v>66880.21000000001</v>
       </c>
-      <c r="D111" s="6" t="n">
+      <c r="D111" s="3" t="n">
         <v>25.67273841</v>
       </c>
       <c r="E111" t="n">
@@ -2866,10 +2971,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C112" s="5" t="n">
+      <c r="C112" s="2" t="n">
         <v>1885.29</v>
       </c>
-      <c r="D112" s="6" t="n">
+      <c r="D112" s="3" t="n">
         <v>0.5105483200000001</v>
       </c>
       <c r="E112" t="n">
@@ -2887,10 +2992,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C113" s="5" t="n">
+      <c r="C113" s="2" t="n">
         <v>642.63</v>
       </c>
-      <c r="D113" s="6" t="n">
+      <c r="D113" s="3" t="n">
         <v>0.17402822</v>
       </c>
       <c r="E113" t="n">
@@ -2908,10 +3013,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C114" s="5" t="n">
+      <c r="C114" s="2" t="n">
         <v>2177.75</v>
       </c>
-      <c r="D114" s="6" t="n">
+      <c r="D114" s="3" t="n">
         <v>0.58974832</v>
       </c>
       <c r="E114" t="n">
@@ -2929,10 +3034,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C115" s="5" t="n">
+      <c r="C115" s="2" t="n">
         <v>202289.9</v>
       </c>
-      <c r="D115" s="6" t="n">
+      <c r="D115" s="3" t="n">
         <v>54.78137012</v>
       </c>
       <c r="E115" t="n">
@@ -2950,10 +3055,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C116" s="5" t="n">
+      <c r="C116" s="2" t="n">
         <v>30328.46</v>
       </c>
-      <c r="D116" s="6" t="n">
+      <c r="D116" s="3" t="n">
         <v>8.213136649999999</v>
       </c>
       <c r="E116" t="n">
@@ -2971,10 +3076,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C117" s="5" t="n">
+      <c r="C117" s="2" t="n">
         <v>131943.66</v>
       </c>
-      <c r="D117" s="6" t="n">
+      <c r="D117" s="3" t="n">
         <v>35.73116836</v>
       </c>
       <c r="E117" t="n">
@@ -2992,10 +3097,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C118" s="5" t="n">
+      <c r="C118" s="2" t="n">
         <v>101.72</v>
       </c>
-      <c r="D118" s="6" t="n">
+      <c r="D118" s="3" t="n">
         <v>0.03804713</v>
       </c>
       <c r="E118" t="n">
@@ -3013,10 +3118,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C119" s="5" t="n">
+      <c r="C119" s="2" t="n">
         <v>58</v>
       </c>
-      <c r="D119" s="6" t="n">
+      <c r="D119" s="3" t="n">
         <v>0.02169419</v>
       </c>
       <c r="E119" t="n">
@@ -3034,10 +3139,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C120" s="5" t="n">
+      <c r="C120" s="2" t="n">
         <v>167439.3</v>
       </c>
-      <c r="D120" s="6" t="n">
+      <c r="D120" s="3" t="n">
         <v>62.62863161</v>
       </c>
       <c r="E120" t="n">
@@ -3055,10 +3160,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C121" s="5" t="n">
+      <c r="C121" s="2" t="n">
         <v>7300.3</v>
       </c>
-      <c r="D121" s="6" t="n">
+      <c r="D121" s="3" t="n">
         <v>2.73058833</v>
       </c>
       <c r="E121" t="n">
@@ -3076,10 +3181,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C122" s="5" t="n">
+      <c r="C122" s="2" t="n">
         <v>92453.32000000001</v>
       </c>
-      <c r="D122" s="6" t="n">
+      <c r="D122" s="3" t="n">
         <v>34.58103874</v>
       </c>
       <c r="E122" t="n">
@@ -3097,10 +3202,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C123" s="5" t="n">
+      <c r="C123" s="2" t="n">
         <v>1475.74</v>
       </c>
-      <c r="D123" s="6" t="n">
+      <c r="D123" s="3" t="n">
         <v>0.33417908</v>
       </c>
       <c r="E123" t="n">
@@ -3118,10 +3223,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C124" s="5" t="n">
+      <c r="C124" s="2" t="n">
         <v>2209.05</v>
       </c>
-      <c r="D124" s="6" t="n">
+      <c r="D124" s="3" t="n">
         <v>0.50023602</v>
       </c>
       <c r="E124" t="n">
@@ -3139,10 +3244,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C125" s="5" t="n">
+      <c r="C125" s="2" t="n">
         <v>232354.93</v>
       </c>
-      <c r="D125" s="6" t="n">
+      <c r="D125" s="3" t="n">
         <v>52.61642084</v>
       </c>
       <c r="E125" t="n">
@@ -3160,10 +3265,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C126" s="5" t="n">
+      <c r="C126" s="2" t="n">
         <v>11084.31</v>
       </c>
-      <c r="D126" s="6" t="n">
+      <c r="D126" s="3" t="n">
         <v>2.51002516</v>
       </c>
       <c r="E126" t="n">
@@ -3181,10 +3286,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C127" s="5" t="n">
+      <c r="C127" s="2" t="n">
         <v>194477.52</v>
       </c>
-      <c r="D127" s="6" t="n">
+      <c r="D127" s="3" t="n">
         <v>44.0391389</v>
       </c>
       <c r="E127" t="n">
@@ -3202,10 +3307,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C128" s="5" t="n">
+      <c r="C128" s="2" t="n">
         <v>2990.78</v>
       </c>
-      <c r="D128" s="6" t="n">
+      <c r="D128" s="3" t="n">
         <v>0.63513389</v>
       </c>
       <c r="E128" t="n">
@@ -3223,10 +3328,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C129" s="5" t="n">
+      <c r="C129" s="2" t="n">
         <v>847.45</v>
       </c>
-      <c r="D129" s="6" t="n">
+      <c r="D129" s="3" t="n">
         <v>0.17996784</v>
       </c>
       <c r="E129" t="n">
@@ -3244,10 +3349,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C130" s="5" t="n">
+      <c r="C130" s="2" t="n">
         <v>211.86</v>
       </c>
-      <c r="D130" s="6" t="n">
+      <c r="D130" s="3" t="n">
         <v>0.04499143</v>
       </c>
       <c r="E130" t="n">
@@ -3265,10 +3370,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C131" s="5" t="n">
+      <c r="C131" s="2" t="n">
         <v>222684.94</v>
       </c>
-      <c r="D131" s="6" t="n">
+      <c r="D131" s="3" t="n">
         <v>47.29025603</v>
       </c>
       <c r="E131" t="n">
@@ -3286,10 +3391,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C132" s="5" t="n">
+      <c r="C132" s="2" t="n">
         <v>10642.51</v>
       </c>
-      <c r="D132" s="6" t="n">
+      <c r="D132" s="3" t="n">
         <v>2.26008558</v>
       </c>
       <c r="E132" t="n">
@@ -3307,10 +3412,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C133" s="5" t="n">
+      <c r="C133" s="2" t="n">
         <v>233512.15</v>
       </c>
-      <c r="D133" s="6" t="n">
+      <c r="D133" s="3" t="n">
         <v>49.58956523</v>
       </c>
       <c r="E133" t="n">
@@ -3328,10 +3433,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C134" s="5" t="n">
+      <c r="C134" s="2" t="n">
         <v>2894.67</v>
       </c>
-      <c r="D134" s="6" t="n">
+      <c r="D134" s="3" t="n">
         <v>0.84868485</v>
       </c>
       <c r="E134" t="n">
@@ -3349,10 +3454,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C135" s="5" t="n">
+      <c r="C135" s="2" t="n">
         <v>2112.75</v>
       </c>
-      <c r="D135" s="6" t="n">
+      <c r="D135" s="3" t="n">
         <v>0.61943465</v>
       </c>
       <c r="E135" t="n">
@@ -3370,10 +3475,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C136" s="5" t="n">
+      <c r="C136" s="2" t="n">
         <v>133738.48</v>
       </c>
-      <c r="D136" s="6" t="n">
+      <c r="D136" s="3" t="n">
         <v>39.21062549</v>
       </c>
       <c r="E136" t="n">
@@ -3391,10 +3496,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C137" s="5" t="n">
+      <c r="C137" s="2" t="n">
         <v>9278.84</v>
       </c>
-      <c r="D137" s="6" t="n">
+      <c r="D137" s="3" t="n">
         <v>2.72045204</v>
       </c>
       <c r="E137" t="n">
@@ -3412,10 +3517,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C138" s="5" t="n">
+      <c r="C138" s="2" t="n">
         <v>193052.4</v>
       </c>
-      <c r="D138" s="6" t="n">
+      <c r="D138" s="3" t="n">
         <v>56.60080297</v>
       </c>
       <c r="E138" t="n">
@@ -3433,10 +3538,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C139" s="5" t="n">
+      <c r="C139" s="2" t="n">
         <v>138.16</v>
       </c>
-      <c r="D139" s="6" t="n">
+      <c r="D139" s="3" t="n">
         <v>0.04037037</v>
       </c>
       <c r="E139" t="n">
@@ -3454,10 +3559,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C140" s="5" t="n">
+      <c r="C140" s="2" t="n">
         <v>165616.96</v>
       </c>
-      <c r="D140" s="6" t="n">
+      <c r="D140" s="3" t="n">
         <v>48.39329811</v>
       </c>
       <c r="E140" t="n">
@@ -3475,10 +3580,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C141" s="5" t="n">
+      <c r="C141" s="2" t="n">
         <v>14589.85</v>
       </c>
-      <c r="D141" s="6" t="n">
+      <c r="D141" s="3" t="n">
         <v>4.26315614</v>
       </c>
       <c r="E141" t="n">
@@ -3496,10 +3601,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C142" s="5" t="n">
+      <c r="C142" s="2" t="n">
         <v>161886.22</v>
       </c>
-      <c r="D142" s="6" t="n">
+      <c r="D142" s="3" t="n">
         <v>47.30317538</v>
       </c>
       <c r="E142" t="n">
@@ -3517,10 +3622,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C143" s="5" t="n">
+      <c r="C143" s="2" t="n">
         <v>39179.97</v>
       </c>
-      <c r="D143" s="6" t="n">
+      <c r="D143" s="3" t="n">
         <v>6.57522763</v>
       </c>
       <c r="E143" t="n">
@@ -3538,10 +3643,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C144" s="5" t="n">
+      <c r="C144" s="2" t="n">
         <v>142325.87</v>
       </c>
-      <c r="D144" s="6" t="n">
+      <c r="D144" s="3" t="n">
         <v>23.88529122</v>
       </c>
       <c r="E144" t="n">
@@ -3559,10 +3664,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C145" s="5" t="n">
+      <c r="C145" s="2" t="n">
         <v>16620.71</v>
       </c>
-      <c r="D145" s="6" t="n">
+      <c r="D145" s="3" t="n">
         <v>2.78930667</v>
       </c>
       <c r="E145" t="n">
@@ -3580,10 +3685,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C146" s="5" t="n">
+      <c r="C146" s="2" t="n">
         <v>397745.9</v>
       </c>
-      <c r="D146" s="6" t="n">
+      <c r="D146" s="3" t="n">
         <v>66.75017447</v>
       </c>
       <c r="E146" t="n">
@@ -3601,10 +3706,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C147" s="5" t="n">
+      <c r="C147" s="2" t="n">
         <v>1244.23</v>
       </c>
-      <c r="D147" s="6" t="n">
+      <c r="D147" s="3" t="n">
         <v>0.42616348</v>
       </c>
       <c r="E147" t="n">
@@ -3622,10 +3727,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C148" s="5" t="n">
+      <c r="C148" s="2" t="n">
         <v>4545.45</v>
       </c>
-      <c r="D148" s="6" t="n">
+      <c r="D148" s="3" t="n">
         <v>1.55687034</v>
       </c>
       <c r="E148" t="n">
@@ -3643,10 +3748,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C149" s="5" t="n">
+      <c r="C149" s="2" t="n">
         <v>54421.47</v>
       </c>
-      <c r="D149" s="6" t="n">
+      <c r="D149" s="3" t="n">
         <v>18.63999655</v>
       </c>
       <c r="E149" t="n">
@@ -3664,10 +3769,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C150" s="5" t="n">
+      <c r="C150" s="2" t="n">
         <v>231749.58</v>
       </c>
-      <c r="D150" s="6" t="n">
+      <c r="D150" s="3" t="n">
         <v>79.37696964</v>
       </c>
       <c r="E150" t="n">
@@ -3685,10 +3790,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C151" s="5" t="n">
+      <c r="C151" s="2" t="n">
         <v>29.6</v>
       </c>
-      <c r="D151" s="6" t="n">
+      <c r="D151" s="3" t="n">
         <v>0.00689719</v>
       </c>
       <c r="E151" t="n">
@@ -3706,10 +3811,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C152" s="5" t="n">
+      <c r="C152" s="2" t="n">
         <v>309.27</v>
       </c>
-      <c r="D152" s="6" t="n">
+      <c r="D152" s="3" t="n">
         <v>0.07206398</v>
       </c>
       <c r="E152" t="n">
@@ -3727,10 +3832,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C153" s="5" t="n">
+      <c r="C153" s="2" t="n">
         <v>3725.16</v>
       </c>
-      <c r="D153" s="6" t="n">
+      <c r="D153" s="3" t="n">
         <v>0.8680113</v>
       </c>
       <c r="E153" t="n">
@@ -3748,10 +3853,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C154" s="5" t="n">
+      <c r="C154" s="2" t="n">
         <v>8.109999999999999</v>
       </c>
-      <c r="D154" s="6" t="n">
+      <c r="D154" s="3" t="n">
         <v>0.00188974</v>
       </c>
       <c r="E154" t="n">
@@ -3769,10 +3874,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C155" s="5" t="n">
+      <c r="C155" s="2" t="n">
         <v>163136.27</v>
       </c>
-      <c r="D155" s="6" t="n">
+      <c r="D155" s="3" t="n">
         <v>38.01289779</v>
       </c>
       <c r="E155" t="n">
@@ -3790,10 +3895,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C156" s="5" t="n">
+      <c r="C156" s="2" t="n">
         <v>261951.9</v>
       </c>
-      <c r="D156" s="6" t="n">
+      <c r="D156" s="3" t="n">
         <v>61.03824</v>
       </c>
       <c r="E156" t="n">
@@ -3811,10 +3916,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C157" s="5" t="n">
+      <c r="C157" s="2" t="n">
         <v>55.55</v>
       </c>
-      <c r="D157" s="6" t="n">
+      <c r="D157" s="3" t="n">
         <v>0.01644298</v>
       </c>
       <c r="E157" t="n">
@@ -3832,10 +3937,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C158" s="5" t="n">
+      <c r="C158" s="2" t="n">
         <v>91.41</v>
       </c>
-      <c r="D158" s="6" t="n">
+      <c r="D158" s="3" t="n">
         <v>0.02705766</v>
       </c>
       <c r="E158" t="n">
@@ -3853,10 +3958,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C159" s="5" t="n">
+      <c r="C159" s="2" t="n">
         <v>5382.13</v>
       </c>
-      <c r="D159" s="6" t="n">
+      <c r="D159" s="3" t="n">
         <v>1.59312834</v>
       </c>
       <c r="E159" t="n">
@@ -3874,10 +3979,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C160" s="5" t="n">
+      <c r="C160" s="2" t="n">
         <v>909.09</v>
       </c>
-      <c r="D160" s="6" t="n">
+      <c r="D160" s="3" t="n">
         <v>0.26909366</v>
       </c>
       <c r="E160" t="n">
@@ -3895,10 +4000,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C161" s="5" t="n">
+      <c r="C161" s="2" t="n">
         <v>32670.17</v>
       </c>
-      <c r="D161" s="6" t="n">
+      <c r="D161" s="3" t="n">
         <v>9.670478749999999</v>
       </c>
       <c r="E161" t="n">
@@ -3916,10 +4021,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C162" s="5" t="n">
+      <c r="C162" s="2" t="n">
         <v>298725.7</v>
       </c>
-      <c r="D162" s="6" t="n">
+      <c r="D162" s="3" t="n">
         <v>88.42379861000001</v>
       </c>
       <c r="E162" t="n">
@@ -3937,10 +4042,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C163" s="5" t="n">
+      <c r="C163" s="2" t="n">
         <v>287.66</v>
       </c>
-      <c r="D163" s="6" t="n">
+      <c r="D163" s="3" t="n">
         <v>0.08204844999999999</v>
       </c>
       <c r="E163" t="n">
@@ -3958,10 +4063,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C164" s="5" t="n">
+      <c r="C164" s="2" t="n">
         <v>9919.66</v>
       </c>
-      <c r="D164" s="6" t="n">
+      <c r="D164" s="3" t="n">
         <v>2.82935676</v>
       </c>
       <c r="E164" t="n">
@@ -3979,10 +4084,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C165" s="5" t="n">
+      <c r="C165" s="2" t="n">
         <v>1385.01</v>
       </c>
-      <c r="D165" s="6" t="n">
+      <c r="D165" s="3" t="n">
         <v>0.39504251</v>
       </c>
       <c r="E165" t="n">
@@ -4000,10 +4105,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C166" s="5" t="n">
+      <c r="C166" s="2" t="n">
         <v>69940.2</v>
       </c>
-      <c r="D166" s="6" t="n">
+      <c r="D166" s="3" t="n">
         <v>19.94884679</v>
       </c>
       <c r="E166" t="n">
@@ -4021,10 +4126,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C167" s="5" t="n">
+      <c r="C167" s="2" t="n">
         <v>269065.18</v>
       </c>
-      <c r="D167" s="6" t="n">
+      <c r="D167" s="3" t="n">
         <v>76.74470549</v>
       </c>
       <c r="E167" t="n">
@@ -4042,10 +4147,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C168" s="5" t="n">
+      <c r="C168" s="2" t="n">
         <v>580.2</v>
       </c>
-      <c r="D168" s="6" t="n">
+      <c r="D168" s="3" t="n">
         <v>0.1561468</v>
       </c>
       <c r="E168" t="n">
@@ -4063,10 +4168,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C169" s="5" t="n">
+      <c r="C169" s="2" t="n">
         <v>98.44</v>
       </c>
-      <c r="D169" s="6" t="n">
+      <c r="D169" s="3" t="n">
         <v>0.02649275</v>
       </c>
       <c r="E169" t="n">
@@ -4084,10 +4189,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C170" s="5" t="n">
+      <c r="C170" s="2" t="n">
         <v>172.72</v>
       </c>
-      <c r="D170" s="6" t="n">
+      <c r="D170" s="3" t="n">
         <v>0.04648341</v>
       </c>
       <c r="E170" t="n">
@@ -4105,10 +4210,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C171" s="5" t="n">
+      <c r="C171" s="2" t="n">
         <v>3342.15</v>
       </c>
-      <c r="D171" s="6" t="n">
+      <c r="D171" s="3" t="n">
         <v>0.89945887</v>
       </c>
       <c r="E171" t="n">
@@ -4126,10 +4231,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C172" s="5" t="n">
+      <c r="C172" s="2" t="n">
         <v>7627.33</v>
       </c>
-      <c r="D172" s="6" t="n">
+      <c r="D172" s="3" t="n">
         <v>2.05271147</v>
       </c>
       <c r="E172" t="n">
@@ -4147,10 +4252,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C173" s="5" t="n">
+      <c r="C173" s="2" t="n">
         <v>359752.57</v>
       </c>
-      <c r="D173" s="6" t="n">
+      <c r="D173" s="3" t="n">
         <v>96.81870670000001</v>
       </c>
       <c r="E173" t="n">
@@ -4168,10 +4273,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C174" s="5" t="n">
+      <c r="C174" s="2" t="n">
         <v>61.94</v>
       </c>
-      <c r="D174" s="6" t="n">
+      <c r="D174" s="3" t="n">
         <v>0.02167129</v>
       </c>
       <c r="E174" t="n">
@@ -4189,10 +4294,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C175" s="5" t="n">
+      <c r="C175" s="2" t="n">
         <v>222</v>
       </c>
-      <c r="D175" s="6" t="n">
+      <c r="D175" s="3" t="n">
         <v>0.07767236</v>
       </c>
       <c r="E175" t="n">
@@ -4210,10 +4315,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C176" s="5" t="n">
+      <c r="C176" s="2" t="n">
         <v>10426.45</v>
       </c>
-      <c r="D176" s="6" t="n">
+      <c r="D176" s="3" t="n">
         <v>3.64795946</v>
       </c>
       <c r="E176" t="n">
@@ -4231,10 +4336,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C177" s="5" t="n">
+      <c r="C177" s="2" t="n">
         <v>36051.27</v>
       </c>
-      <c r="D177" s="6" t="n">
+      <c r="D177" s="3" t="n">
         <v>12.61345632</v>
       </c>
       <c r="E177" t="n">
@@ -4252,10 +4357,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C178" s="5" t="n">
+      <c r="C178" s="2" t="n">
         <v>239054.29</v>
       </c>
-      <c r="D178" s="6" t="n">
+      <c r="D178" s="3" t="n">
         <v>83.63924057</v>
       </c>
       <c r="E178" t="n">
@@ -4273,10 +4378,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C179" s="5" t="n">
+      <c r="C179" s="2" t="n">
         <v>1971.96</v>
       </c>
-      <c r="D179" s="6" t="n">
+      <c r="D179" s="3" t="n">
         <v>0.29536296</v>
       </c>
       <c r="E179" t="n">
@@ -4294,10 +4399,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C180" s="5" t="n">
+      <c r="C180" s="2" t="n">
         <v>970.1799999999999</v>
       </c>
-      <c r="D180" s="6" t="n">
+      <c r="D180" s="3" t="n">
         <v>0.14531493</v>
       </c>
       <c r="E180" t="n">
@@ -4315,10 +4420,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C181" s="5" t="n">
+      <c r="C181" s="2" t="n">
         <v>23400.38</v>
       </c>
-      <c r="D181" s="6" t="n">
+      <c r="D181" s="3" t="n">
         <v>3.50494199</v>
       </c>
       <c r="E181" t="n">
@@ -4336,10 +4441,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C182" s="5" t="n">
+      <c r="C182" s="2" t="n">
         <v>158698.51</v>
       </c>
-      <c r="D182" s="6" t="n">
+      <c r="D182" s="3" t="n">
         <v>23.77008715</v>
       </c>
       <c r="E182" t="n">
@@ -4357,10 +4462,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C183" s="5" t="n">
+      <c r="C183" s="2" t="n">
         <v>482598.55</v>
       </c>
-      <c r="D183" s="6" t="n">
+      <c r="D183" s="3" t="n">
         <v>72.28429297</v>
       </c>
       <c r="E183" t="n">
@@ -4378,10 +4483,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C184" s="5" t="n">
+      <c r="C184" s="2" t="n">
         <v>349.42</v>
       </c>
-      <c r="D184" s="6" t="n">
+      <c r="D184" s="3" t="n">
         <v>0.0757804</v>
       </c>
       <c r="E184" t="n">
@@ -4399,10 +4504,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C185" s="5" t="n">
+      <c r="C185" s="2" t="n">
         <v>5203.15</v>
       </c>
-      <c r="D185" s="6" t="n">
+      <c r="D185" s="3" t="n">
         <v>1.12843225</v>
       </c>
       <c r="E185" t="n">
@@ -4420,10 +4525,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C186" s="5" t="n">
+      <c r="C186" s="2" t="n">
         <v>43002.78</v>
       </c>
-      <c r="D186" s="6" t="n">
+      <c r="D186" s="3" t="n">
         <v>9.326220449999999</v>
       </c>
       <c r="E186" t="n">
@@ -4441,10 +4546,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C187" s="5" t="n">
+      <c r="C187" s="2" t="n">
         <v>412540.12</v>
       </c>
-      <c r="D187" s="6" t="n">
+      <c r="D187" s="3" t="n">
         <v>89.4695669</v>
       </c>
       <c r="E187" t="n">
@@ -4462,10 +4567,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C188" s="5" t="n">
+      <c r="C188" s="2" t="n">
         <v>1231.47</v>
       </c>
-      <c r="D188" s="6" t="n">
+      <c r="D188" s="3" t="n">
         <v>0.34199572</v>
       </c>
       <c r="E188" t="n">
@@ -4483,10 +4588,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C189" s="5" t="n">
+      <c r="C189" s="2" t="n">
         <v>484.18</v>
       </c>
-      <c r="D189" s="6" t="n">
+      <c r="D189" s="3" t="n">
         <v>0.13446328</v>
       </c>
       <c r="E189" t="n">
@@ -4504,10 +4609,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C190" s="5" t="n">
+      <c r="C190" s="2" t="n">
         <v>29461.66</v>
       </c>
-      <c r="D190" s="6" t="n">
+      <c r="D190" s="3" t="n">
         <v>8.18189784</v>
       </c>
       <c r="E190" t="n">
@@ -4525,10 +4630,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C191" s="5" t="n">
+      <c r="C191" s="2" t="n">
         <v>328906.14</v>
       </c>
-      <c r="D191" s="6" t="n">
+      <c r="D191" s="3" t="n">
         <v>91.34164317</v>
       </c>
       <c r="E191" t="n">
@@ -4546,10 +4651,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C192" s="5" t="n">
+      <c r="C192" s="2" t="n">
         <v>23.47</v>
       </c>
-      <c r="D192" s="6" t="n">
+      <c r="D192" s="3" t="n">
         <v>0.00471838</v>
       </c>
       <c r="E192" t="n">
@@ -4567,10 +4672,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C193" s="5" t="n">
+      <c r="C193" s="2" t="n">
         <v>13128.29</v>
       </c>
-      <c r="D193" s="6" t="n">
+      <c r="D193" s="3" t="n">
         <v>2.63929312</v>
       </c>
       <c r="E193" t="n">
@@ -4588,10 +4693,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C194" s="5" t="n">
+      <c r="C194" s="2" t="n">
         <v>42522.52</v>
       </c>
-      <c r="D194" s="6" t="n">
+      <c r="D194" s="3" t="n">
         <v>8.548668129999999</v>
       </c>
       <c r="E194" t="n">
@@ -4609,10 +4714,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C195" s="5" t="n">
+      <c r="C195" s="2" t="n">
         <v>441742.62</v>
       </c>
-      <c r="D195" s="6" t="n">
+      <c r="D195" s="3" t="n">
         <v>88.80732037999999</v>
       </c>
       <c r="E195" t="n">
@@ -4630,10 +4735,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C196" s="5" t="n">
+      <c r="C196" s="2" t="n">
         <v>14510.35</v>
       </c>
-      <c r="D196" s="6" t="n">
+      <c r="D196" s="3" t="n">
         <v>2.82318771</v>
       </c>
       <c r="E196" t="n">
@@ -4651,10 +4756,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C197" s="5" t="n">
+      <c r="C197" s="2" t="n">
         <v>29796.3</v>
       </c>
-      <c r="D197" s="6" t="n">
+      <c r="D197" s="3" t="n">
         <v>5.79727904</v>
       </c>
       <c r="E197" t="n">
@@ -4672,10 +4777,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C198" s="5" t="n">
+      <c r="C198" s="2" t="n">
         <v>489.48</v>
       </c>
-      <c r="D198" s="6" t="n">
+      <c r="D198" s="3" t="n">
         <v>0.09523505</v>
       </c>
       <c r="E198" t="n">
@@ -4693,10 +4798,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C199" s="5" t="n">
+      <c r="C199" s="2" t="n">
         <v>45623.94</v>
       </c>
-      <c r="D199" s="6" t="n">
+      <c r="D199" s="3" t="n">
         <v>8.876763589999999</v>
       </c>
       <c r="E199" t="n">
@@ -4714,10 +4819,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C200" s="5" t="n">
+      <c r="C200" s="2" t="n">
         <v>423550.36</v>
       </c>
-      <c r="D200" s="6" t="n">
+      <c r="D200" s="3" t="n">
         <v>82.40753461</v>
       </c>
       <c r="E200" t="n">
@@ -4735,10 +4840,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C201" s="5" t="n">
+      <c r="C201" s="2" t="n">
         <v>2894.83</v>
       </c>
-      <c r="D201" s="6" t="n">
+      <c r="D201" s="3" t="n">
         <v>0.57425271</v>
       </c>
       <c r="E201" t="n">
@@ -4756,10 +4861,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C202" s="5" t="n">
+      <c r="C202" s="2" t="n">
         <v>19389.84</v>
       </c>
-      <c r="D202" s="6" t="n">
+      <c r="D202" s="3" t="n">
         <v>3.84639792</v>
       </c>
       <c r="E202" t="n">
@@ -4777,10 +4882,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C203" s="5" t="n">
+      <c r="C203" s="2" t="n">
         <v>7103.09</v>
       </c>
-      <c r="D203" s="6" t="n">
+      <c r="D203" s="3" t="n">
         <v>1.40905292</v>
       </c>
       <c r="E203" t="n">
@@ -4798,10 +4903,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C204" s="5" t="n">
+      <c r="C204" s="2" t="n">
         <v>71555.96000000001</v>
       </c>
-      <c r="D204" s="6" t="n">
+      <c r="D204" s="3" t="n">
         <v>14.19468627</v>
       </c>
       <c r="E204" t="n">
@@ -4819,10 +4924,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C205" s="5" t="n">
+      <c r="C205" s="2" t="n">
         <v>403160.13</v>
       </c>
-      <c r="D205" s="6" t="n">
+      <c r="D205" s="3" t="n">
         <v>79.97561018</v>
       </c>
       <c r="E205" t="n">
@@ -4840,10 +4945,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C206" s="5" t="n">
+      <c r="C206" s="2" t="n">
         <v>13873.76</v>
       </c>
-      <c r="D206" s="6" t="n">
+      <c r="D206" s="3" t="n">
         <v>4.61749343</v>
       </c>
       <c r="E206" t="n">
@@ -4861,10 +4966,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C207" s="5" t="n">
+      <c r="C207" s="2" t="n">
         <v>5637.21</v>
       </c>
-      <c r="D207" s="6" t="n">
+      <c r="D207" s="3" t="n">
         <v>1.87618786</v>
       </c>
       <c r="E207" t="n">
@@ -4882,10 +4987,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C208" s="5" t="n">
+      <c r="C208" s="2" t="n">
         <v>1363.63</v>
       </c>
-      <c r="D208" s="6" t="n">
+      <c r="D208" s="3" t="n">
         <v>0.45384615</v>
       </c>
       <c r="E208" t="n">
@@ -4903,10 +5008,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C209" s="5" t="n">
+      <c r="C209" s="2" t="n">
         <v>35429.67</v>
       </c>
-      <c r="D209" s="6" t="n">
+      <c r="D209" s="3" t="n">
         <v>11.79177587</v>
       </c>
       <c r="E209" t="n">
@@ -4924,10 +5029,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C210" s="5" t="n">
+      <c r="C210" s="2" t="n">
         <v>244156.58</v>
       </c>
-      <c r="D210" s="6" t="n">
+      <c r="D210" s="3" t="n">
         <v>81.26069669</v>
       </c>
       <c r="E210" t="n">
@@ -4945,10 +5050,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C211" s="5" t="n">
+      <c r="C211" s="2" t="n">
         <v>3194.31</v>
       </c>
-      <c r="D211" s="6" t="n">
+      <c r="D211" s="3" t="n">
         <v>0.86754762</v>
       </c>
       <c r="E211" t="n">
@@ -4966,10 +5071,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C212" s="5" t="n">
+      <c r="C212" s="2" t="n">
         <v>53332.81</v>
       </c>
-      <c r="D212" s="6" t="n">
+      <c r="D212" s="3" t="n">
         <v>14.48474085</v>
       </c>
       <c r="E212" t="n">
@@ -4987,10 +5092,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C213" s="5" t="n">
+      <c r="C213" s="2" t="n">
         <v>5480.02</v>
       </c>
-      <c r="D213" s="6" t="n">
+      <c r="D213" s="3" t="n">
         <v>1.48832716</v>
       </c>
       <c r="E213" t="n">
@@ -5008,10 +5113,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C214" s="5" t="n">
+      <c r="C214" s="2" t="n">
         <v>54619.67</v>
       </c>
-      <c r="D214" s="6" t="n">
+      <c r="D214" s="3" t="n">
         <v>14.83424116</v>
       </c>
       <c r="E214" t="n">
@@ -5029,10 +5134,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C215" s="5" t="n">
+      <c r="C215" s="2" t="n">
         <v>251573.15</v>
       </c>
-      <c r="D215" s="6" t="n">
+      <c r="D215" s="3" t="n">
         <v>68.32514322</v>
       </c>
       <c r="E215" t="n">
@@ -5050,10 +5155,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C216" s="5" t="n">
+      <c r="C216" s="2" t="n">
         <v>892</v>
       </c>
-      <c r="D216" s="6" t="n">
+      <c r="D216" s="3" t="n">
         <v>0.30548187</v>
       </c>
       <c r="E216" t="n">
@@ -5071,10 +5176,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C217" s="5" t="n">
+      <c r="C217" s="2" t="n">
         <v>7918.09</v>
       </c>
-      <c r="D217" s="6" t="n">
+      <c r="D217" s="3" t="n">
         <v>2.71169611</v>
       </c>
       <c r="E217" t="n">
@@ -5092,10 +5197,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C218" s="5" t="n">
+      <c r="C218" s="2" t="n">
         <v>37.66</v>
       </c>
-      <c r="D218" s="6" t="n">
+      <c r="D218" s="3" t="n">
         <v>0.01289736</v>
       </c>
       <c r="E218" t="n">
@@ -5113,10 +5218,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C219" s="5" t="n">
+      <c r="C219" s="2" t="n">
         <v>14209.15</v>
       </c>
-      <c r="D219" s="6" t="n">
+      <c r="D219" s="3" t="n">
         <v>4.86618576</v>
       </c>
       <c r="E219" t="n">
@@ -5134,10 +5239,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C220" s="5" t="n">
+      <c r="C220" s="2" t="n">
         <v>268940.79</v>
       </c>
-      <c r="D220" s="6" t="n">
+      <c r="D220" s="3" t="n">
         <v>92.1037389</v>
       </c>
       <c r="E220" t="n">
@@ -5155,10 +5260,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C221" s="5" t="n">
+      <c r="C221" s="2" t="n">
         <v>287</v>
       </c>
-      <c r="D221" s="6" t="n">
+      <c r="D221" s="3" t="n">
         <v>0.07919683</v>
       </c>
       <c r="E221" t="n">
@@ -5176,10 +5281,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C222" s="5" t="n">
+      <c r="C222" s="2" t="n">
         <v>17982.75</v>
       </c>
-      <c r="D222" s="6" t="n">
+      <c r="D222" s="3" t="n">
         <v>4.96228879</v>
       </c>
       <c r="E222" t="n">
@@ -5197,10 +5302,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C223" s="5" t="n">
+      <c r="C223" s="2" t="n">
         <v>2603.68</v>
       </c>
-      <c r="D223" s="6" t="n">
+      <c r="D223" s="3" t="n">
         <v>0.7184781</v>
       </c>
       <c r="E223" t="n">
@@ -5218,10 +5323,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C224" s="5" t="n">
+      <c r="C224" s="2" t="n">
         <v>34911.64</v>
       </c>
-      <c r="D224" s="6" t="n">
+      <c r="D224" s="3" t="n">
         <v>9.6337679</v>
       </c>
       <c r="E224" t="n">
@@ -5239,10 +5344,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C225" s="5" t="n">
+      <c r="C225" s="2" t="n">
         <v>306603.15</v>
       </c>
-      <c r="D225" s="6" t="n">
+      <c r="D225" s="3" t="n">
         <v>84.60626838</v>
       </c>
       <c r="E225" t="n">
@@ -5260,10 +5365,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C226" s="5" t="n">
+      <c r="C226" s="2" t="n">
         <v>1099.13</v>
       </c>
-      <c r="D226" s="6" t="n">
+      <c r="D226" s="3" t="n">
         <v>0.35003695</v>
       </c>
       <c r="E226" t="n">
@@ -5281,10 +5386,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C227" s="5" t="n">
+      <c r="C227" s="2" t="n">
         <v>1908.13</v>
       </c>
-      <c r="D227" s="6" t="n">
+      <c r="D227" s="3" t="n">
         <v>0.60767699</v>
       </c>
       <c r="E227" t="n">
@@ -5302,10 +5407,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C228" s="5" t="n">
+      <c r="C228" s="2" t="n">
         <v>1788.1</v>
       </c>
-      <c r="D228" s="6" t="n">
+      <c r="D228" s="3" t="n">
         <v>0.56945136</v>
       </c>
       <c r="E228" t="n">
@@ -5323,10 +5428,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C229" s="5" t="n">
+      <c r="C229" s="2" t="n">
         <v>54065.52</v>
       </c>
-      <c r="D229" s="6" t="n">
+      <c r="D229" s="3" t="n">
         <v>17.21809968</v>
       </c>
       <c r="E229" t="n">
@@ -5344,10 +5449,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C230" s="5" t="n">
+      <c r="C230" s="2" t="n">
         <v>255143.11</v>
       </c>
-      <c r="D230" s="6" t="n">
+      <c r="D230" s="3" t="n">
         <v>81.25473501</v>
       </c>
       <c r="E230" t="n">
@@ -5365,10 +5470,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C231" s="5" t="n">
+      <c r="C231" s="2" t="n">
         <v>2988.23</v>
       </c>
-      <c r="D231" s="6" t="n">
+      <c r="D231" s="3" t="n">
         <v>1.09502707</v>
       </c>
       <c r="E231" t="n">
@@ -5386,10 +5491,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C232" s="5" t="n">
+      <c r="C232" s="2" t="n">
         <v>89030.31</v>
       </c>
-      <c r="D232" s="6" t="n">
+      <c r="D232" s="3" t="n">
         <v>32.62486479</v>
       </c>
       <c r="E232" t="n">
@@ -5407,10 +5512,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C233" s="5" t="n">
+      <c r="C233" s="2" t="n">
         <v>180872.43</v>
       </c>
-      <c r="D233" s="6" t="n">
+      <c r="D233" s="3" t="n">
         <v>66.28010813</v>
       </c>
       <c r="E233" t="n">
@@ -5428,10 +5533,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C234" s="5" t="n">
+      <c r="C234" s="2" t="n">
         <v>232.92</v>
       </c>
-      <c r="D234" s="6" t="n">
+      <c r="D234" s="3" t="n">
         <v>0.10614272</v>
       </c>
       <c r="E234" t="n">
@@ -5449,10 +5554,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C235" s="5" t="n">
+      <c r="C235" s="2" t="n">
         <v>27443.48</v>
       </c>
-      <c r="D235" s="6" t="n">
+      <c r="D235" s="3" t="n">
         <v>12.50612011</v>
       </c>
       <c r="E235" t="n">
@@ -5470,10 +5575,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C236" s="5" t="n">
+      <c r="C236" s="2" t="n">
         <v>66453.41</v>
       </c>
-      <c r="D236" s="6" t="n">
+      <c r="D236" s="3" t="n">
         <v>30.28312471</v>
       </c>
       <c r="E236" t="n">
@@ -5491,10 +5596,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C237" s="5" t="n">
+      <c r="C237" s="2" t="n">
         <v>125310.59</v>
       </c>
-      <c r="D237" s="6" t="n">
+      <c r="D237" s="3" t="n">
         <v>57.10461246</v>
       </c>
       <c r="E237" t="n">
@@ -5512,10 +5617,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C238" s="5" t="n">
+      <c r="C238" s="2" t="n">
         <v>12206.63</v>
       </c>
-      <c r="D238" s="6" t="n">
+      <c r="D238" s="3" t="n">
         <v>2.80910278</v>
       </c>
       <c r="E238" t="n">
@@ -5533,10 +5638,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C239" s="5" t="n">
+      <c r="C239" s="2" t="n">
         <v>14439.81</v>
       </c>
-      <c r="D239" s="6" t="n">
+      <c r="D239" s="3" t="n">
         <v>3.32302285</v>
       </c>
       <c r="E239" t="n">
@@ -5554,10 +5659,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C240" s="5" t="n">
+      <c r="C240" s="2" t="n">
         <v>73404.17</v>
       </c>
-      <c r="D240" s="6" t="n">
+      <c r="D240" s="3" t="n">
         <v>16.89244764</v>
       </c>
       <c r="E240" t="n">
@@ -5575,10 +5680,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C241" s="5" t="n">
+      <c r="C241" s="2" t="n">
         <v>334487.78</v>
       </c>
-      <c r="D241" s="6" t="n">
+      <c r="D241" s="3" t="n">
         <v>76.97542673</v>
       </c>
       <c r="E241" t="n">
@@ -5596,10 +5701,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C242" s="5" t="n">
+      <c r="C242" s="2" t="n">
         <v>4414.12</v>
       </c>
-      <c r="D242" s="6" t="n">
+      <c r="D242" s="3" t="n">
         <v>2.02734127</v>
       </c>
       <c r="E242" t="n">
@@ -5617,10 +5722,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C243" s="5" t="n">
+      <c r="C243" s="2" t="n">
         <v>206.75</v>
       </c>
-      <c r="D243" s="6" t="n">
+      <c r="D243" s="3" t="n">
         <v>0.09495727</v>
       </c>
       <c r="E243" t="n">
@@ -5638,10 +5743,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C244" s="5" t="n">
+      <c r="C244" s="2" t="n">
         <v>6938.86</v>
       </c>
-      <c r="D244" s="6" t="n">
+      <c r="D244" s="3" t="n">
         <v>3.18691771</v>
       </c>
       <c r="E244" t="n">
@@ -5659,10 +5764,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C245" s="5" t="n">
+      <c r="C245" s="2" t="n">
         <v>206169.77</v>
       </c>
-      <c r="D245" s="6" t="n">
+      <c r="D245" s="3" t="n">
         <v>94.69078374999999</v>
       </c>
       <c r="E245" t="n">
@@ -5680,10 +5785,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C246" s="5" t="n">
+      <c r="C246" s="2" t="n">
         <v>45195.76</v>
       </c>
-      <c r="D246" s="6" t="n">
+      <c r="D246" s="3" t="n">
         <v>10.41762819</v>
       </c>
       <c r="E246" t="n">
@@ -5701,10 +5806,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C247" s="5" t="n">
+      <c r="C247" s="2" t="n">
         <v>9882.6</v>
       </c>
-      <c r="D247" s="6" t="n">
+      <c r="D247" s="3" t="n">
         <v>2.2779405</v>
       </c>
       <c r="E247" t="n">
@@ -5722,10 +5827,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C248" s="5" t="n">
+      <c r="C248" s="2" t="n">
         <v>305.19</v>
       </c>
-      <c r="D248" s="6" t="n">
+      <c r="D248" s="3" t="n">
         <v>0.07034633</v>
       </c>
       <c r="E248" t="n">
@@ -5743,10 +5848,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C249" s="5" t="n">
+      <c r="C249" s="2" t="n">
         <v>9384.76</v>
       </c>
-      <c r="D249" s="6" t="n">
+      <c r="D249" s="3" t="n">
         <v>2.16318832</v>
       </c>
       <c r="E249" t="n">
@@ -5764,10 +5869,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C250" s="5" t="n">
+      <c r="C250" s="2" t="n">
         <v>369070.94</v>
       </c>
-      <c r="D250" s="6" t="n">
+      <c r="D250" s="3" t="n">
         <v>85.07089664999999</v>
       </c>
       <c r="E250" t="n">
@@ -5785,10 +5890,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C251" s="5" t="n">
+      <c r="C251" s="2" t="n">
         <v>387.59</v>
       </c>
-      <c r="D251" s="6" t="n">
+      <c r="D251" s="3" t="n">
         <v>0.10977502</v>
       </c>
       <c r="E251" t="n">
@@ -5806,10 +5911,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C252" s="5" t="n">
+      <c r="C252" s="2" t="n">
         <v>3000</v>
       </c>
-      <c r="D252" s="6" t="n">
+      <c r="D252" s="3" t="n">
         <v>0.84967379</v>
       </c>
       <c r="E252" t="n">
@@ -5827,10 +5932,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C253" s="5" t="n">
+      <c r="C253" s="2" t="n">
         <v>114879.27</v>
       </c>
-      <c r="D253" s="6" t="n">
+      <c r="D253" s="3" t="n">
         <v>32.53663482</v>
       </c>
       <c r="E253" t="n">
@@ -5848,10 +5953,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C254" s="5" t="n">
+      <c r="C254" s="2" t="n">
         <v>234809.82</v>
       </c>
-      <c r="D254" s="6" t="n">
+      <c r="D254" s="3" t="n">
         <v>66.50391637</v>
       </c>
       <c r="E254" t="n">
@@ -5869,10 +5974,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C255" s="5" t="n">
+      <c r="C255" s="2" t="n">
         <v>8859.66</v>
       </c>
-      <c r="D255" s="6" t="n">
+      <c r="D255" s="3" t="n">
         <v>5.34081687</v>
       </c>
       <c r="E255" t="n">
@@ -5890,10 +5995,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C256" s="5" t="n">
+      <c r="C256" s="2" t="n">
         <v>1006.9</v>
       </c>
-      <c r="D256" s="6" t="n">
+      <c r="D256" s="3" t="n">
         <v>0.6069836199999999</v>
       </c>
       <c r="E256" t="n">
@@ -5911,10 +6016,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C257" s="5" t="n">
+      <c r="C257" s="2" t="n">
         <v>1000</v>
       </c>
-      <c r="D257" s="6" t="n">
+      <c r="D257" s="3" t="n">
         <v>0.60282413</v>
       </c>
       <c r="E257" t="n">
@@ -5932,10 +6037,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C258" s="5" t="n">
+      <c r="C258" s="2" t="n">
         <v>51121.7</v>
       </c>
-      <c r="D258" s="6" t="n">
+      <c r="D258" s="3" t="n">
         <v>30.81739456</v>
       </c>
       <c r="E258" t="n">
@@ -5953,10 +6058,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C259" s="5" t="n">
+      <c r="C259" s="2" t="n">
         <v>103897.6</v>
       </c>
-      <c r="D259" s="6" t="n">
+      <c r="D259" s="3" t="n">
         <v>62.63198081</v>
       </c>
       <c r="E259" t="n">
@@ -5974,10 +6079,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C260" s="5" t="n">
+      <c r="C260" s="2" t="n">
         <v>7692.3</v>
       </c>
-      <c r="D260" s="6" t="n">
+      <c r="D260" s="3" t="n">
         <v>6.29078176</v>
       </c>
       <c r="E260" t="n">
@@ -5995,10 +6100,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C261" s="5" t="n">
+      <c r="C261" s="2" t="n">
         <v>1882.73</v>
       </c>
-      <c r="D261" s="6" t="n">
+      <c r="D261" s="3" t="n">
         <v>1.5397012</v>
       </c>
       <c r="E261" t="n">
@@ -6016,10 +6121,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C262" s="5" t="n">
+      <c r="C262" s="2" t="n">
         <v>14869.63</v>
       </c>
-      <c r="D262" s="6" t="n">
+      <c r="D262" s="3" t="n">
         <v>12.1604198</v>
       </c>
       <c r="E262" t="n">
@@ -6037,10 +6142,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C263" s="5" t="n">
+      <c r="C263" s="2" t="n">
         <v>97834.25999999999</v>
       </c>
-      <c r="D263" s="6" t="n">
+      <c r="D263" s="3" t="n">
         <v>80.00909722999999</v>
       </c>
       <c r="E263" t="n">
@@ -6058,10 +6163,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C264" s="5" t="n">
+      <c r="C264" s="2" t="n">
         <v>3303.59</v>
       </c>
-      <c r="D264" s="6" t="n">
+      <c r="D264" s="3" t="n">
         <v>1.27093949</v>
       </c>
       <c r="E264" t="n">
@@ -6079,10 +6184,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C265" s="5" t="n">
+      <c r="C265" s="2" t="n">
         <v>18435.53</v>
       </c>
-      <c r="D265" s="6" t="n">
+      <c r="D265" s="3" t="n">
         <v>7.09241858</v>
       </c>
       <c r="E265" t="n">
@@ -6100,10 +6205,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C266" s="5" t="n">
+      <c r="C266" s="2" t="n">
         <v>2222.22</v>
       </c>
-      <c r="D266" s="6" t="n">
+      <c r="D266" s="3" t="n">
         <v>0.8549206</v>
       </c>
       <c r="E266" t="n">
@@ -6121,10 +6226,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C267" s="5" t="n">
+      <c r="C267" s="2" t="n">
         <v>50871.54</v>
       </c>
-      <c r="D267" s="6" t="n">
+      <c r="D267" s="3" t="n">
         <v>19.571027</v>
       </c>
       <c r="E267" t="n">
@@ -6142,10 +6247,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C268" s="5" t="n">
+      <c r="C268" s="2" t="n">
         <v>185100.03</v>
       </c>
-      <c r="D268" s="6" t="n">
+      <c r="D268" s="3" t="n">
         <v>71.21069433</v>
       </c>
       <c r="E268" t="n">
@@ -6163,10 +6268,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C269" s="5" t="n">
+      <c r="C269" s="2" t="n">
         <v>26854.86</v>
       </c>
-      <c r="D269" s="6" t="n">
+      <c r="D269" s="3" t="n">
         <v>6.60466391</v>
       </c>
       <c r="E269" t="n">
@@ -6184,10 +6289,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="C270" s="5" t="n">
+      <c r="C270" s="2" t="n">
         <v>554.28</v>
       </c>
-      <c r="D270" s="6" t="n">
+      <c r="D270" s="3" t="n">
         <v>0.1363192</v>
       </c>
       <c r="E270" t="n">
@@ -6205,10 +6310,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C271" s="5" t="n">
+      <c r="C271" s="2" t="n">
         <v>487.8</v>
       </c>
-      <c r="D271" s="6" t="n">
+      <c r="D271" s="3" t="n">
         <v>0.11996916</v>
       </c>
       <c r="E271" t="n">
@@ -6226,10 +6331,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C272" s="5" t="n">
+      <c r="C272" s="2" t="n">
         <v>12206.22</v>
       </c>
-      <c r="D272" s="6" t="n">
+      <c r="D272" s="3" t="n">
         <v>3.00198849</v>
       </c>
       <c r="E272" t="n">
@@ -6247,10 +6352,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C273" s="5" t="n">
+      <c r="C273" s="2" t="n">
         <v>28370.02</v>
       </c>
-      <c r="D273" s="6" t="n">
+      <c r="D273" s="3" t="n">
         <v>6.97730121</v>
       </c>
       <c r="E273" t="n">
@@ -6268,10 +6373,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C274" s="5" t="n">
+      <c r="C274" s="2" t="n">
         <v>338131.31</v>
       </c>
-      <c r="D274" s="6" t="n">
+      <c r="D274" s="3" t="n">
         <v>83.15975802</v>
       </c>
       <c r="E274" t="n">
@@ -6289,10 +6394,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C275" s="5" t="n">
+      <c r="C275" s="2" t="n">
         <v>19985.78</v>
       </c>
-      <c r="D275" s="6" t="n">
+      <c r="D275" s="3" t="n">
         <v>7.97052191</v>
       </c>
       <c r="E275" t="n">
@@ -6310,10 +6415,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="C276" s="5" t="n">
+      <c r="C276" s="2" t="n">
         <v>2222.22</v>
       </c>
-      <c r="D276" s="6" t="n">
+      <c r="D276" s="3" t="n">
         <v>0.88624278</v>
       </c>
       <c r="E276" t="n">
@@ -6331,10 +6436,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C277" s="5" t="n">
+      <c r="C277" s="2" t="n">
         <v>4445.7</v>
       </c>
-      <c r="D277" s="6" t="n">
+      <c r="D277" s="3" t="n">
         <v>1.77298806</v>
       </c>
       <c r="E277" t="n">
@@ -6352,10 +6457,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C278" s="5" t="n">
+      <c r="C278" s="2" t="n">
         <v>50514.02</v>
       </c>
-      <c r="D278" s="6" t="n">
+      <c r="D278" s="3" t="n">
         <v>20.14547858</v>
       </c>
       <c r="E278" t="n">
@@ -6373,10 +6478,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C279" s="5" t="n">
+      <c r="C279" s="2" t="n">
         <v>173578.47</v>
       </c>
-      <c r="D279" s="6" t="n">
+      <c r="D279" s="3" t="n">
         <v>69.22476868</v>
       </c>
       <c r="E279" t="n">
@@ -6394,10 +6499,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C280" s="5" t="n">
+      <c r="C280" s="2" t="n">
         <v>40560.99</v>
       </c>
-      <c r="D280" s="6" t="n">
+      <c r="D280" s="3" t="n">
         <v>8.644859670000001</v>
       </c>
       <c r="E280" t="n">
@@ -6415,10 +6520,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C281" s="5" t="n">
+      <c r="C281" s="2" t="n">
         <v>6836.42</v>
       </c>
-      <c r="D281" s="6" t="n">
+      <c r="D281" s="3" t="n">
         <v>1.45706235</v>
       </c>
       <c r="E281" t="n">
@@ -6436,10 +6541,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C282" s="5" t="n">
+      <c r="C282" s="2" t="n">
         <v>34873.15</v>
       </c>
-      <c r="D282" s="6" t="n">
+      <c r="D282" s="3" t="n">
         <v>7.43259689</v>
       </c>
       <c r="E282" t="n">
@@ -6457,10 +6562,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C283" s="5" t="n">
+      <c r="C283" s="2" t="n">
         <v>386921.44</v>
       </c>
-      <c r="D283" s="6" t="n">
+      <c r="D283" s="3" t="n">
         <v>82.46548108</v>
       </c>
       <c r="E283" t="n">
@@ -6478,10 +6583,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="C284" s="5" t="n">
+      <c r="C284" s="2" t="n">
         <v>2062.08</v>
       </c>
-      <c r="D284" s="6" t="n">
+      <c r="D284" s="3" t="n">
         <v>0.67843969</v>
       </c>
       <c r="E284" t="n">
@@ -6499,10 +6604,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C285" s="5" t="n">
+      <c r="C285" s="2" t="n">
         <v>67302.87</v>
       </c>
-      <c r="D285" s="6" t="n">
+      <c r="D285" s="3" t="n">
         <v>22.14314601</v>
       </c>
       <c r="E285" t="n">
@@ -6520,10 +6625,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C286" s="5" t="n">
+      <c r="C286" s="2" t="n">
         <v>37.83</v>
       </c>
-      <c r="D286" s="6" t="n">
+      <c r="D286" s="3" t="n">
         <v>0.01244635</v>
       </c>
       <c r="E286" t="n">
@@ -6541,10 +6646,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C287" s="5" t="n">
+      <c r="C287" s="2" t="n">
         <v>82048.36</v>
       </c>
-      <c r="D287" s="6" t="n">
+      <c r="D287" s="3" t="n">
         <v>26.99452216</v>
       </c>
       <c r="E287" t="n">
@@ -6562,10 +6667,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C288" s="5" t="n">
+      <c r="C288" s="2" t="n">
         <v>152493.34</v>
       </c>
-      <c r="D288" s="6" t="n">
+      <c r="D288" s="3" t="n">
         <v>50.17144579</v>
       </c>
       <c r="E288" t="n">
@@ -6583,10 +6688,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C289" s="5" t="n">
+      <c r="C289" s="2" t="n">
         <v>16850.05</v>
       </c>
-      <c r="D289" s="6" t="n">
+      <c r="D289" s="3" t="n">
         <v>8.3557591</v>
       </c>
       <c r="E289" t="n">
@@ -6604,10 +6709,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C290" s="5" t="n">
+      <c r="C290" s="2" t="n">
         <v>1221.31</v>
       </c>
-      <c r="D290" s="6" t="n">
+      <c r="D290" s="3" t="n">
         <v>0.60563453</v>
       </c>
       <c r="E290" t="n">
@@ -6625,10 +6730,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C291" s="5" t="n">
+      <c r="C291" s="2" t="n">
         <v>542.72</v>
       </c>
-      <c r="D291" s="6" t="n">
+      <c r="D291" s="3" t="n">
         <v>0.26912903</v>
       </c>
       <c r="E291" t="n">
@@ -6646,10 +6751,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C292" s="5" t="n">
+      <c r="C292" s="2" t="n">
         <v>1989.87</v>
       </c>
-      <c r="D292" s="6" t="n">
+      <c r="D292" s="3" t="n">
         <v>0.98675519</v>
       </c>
       <c r="E292" t="n">
@@ -6667,10 +6772,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C293" s="5" t="n">
+      <c r="C293" s="2" t="n">
         <v>181053.97</v>
       </c>
-      <c r="D293" s="6" t="n">
+      <c r="D293" s="3" t="n">
         <v>89.78272215</v>
       </c>
       <c r="E293" t="n">
@@ -6688,10 +6793,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C294" s="5" t="n">
+      <c r="C294" s="2" t="n">
         <v>2791.46</v>
       </c>
-      <c r="D294" s="6" t="n">
+      <c r="D294" s="3" t="n">
         <v>1.6215349</v>
       </c>
       <c r="E294" t="n">
@@ -6709,10 +6814,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C295" s="5" t="n">
+      <c r="C295" s="2" t="n">
         <v>6752.82</v>
       </c>
-      <c r="D295" s="6" t="n">
+      <c r="D295" s="3" t="n">
         <v>3.92265455</v>
       </c>
       <c r="E295" t="n">
@@ -6730,10 +6835,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C296" s="5" t="n">
+      <c r="C296" s="2" t="n">
         <v>42038.15</v>
       </c>
-      <c r="D296" s="6" t="n">
+      <c r="D296" s="3" t="n">
         <v>24.41959662</v>
       </c>
       <c r="E296" t="n">
@@ -6751,10 +6856,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C297" s="5" t="n">
+      <c r="C297" s="2" t="n">
         <v>120566.81</v>
       </c>
-      <c r="D297" s="6" t="n">
+      <c r="D297" s="3" t="n">
         <v>70.03621393</v>
       </c>
       <c r="E297" t="n">
@@ -6772,10 +6877,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C298" s="5" t="n">
+      <c r="C298" s="2" t="n">
         <v>360</v>
       </c>
-      <c r="D298" s="6" t="n">
+      <c r="D298" s="3" t="n">
         <v>0.13798773</v>
       </c>
       <c r="E298" t="n">
@@ -6793,10 +6898,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C299" s="5" t="n">
+      <c r="C299" s="2" t="n">
         <v>9364.209999999999</v>
       </c>
-      <c r="D299" s="6" t="n">
+      <c r="D299" s="3" t="n">
         <v>3.58929456</v>
       </c>
       <c r="E299" t="n">
@@ -6814,10 +6919,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C300" s="5" t="n">
+      <c r="C300" s="2" t="n">
         <v>4780.88</v>
       </c>
-      <c r="D300" s="6" t="n">
+      <c r="D300" s="3" t="n">
         <v>1.83250766</v>
       </c>
       <c r="E300" t="n">
@@ -6835,10 +6940,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C301" s="5" t="n">
+      <c r="C301" s="2" t="n">
         <v>246387.68</v>
       </c>
-      <c r="D301" s="6" t="n">
+      <c r="D301" s="3" t="n">
         <v>94.44021005</v>
       </c>
       <c r="E301" t="n">
@@ -6856,10 +6961,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C302" s="5" t="n">
+      <c r="C302" s="2" t="n">
         <v>6057.75</v>
       </c>
-      <c r="D302" s="6" t="n">
+      <c r="D302" s="3" t="n">
         <v>2.33727832</v>
       </c>
       <c r="E302" t="n">
@@ -6877,10 +6982,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C303" s="5" t="n">
+      <c r="C303" s="2" t="n">
         <v>48766.63</v>
       </c>
-      <c r="D303" s="6" t="n">
+      <c r="D303" s="3" t="n">
         <v>18.81576278</v>
       </c>
       <c r="E303" t="n">
@@ -6898,10 +7003,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C304" s="5" t="n">
+      <c r="C304" s="2" t="n">
         <v>204355.28</v>
       </c>
-      <c r="D304" s="6" t="n">
+      <c r="D304" s="3" t="n">
         <v>78.8469589</v>
       </c>
       <c r="E304" t="n">
@@ -6919,10 +7024,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C305" s="5" t="n">
+      <c r="C305" s="2" t="n">
         <v>16523.23</v>
       </c>
-      <c r="D305" s="6" t="n">
+      <c r="D305" s="3" t="n">
         <v>6.18627246</v>
       </c>
       <c r="E305" t="n">
@@ -6940,10 +7045,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="C306" s="5" t="n">
+      <c r="C306" s="2" t="n">
         <v>1000</v>
       </c>
-      <c r="D306" s="6" t="n">
+      <c r="D306" s="3" t="n">
         <v>0.3743985</v>
       </c>
       <c r="E306" t="n">
@@ -6961,10 +7066,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C307" s="5" t="n">
+      <c r="C307" s="2" t="n">
         <v>19175.48</v>
       </c>
-      <c r="D307" s="6" t="n">
+      <c r="D307" s="3" t="n">
         <v>7.17927087</v>
       </c>
       <c r="E307" t="n">
@@ -6982,10 +7087,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C308" s="5" t="n">
+      <c r="C308" s="2" t="n">
         <v>22548.18</v>
       </c>
-      <c r="D308" s="6" t="n">
+      <c r="D308" s="3" t="n">
         <v>8.44200468</v>
       </c>
       <c r="E308" t="n">
@@ -7003,10 +7108,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C309" s="5" t="n">
+      <c r="C309" s="2" t="n">
         <v>3105.38</v>
       </c>
-      <c r="D309" s="6" t="n">
+      <c r="D309" s="3" t="n">
         <v>1.1626496</v>
       </c>
       <c r="E309" t="n">
@@ -7024,10 +7129,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C310" s="5" t="n">
+      <c r="C310" s="2" t="n">
         <v>9171.51</v>
       </c>
-      <c r="D310" s="6" t="n">
+      <c r="D310" s="3" t="n">
         <v>3.43379955</v>
       </c>
       <c r="E310" t="n">
@@ -7045,10 +7150,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C311" s="5" t="n">
+      <c r="C311" s="2" t="n">
         <v>195571.31</v>
       </c>
-      <c r="D311" s="6" t="n">
+      <c r="D311" s="3" t="n">
         <v>73.22160434</v>
       </c>
       <c r="E311" t="n">
@@ -7066,10 +7171,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C312" s="5" t="n">
+      <c r="C312" s="2" t="n">
         <v>27350.51</v>
       </c>
-      <c r="D312" s="6" t="n">
+      <c r="D312" s="3" t="n">
         <v>9.8197723</v>
       </c>
       <c r="E312" t="n">
@@ -7087,10 +7192,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C313" s="5" t="n">
+      <c r="C313" s="2" t="n">
         <v>21653.68</v>
       </c>
-      <c r="D313" s="6" t="n">
+      <c r="D313" s="3" t="n">
         <v>7.7744147</v>
       </c>
       <c r="E313" t="n">
@@ -7108,10 +7213,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C314" s="5" t="n">
+      <c r="C314" s="2" t="n">
         <v>30092.08</v>
       </c>
-      <c r="D314" s="6" t="n">
+      <c r="D314" s="3" t="n">
         <v>10.80409008</v>
       </c>
       <c r="E314" t="n">
@@ -7129,10 +7234,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C315" s="5" t="n">
+      <c r="C315" s="2" t="n">
         <v>199428.62</v>
       </c>
-      <c r="D315" s="6" t="n">
+      <c r="D315" s="3" t="n">
         <v>71.60172292</v>
       </c>
       <c r="E315" t="n">
@@ -7150,10 +7255,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C316" s="5" t="n">
+      <c r="C316" s="2" t="n">
         <v>18403.89</v>
       </c>
-      <c r="D316" s="6" t="n">
+      <c r="D316" s="3" t="n">
         <v>5.9503914</v>
       </c>
       <c r="E316" t="n">
@@ -7171,10 +7276,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C317" s="5" t="n">
+      <c r="C317" s="2" t="n">
         <v>88.88</v>
       </c>
-      <c r="D317" s="6" t="n">
+      <c r="D317" s="3" t="n">
         <v>0.0287369</v>
       </c>
       <c r="E317" t="n">
@@ -7192,10 +7297,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C318" s="5" t="n">
+      <c r="C318" s="2" t="n">
         <v>72445.86</v>
       </c>
-      <c r="D318" s="6" t="n">
+      <c r="D318" s="3" t="n">
         <v>23.4233753</v>
       </c>
       <c r="E318" t="n">
@@ -7213,10 +7318,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C319" s="5" t="n">
+      <c r="C319" s="2" t="n">
         <v>1021.81</v>
       </c>
-      <c r="D319" s="6" t="n">
+      <c r="D319" s="3" t="n">
         <v>0.33037415</v>
       </c>
       <c r="E319" t="n">
@@ -7234,10 +7339,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C320" s="5" t="n">
+      <c r="C320" s="2" t="n">
         <v>23146.75</v>
       </c>
-      <c r="D320" s="6" t="n">
+      <c r="D320" s="3" t="n">
         <v>7.48386467</v>
       </c>
       <c r="E320" t="n">
@@ -7255,10 +7360,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C321" s="5" t="n">
+      <c r="C321" s="2" t="n">
         <v>194181.54</v>
       </c>
-      <c r="D321" s="6" t="n">
+      <c r="D321" s="3" t="n">
         <v>62.78325757</v>
       </c>
       <c r="E321" t="n">
@@ -7276,10 +7381,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C322" s="5" t="n">
+      <c r="C322" s="2" t="n">
         <v>3620.25</v>
       </c>
-      <c r="D322" s="6" t="n">
+      <c r="D322" s="3" t="n">
         <v>1.23604851</v>
       </c>
       <c r="E322" t="n">
@@ -7297,10 +7402,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C323" s="5" t="n">
+      <c r="C323" s="2" t="n">
         <v>19747.53</v>
       </c>
-      <c r="D323" s="6" t="n">
+      <c r="D323" s="3" t="n">
         <v>6.74232582</v>
       </c>
       <c r="E323" t="n">
@@ -7318,10 +7423,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C324" s="5" t="n">
+      <c r="C324" s="2" t="n">
         <v>148.8</v>
       </c>
-      <c r="D324" s="6" t="n">
+      <c r="D324" s="3" t="n">
         <v>0.05080423</v>
       </c>
       <c r="E324" t="n">
@@ -7339,10 +7444,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C325" s="5" t="n">
+      <c r="C325" s="2" t="n">
         <v>59465.09</v>
       </c>
-      <c r="D325" s="6" t="n">
+      <c r="D325" s="3" t="n">
         <v>20.30294481</v>
       </c>
       <c r="E325" t="n">
@@ -7360,10 +7465,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C326" s="5" t="n">
+      <c r="C326" s="2" t="n">
         <v>209907.32</v>
       </c>
-      <c r="D326" s="6" t="n">
+      <c r="D326" s="3" t="n">
         <v>71.66787662</v>
       </c>
       <c r="E326" t="n">
@@ -7381,10 +7486,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C327" s="5" t="n">
+      <c r="C327" s="2" t="n">
         <v>6884.07</v>
       </c>
-      <c r="D327" s="6" t="n">
+      <c r="D327" s="3" t="n">
         <v>2.33908458</v>
       </c>
       <c r="E327" t="n">
@@ -7402,10 +7507,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C328" s="5" t="n">
+      <c r="C328" s="2" t="n">
         <v>1851.18</v>
       </c>
-      <c r="D328" s="6" t="n">
+      <c r="D328" s="3" t="n">
         <v>0.62899805</v>
       </c>
       <c r="E328" t="n">
@@ -7423,10 +7528,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C329" s="5" t="n">
+      <c r="C329" s="2" t="n">
         <v>27.27</v>
       </c>
-      <c r="D329" s="6" t="n">
+      <c r="D329" s="3" t="n">
         <v>0.009265860000000001</v>
       </c>
       <c r="E329" t="n">
@@ -7444,10 +7549,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C330" s="5" t="n">
+      <c r="C330" s="2" t="n">
         <v>48724.48</v>
       </c>
-      <c r="D330" s="6" t="n">
+      <c r="D330" s="3" t="n">
         <v>16.55571192</v>
       </c>
       <c r="E330" t="n">
@@ -7465,10 +7570,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C331" s="5" t="n">
+      <c r="C331" s="2" t="n">
         <v>236819.16</v>
       </c>
-      <c r="D331" s="6" t="n">
+      <c r="D331" s="3" t="n">
         <v>80.4669396</v>
       </c>
       <c r="E331" t="n">
@@ -7486,10 +7591,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C332" s="5" t="n">
+      <c r="C332" s="2" t="n">
         <v>1121.22</v>
       </c>
-      <c r="D332" s="6" t="n">
+      <c r="D332" s="3" t="n">
         <v>0.3654631</v>
       </c>
       <c r="E332" t="n">
@@ -7507,10 +7612,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C333" s="5" t="n">
+      <c r="C333" s="2" t="n">
         <v>44200.33</v>
       </c>
-      <c r="D333" s="6" t="n">
+      <c r="D333" s="3" t="n">
         <v>14.40715442</v>
       </c>
       <c r="E333" t="n">
@@ -7528,10 +7633,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C334" s="5" t="n">
+      <c r="C334" s="2" t="n">
         <v>1029.79</v>
       </c>
-      <c r="D334" s="6" t="n">
+      <c r="D334" s="3" t="n">
         <v>0.33566138</v>
       </c>
       <c r="E334" t="n">
@@ -7549,10 +7654,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C335" s="5" t="n">
+      <c r="C335" s="2" t="n">
         <v>47810.16</v>
       </c>
-      <c r="D335" s="6" t="n">
+      <c r="D335" s="3" t="n">
         <v>15.58378315</v>
       </c>
       <c r="E335" t="n">
@@ -7570,10 +7675,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C336" s="5" t="n">
+      <c r="C336" s="2" t="n">
         <v>212632.81</v>
       </c>
-      <c r="D336" s="6" t="n">
+      <c r="D336" s="3" t="n">
         <v>69.30793795</v>
       </c>
       <c r="E336" t="n">
@@ -7591,10 +7696,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C337" s="5" t="n">
+      <c r="C337" s="2" t="n">
         <v>6174.11</v>
       </c>
-      <c r="D337" s="6" t="n">
+      <c r="D337" s="3" t="n">
         <v>2.21572231</v>
       </c>
       <c r="E337" t="n">
@@ -7612,10 +7717,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C338" s="5" t="n">
+      <c r="C338" s="2" t="n">
         <v>41944.2</v>
       </c>
-      <c r="D338" s="6" t="n">
+      <c r="D338" s="3" t="n">
         <v>15.05264723</v>
       </c>
       <c r="E338" t="n">
@@ -7633,10 +7738,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C339" s="5" t="n">
+      <c r="C339" s="2" t="n">
         <v>77569.86</v>
       </c>
-      <c r="D339" s="6" t="n">
+      <c r="D339" s="3" t="n">
         <v>27.8377401</v>
       </c>
       <c r="E339" t="n">
@@ -7654,10 +7759,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C340" s="5" t="n">
+      <c r="C340" s="2" t="n">
         <v>152961.82</v>
       </c>
-      <c r="D340" s="6" t="n">
+      <c r="D340" s="3" t="n">
         <v>54.89389036</v>
       </c>
       <c r="E340" t="n">
@@ -7675,10 +7780,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C341" s="5" t="n">
+      <c r="C341" s="2" t="n">
         <v>4327.58</v>
       </c>
-      <c r="D341" s="6" t="n">
+      <c r="D341" s="3" t="n">
         <v>1.21146897</v>
       </c>
       <c r="E341" t="n">
@@ -7696,10 +7801,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C342" s="5" t="n">
+      <c r="C342" s="2" t="n">
         <v>28414.86</v>
       </c>
-      <c r="D342" s="6" t="n">
+      <c r="D342" s="3" t="n">
         <v>7.95449675</v>
       </c>
       <c r="E342" t="n">
@@ -7717,10 +7822,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C343" s="5" t="n">
+      <c r="C343" s="2" t="n">
         <v>57985.61</v>
       </c>
-      <c r="D343" s="6" t="n">
+      <c r="D343" s="3" t="n">
         <v>16.23257501</v>
       </c>
       <c r="E343" t="n">
@@ -7738,10 +7843,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C344" s="5" t="n">
+      <c r="C344" s="2" t="n">
         <v>164042.55</v>
       </c>
-      <c r="D344" s="6" t="n">
+      <c r="D344" s="3" t="n">
         <v>45.92230724</v>
       </c>
       <c r="E344" t="n">
@@ -7759,10 +7864,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C345" s="5" t="n">
+      <c r="C345" s="2" t="n">
         <v>102446.97</v>
       </c>
-      <c r="D345" s="6" t="n">
+      <c r="D345" s="3" t="n">
         <v>28.67915204</v>
       </c>
       <c r="E345" t="n">
@@ -7780,10 +7885,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C346" s="5" t="n">
+      <c r="C346" s="2" t="n">
         <v>6549.34</v>
       </c>
-      <c r="D346" s="6" t="n">
+      <c r="D346" s="3" t="n">
         <v>1.3658538</v>
       </c>
       <c r="E346" t="n">
@@ -7801,10 +7906,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C347" s="5" t="n">
+      <c r="C347" s="2" t="n">
         <v>70012.2</v>
       </c>
-      <c r="D347" s="6" t="n">
+      <c r="D347" s="3" t="n">
         <v>14.60092612</v>
       </c>
       <c r="E347" t="n">
@@ -7822,10 +7927,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C348" s="5" t="n">
+      <c r="C348" s="2" t="n">
         <v>131512.85</v>
       </c>
-      <c r="D348" s="6" t="n">
+      <c r="D348" s="3" t="n">
         <v>27.42678286</v>
       </c>
       <c r="E348" t="n">
@@ -7843,14 +7948,119 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C349" s="5" t="n">
+      <c r="C349" s="2" t="n">
         <v>271430.81</v>
       </c>
-      <c r="D349" s="6" t="n">
+      <c r="D349" s="3" t="n">
         <v>56.60643722</v>
       </c>
       <c r="E349" t="n">
         <v>153</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C350" s="2" t="n">
+        <v>15339.66</v>
+      </c>
+      <c r="D350" s="3" t="n">
+        <v>4.55580253</v>
+      </c>
+      <c r="E350" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C351" s="2" t="n">
+        <v>24900.55</v>
+      </c>
+      <c r="D351" s="3" t="n">
+        <v>7.39533918</v>
+      </c>
+      <c r="E351" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C352" s="2" t="n">
+        <v>7486.19</v>
+      </c>
+      <c r="D352" s="3" t="n">
+        <v>2.2233611</v>
+      </c>
+      <c r="E352" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C353" s="2" t="n">
+        <v>75899.28</v>
+      </c>
+      <c r="D353" s="3" t="n">
+        <v>22.54170768</v>
+      </c>
+      <c r="E353" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C354" s="2" t="n">
+        <v>213080.31</v>
+      </c>
+      <c r="D354" s="3" t="n">
+        <v>63.28378952</v>
+      </c>
+      <c r="E354" t="n">
+        <v>211</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,103 +488,103 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>213080.31</v>
+        <v>125391.41</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>63.28378952</v>
+        <v>68.99966630999999</v>
       </c>
       <c r="E2" t="n">
-        <v>211</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tech &amp; Science</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>75899.28</v>
+        <v>40317.43</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.54170768</v>
+        <v>22.18564427</v>
       </c>
       <c r="E3" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Tech &amp; Science</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>24900.55</v>
+        <v>15478.5</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>7.39533918</v>
+        <v>8.517420250000001</v>
       </c>
       <c r="E4" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Business/Economy</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>15339.66</v>
+        <v>441.17</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>4.55580253</v>
+        <v>0.2427645</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Business/Economy</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>7486.19</v>
+        <v>99.05</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2.2233611</v>
+        <v>0.05450467</v>
       </c>
       <c r="E6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>336705.99</v>
+        <v>181727.56</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>275</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -613,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E354"/>
+  <dimension ref="A1:E359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8063,6 +8063,111 @@
         <v>211</v>
       </c>
     </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C355" s="2" t="n">
+        <v>99.05</v>
+      </c>
+      <c r="D355" s="3" t="n">
+        <v>0.05450467</v>
+      </c>
+      <c r="E355" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C356" s="2" t="n">
+        <v>40317.43</v>
+      </c>
+      <c r="D356" s="3" t="n">
+        <v>22.18564427</v>
+      </c>
+      <c r="E356" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C357" s="2" t="n">
+        <v>441.17</v>
+      </c>
+      <c r="D357" s="3" t="n">
+        <v>0.2427645</v>
+      </c>
+      <c r="E357" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C358" s="2" t="n">
+        <v>15478.5</v>
+      </c>
+      <c r="D358" s="3" t="n">
+        <v>8.517420250000001</v>
+      </c>
+      <c r="E358" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C359" s="2" t="n">
+        <v>125391.41</v>
+      </c>
+      <c r="D359" s="3" t="n">
+        <v>68.99966630999999</v>
+      </c>
+      <c r="E359" t="n">
+        <v>135</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,118 +488,97 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>125391.41</v>
+        <v>260836.19</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>68.99966630999999</v>
+        <v>63.27632591</v>
       </c>
       <c r="E2" t="n">
-        <v>135</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Tech &amp; Science</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>40317.43</v>
+        <v>131529.74</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.18564427</v>
+        <v>31.90783723</v>
       </c>
       <c r="E3" t="n">
-        <v>17</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tech &amp; Science</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>15478.5</v>
+        <v>18773.2</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>8.517420250000001</v>
+        <v>4.55419596</v>
       </c>
       <c r="E4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Business/Economy</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>441.17</v>
+        <v>1078.53</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.2427645</v>
+        <v>0.2616409</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Business/Economy</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>99.05</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0.05450467</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
-        <v>181727.56</v>
-      </c>
-      <c r="D7" s="6" t="n">
+      <c r="C6" s="5" t="n">
+        <v>412217.66</v>
+      </c>
+      <c r="D6" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E7" s="4" t="n">
-        <v>173</v>
+      <c r="E6" s="4" t="n">
+        <v>244</v>
       </c>
     </row>
   </sheetData>
@@ -613,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E359"/>
+  <dimension ref="A1:E363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8168,6 +8147,90 @@
         <v>135</v>
       </c>
     </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C360" s="2" t="n">
+        <v>1078.53</v>
+      </c>
+      <c r="D360" s="3" t="n">
+        <v>0.2616409</v>
+      </c>
+      <c r="E360" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C361" s="2" t="n">
+        <v>18773.2</v>
+      </c>
+      <c r="D361" s="3" t="n">
+        <v>4.55419596</v>
+      </c>
+      <c r="E361" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C362" s="2" t="n">
+        <v>131529.74</v>
+      </c>
+      <c r="D362" s="3" t="n">
+        <v>31.90783723</v>
+      </c>
+      <c r="E362" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C363" s="2" t="n">
+        <v>260836.19</v>
+      </c>
+      <c r="D363" s="3" t="n">
+        <v>63.27632591</v>
+      </c>
+      <c r="E363" t="n">
+        <v>174</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,97 +488,118 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>260836.19</v>
+        <v>264762.77</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>63.27632591</v>
+        <v>60.93141985</v>
       </c>
       <c r="E2" t="n">
-        <v>174</v>
+        <v>227</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tech &amp; Science</t>
+          <t>Business/Economy</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>131529.74</v>
+        <v>101597</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>31.90783723</v>
+        <v>23.3811176</v>
       </c>
       <c r="E3" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Tech &amp; Science</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>18773.2</v>
+        <v>39974.48</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>4.55419596</v>
+        <v>9.19956316</v>
       </c>
       <c r="E4" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Business/Economy</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1078.53</v>
+        <v>28150.66</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.2616409</v>
+        <v>6.47847763</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-04</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>40.94</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0.00942176</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n">
-        <v>412217.66</v>
-      </c>
-      <c r="D6" s="6" t="n">
+      <c r="C7" s="5" t="n">
+        <v>434525.85</v>
+      </c>
+      <c r="D7" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>244</v>
+      <c r="E7" s="4" t="n">
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -592,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E363"/>
+  <dimension ref="A1:E368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8231,6 +8252,111 @@
         <v>174</v>
       </c>
     </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C364" s="2" t="n">
+        <v>101597</v>
+      </c>
+      <c r="D364" s="3" t="n">
+        <v>23.3811176</v>
+      </c>
+      <c r="E364" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C365" s="2" t="n">
+        <v>28150.66</v>
+      </c>
+      <c r="D365" s="3" t="n">
+        <v>6.47847763</v>
+      </c>
+      <c r="E365" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C366" s="2" t="n">
+        <v>40.94</v>
+      </c>
+      <c r="D366" s="3" t="n">
+        <v>0.00942176</v>
+      </c>
+      <c r="E366" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C367" s="2" t="n">
+        <v>39974.48</v>
+      </c>
+      <c r="D367" s="3" t="n">
+        <v>9.19956316</v>
+      </c>
+      <c r="E367" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C368" s="2" t="n">
+        <v>264762.77</v>
+      </c>
+      <c r="D368" s="3" t="n">
+        <v>60.93141985</v>
+      </c>
+      <c r="E368" t="n">
+        <v>227</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,118 +488,97 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>264762.77</v>
+        <v>173288.98</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>60.93141985</v>
+        <v>47.54928489</v>
       </c>
       <c r="E2" t="n">
-        <v>227</v>
+        <v>220</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Business/Economy</t>
+          <t>Tech &amp; Science</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>101597</v>
+        <v>121692.04</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>23.3811176</v>
+        <v>33.3914452</v>
       </c>
       <c r="E3" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tech &amp; Science</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>39974.48</v>
+        <v>65068.55</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>9.19956316</v>
+        <v>17.85435532</v>
       </c>
       <c r="E4" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Business/Economy</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>28150.66</v>
+        <v>4391.2</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>6.47847763</v>
+        <v>1.20491459</v>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Sports</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>40.94</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0.00942176</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
-        <v>434525.85</v>
-      </c>
-      <c r="D7" s="6" t="n">
+      <c r="C6" s="5" t="n">
+        <v>364440.77</v>
+      </c>
+      <c r="D6" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E7" s="4" t="n">
-        <v>311</v>
+      <c r="E6" s="4" t="n">
+        <v>298</v>
       </c>
     </row>
   </sheetData>
@@ -613,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E368"/>
+  <dimension ref="A1:E372"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8357,6 +8336,90 @@
         <v>227</v>
       </c>
     </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C369" s="2" t="n">
+        <v>4391.2</v>
+      </c>
+      <c r="D369" s="3" t="n">
+        <v>1.20491459</v>
+      </c>
+      <c r="E369" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C370" s="2" t="n">
+        <v>65068.55</v>
+      </c>
+      <c r="D370" s="3" t="n">
+        <v>17.85435532</v>
+      </c>
+      <c r="E370" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C371" s="2" t="n">
+        <v>121692.04</v>
+      </c>
+      <c r="D371" s="3" t="n">
+        <v>33.3914452</v>
+      </c>
+      <c r="E371" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C372" s="2" t="n">
+        <v>173288.98</v>
+      </c>
+      <c r="D372" s="3" t="n">
+        <v>47.54928489</v>
+      </c>
+      <c r="E372" t="n">
+        <v>220</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>173288.98</v>
+        <v>142100.46</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>47.54928489</v>
+        <v>58.92675689</v>
       </c>
       <c r="E2" t="n">
-        <v>220</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>121692.04</v>
+        <v>52107.99</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>33.3914452</v>
+        <v>21.60833863</v>
       </c>
       <c r="E3" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>65068.55</v>
+        <v>29163.77</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>17.85435532</v>
+        <v>12.09374259</v>
       </c>
       <c r="E4" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>4391.2</v>
+        <v>17775.38</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1.20491459</v>
+        <v>7.37116189</v>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -572,13 +572,13 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>364440.77</v>
+        <v>241147.6</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>298</v>
+        <v>250</v>
       </c>
     </row>
   </sheetData>
@@ -592,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E372"/>
+  <dimension ref="A1:E376"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8420,6 +8420,90 @@
         <v>220</v>
       </c>
     </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C373" s="2" t="n">
+        <v>17775.38</v>
+      </c>
+      <c r="D373" s="3" t="n">
+        <v>7.37116189</v>
+      </c>
+      <c r="E373" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C374" s="2" t="n">
+        <v>29163.77</v>
+      </c>
+      <c r="D374" s="3" t="n">
+        <v>12.09374259</v>
+      </c>
+      <c r="E374" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C375" s="2" t="n">
+        <v>52107.99</v>
+      </c>
+      <c r="D375" s="3" t="n">
+        <v>21.60833863</v>
+      </c>
+      <c r="E375" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C376" s="2" t="n">
+        <v>142100.46</v>
+      </c>
+      <c r="D376" s="3" t="n">
+        <v>58.92675689</v>
+      </c>
+      <c r="E376" t="n">
+        <v>172</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -69,11 +69,11 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -477,108 +477,24 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Unclassified</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>142100.46</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>58.92675689</v>
-      </c>
-      <c r="E2" t="n">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Tech &amp; Science</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>52107.99</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>21.60833863</v>
-      </c>
-      <c r="E3" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Geopolitics</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>29163.77</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>12.09374259</v>
-      </c>
-      <c r="E4" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Business/Economy</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>17775.38</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>7.37116189</v>
-      </c>
-      <c r="E5" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-07</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n">
-        <v>241147.6</v>
-      </c>
-      <c r="D6" s="6" t="n">
+      <c r="C2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>250</v>
+      <c r="E2" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -640,10 +556,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="5" t="n">
         <v>948.86</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="6" t="n">
         <v>0.19126904</v>
       </c>
       <c r="E2" t="n">
@@ -661,10 +577,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="5" t="n">
         <v>461123.2</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="6" t="n">
         <v>92.95216732</v>
       </c>
       <c r="E3" t="n">
@@ -682,10 +598,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" s="5" t="n">
         <v>333</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="6" t="n">
         <v>0.06712538</v>
       </c>
       <c r="E4" t="n">
@@ -703,10 +619,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" s="5" t="n">
         <v>33681.49</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="6" t="n">
         <v>6.78943825</v>
       </c>
       <c r="E5" t="n">
@@ -724,10 +640,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" s="5" t="n">
         <v>3947.95</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="6" t="n">
         <v>0.94921987</v>
       </c>
       <c r="E6" t="n">
@@ -745,10 +661,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" s="5" t="n">
         <v>316928.34</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="6" t="n">
         <v>76.20022474</v>
       </c>
       <c r="E7" t="n">
@@ -766,10 +682,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="C8" s="5" t="n">
         <v>28879.81</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="6" t="n">
         <v>6.94367696</v>
       </c>
       <c r="E8" t="n">
@@ -787,10 +703,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n">
+      <c r="C9" s="5" t="n">
         <v>66159.13</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" s="6" t="n">
         <v>15.90687843</v>
       </c>
       <c r="E9" t="n">
@@ -808,10 +724,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n">
+      <c r="C10" s="5" t="n">
         <v>672.72</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D10" s="6" t="n">
         <v>0.12167625</v>
       </c>
       <c r="E10" t="n">
@@ -829,10 +745,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n">
+      <c r="C11" s="5" t="n">
         <v>506109.58</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="D11" s="6" t="n">
         <v>91.54108388</v>
       </c>
       <c r="E11" t="n">
@@ -850,10 +766,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n">
+      <c r="C12" s="5" t="n">
         <v>13144.61</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" s="6" t="n">
         <v>2.37749273</v>
       </c>
       <c r="E12" t="n">
@@ -871,10 +787,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n">
+      <c r="C13" s="5" t="n">
         <v>32950.07</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" s="6" t="n">
         <v>5.95974714</v>
       </c>
       <c r="E13" t="n">
@@ -892,10 +808,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
+      <c r="C14" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D14" s="6" t="n">
         <v>0.00340356</v>
       </c>
       <c r="E14" t="n">
@@ -913,10 +829,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n">
+      <c r="C15" s="5" t="n">
         <v>3803.45</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="D15" s="6" t="n">
         <v>1.43836189</v>
       </c>
       <c r="E15" t="n">
@@ -934,10 +850,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n">
+      <c r="C16" s="5" t="n">
         <v>229609.87</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D16" s="6" t="n">
         <v>86.83224112000001</v>
       </c>
       <c r="E16" t="n">
@@ -955,10 +871,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C17" s="2" t="n">
+      <c r="C17" s="5" t="n">
         <v>884.04</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="D17" s="6" t="n">
         <v>0.33432001</v>
       </c>
       <c r="E17" t="n">
@@ -976,10 +892,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C18" s="2" t="n">
+      <c r="C18" s="5" t="n">
         <v>30122.92</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="D18" s="6" t="n">
         <v>11.39167342</v>
       </c>
       <c r="E18" t="n">
@@ -997,10 +913,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C19" s="2" t="n">
+      <c r="C19" s="5" t="n">
         <v>23268.18</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="D19" s="6" t="n">
         <v>4.17124226</v>
       </c>
       <c r="E19" t="n">
@@ -1018,10 +934,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C20" s="2" t="n">
+      <c r="C20" s="5" t="n">
         <v>451338.15</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="D20" s="6" t="n">
         <v>80.91052954</v>
       </c>
       <c r="E20" t="n">
@@ -1039,10 +955,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C21" s="2" t="n">
+      <c r="C21" s="5" t="n">
         <v>20229.42</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="D21" s="6" t="n">
         <v>3.62648955</v>
       </c>
       <c r="E21" t="n">
@@ -1060,10 +976,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C22" s="2" t="n">
+      <c r="C22" s="5" t="n">
         <v>62988</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="D22" s="6" t="n">
         <v>11.29173865</v>
       </c>
       <c r="E22" t="n">
@@ -1081,10 +997,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C23" s="2" t="n">
+      <c r="C23" s="5" t="n">
         <v>103.09</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="D23" s="6" t="n">
         <v>0.02902112</v>
       </c>
       <c r="E23" t="n">
@@ -1102,10 +1018,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C24" s="2" t="n">
+      <c r="C24" s="5" t="n">
         <v>283.13</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="D24" s="6" t="n">
         <v>0.07970463</v>
       </c>
       <c r="E24" t="n">
@@ -1123,10 +1039,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n">
+      <c r="C25" s="5" t="n">
         <v>341584.75</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="D25" s="6" t="n">
         <v>96.16036696</v>
       </c>
       <c r="E25" t="n">
@@ -1144,10 +1060,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C26" s="2" t="n">
+      <c r="C26" s="5" t="n">
         <v>13253.08</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="D26" s="6" t="n">
         <v>3.7309073</v>
       </c>
       <c r="E26" t="n">
@@ -1165,10 +1081,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C27" s="2" t="n">
+      <c r="C27" s="5" t="n">
         <v>366675.1</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="D27" s="6" t="n">
         <v>88.88052623</v>
       </c>
       <c r="E27" t="n">
@@ -1186,10 +1102,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C28" s="2" t="n">
+      <c r="C28" s="5" t="n">
         <v>10967.83</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="D28" s="6" t="n">
         <v>2.65855659</v>
       </c>
       <c r="E28" t="n">
@@ -1207,10 +1123,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C29" s="2" t="n">
+      <c r="C29" s="5" t="n">
         <v>34905.37</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="D29" s="6" t="n">
         <v>8.460917179999999</v>
       </c>
       <c r="E29" t="n">
@@ -1228,10 +1144,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C30" s="2" t="n">
+      <c r="C30" s="5" t="n">
         <v>431085.81</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="D30" s="6" t="n">
         <v>81.83421629999999</v>
       </c>
       <c r="E30" t="n">
@@ -1249,10 +1165,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C31" s="2" t="n">
+      <c r="C31" s="5" t="n">
         <v>1633.45</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="D31" s="6" t="n">
         <v>0.31008235</v>
       </c>
       <c r="E31" t="n">
@@ -1270,10 +1186,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C32" s="2" t="n">
+      <c r="C32" s="5" t="n">
         <v>94060.16</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="D32" s="6" t="n">
         <v>17.85570135</v>
       </c>
       <c r="E32" t="n">
@@ -1291,10 +1207,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C33" s="2" t="n">
+      <c r="C33" s="5" t="n">
         <v>321805.16</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="D33" s="6" t="n">
         <v>78.53984421</v>
       </c>
       <c r="E33" t="n">
@@ -1312,10 +1228,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C34" s="2" t="n">
+      <c r="C34" s="5" t="n">
         <v>81063.48</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="D34" s="6" t="n">
         <v>19.78437229</v>
       </c>
       <c r="E34" t="n">
@@ -1333,10 +1249,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C35" s="2" t="n">
+      <c r="C35" s="5" t="n">
         <v>6866.27</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="D35" s="6" t="n">
         <v>1.6757835</v>
       </c>
       <c r="E35" t="n">
@@ -1354,10 +1270,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C36" s="2" t="n">
+      <c r="C36" s="5" t="n">
         <v>352851.14</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="D36" s="6" t="n">
         <v>94.15474251000001</v>
       </c>
       <c r="E36" t="n">
@@ -1375,10 +1291,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C37" s="2" t="n">
+      <c r="C37" s="5" t="n">
         <v>576.49</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="D37" s="6" t="n">
         <v>0.1538305</v>
       </c>
       <c r="E37" t="n">
@@ -1396,10 +1312,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C38" s="2" t="n">
+      <c r="C38" s="5" t="n">
         <v>21329</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="D38" s="6" t="n">
         <v>5.69142699</v>
       </c>
       <c r="E38" t="n">
@@ -1417,10 +1333,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C39" s="2" t="n">
+      <c r="C39" s="5" t="n">
         <v>83.52</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="D39" s="6" t="n">
         <v>0.01466719</v>
       </c>
       <c r="E39" t="n">
@@ -1438,10 +1354,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C40" s="2" t="n">
+      <c r="C40" s="5" t="n">
         <v>509873.13</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="D40" s="6" t="n">
         <v>89.54027855</v>
       </c>
       <c r="E40" t="n">
@@ -1459,10 +1375,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C41" s="2" t="n">
+      <c r="C41" s="5" t="n">
         <v>8520.23</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="D41" s="6" t="n">
         <v>1.49626196</v>
       </c>
       <c r="E41" t="n">
@@ -1480,10 +1396,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C42" s="2" t="n">
+      <c r="C42" s="5" t="n">
         <v>50957.5</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="D42" s="6" t="n">
         <v>8.94879231</v>
       </c>
       <c r="E42" t="n">
@@ -1501,10 +1417,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C43" s="2" t="n">
+      <c r="C43" s="5" t="n">
         <v>9326.15</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="D43" s="6" t="n">
         <v>1.62650962</v>
       </c>
       <c r="E43" t="n">
@@ -1522,10 +1438,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C44" s="2" t="n">
+      <c r="C44" s="5" t="n">
         <v>510341.61</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="D44" s="6" t="n">
         <v>89.00516713</v>
       </c>
       <c r="E44" t="n">
@@ -1543,10 +1459,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C45" s="2" t="n">
+      <c r="C45" s="5" t="n">
         <v>2517.04</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="D45" s="6" t="n">
         <v>0.43897962</v>
       </c>
       <c r="E45" t="n">
@@ -1564,10 +1480,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C46" s="2" t="n">
+      <c r="C46" s="5" t="n">
         <v>51199.45</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="D46" s="6" t="n">
         <v>8.92934363</v>
       </c>
       <c r="E46" t="n">
@@ -1585,10 +1501,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="C47" s="2" t="n">
+      <c r="C47" s="5" t="n">
         <v>850</v>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="D47" s="6" t="n">
         <v>0.25302704</v>
       </c>
       <c r="E47" t="n">
@@ -1606,10 +1522,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C48" s="2" t="n">
+      <c r="C48" s="5" t="n">
         <v>1223.36</v>
       </c>
-      <c r="D48" s="3" t="n">
+      <c r="D48" s="6" t="n">
         <v>0.36416843</v>
       </c>
       <c r="E48" t="n">
@@ -1627,10 +1543,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C49" s="2" t="n">
+      <c r="C49" s="5" t="n">
         <v>270843.56</v>
       </c>
-      <c r="D49" s="3" t="n">
+      <c r="D49" s="6" t="n">
         <v>80.62440645</v>
       </c>
       <c r="E49" t="n">
@@ -1648,10 +1564,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C50" s="2" t="n">
+      <c r="C50" s="5" t="n">
         <v>612.64</v>
       </c>
-      <c r="D50" s="3" t="n">
+      <c r="D50" s="6" t="n">
         <v>0.18236999</v>
       </c>
       <c r="E50" t="n">
@@ -1669,10 +1585,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C51" s="2" t="n">
+      <c r="C51" s="5" t="n">
         <v>62402.91</v>
       </c>
-      <c r="D51" s="3" t="n">
+      <c r="D51" s="6" t="n">
         <v>18.57602809</v>
       </c>
       <c r="E51" t="n">
@@ -1690,10 +1606,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C52" s="2" t="n">
+      <c r="C52" s="5" t="n">
         <v>555930.41</v>
       </c>
-      <c r="D52" s="3" t="n">
+      <c r="D52" s="6" t="n">
         <v>91.1452503</v>
       </c>
       <c r="E52" t="n">
@@ -1711,10 +1627,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C53" s="2" t="n">
+      <c r="C53" s="5" t="n">
         <v>1590.9</v>
       </c>
-      <c r="D53" s="3" t="n">
+      <c r="D53" s="6" t="n">
         <v>0.26082937</v>
       </c>
       <c r="E53" t="n">
@@ -1732,10 +1648,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C54" s="2" t="n">
+      <c r="C54" s="5" t="n">
         <v>52417.67</v>
       </c>
-      <c r="D54" s="3" t="n">
+      <c r="D54" s="6" t="n">
         <v>8.59392033</v>
       </c>
       <c r="E54" t="n">
@@ -1753,10 +1669,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C55" s="2" t="n">
+      <c r="C55" s="5" t="n">
         <v>10.55</v>
       </c>
-      <c r="D55" s="3" t="n">
+      <c r="D55" s="6" t="n">
         <v>0.00287103</v>
       </c>
       <c r="E55" t="n">
@@ -1774,10 +1690,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C56" s="2" t="n">
+      <c r="C56" s="5" t="n">
         <v>319888.32</v>
       </c>
-      <c r="D56" s="3" t="n">
+      <c r="D56" s="6" t="n">
         <v>87.05305848</v>
       </c>
       <c r="E56" t="n">
@@ -1795,10 +1711,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C57" s="2" t="n">
+      <c r="C57" s="5" t="n">
         <v>1278.17</v>
       </c>
-      <c r="D57" s="3" t="n">
+      <c r="D57" s="6" t="n">
         <v>0.34783579</v>
       </c>
       <c r="E57" t="n">
@@ -1816,10 +1732,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C58" s="2" t="n">
+      <c r="C58" s="5" t="n">
         <v>46286.58</v>
       </c>
-      <c r="D58" s="3" t="n">
+      <c r="D58" s="6" t="n">
         <v>12.5962347</v>
       </c>
       <c r="E58" t="n">
@@ -1837,10 +1753,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C59" s="2" t="n">
+      <c r="C59" s="5" t="n">
         <v>354.29</v>
       </c>
-      <c r="D59" s="3" t="n">
+      <c r="D59" s="6" t="n">
         <v>0.1171275</v>
       </c>
       <c r="E59" t="n">
@@ -1858,10 +1774,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C60" s="2" t="n">
+      <c r="C60" s="5" t="n">
         <v>121.49</v>
       </c>
-      <c r="D60" s="3" t="n">
+      <c r="D60" s="6" t="n">
         <v>0.04016433</v>
       </c>
       <c r="E60" t="n">
@@ -1879,10 +1795,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C61" s="2" t="n">
+      <c r="C61" s="5" t="n">
         <v>264522.3</v>
       </c>
-      <c r="D61" s="3" t="n">
+      <c r="D61" s="6" t="n">
         <v>87.4504938</v>
       </c>
       <c r="E61" t="n">
@@ -1900,10 +1816,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C62" s="2" t="n">
+      <c r="C62" s="5" t="n">
         <v>1149.77</v>
       </c>
-      <c r="D62" s="3" t="n">
+      <c r="D62" s="6" t="n">
         <v>0.38011145</v>
       </c>
       <c r="E62" t="n">
@@ -1921,10 +1837,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C63" s="2" t="n">
+      <c r="C63" s="5" t="n">
         <v>36334.49</v>
       </c>
-      <c r="D63" s="3" t="n">
+      <c r="D63" s="6" t="n">
         <v>12.01210292</v>
       </c>
       <c r="E63" t="n">
@@ -1942,10 +1858,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C64" s="2" t="n">
+      <c r="C64" s="5" t="n">
         <v>4545.45</v>
       </c>
-      <c r="D64" s="3" t="n">
+      <c r="D64" s="6" t="n">
         <v>1.24043036</v>
       </c>
       <c r="E64" t="n">
@@ -1963,10 +1879,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C65" s="2" t="n">
+      <c r="C65" s="5" t="n">
         <v>874</v>
       </c>
-      <c r="D65" s="3" t="n">
+      <c r="D65" s="6" t="n">
         <v>0.23851019</v>
       </c>
       <c r="E65" t="n">
@@ -1984,10 +1900,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C66" s="2" t="n">
+      <c r="C66" s="5" t="n">
         <v>284866.12</v>
       </c>
-      <c r="D66" s="3" t="n">
+      <c r="D66" s="6" t="n">
         <v>77.73852608</v>
       </c>
       <c r="E66" t="n">
@@ -2005,10 +1921,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C67" s="2" t="n">
+      <c r="C67" s="5" t="n">
         <v>1590.95</v>
       </c>
-      <c r="D67" s="3" t="n">
+      <c r="D67" s="6" t="n">
         <v>0.43416222</v>
       </c>
       <c r="E67" t="n">
@@ -2026,10 +1942,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C68" s="2" t="n">
+      <c r="C68" s="5" t="n">
         <v>74564.85000000001</v>
       </c>
-      <c r="D68" s="3" t="n">
+      <c r="D68" s="6" t="n">
         <v>20.34837115</v>
       </c>
       <c r="E68" t="n">
@@ -2047,10 +1963,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C69" s="2" t="n">
+      <c r="C69" s="5" t="n">
         <v>442814.15</v>
       </c>
-      <c r="D69" s="3" t="n">
+      <c r="D69" s="6" t="n">
         <v>80.48822254</v>
       </c>
       <c r="E69" t="n">
@@ -2068,10 +1984,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C70" s="2" t="n">
+      <c r="C70" s="5" t="n">
         <v>914.39</v>
       </c>
-      <c r="D70" s="3" t="n">
+      <c r="D70" s="6" t="n">
         <v>0.16620432</v>
       </c>
       <c r="E70" t="n">
@@ -2089,10 +2005,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C71" s="2" t="n">
+      <c r="C71" s="5" t="n">
         <v>106431.64</v>
       </c>
-      <c r="D71" s="3" t="n">
+      <c r="D71" s="6" t="n">
         <v>19.34557314</v>
       </c>
       <c r="E71" t="n">
@@ -2110,10 +2026,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C72" s="2" t="n">
+      <c r="C72" s="5" t="n">
         <v>166</v>
       </c>
-      <c r="D72" s="3" t="n">
+      <c r="D72" s="6" t="n">
         <v>0.02878159</v>
       </c>
       <c r="E72" t="n">
@@ -2131,10 +2047,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C73" s="2" t="n">
+      <c r="C73" s="5" t="n">
         <v>81.83</v>
       </c>
-      <c r="D73" s="3" t="n">
+      <c r="D73" s="6" t="n">
         <v>0.01418794</v>
       </c>
       <c r="E73" t="n">
@@ -2152,10 +2068,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C74" s="2" t="n">
+      <c r="C74" s="5" t="n">
         <v>528120.33</v>
       </c>
-      <c r="D74" s="3" t="n">
+      <c r="D74" s="6" t="n">
         <v>91.56712743999999</v>
       </c>
       <c r="E74" t="n">
@@ -2173,10 +2089,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C75" s="2" t="n">
+      <c r="C75" s="5" t="n">
         <v>567.3200000000001</v>
       </c>
-      <c r="D75" s="3" t="n">
+      <c r="D75" s="6" t="n">
         <v>0.09836369</v>
       </c>
       <c r="E75" t="n">
@@ -2194,10 +2110,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C76" s="2" t="n">
+      <c r="C76" s="5" t="n">
         <v>47822.08</v>
       </c>
-      <c r="D76" s="3" t="n">
+      <c r="D76" s="6" t="n">
         <v>8.29153934</v>
       </c>
       <c r="E76" t="n">
@@ -2215,10 +2131,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C77" s="2" t="n">
+      <c r="C77" s="5" t="n">
         <v>2157.29</v>
       </c>
-      <c r="D77" s="3" t="n">
+      <c r="D77" s="6" t="n">
         <v>1.00708473</v>
       </c>
       <c r="E77" t="n">
@@ -2236,10 +2152,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C78" s="2" t="n">
+      <c r="C78" s="5" t="n">
         <v>177127.26</v>
       </c>
-      <c r="D78" s="3" t="n">
+      <c r="D78" s="6" t="n">
         <v>82.68807579999999</v>
       </c>
       <c r="E78" t="n">
@@ -2257,10 +2173,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C79" s="2" t="n">
+      <c r="C79" s="5" t="n">
         <v>826.1799999999999</v>
       </c>
-      <c r="D79" s="3" t="n">
+      <c r="D79" s="6" t="n">
         <v>0.38568448</v>
       </c>
       <c r="E79" t="n">
@@ -2278,10 +2194,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C80" s="2" t="n">
+      <c r="C80" s="5" t="n">
         <v>34100.64</v>
       </c>
-      <c r="D80" s="3" t="n">
+      <c r="D80" s="6" t="n">
         <v>15.91915499</v>
       </c>
       <c r="E80" t="n">
@@ -2299,10 +2215,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C81" s="2" t="n">
+      <c r="C81" s="5" t="n">
         <v>54.12</v>
       </c>
-      <c r="D81" s="3" t="n">
+      <c r="D81" s="6" t="n">
         <v>0.01747125</v>
       </c>
       <c r="E81" t="n">
@@ -2320,10 +2236,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C82" s="2" t="n">
+      <c r="C82" s="5" t="n">
         <v>66</v>
       </c>
-      <c r="D82" s="3" t="n">
+      <c r="D82" s="6" t="n">
         <v>0.0213064</v>
       </c>
       <c r="E82" t="n">
@@ -2341,10 +2257,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C83" s="2" t="n">
+      <c r="C83" s="5" t="n">
         <v>21771.31</v>
       </c>
-      <c r="D83" s="3" t="n">
+      <c r="D83" s="6" t="n">
         <v>7.02830778</v>
       </c>
       <c r="E83" t="n">
@@ -2362,10 +2278,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C84" s="2" t="n">
+      <c r="C84" s="5" t="n">
         <v>214416.2</v>
       </c>
-      <c r="D84" s="3" t="n">
+      <c r="D84" s="6" t="n">
         <v>69.21875842999999</v>
       </c>
       <c r="E84" t="n">
@@ -2383,10 +2299,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C85" s="2" t="n">
+      <c r="C85" s="5" t="n">
         <v>9060.450000000001</v>
       </c>
-      <c r="D85" s="3" t="n">
+      <c r="D85" s="6" t="n">
         <v>2.92493338</v>
       </c>
       <c r="E85" t="n">
@@ -2404,10 +2320,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C86" s="2" t="n">
+      <c r="C86" s="5" t="n">
         <v>64397.95</v>
       </c>
-      <c r="D86" s="3" t="n">
+      <c r="D86" s="6" t="n">
         <v>20.78922276</v>
       </c>
       <c r="E86" t="n">
@@ -2425,10 +2341,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C87" s="2" t="n">
+      <c r="C87" s="5" t="n">
         <v>1067.9</v>
       </c>
-      <c r="D87" s="3" t="n">
+      <c r="D87" s="6" t="n">
         <v>0.29681338</v>
       </c>
       <c r="E87" t="n">
@@ -2446,10 +2362,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C88" s="2" t="n">
+      <c r="C88" s="5" t="n">
         <v>260988.37</v>
       </c>
-      <c r="D88" s="3" t="n">
+      <c r="D88" s="6" t="n">
         <v>72.53941456</v>
       </c>
       <c r="E88" t="n">
@@ -2467,10 +2383,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C89" s="2" t="n">
+      <c r="C89" s="5" t="n">
         <v>7522.28</v>
       </c>
-      <c r="D89" s="3" t="n">
+      <c r="D89" s="6" t="n">
         <v>2.09075135</v>
       </c>
       <c r="E89" t="n">
@@ -2488,10 +2404,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C90" s="2" t="n">
+      <c r="C90" s="5" t="n">
         <v>90209.81</v>
       </c>
-      <c r="D90" s="3" t="n">
+      <c r="D90" s="6" t="n">
         <v>25.07302071</v>
       </c>
       <c r="E90" t="n">
@@ -2509,10 +2425,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C91" s="2" t="n">
+      <c r="C91" s="5" t="n">
         <v>11124.49</v>
       </c>
-      <c r="D91" s="3" t="n">
+      <c r="D91" s="6" t="n">
         <v>3.35098295</v>
       </c>
       <c r="E91" t="n">
@@ -2530,10 +2446,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C92" s="2" t="n">
+      <c r="C92" s="5" t="n">
         <v>201888.41</v>
       </c>
-      <c r="D92" s="3" t="n">
+      <c r="D92" s="6" t="n">
         <v>60.81398972</v>
       </c>
       <c r="E92" t="n">
@@ -2551,10 +2467,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C93" s="2" t="n">
+      <c r="C93" s="5" t="n">
         <v>15503.87</v>
       </c>
-      <c r="D93" s="3" t="n">
+      <c r="D93" s="6" t="n">
         <v>4.67016502</v>
       </c>
       <c r="E93" t="n">
@@ -2572,10 +2488,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C94" s="2" t="n">
+      <c r="C94" s="5" t="n">
         <v>103460.15</v>
       </c>
-      <c r="D94" s="3" t="n">
+      <c r="D94" s="6" t="n">
         <v>31.1648623</v>
       </c>
       <c r="E94" t="n">
@@ -2593,10 +2509,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C95" s="2" t="n">
+      <c r="C95" s="5" t="n">
         <v>1029.41</v>
       </c>
-      <c r="D95" s="3" t="n">
+      <c r="D95" s="6" t="n">
         <v>0.31513536</v>
       </c>
       <c r="E95" t="n">
@@ -2614,10 +2530,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C96" s="2" t="n">
+      <c r="C96" s="5" t="n">
         <v>1848</v>
       </c>
-      <c r="D96" s="3" t="n">
+      <c r="D96" s="6" t="n">
         <v>0.56573196</v>
       </c>
       <c r="E96" t="n">
@@ -2635,10 +2551,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C97" s="2" t="n">
+      <c r="C97" s="5" t="n">
         <v>126297.98</v>
       </c>
-      <c r="D97" s="3" t="n">
+      <c r="D97" s="6" t="n">
         <v>38.66385499</v>
       </c>
       <c r="E97" t="n">
@@ -2656,10 +2572,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C98" s="2" t="n">
+      <c r="C98" s="5" t="n">
         <v>23680.09</v>
       </c>
-      <c r="D98" s="3" t="n">
+      <c r="D98" s="6" t="n">
         <v>7.24923364</v>
       </c>
       <c r="E98" t="n">
@@ -2677,10 +2593,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C99" s="2" t="n">
+      <c r="C99" s="5" t="n">
         <v>173800.98</v>
       </c>
-      <c r="D99" s="3" t="n">
+      <c r="D99" s="6" t="n">
         <v>53.20604405</v>
       </c>
       <c r="E99" t="n">
@@ -2698,10 +2614,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C100" s="2" t="n">
+      <c r="C100" s="5" t="n">
         <v>856.11</v>
       </c>
-      <c r="D100" s="3" t="n">
+      <c r="D100" s="6" t="n">
         <v>0.22747196</v>
       </c>
       <c r="E100" t="n">
@@ -2719,10 +2635,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C101" s="2" t="n">
+      <c r="C101" s="5" t="n">
         <v>9.68</v>
       </c>
-      <c r="D101" s="3" t="n">
+      <c r="D101" s="6" t="n">
         <v>0.00257202</v>
       </c>
       <c r="E101" t="n">
@@ -2740,10 +2656,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C102" s="2" t="n">
+      <c r="C102" s="5" t="n">
         <v>296012.79</v>
       </c>
-      <c r="D102" s="3" t="n">
+      <c r="D102" s="6" t="n">
         <v>78.65181887</v>
       </c>
       <c r="E102" t="n">
@@ -2761,10 +2677,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C103" s="2" t="n">
+      <c r="C103" s="5" t="n">
         <v>3709.15</v>
       </c>
-      <c r="D103" s="3" t="n">
+      <c r="D103" s="6" t="n">
         <v>0.98553645</v>
       </c>
       <c r="E103" t="n">
@@ -2782,10 +2698,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C104" s="2" t="n">
+      <c r="C104" s="5" t="n">
         <v>75770.75</v>
       </c>
-      <c r="D104" s="3" t="n">
+      <c r="D104" s="6" t="n">
         <v>20.13260071</v>
       </c>
       <c r="E104" t="n">
@@ -2803,10 +2719,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C105" s="2" t="n">
+      <c r="C105" s="5" t="n">
         <v>363.62</v>
       </c>
-      <c r="D105" s="3" t="n">
+      <c r="D105" s="6" t="n">
         <v>0.09792976</v>
       </c>
       <c r="E105" t="n">
@@ -2824,10 +2740,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C106" s="2" t="n">
+      <c r="C106" s="5" t="n">
         <v>303265.05</v>
       </c>
-      <c r="D106" s="3" t="n">
+      <c r="D106" s="6" t="n">
         <v>81.67502655</v>
       </c>
       <c r="E106" t="n">
@@ -2845,10 +2761,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C107" s="2" t="n">
+      <c r="C107" s="5" t="n">
         <v>829.42</v>
       </c>
-      <c r="D107" s="3" t="n">
+      <c r="D107" s="6" t="n">
         <v>0.22337853</v>
       </c>
       <c r="E107" t="n">
@@ -2866,10 +2782,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C108" s="2" t="n">
+      <c r="C108" s="5" t="n">
         <v>66848.86</v>
       </c>
-      <c r="D108" s="3" t="n">
+      <c r="D108" s="6" t="n">
         <v>18.00366516</v>
       </c>
       <c r="E108" t="n">
@@ -2887,10 +2803,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C109" s="2" t="n">
+      <c r="C109" s="5" t="n">
         <v>174192.16</v>
       </c>
-      <c r="D109" s="3" t="n">
+      <c r="D109" s="6" t="n">
         <v>66.86566559000001</v>
       </c>
       <c r="E109" t="n">
@@ -2908,10 +2824,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C110" s="2" t="n">
+      <c r="C110" s="5" t="n">
         <v>19438.25</v>
       </c>
-      <c r="D110" s="3" t="n">
+      <c r="D110" s="6" t="n">
         <v>7.461596</v>
       </c>
       <c r="E110" t="n">
@@ -2929,10 +2845,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C111" s="2" t="n">
+      <c r="C111" s="5" t="n">
         <v>66880.21000000001</v>
       </c>
-      <c r="D111" s="3" t="n">
+      <c r="D111" s="6" t="n">
         <v>25.67273841</v>
       </c>
       <c r="E111" t="n">
@@ -2950,10 +2866,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C112" s="2" t="n">
+      <c r="C112" s="5" t="n">
         <v>1885.29</v>
       </c>
-      <c r="D112" s="3" t="n">
+      <c r="D112" s="6" t="n">
         <v>0.5105483200000001</v>
       </c>
       <c r="E112" t="n">
@@ -2971,10 +2887,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C113" s="2" t="n">
+      <c r="C113" s="5" t="n">
         <v>642.63</v>
       </c>
-      <c r="D113" s="3" t="n">
+      <c r="D113" s="6" t="n">
         <v>0.17402822</v>
       </c>
       <c r="E113" t="n">
@@ -2992,10 +2908,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C114" s="2" t="n">
+      <c r="C114" s="5" t="n">
         <v>2177.75</v>
       </c>
-      <c r="D114" s="3" t="n">
+      <c r="D114" s="6" t="n">
         <v>0.58974832</v>
       </c>
       <c r="E114" t="n">
@@ -3013,10 +2929,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C115" s="2" t="n">
+      <c r="C115" s="5" t="n">
         <v>202289.9</v>
       </c>
-      <c r="D115" s="3" t="n">
+      <c r="D115" s="6" t="n">
         <v>54.78137012</v>
       </c>
       <c r="E115" t="n">
@@ -3034,10 +2950,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C116" s="2" t="n">
+      <c r="C116" s="5" t="n">
         <v>30328.46</v>
       </c>
-      <c r="D116" s="3" t="n">
+      <c r="D116" s="6" t="n">
         <v>8.213136649999999</v>
       </c>
       <c r="E116" t="n">
@@ -3055,10 +2971,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C117" s="2" t="n">
+      <c r="C117" s="5" t="n">
         <v>131943.66</v>
       </c>
-      <c r="D117" s="3" t="n">
+      <c r="D117" s="6" t="n">
         <v>35.73116836</v>
       </c>
       <c r="E117" t="n">
@@ -3076,10 +2992,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C118" s="2" t="n">
+      <c r="C118" s="5" t="n">
         <v>101.72</v>
       </c>
-      <c r="D118" s="3" t="n">
+      <c r="D118" s="6" t="n">
         <v>0.03804713</v>
       </c>
       <c r="E118" t="n">
@@ -3097,10 +3013,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C119" s="2" t="n">
+      <c r="C119" s="5" t="n">
         <v>58</v>
       </c>
-      <c r="D119" s="3" t="n">
+      <c r="D119" s="6" t="n">
         <v>0.02169419</v>
       </c>
       <c r="E119" t="n">
@@ -3118,10 +3034,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C120" s="2" t="n">
+      <c r="C120" s="5" t="n">
         <v>167439.3</v>
       </c>
-      <c r="D120" s="3" t="n">
+      <c r="D120" s="6" t="n">
         <v>62.62863161</v>
       </c>
       <c r="E120" t="n">
@@ -3139,10 +3055,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C121" s="2" t="n">
+      <c r="C121" s="5" t="n">
         <v>7300.3</v>
       </c>
-      <c r="D121" s="3" t="n">
+      <c r="D121" s="6" t="n">
         <v>2.73058833</v>
       </c>
       <c r="E121" t="n">
@@ -3160,10 +3076,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C122" s="2" t="n">
+      <c r="C122" s="5" t="n">
         <v>92453.32000000001</v>
       </c>
-      <c r="D122" s="3" t="n">
+      <c r="D122" s="6" t="n">
         <v>34.58103874</v>
       </c>
       <c r="E122" t="n">
@@ -3181,10 +3097,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C123" s="2" t="n">
+      <c r="C123" s="5" t="n">
         <v>1475.74</v>
       </c>
-      <c r="D123" s="3" t="n">
+      <c r="D123" s="6" t="n">
         <v>0.33417908</v>
       </c>
       <c r="E123" t="n">
@@ -3202,10 +3118,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C124" s="2" t="n">
+      <c r="C124" s="5" t="n">
         <v>2209.05</v>
       </c>
-      <c r="D124" s="3" t="n">
+      <c r="D124" s="6" t="n">
         <v>0.50023602</v>
       </c>
       <c r="E124" t="n">
@@ -3223,10 +3139,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C125" s="2" t="n">
+      <c r="C125" s="5" t="n">
         <v>232354.93</v>
       </c>
-      <c r="D125" s="3" t="n">
+      <c r="D125" s="6" t="n">
         <v>52.61642084</v>
       </c>
       <c r="E125" t="n">
@@ -3244,10 +3160,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C126" s="2" t="n">
+      <c r="C126" s="5" t="n">
         <v>11084.31</v>
       </c>
-      <c r="D126" s="3" t="n">
+      <c r="D126" s="6" t="n">
         <v>2.51002516</v>
       </c>
       <c r="E126" t="n">
@@ -3265,10 +3181,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C127" s="2" t="n">
+      <c r="C127" s="5" t="n">
         <v>194477.52</v>
       </c>
-      <c r="D127" s="3" t="n">
+      <c r="D127" s="6" t="n">
         <v>44.0391389</v>
       </c>
       <c r="E127" t="n">
@@ -3286,10 +3202,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C128" s="2" t="n">
+      <c r="C128" s="5" t="n">
         <v>2990.78</v>
       </c>
-      <c r="D128" s="3" t="n">
+      <c r="D128" s="6" t="n">
         <v>0.63513389</v>
       </c>
       <c r="E128" t="n">
@@ -3307,10 +3223,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C129" s="2" t="n">
+      <c r="C129" s="5" t="n">
         <v>847.45</v>
       </c>
-      <c r="D129" s="3" t="n">
+      <c r="D129" s="6" t="n">
         <v>0.17996784</v>
       </c>
       <c r="E129" t="n">
@@ -3328,10 +3244,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C130" s="2" t="n">
+      <c r="C130" s="5" t="n">
         <v>211.86</v>
       </c>
-      <c r="D130" s="3" t="n">
+      <c r="D130" s="6" t="n">
         <v>0.04499143</v>
       </c>
       <c r="E130" t="n">
@@ -3349,10 +3265,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C131" s="2" t="n">
+      <c r="C131" s="5" t="n">
         <v>222684.94</v>
       </c>
-      <c r="D131" s="3" t="n">
+      <c r="D131" s="6" t="n">
         <v>47.29025603</v>
       </c>
       <c r="E131" t="n">
@@ -3370,10 +3286,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C132" s="2" t="n">
+      <c r="C132" s="5" t="n">
         <v>10642.51</v>
       </c>
-      <c r="D132" s="3" t="n">
+      <c r="D132" s="6" t="n">
         <v>2.26008558</v>
       </c>
       <c r="E132" t="n">
@@ -3391,10 +3307,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C133" s="2" t="n">
+      <c r="C133" s="5" t="n">
         <v>233512.15</v>
       </c>
-      <c r="D133" s="3" t="n">
+      <c r="D133" s="6" t="n">
         <v>49.58956523</v>
       </c>
       <c r="E133" t="n">
@@ -3412,10 +3328,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C134" s="2" t="n">
+      <c r="C134" s="5" t="n">
         <v>2894.67</v>
       </c>
-      <c r="D134" s="3" t="n">
+      <c r="D134" s="6" t="n">
         <v>0.84868485</v>
       </c>
       <c r="E134" t="n">
@@ -3433,10 +3349,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C135" s="2" t="n">
+      <c r="C135" s="5" t="n">
         <v>2112.75</v>
       </c>
-      <c r="D135" s="3" t="n">
+      <c r="D135" s="6" t="n">
         <v>0.61943465</v>
       </c>
       <c r="E135" t="n">
@@ -3454,10 +3370,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C136" s="2" t="n">
+      <c r="C136" s="5" t="n">
         <v>133738.48</v>
       </c>
-      <c r="D136" s="3" t="n">
+      <c r="D136" s="6" t="n">
         <v>39.21062549</v>
       </c>
       <c r="E136" t="n">
@@ -3475,10 +3391,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C137" s="2" t="n">
+      <c r="C137" s="5" t="n">
         <v>9278.84</v>
       </c>
-      <c r="D137" s="3" t="n">
+      <c r="D137" s="6" t="n">
         <v>2.72045204</v>
       </c>
       <c r="E137" t="n">
@@ -3496,10 +3412,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C138" s="2" t="n">
+      <c r="C138" s="5" t="n">
         <v>193052.4</v>
       </c>
-      <c r="D138" s="3" t="n">
+      <c r="D138" s="6" t="n">
         <v>56.60080297</v>
       </c>
       <c r="E138" t="n">
@@ -3517,10 +3433,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C139" s="2" t="n">
+      <c r="C139" s="5" t="n">
         <v>138.16</v>
       </c>
-      <c r="D139" s="3" t="n">
+      <c r="D139" s="6" t="n">
         <v>0.04037037</v>
       </c>
       <c r="E139" t="n">
@@ -3538,10 +3454,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C140" s="2" t="n">
+      <c r="C140" s="5" t="n">
         <v>165616.96</v>
       </c>
-      <c r="D140" s="3" t="n">
+      <c r="D140" s="6" t="n">
         <v>48.39329811</v>
       </c>
       <c r="E140" t="n">
@@ -3559,10 +3475,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C141" s="2" t="n">
+      <c r="C141" s="5" t="n">
         <v>14589.85</v>
       </c>
-      <c r="D141" s="3" t="n">
+      <c r="D141" s="6" t="n">
         <v>4.26315614</v>
       </c>
       <c r="E141" t="n">
@@ -3580,10 +3496,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C142" s="2" t="n">
+      <c r="C142" s="5" t="n">
         <v>161886.22</v>
       </c>
-      <c r="D142" s="3" t="n">
+      <c r="D142" s="6" t="n">
         <v>47.30317538</v>
       </c>
       <c r="E142" t="n">
@@ -3601,10 +3517,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C143" s="2" t="n">
+      <c r="C143" s="5" t="n">
         <v>39179.97</v>
       </c>
-      <c r="D143" s="3" t="n">
+      <c r="D143" s="6" t="n">
         <v>6.57522763</v>
       </c>
       <c r="E143" t="n">
@@ -3622,10 +3538,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C144" s="2" t="n">
+      <c r="C144" s="5" t="n">
         <v>142325.87</v>
       </c>
-      <c r="D144" s="3" t="n">
+      <c r="D144" s="6" t="n">
         <v>23.88529122</v>
       </c>
       <c r="E144" t="n">
@@ -3643,10 +3559,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C145" s="2" t="n">
+      <c r="C145" s="5" t="n">
         <v>16620.71</v>
       </c>
-      <c r="D145" s="3" t="n">
+      <c r="D145" s="6" t="n">
         <v>2.78930667</v>
       </c>
       <c r="E145" t="n">
@@ -3664,10 +3580,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C146" s="2" t="n">
+      <c r="C146" s="5" t="n">
         <v>397745.9</v>
       </c>
-      <c r="D146" s="3" t="n">
+      <c r="D146" s="6" t="n">
         <v>66.75017447</v>
       </c>
       <c r="E146" t="n">
@@ -3685,10 +3601,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C147" s="2" t="n">
+      <c r="C147" s="5" t="n">
         <v>1244.23</v>
       </c>
-      <c r="D147" s="3" t="n">
+      <c r="D147" s="6" t="n">
         <v>0.42616348</v>
       </c>
       <c r="E147" t="n">
@@ -3706,10 +3622,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C148" s="2" t="n">
+      <c r="C148" s="5" t="n">
         <v>4545.45</v>
       </c>
-      <c r="D148" s="3" t="n">
+      <c r="D148" s="6" t="n">
         <v>1.55687034</v>
       </c>
       <c r="E148" t="n">
@@ -3727,10 +3643,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C149" s="2" t="n">
+      <c r="C149" s="5" t="n">
         <v>54421.47</v>
       </c>
-      <c r="D149" s="3" t="n">
+      <c r="D149" s="6" t="n">
         <v>18.63999655</v>
       </c>
       <c r="E149" t="n">
@@ -3748,10 +3664,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C150" s="2" t="n">
+      <c r="C150" s="5" t="n">
         <v>231749.58</v>
       </c>
-      <c r="D150" s="3" t="n">
+      <c r="D150" s="6" t="n">
         <v>79.37696964</v>
       </c>
       <c r="E150" t="n">
@@ -3769,10 +3685,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C151" s="2" t="n">
+      <c r="C151" s="5" t="n">
         <v>29.6</v>
       </c>
-      <c r="D151" s="3" t="n">
+      <c r="D151" s="6" t="n">
         <v>0.00689719</v>
       </c>
       <c r="E151" t="n">
@@ -3790,10 +3706,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C152" s="2" t="n">
+      <c r="C152" s="5" t="n">
         <v>309.27</v>
       </c>
-      <c r="D152" s="3" t="n">
+      <c r="D152" s="6" t="n">
         <v>0.07206398</v>
       </c>
       <c r="E152" t="n">
@@ -3811,10 +3727,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C153" s="2" t="n">
+      <c r="C153" s="5" t="n">
         <v>3725.16</v>
       </c>
-      <c r="D153" s="3" t="n">
+      <c r="D153" s="6" t="n">
         <v>0.8680113</v>
       </c>
       <c r="E153" t="n">
@@ -3832,10 +3748,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C154" s="2" t="n">
+      <c r="C154" s="5" t="n">
         <v>8.109999999999999</v>
       </c>
-      <c r="D154" s="3" t="n">
+      <c r="D154" s="6" t="n">
         <v>0.00188974</v>
       </c>
       <c r="E154" t="n">
@@ -3853,10 +3769,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C155" s="2" t="n">
+      <c r="C155" s="5" t="n">
         <v>163136.27</v>
       </c>
-      <c r="D155" s="3" t="n">
+      <c r="D155" s="6" t="n">
         <v>38.01289779</v>
       </c>
       <c r="E155" t="n">
@@ -3874,10 +3790,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C156" s="2" t="n">
+      <c r="C156" s="5" t="n">
         <v>261951.9</v>
       </c>
-      <c r="D156" s="3" t="n">
+      <c r="D156" s="6" t="n">
         <v>61.03824</v>
       </c>
       <c r="E156" t="n">
@@ -3895,10 +3811,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C157" s="2" t="n">
+      <c r="C157" s="5" t="n">
         <v>55.55</v>
       </c>
-      <c r="D157" s="3" t="n">
+      <c r="D157" s="6" t="n">
         <v>0.01644298</v>
       </c>
       <c r="E157" t="n">
@@ -3916,10 +3832,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C158" s="2" t="n">
+      <c r="C158" s="5" t="n">
         <v>91.41</v>
       </c>
-      <c r="D158" s="3" t="n">
+      <c r="D158" s="6" t="n">
         <v>0.02705766</v>
       </c>
       <c r="E158" t="n">
@@ -3937,10 +3853,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C159" s="2" t="n">
+      <c r="C159" s="5" t="n">
         <v>5382.13</v>
       </c>
-      <c r="D159" s="3" t="n">
+      <c r="D159" s="6" t="n">
         <v>1.59312834</v>
       </c>
       <c r="E159" t="n">
@@ -3958,10 +3874,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C160" s="2" t="n">
+      <c r="C160" s="5" t="n">
         <v>909.09</v>
       </c>
-      <c r="D160" s="3" t="n">
+      <c r="D160" s="6" t="n">
         <v>0.26909366</v>
       </c>
       <c r="E160" t="n">
@@ -3979,10 +3895,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C161" s="2" t="n">
+      <c r="C161" s="5" t="n">
         <v>32670.17</v>
       </c>
-      <c r="D161" s="3" t="n">
+      <c r="D161" s="6" t="n">
         <v>9.670478749999999</v>
       </c>
       <c r="E161" t="n">
@@ -4000,10 +3916,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C162" s="2" t="n">
+      <c r="C162" s="5" t="n">
         <v>298725.7</v>
       </c>
-      <c r="D162" s="3" t="n">
+      <c r="D162" s="6" t="n">
         <v>88.42379861000001</v>
       </c>
       <c r="E162" t="n">
@@ -4021,10 +3937,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C163" s="2" t="n">
+      <c r="C163" s="5" t="n">
         <v>287.66</v>
       </c>
-      <c r="D163" s="3" t="n">
+      <c r="D163" s="6" t="n">
         <v>0.08204844999999999</v>
       </c>
       <c r="E163" t="n">
@@ -4042,10 +3958,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C164" s="2" t="n">
+      <c r="C164" s="5" t="n">
         <v>9919.66</v>
       </c>
-      <c r="D164" s="3" t="n">
+      <c r="D164" s="6" t="n">
         <v>2.82935676</v>
       </c>
       <c r="E164" t="n">
@@ -4063,10 +3979,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C165" s="2" t="n">
+      <c r="C165" s="5" t="n">
         <v>1385.01</v>
       </c>
-      <c r="D165" s="3" t="n">
+      <c r="D165" s="6" t="n">
         <v>0.39504251</v>
       </c>
       <c r="E165" t="n">
@@ -4084,10 +4000,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C166" s="2" t="n">
+      <c r="C166" s="5" t="n">
         <v>69940.2</v>
       </c>
-      <c r="D166" s="3" t="n">
+      <c r="D166" s="6" t="n">
         <v>19.94884679</v>
       </c>
       <c r="E166" t="n">
@@ -4105,10 +4021,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C167" s="2" t="n">
+      <c r="C167" s="5" t="n">
         <v>269065.18</v>
       </c>
-      <c r="D167" s="3" t="n">
+      <c r="D167" s="6" t="n">
         <v>76.74470549</v>
       </c>
       <c r="E167" t="n">
@@ -4126,10 +4042,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C168" s="2" t="n">
+      <c r="C168" s="5" t="n">
         <v>580.2</v>
       </c>
-      <c r="D168" s="3" t="n">
+      <c r="D168" s="6" t="n">
         <v>0.1561468</v>
       </c>
       <c r="E168" t="n">
@@ -4147,10 +4063,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C169" s="2" t="n">
+      <c r="C169" s="5" t="n">
         <v>98.44</v>
       </c>
-      <c r="D169" s="3" t="n">
+      <c r="D169" s="6" t="n">
         <v>0.02649275</v>
       </c>
       <c r="E169" t="n">
@@ -4168,10 +4084,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C170" s="2" t="n">
+      <c r="C170" s="5" t="n">
         <v>172.72</v>
       </c>
-      <c r="D170" s="3" t="n">
+      <c r="D170" s="6" t="n">
         <v>0.04648341</v>
       </c>
       <c r="E170" t="n">
@@ -4189,10 +4105,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C171" s="2" t="n">
+      <c r="C171" s="5" t="n">
         <v>3342.15</v>
       </c>
-      <c r="D171" s="3" t="n">
+      <c r="D171" s="6" t="n">
         <v>0.89945887</v>
       </c>
       <c r="E171" t="n">
@@ -4210,10 +4126,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C172" s="2" t="n">
+      <c r="C172" s="5" t="n">
         <v>7627.33</v>
       </c>
-      <c r="D172" s="3" t="n">
+      <c r="D172" s="6" t="n">
         <v>2.05271147</v>
       </c>
       <c r="E172" t="n">
@@ -4231,10 +4147,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C173" s="2" t="n">
+      <c r="C173" s="5" t="n">
         <v>359752.57</v>
       </c>
-      <c r="D173" s="3" t="n">
+      <c r="D173" s="6" t="n">
         <v>96.81870670000001</v>
       </c>
       <c r="E173" t="n">
@@ -4252,10 +4168,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C174" s="2" t="n">
+      <c r="C174" s="5" t="n">
         <v>61.94</v>
       </c>
-      <c r="D174" s="3" t="n">
+      <c r="D174" s="6" t="n">
         <v>0.02167129</v>
       </c>
       <c r="E174" t="n">
@@ -4273,10 +4189,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C175" s="2" t="n">
+      <c r="C175" s="5" t="n">
         <v>222</v>
       </c>
-      <c r="D175" s="3" t="n">
+      <c r="D175" s="6" t="n">
         <v>0.07767236</v>
       </c>
       <c r="E175" t="n">
@@ -4294,10 +4210,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C176" s="2" t="n">
+      <c r="C176" s="5" t="n">
         <v>10426.45</v>
       </c>
-      <c r="D176" s="3" t="n">
+      <c r="D176" s="6" t="n">
         <v>3.64795946</v>
       </c>
       <c r="E176" t="n">
@@ -4315,10 +4231,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C177" s="2" t="n">
+      <c r="C177" s="5" t="n">
         <v>36051.27</v>
       </c>
-      <c r="D177" s="3" t="n">
+      <c r="D177" s="6" t="n">
         <v>12.61345632</v>
       </c>
       <c r="E177" t="n">
@@ -4336,10 +4252,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C178" s="2" t="n">
+      <c r="C178" s="5" t="n">
         <v>239054.29</v>
       </c>
-      <c r="D178" s="3" t="n">
+      <c r="D178" s="6" t="n">
         <v>83.63924057</v>
       </c>
       <c r="E178" t="n">
@@ -4357,10 +4273,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C179" s="2" t="n">
+      <c r="C179" s="5" t="n">
         <v>1971.96</v>
       </c>
-      <c r="D179" s="3" t="n">
+      <c r="D179" s="6" t="n">
         <v>0.29536296</v>
       </c>
       <c r="E179" t="n">
@@ -4378,10 +4294,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C180" s="2" t="n">
+      <c r="C180" s="5" t="n">
         <v>970.1799999999999</v>
       </c>
-      <c r="D180" s="3" t="n">
+      <c r="D180" s="6" t="n">
         <v>0.14531493</v>
       </c>
       <c r="E180" t="n">
@@ -4399,10 +4315,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C181" s="2" t="n">
+      <c r="C181" s="5" t="n">
         <v>23400.38</v>
       </c>
-      <c r="D181" s="3" t="n">
+      <c r="D181" s="6" t="n">
         <v>3.50494199</v>
       </c>
       <c r="E181" t="n">
@@ -4420,10 +4336,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C182" s="2" t="n">
+      <c r="C182" s="5" t="n">
         <v>158698.51</v>
       </c>
-      <c r="D182" s="3" t="n">
+      <c r="D182" s="6" t="n">
         <v>23.77008715</v>
       </c>
       <c r="E182" t="n">
@@ -4441,10 +4357,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C183" s="2" t="n">
+      <c r="C183" s="5" t="n">
         <v>482598.55</v>
       </c>
-      <c r="D183" s="3" t="n">
+      <c r="D183" s="6" t="n">
         <v>72.28429297</v>
       </c>
       <c r="E183" t="n">
@@ -4462,10 +4378,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C184" s="2" t="n">
+      <c r="C184" s="5" t="n">
         <v>349.42</v>
       </c>
-      <c r="D184" s="3" t="n">
+      <c r="D184" s="6" t="n">
         <v>0.0757804</v>
       </c>
       <c r="E184" t="n">
@@ -4483,10 +4399,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C185" s="2" t="n">
+      <c r="C185" s="5" t="n">
         <v>5203.15</v>
       </c>
-      <c r="D185" s="3" t="n">
+      <c r="D185" s="6" t="n">
         <v>1.12843225</v>
       </c>
       <c r="E185" t="n">
@@ -4504,10 +4420,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C186" s="2" t="n">
+      <c r="C186" s="5" t="n">
         <v>43002.78</v>
       </c>
-      <c r="D186" s="3" t="n">
+      <c r="D186" s="6" t="n">
         <v>9.326220449999999</v>
       </c>
       <c r="E186" t="n">
@@ -4525,10 +4441,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C187" s="2" t="n">
+      <c r="C187" s="5" t="n">
         <v>412540.12</v>
       </c>
-      <c r="D187" s="3" t="n">
+      <c r="D187" s="6" t="n">
         <v>89.4695669</v>
       </c>
       <c r="E187" t="n">
@@ -4546,10 +4462,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C188" s="2" t="n">
+      <c r="C188" s="5" t="n">
         <v>1231.47</v>
       </c>
-      <c r="D188" s="3" t="n">
+      <c r="D188" s="6" t="n">
         <v>0.34199572</v>
       </c>
       <c r="E188" t="n">
@@ -4567,10 +4483,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C189" s="2" t="n">
+      <c r="C189" s="5" t="n">
         <v>484.18</v>
       </c>
-      <c r="D189" s="3" t="n">
+      <c r="D189" s="6" t="n">
         <v>0.13446328</v>
       </c>
       <c r="E189" t="n">
@@ -4588,10 +4504,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C190" s="2" t="n">
+      <c r="C190" s="5" t="n">
         <v>29461.66</v>
       </c>
-      <c r="D190" s="3" t="n">
+      <c r="D190" s="6" t="n">
         <v>8.18189784</v>
       </c>
       <c r="E190" t="n">
@@ -4609,10 +4525,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C191" s="2" t="n">
+      <c r="C191" s="5" t="n">
         <v>328906.14</v>
       </c>
-      <c r="D191" s="3" t="n">
+      <c r="D191" s="6" t="n">
         <v>91.34164317</v>
       </c>
       <c r="E191" t="n">
@@ -4630,10 +4546,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C192" s="2" t="n">
+      <c r="C192" s="5" t="n">
         <v>23.47</v>
       </c>
-      <c r="D192" s="3" t="n">
+      <c r="D192" s="6" t="n">
         <v>0.00471838</v>
       </c>
       <c r="E192" t="n">
@@ -4651,10 +4567,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C193" s="2" t="n">
+      <c r="C193" s="5" t="n">
         <v>13128.29</v>
       </c>
-      <c r="D193" s="3" t="n">
+      <c r="D193" s="6" t="n">
         <v>2.63929312</v>
       </c>
       <c r="E193" t="n">
@@ -4672,10 +4588,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C194" s="2" t="n">
+      <c r="C194" s="5" t="n">
         <v>42522.52</v>
       </c>
-      <c r="D194" s="3" t="n">
+      <c r="D194" s="6" t="n">
         <v>8.548668129999999</v>
       </c>
       <c r="E194" t="n">
@@ -4693,10 +4609,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C195" s="2" t="n">
+      <c r="C195" s="5" t="n">
         <v>441742.62</v>
       </c>
-      <c r="D195" s="3" t="n">
+      <c r="D195" s="6" t="n">
         <v>88.80732037999999</v>
       </c>
       <c r="E195" t="n">
@@ -4714,10 +4630,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C196" s="2" t="n">
+      <c r="C196" s="5" t="n">
         <v>14510.35</v>
       </c>
-      <c r="D196" s="3" t="n">
+      <c r="D196" s="6" t="n">
         <v>2.82318771</v>
       </c>
       <c r="E196" t="n">
@@ -4735,10 +4651,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C197" s="2" t="n">
+      <c r="C197" s="5" t="n">
         <v>29796.3</v>
       </c>
-      <c r="D197" s="3" t="n">
+      <c r="D197" s="6" t="n">
         <v>5.79727904</v>
       </c>
       <c r="E197" t="n">
@@ -4756,10 +4672,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C198" s="2" t="n">
+      <c r="C198" s="5" t="n">
         <v>489.48</v>
       </c>
-      <c r="D198" s="3" t="n">
+      <c r="D198" s="6" t="n">
         <v>0.09523505</v>
       </c>
       <c r="E198" t="n">
@@ -4777,10 +4693,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C199" s="2" t="n">
+      <c r="C199" s="5" t="n">
         <v>45623.94</v>
       </c>
-      <c r="D199" s="3" t="n">
+      <c r="D199" s="6" t="n">
         <v>8.876763589999999</v>
       </c>
       <c r="E199" t="n">
@@ -4798,10 +4714,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C200" s="2" t="n">
+      <c r="C200" s="5" t="n">
         <v>423550.36</v>
       </c>
-      <c r="D200" s="3" t="n">
+      <c r="D200" s="6" t="n">
         <v>82.40753461</v>
       </c>
       <c r="E200" t="n">
@@ -4819,10 +4735,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C201" s="2" t="n">
+      <c r="C201" s="5" t="n">
         <v>2894.83</v>
       </c>
-      <c r="D201" s="3" t="n">
+      <c r="D201" s="6" t="n">
         <v>0.57425271</v>
       </c>
       <c r="E201" t="n">
@@ -4840,10 +4756,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C202" s="2" t="n">
+      <c r="C202" s="5" t="n">
         <v>19389.84</v>
       </c>
-      <c r="D202" s="3" t="n">
+      <c r="D202" s="6" t="n">
         <v>3.84639792</v>
       </c>
       <c r="E202" t="n">
@@ -4861,10 +4777,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C203" s="2" t="n">
+      <c r="C203" s="5" t="n">
         <v>7103.09</v>
       </c>
-      <c r="D203" s="3" t="n">
+      <c r="D203" s="6" t="n">
         <v>1.40905292</v>
       </c>
       <c r="E203" t="n">
@@ -4882,10 +4798,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C204" s="2" t="n">
+      <c r="C204" s="5" t="n">
         <v>71555.96000000001</v>
       </c>
-      <c r="D204" s="3" t="n">
+      <c r="D204" s="6" t="n">
         <v>14.19468627</v>
       </c>
       <c r="E204" t="n">
@@ -4903,10 +4819,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C205" s="2" t="n">
+      <c r="C205" s="5" t="n">
         <v>403160.13</v>
       </c>
-      <c r="D205" s="3" t="n">
+      <c r="D205" s="6" t="n">
         <v>79.97561018</v>
       </c>
       <c r="E205" t="n">
@@ -4924,10 +4840,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C206" s="2" t="n">
+      <c r="C206" s="5" t="n">
         <v>13873.76</v>
       </c>
-      <c r="D206" s="3" t="n">
+      <c r="D206" s="6" t="n">
         <v>4.61749343</v>
       </c>
       <c r="E206" t="n">
@@ -4945,10 +4861,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C207" s="2" t="n">
+      <c r="C207" s="5" t="n">
         <v>5637.21</v>
       </c>
-      <c r="D207" s="3" t="n">
+      <c r="D207" s="6" t="n">
         <v>1.87618786</v>
       </c>
       <c r="E207" t="n">
@@ -4966,10 +4882,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C208" s="2" t="n">
+      <c r="C208" s="5" t="n">
         <v>1363.63</v>
       </c>
-      <c r="D208" s="3" t="n">
+      <c r="D208" s="6" t="n">
         <v>0.45384615</v>
       </c>
       <c r="E208" t="n">
@@ -4987,10 +4903,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C209" s="2" t="n">
+      <c r="C209" s="5" t="n">
         <v>35429.67</v>
       </c>
-      <c r="D209" s="3" t="n">
+      <c r="D209" s="6" t="n">
         <v>11.79177587</v>
       </c>
       <c r="E209" t="n">
@@ -5008,10 +4924,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C210" s="2" t="n">
+      <c r="C210" s="5" t="n">
         <v>244156.58</v>
       </c>
-      <c r="D210" s="3" t="n">
+      <c r="D210" s="6" t="n">
         <v>81.26069669</v>
       </c>
       <c r="E210" t="n">
@@ -5029,10 +4945,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C211" s="2" t="n">
+      <c r="C211" s="5" t="n">
         <v>3194.31</v>
       </c>
-      <c r="D211" s="3" t="n">
+      <c r="D211" s="6" t="n">
         <v>0.86754762</v>
       </c>
       <c r="E211" t="n">
@@ -5050,10 +4966,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C212" s="2" t="n">
+      <c r="C212" s="5" t="n">
         <v>53332.81</v>
       </c>
-      <c r="D212" s="3" t="n">
+      <c r="D212" s="6" t="n">
         <v>14.48474085</v>
       </c>
       <c r="E212" t="n">
@@ -5071,10 +4987,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C213" s="2" t="n">
+      <c r="C213" s="5" t="n">
         <v>5480.02</v>
       </c>
-      <c r="D213" s="3" t="n">
+      <c r="D213" s="6" t="n">
         <v>1.48832716</v>
       </c>
       <c r="E213" t="n">
@@ -5092,10 +5008,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C214" s="2" t="n">
+      <c r="C214" s="5" t="n">
         <v>54619.67</v>
       </c>
-      <c r="D214" s="3" t="n">
+      <c r="D214" s="6" t="n">
         <v>14.83424116</v>
       </c>
       <c r="E214" t="n">
@@ -5113,10 +5029,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C215" s="2" t="n">
+      <c r="C215" s="5" t="n">
         <v>251573.15</v>
       </c>
-      <c r="D215" s="3" t="n">
+      <c r="D215" s="6" t="n">
         <v>68.32514322</v>
       </c>
       <c r="E215" t="n">
@@ -5134,10 +5050,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C216" s="2" t="n">
+      <c r="C216" s="5" t="n">
         <v>892</v>
       </c>
-      <c r="D216" s="3" t="n">
+      <c r="D216" s="6" t="n">
         <v>0.30548187</v>
       </c>
       <c r="E216" t="n">
@@ -5155,10 +5071,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C217" s="2" t="n">
+      <c r="C217" s="5" t="n">
         <v>7918.09</v>
       </c>
-      <c r="D217" s="3" t="n">
+      <c r="D217" s="6" t="n">
         <v>2.71169611</v>
       </c>
       <c r="E217" t="n">
@@ -5176,10 +5092,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C218" s="2" t="n">
+      <c r="C218" s="5" t="n">
         <v>37.66</v>
       </c>
-      <c r="D218" s="3" t="n">
+      <c r="D218" s="6" t="n">
         <v>0.01289736</v>
       </c>
       <c r="E218" t="n">
@@ -5197,10 +5113,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C219" s="2" t="n">
+      <c r="C219" s="5" t="n">
         <v>14209.15</v>
       </c>
-      <c r="D219" s="3" t="n">
+      <c r="D219" s="6" t="n">
         <v>4.86618576</v>
       </c>
       <c r="E219" t="n">
@@ -5218,10 +5134,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C220" s="2" t="n">
+      <c r="C220" s="5" t="n">
         <v>268940.79</v>
       </c>
-      <c r="D220" s="3" t="n">
+      <c r="D220" s="6" t="n">
         <v>92.1037389</v>
       </c>
       <c r="E220" t="n">
@@ -5239,10 +5155,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C221" s="2" t="n">
+      <c r="C221" s="5" t="n">
         <v>287</v>
       </c>
-      <c r="D221" s="3" t="n">
+      <c r="D221" s="6" t="n">
         <v>0.07919683</v>
       </c>
       <c r="E221" t="n">
@@ -5260,10 +5176,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C222" s="2" t="n">
+      <c r="C222" s="5" t="n">
         <v>17982.75</v>
       </c>
-      <c r="D222" s="3" t="n">
+      <c r="D222" s="6" t="n">
         <v>4.96228879</v>
       </c>
       <c r="E222" t="n">
@@ -5281,10 +5197,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C223" s="2" t="n">
+      <c r="C223" s="5" t="n">
         <v>2603.68</v>
       </c>
-      <c r="D223" s="3" t="n">
+      <c r="D223" s="6" t="n">
         <v>0.7184781</v>
       </c>
       <c r="E223" t="n">
@@ -5302,10 +5218,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C224" s="2" t="n">
+      <c r="C224" s="5" t="n">
         <v>34911.64</v>
       </c>
-      <c r="D224" s="3" t="n">
+      <c r="D224" s="6" t="n">
         <v>9.6337679</v>
       </c>
       <c r="E224" t="n">
@@ -5323,10 +5239,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C225" s="2" t="n">
+      <c r="C225" s="5" t="n">
         <v>306603.15</v>
       </c>
-      <c r="D225" s="3" t="n">
+      <c r="D225" s="6" t="n">
         <v>84.60626838</v>
       </c>
       <c r="E225" t="n">
@@ -5344,10 +5260,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C226" s="2" t="n">
+      <c r="C226" s="5" t="n">
         <v>1099.13</v>
       </c>
-      <c r="D226" s="3" t="n">
+      <c r="D226" s="6" t="n">
         <v>0.35003695</v>
       </c>
       <c r="E226" t="n">
@@ -5365,10 +5281,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C227" s="2" t="n">
+      <c r="C227" s="5" t="n">
         <v>1908.13</v>
       </c>
-      <c r="D227" s="3" t="n">
+      <c r="D227" s="6" t="n">
         <v>0.60767699</v>
       </c>
       <c r="E227" t="n">
@@ -5386,10 +5302,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C228" s="2" t="n">
+      <c r="C228" s="5" t="n">
         <v>1788.1</v>
       </c>
-      <c r="D228" s="3" t="n">
+      <c r="D228" s="6" t="n">
         <v>0.56945136</v>
       </c>
       <c r="E228" t="n">
@@ -5407,10 +5323,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C229" s="2" t="n">
+      <c r="C229" s="5" t="n">
         <v>54065.52</v>
       </c>
-      <c r="D229" s="3" t="n">
+      <c r="D229" s="6" t="n">
         <v>17.21809968</v>
       </c>
       <c r="E229" t="n">
@@ -5428,10 +5344,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C230" s="2" t="n">
+      <c r="C230" s="5" t="n">
         <v>255143.11</v>
       </c>
-      <c r="D230" s="3" t="n">
+      <c r="D230" s="6" t="n">
         <v>81.25473501</v>
       </c>
       <c r="E230" t="n">
@@ -5449,10 +5365,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C231" s="2" t="n">
+      <c r="C231" s="5" t="n">
         <v>2988.23</v>
       </c>
-      <c r="D231" s="3" t="n">
+      <c r="D231" s="6" t="n">
         <v>1.09502707</v>
       </c>
       <c r="E231" t="n">
@@ -5470,10 +5386,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C232" s="2" t="n">
+      <c r="C232" s="5" t="n">
         <v>89030.31</v>
       </c>
-      <c r="D232" s="3" t="n">
+      <c r="D232" s="6" t="n">
         <v>32.62486479</v>
       </c>
       <c r="E232" t="n">
@@ -5491,10 +5407,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C233" s="2" t="n">
+      <c r="C233" s="5" t="n">
         <v>180872.43</v>
       </c>
-      <c r="D233" s="3" t="n">
+      <c r="D233" s="6" t="n">
         <v>66.28010813</v>
       </c>
       <c r="E233" t="n">
@@ -5512,10 +5428,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C234" s="2" t="n">
+      <c r="C234" s="5" t="n">
         <v>232.92</v>
       </c>
-      <c r="D234" s="3" t="n">
+      <c r="D234" s="6" t="n">
         <v>0.10614272</v>
       </c>
       <c r="E234" t="n">
@@ -5533,10 +5449,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C235" s="2" t="n">
+      <c r="C235" s="5" t="n">
         <v>27443.48</v>
       </c>
-      <c r="D235" s="3" t="n">
+      <c r="D235" s="6" t="n">
         <v>12.50612011</v>
       </c>
       <c r="E235" t="n">
@@ -5554,10 +5470,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C236" s="2" t="n">
+      <c r="C236" s="5" t="n">
         <v>66453.41</v>
       </c>
-      <c r="D236" s="3" t="n">
+      <c r="D236" s="6" t="n">
         <v>30.28312471</v>
       </c>
       <c r="E236" t="n">
@@ -5575,10 +5491,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C237" s="2" t="n">
+      <c r="C237" s="5" t="n">
         <v>125310.59</v>
       </c>
-      <c r="D237" s="3" t="n">
+      <c r="D237" s="6" t="n">
         <v>57.10461246</v>
       </c>
       <c r="E237" t="n">
@@ -5596,10 +5512,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C238" s="2" t="n">
+      <c r="C238" s="5" t="n">
         <v>12206.63</v>
       </c>
-      <c r="D238" s="3" t="n">
+      <c r="D238" s="6" t="n">
         <v>2.80910278</v>
       </c>
       <c r="E238" t="n">
@@ -5617,10 +5533,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C239" s="2" t="n">
+      <c r="C239" s="5" t="n">
         <v>14439.81</v>
       </c>
-      <c r="D239" s="3" t="n">
+      <c r="D239" s="6" t="n">
         <v>3.32302285</v>
       </c>
       <c r="E239" t="n">
@@ -5638,10 +5554,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C240" s="2" t="n">
+      <c r="C240" s="5" t="n">
         <v>73404.17</v>
       </c>
-      <c r="D240" s="3" t="n">
+      <c r="D240" s="6" t="n">
         <v>16.89244764</v>
       </c>
       <c r="E240" t="n">
@@ -5659,10 +5575,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C241" s="2" t="n">
+      <c r="C241" s="5" t="n">
         <v>334487.78</v>
       </c>
-      <c r="D241" s="3" t="n">
+      <c r="D241" s="6" t="n">
         <v>76.97542673</v>
       </c>
       <c r="E241" t="n">
@@ -5680,10 +5596,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C242" s="2" t="n">
+      <c r="C242" s="5" t="n">
         <v>4414.12</v>
       </c>
-      <c r="D242" s="3" t="n">
+      <c r="D242" s="6" t="n">
         <v>2.02734127</v>
       </c>
       <c r="E242" t="n">
@@ -5701,10 +5617,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C243" s="2" t="n">
+      <c r="C243" s="5" t="n">
         <v>206.75</v>
       </c>
-      <c r="D243" s="3" t="n">
+      <c r="D243" s="6" t="n">
         <v>0.09495727</v>
       </c>
       <c r="E243" t="n">
@@ -5722,10 +5638,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C244" s="2" t="n">
+      <c r="C244" s="5" t="n">
         <v>6938.86</v>
       </c>
-      <c r="D244" s="3" t="n">
+      <c r="D244" s="6" t="n">
         <v>3.18691771</v>
       </c>
       <c r="E244" t="n">
@@ -5743,10 +5659,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C245" s="2" t="n">
+      <c r="C245" s="5" t="n">
         <v>206169.77</v>
       </c>
-      <c r="D245" s="3" t="n">
+      <c r="D245" s="6" t="n">
         <v>94.69078374999999</v>
       </c>
       <c r="E245" t="n">
@@ -5764,10 +5680,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C246" s="2" t="n">
+      <c r="C246" s="5" t="n">
         <v>45195.76</v>
       </c>
-      <c r="D246" s="3" t="n">
+      <c r="D246" s="6" t="n">
         <v>10.41762819</v>
       </c>
       <c r="E246" t="n">
@@ -5785,10 +5701,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C247" s="2" t="n">
+      <c r="C247" s="5" t="n">
         <v>9882.6</v>
       </c>
-      <c r="D247" s="3" t="n">
+      <c r="D247" s="6" t="n">
         <v>2.2779405</v>
       </c>
       <c r="E247" t="n">
@@ -5806,10 +5722,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C248" s="2" t="n">
+      <c r="C248" s="5" t="n">
         <v>305.19</v>
       </c>
-      <c r="D248" s="3" t="n">
+      <c r="D248" s="6" t="n">
         <v>0.07034633</v>
       </c>
       <c r="E248" t="n">
@@ -5827,10 +5743,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C249" s="2" t="n">
+      <c r="C249" s="5" t="n">
         <v>9384.76</v>
       </c>
-      <c r="D249" s="3" t="n">
+      <c r="D249" s="6" t="n">
         <v>2.16318832</v>
       </c>
       <c r="E249" t="n">
@@ -5848,10 +5764,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C250" s="2" t="n">
+      <c r="C250" s="5" t="n">
         <v>369070.94</v>
       </c>
-      <c r="D250" s="3" t="n">
+      <c r="D250" s="6" t="n">
         <v>85.07089664999999</v>
       </c>
       <c r="E250" t="n">
@@ -5869,10 +5785,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C251" s="2" t="n">
+      <c r="C251" s="5" t="n">
         <v>387.59</v>
       </c>
-      <c r="D251" s="3" t="n">
+      <c r="D251" s="6" t="n">
         <v>0.10977502</v>
       </c>
       <c r="E251" t="n">
@@ -5890,10 +5806,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C252" s="2" t="n">
+      <c r="C252" s="5" t="n">
         <v>3000</v>
       </c>
-      <c r="D252" s="3" t="n">
+      <c r="D252" s="6" t="n">
         <v>0.84967379</v>
       </c>
       <c r="E252" t="n">
@@ -5911,10 +5827,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C253" s="2" t="n">
+      <c r="C253" s="5" t="n">
         <v>114879.27</v>
       </c>
-      <c r="D253" s="3" t="n">
+      <c r="D253" s="6" t="n">
         <v>32.53663482</v>
       </c>
       <c r="E253" t="n">
@@ -5932,10 +5848,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C254" s="2" t="n">
+      <c r="C254" s="5" t="n">
         <v>234809.82</v>
       </c>
-      <c r="D254" s="3" t="n">
+      <c r="D254" s="6" t="n">
         <v>66.50391637</v>
       </c>
       <c r="E254" t="n">
@@ -5953,10 +5869,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C255" s="2" t="n">
+      <c r="C255" s="5" t="n">
         <v>8859.66</v>
       </c>
-      <c r="D255" s="3" t="n">
+      <c r="D255" s="6" t="n">
         <v>5.34081687</v>
       </c>
       <c r="E255" t="n">
@@ -5974,10 +5890,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C256" s="2" t="n">
+      <c r="C256" s="5" t="n">
         <v>1006.9</v>
       </c>
-      <c r="D256" s="3" t="n">
+      <c r="D256" s="6" t="n">
         <v>0.6069836199999999</v>
       </c>
       <c r="E256" t="n">
@@ -5995,10 +5911,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C257" s="2" t="n">
+      <c r="C257" s="5" t="n">
         <v>1000</v>
       </c>
-      <c r="D257" s="3" t="n">
+      <c r="D257" s="6" t="n">
         <v>0.60282413</v>
       </c>
       <c r="E257" t="n">
@@ -6016,10 +5932,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C258" s="2" t="n">
+      <c r="C258" s="5" t="n">
         <v>51121.7</v>
       </c>
-      <c r="D258" s="3" t="n">
+      <c r="D258" s="6" t="n">
         <v>30.81739456</v>
       </c>
       <c r="E258" t="n">
@@ -6037,10 +5953,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C259" s="2" t="n">
+      <c r="C259" s="5" t="n">
         <v>103897.6</v>
       </c>
-      <c r="D259" s="3" t="n">
+      <c r="D259" s="6" t="n">
         <v>62.63198081</v>
       </c>
       <c r="E259" t="n">
@@ -6058,10 +5974,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C260" s="2" t="n">
+      <c r="C260" s="5" t="n">
         <v>7692.3</v>
       </c>
-      <c r="D260" s="3" t="n">
+      <c r="D260" s="6" t="n">
         <v>6.29078176</v>
       </c>
       <c r="E260" t="n">
@@ -6079,10 +5995,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C261" s="2" t="n">
+      <c r="C261" s="5" t="n">
         <v>1882.73</v>
       </c>
-      <c r="D261" s="3" t="n">
+      <c r="D261" s="6" t="n">
         <v>1.5397012</v>
       </c>
       <c r="E261" t="n">
@@ -6100,10 +6016,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C262" s="2" t="n">
+      <c r="C262" s="5" t="n">
         <v>14869.63</v>
       </c>
-      <c r="D262" s="3" t="n">
+      <c r="D262" s="6" t="n">
         <v>12.1604198</v>
       </c>
       <c r="E262" t="n">
@@ -6121,10 +6037,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C263" s="2" t="n">
+      <c r="C263" s="5" t="n">
         <v>97834.25999999999</v>
       </c>
-      <c r="D263" s="3" t="n">
+      <c r="D263" s="6" t="n">
         <v>80.00909722999999</v>
       </c>
       <c r="E263" t="n">
@@ -6142,10 +6058,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C264" s="2" t="n">
+      <c r="C264" s="5" t="n">
         <v>3303.59</v>
       </c>
-      <c r="D264" s="3" t="n">
+      <c r="D264" s="6" t="n">
         <v>1.27093949</v>
       </c>
       <c r="E264" t="n">
@@ -6163,10 +6079,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C265" s="2" t="n">
+      <c r="C265" s="5" t="n">
         <v>18435.53</v>
       </c>
-      <c r="D265" s="3" t="n">
+      <c r="D265" s="6" t="n">
         <v>7.09241858</v>
       </c>
       <c r="E265" t="n">
@@ -6184,10 +6100,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C266" s="2" t="n">
+      <c r="C266" s="5" t="n">
         <v>2222.22</v>
       </c>
-      <c r="D266" s="3" t="n">
+      <c r="D266" s="6" t="n">
         <v>0.8549206</v>
       </c>
       <c r="E266" t="n">
@@ -6205,10 +6121,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C267" s="2" t="n">
+      <c r="C267" s="5" t="n">
         <v>50871.54</v>
       </c>
-      <c r="D267" s="3" t="n">
+      <c r="D267" s="6" t="n">
         <v>19.571027</v>
       </c>
       <c r="E267" t="n">
@@ -6226,10 +6142,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C268" s="2" t="n">
+      <c r="C268" s="5" t="n">
         <v>185100.03</v>
       </c>
-      <c r="D268" s="3" t="n">
+      <c r="D268" s="6" t="n">
         <v>71.21069433</v>
       </c>
       <c r="E268" t="n">
@@ -6247,10 +6163,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C269" s="2" t="n">
+      <c r="C269" s="5" t="n">
         <v>26854.86</v>
       </c>
-      <c r="D269" s="3" t="n">
+      <c r="D269" s="6" t="n">
         <v>6.60466391</v>
       </c>
       <c r="E269" t="n">
@@ -6268,10 +6184,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="C270" s="2" t="n">
+      <c r="C270" s="5" t="n">
         <v>554.28</v>
       </c>
-      <c r="D270" s="3" t="n">
+      <c r="D270" s="6" t="n">
         <v>0.1363192</v>
       </c>
       <c r="E270" t="n">
@@ -6289,10 +6205,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C271" s="2" t="n">
+      <c r="C271" s="5" t="n">
         <v>487.8</v>
       </c>
-      <c r="D271" s="3" t="n">
+      <c r="D271" s="6" t="n">
         <v>0.11996916</v>
       </c>
       <c r="E271" t="n">
@@ -6310,10 +6226,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C272" s="2" t="n">
+      <c r="C272" s="5" t="n">
         <v>12206.22</v>
       </c>
-      <c r="D272" s="3" t="n">
+      <c r="D272" s="6" t="n">
         <v>3.00198849</v>
       </c>
       <c r="E272" t="n">
@@ -6331,10 +6247,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C273" s="2" t="n">
+      <c r="C273" s="5" t="n">
         <v>28370.02</v>
       </c>
-      <c r="D273" s="3" t="n">
+      <c r="D273" s="6" t="n">
         <v>6.97730121</v>
       </c>
       <c r="E273" t="n">
@@ -6352,10 +6268,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C274" s="2" t="n">
+      <c r="C274" s="5" t="n">
         <v>338131.31</v>
       </c>
-      <c r="D274" s="3" t="n">
+      <c r="D274" s="6" t="n">
         <v>83.15975802</v>
       </c>
       <c r="E274" t="n">
@@ -6373,10 +6289,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C275" s="2" t="n">
+      <c r="C275" s="5" t="n">
         <v>19985.78</v>
       </c>
-      <c r="D275" s="3" t="n">
+      <c r="D275" s="6" t="n">
         <v>7.97052191</v>
       </c>
       <c r="E275" t="n">
@@ -6394,10 +6310,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="C276" s="2" t="n">
+      <c r="C276" s="5" t="n">
         <v>2222.22</v>
       </c>
-      <c r="D276" s="3" t="n">
+      <c r="D276" s="6" t="n">
         <v>0.88624278</v>
       </c>
       <c r="E276" t="n">
@@ -6415,10 +6331,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C277" s="2" t="n">
+      <c r="C277" s="5" t="n">
         <v>4445.7</v>
       </c>
-      <c r="D277" s="3" t="n">
+      <c r="D277" s="6" t="n">
         <v>1.77298806</v>
       </c>
       <c r="E277" t="n">
@@ -6436,10 +6352,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C278" s="2" t="n">
+      <c r="C278" s="5" t="n">
         <v>50514.02</v>
       </c>
-      <c r="D278" s="3" t="n">
+      <c r="D278" s="6" t="n">
         <v>20.14547858</v>
       </c>
       <c r="E278" t="n">
@@ -6457,10 +6373,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C279" s="2" t="n">
+      <c r="C279" s="5" t="n">
         <v>173578.47</v>
       </c>
-      <c r="D279" s="3" t="n">
+      <c r="D279" s="6" t="n">
         <v>69.22476868</v>
       </c>
       <c r="E279" t="n">
@@ -6478,10 +6394,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C280" s="2" t="n">
+      <c r="C280" s="5" t="n">
         <v>40560.99</v>
       </c>
-      <c r="D280" s="3" t="n">
+      <c r="D280" s="6" t="n">
         <v>8.644859670000001</v>
       </c>
       <c r="E280" t="n">
@@ -6499,10 +6415,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C281" s="2" t="n">
+      <c r="C281" s="5" t="n">
         <v>6836.42</v>
       </c>
-      <c r="D281" s="3" t="n">
+      <c r="D281" s="6" t="n">
         <v>1.45706235</v>
       </c>
       <c r="E281" t="n">
@@ -6520,10 +6436,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C282" s="2" t="n">
+      <c r="C282" s="5" t="n">
         <v>34873.15</v>
       </c>
-      <c r="D282" s="3" t="n">
+      <c r="D282" s="6" t="n">
         <v>7.43259689</v>
       </c>
       <c r="E282" t="n">
@@ -6541,10 +6457,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C283" s="2" t="n">
+      <c r="C283" s="5" t="n">
         <v>386921.44</v>
       </c>
-      <c r="D283" s="3" t="n">
+      <c r="D283" s="6" t="n">
         <v>82.46548108</v>
       </c>
       <c r="E283" t="n">
@@ -6562,10 +6478,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="C284" s="2" t="n">
+      <c r="C284" s="5" t="n">
         <v>2062.08</v>
       </c>
-      <c r="D284" s="3" t="n">
+      <c r="D284" s="6" t="n">
         <v>0.67843969</v>
       </c>
       <c r="E284" t="n">
@@ -6583,10 +6499,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C285" s="2" t="n">
+      <c r="C285" s="5" t="n">
         <v>67302.87</v>
       </c>
-      <c r="D285" s="3" t="n">
+      <c r="D285" s="6" t="n">
         <v>22.14314601</v>
       </c>
       <c r="E285" t="n">
@@ -6604,10 +6520,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C286" s="2" t="n">
+      <c r="C286" s="5" t="n">
         <v>37.83</v>
       </c>
-      <c r="D286" s="3" t="n">
+      <c r="D286" s="6" t="n">
         <v>0.01244635</v>
       </c>
       <c r="E286" t="n">
@@ -6625,10 +6541,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C287" s="2" t="n">
+      <c r="C287" s="5" t="n">
         <v>82048.36</v>
       </c>
-      <c r="D287" s="3" t="n">
+      <c r="D287" s="6" t="n">
         <v>26.99452216</v>
       </c>
       <c r="E287" t="n">
@@ -6646,10 +6562,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C288" s="2" t="n">
+      <c r="C288" s="5" t="n">
         <v>152493.34</v>
       </c>
-      <c r="D288" s="3" t="n">
+      <c r="D288" s="6" t="n">
         <v>50.17144579</v>
       </c>
       <c r="E288" t="n">
@@ -6667,10 +6583,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C289" s="2" t="n">
+      <c r="C289" s="5" t="n">
         <v>16850.05</v>
       </c>
-      <c r="D289" s="3" t="n">
+      <c r="D289" s="6" t="n">
         <v>8.3557591</v>
       </c>
       <c r="E289" t="n">
@@ -6688,10 +6604,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C290" s="2" t="n">
+      <c r="C290" s="5" t="n">
         <v>1221.31</v>
       </c>
-      <c r="D290" s="3" t="n">
+      <c r="D290" s="6" t="n">
         <v>0.60563453</v>
       </c>
       <c r="E290" t="n">
@@ -6709,10 +6625,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C291" s="2" t="n">
+      <c r="C291" s="5" t="n">
         <v>542.72</v>
       </c>
-      <c r="D291" s="3" t="n">
+      <c r="D291" s="6" t="n">
         <v>0.26912903</v>
       </c>
       <c r="E291" t="n">
@@ -6730,10 +6646,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C292" s="2" t="n">
+      <c r="C292" s="5" t="n">
         <v>1989.87</v>
       </c>
-      <c r="D292" s="3" t="n">
+      <c r="D292" s="6" t="n">
         <v>0.98675519</v>
       </c>
       <c r="E292" t="n">
@@ -6751,10 +6667,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C293" s="2" t="n">
+      <c r="C293" s="5" t="n">
         <v>181053.97</v>
       </c>
-      <c r="D293" s="3" t="n">
+      <c r="D293" s="6" t="n">
         <v>89.78272215</v>
       </c>
       <c r="E293" t="n">
@@ -6772,10 +6688,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C294" s="2" t="n">
+      <c r="C294" s="5" t="n">
         <v>2791.46</v>
       </c>
-      <c r="D294" s="3" t="n">
+      <c r="D294" s="6" t="n">
         <v>1.6215349</v>
       </c>
       <c r="E294" t="n">
@@ -6793,10 +6709,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C295" s="2" t="n">
+      <c r="C295" s="5" t="n">
         <v>6752.82</v>
       </c>
-      <c r="D295" s="3" t="n">
+      <c r="D295" s="6" t="n">
         <v>3.92265455</v>
       </c>
       <c r="E295" t="n">
@@ -6814,10 +6730,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C296" s="2" t="n">
+      <c r="C296" s="5" t="n">
         <v>42038.15</v>
       </c>
-      <c r="D296" s="3" t="n">
+      <c r="D296" s="6" t="n">
         <v>24.41959662</v>
       </c>
       <c r="E296" t="n">
@@ -6835,10 +6751,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C297" s="2" t="n">
+      <c r="C297" s="5" t="n">
         <v>120566.81</v>
       </c>
-      <c r="D297" s="3" t="n">
+      <c r="D297" s="6" t="n">
         <v>70.03621393</v>
       </c>
       <c r="E297" t="n">
@@ -6856,10 +6772,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C298" s="2" t="n">
+      <c r="C298" s="5" t="n">
         <v>360</v>
       </c>
-      <c r="D298" s="3" t="n">
+      <c r="D298" s="6" t="n">
         <v>0.13798773</v>
       </c>
       <c r="E298" t="n">
@@ -6877,10 +6793,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C299" s="2" t="n">
+      <c r="C299" s="5" t="n">
         <v>9364.209999999999</v>
       </c>
-      <c r="D299" s="3" t="n">
+      <c r="D299" s="6" t="n">
         <v>3.58929456</v>
       </c>
       <c r="E299" t="n">
@@ -6898,10 +6814,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C300" s="2" t="n">
+      <c r="C300" s="5" t="n">
         <v>4780.88</v>
       </c>
-      <c r="D300" s="3" t="n">
+      <c r="D300" s="6" t="n">
         <v>1.83250766</v>
       </c>
       <c r="E300" t="n">
@@ -6919,10 +6835,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C301" s="2" t="n">
+      <c r="C301" s="5" t="n">
         <v>246387.68</v>
       </c>
-      <c r="D301" s="3" t="n">
+      <c r="D301" s="6" t="n">
         <v>94.44021005</v>
       </c>
       <c r="E301" t="n">
@@ -6940,10 +6856,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C302" s="2" t="n">
+      <c r="C302" s="5" t="n">
         <v>6057.75</v>
       </c>
-      <c r="D302" s="3" t="n">
+      <c r="D302" s="6" t="n">
         <v>2.33727832</v>
       </c>
       <c r="E302" t="n">
@@ -6961,10 +6877,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C303" s="2" t="n">
+      <c r="C303" s="5" t="n">
         <v>48766.63</v>
       </c>
-      <c r="D303" s="3" t="n">
+      <c r="D303" s="6" t="n">
         <v>18.81576278</v>
       </c>
       <c r="E303" t="n">
@@ -6982,10 +6898,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C304" s="2" t="n">
+      <c r="C304" s="5" t="n">
         <v>204355.28</v>
       </c>
-      <c r="D304" s="3" t="n">
+      <c r="D304" s="6" t="n">
         <v>78.8469589</v>
       </c>
       <c r="E304" t="n">
@@ -7003,10 +6919,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C305" s="2" t="n">
+      <c r="C305" s="5" t="n">
         <v>16523.23</v>
       </c>
-      <c r="D305" s="3" t="n">
+      <c r="D305" s="6" t="n">
         <v>6.18627246</v>
       </c>
       <c r="E305" t="n">
@@ -7024,10 +6940,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="C306" s="2" t="n">
+      <c r="C306" s="5" t="n">
         <v>1000</v>
       </c>
-      <c r="D306" s="3" t="n">
+      <c r="D306" s="6" t="n">
         <v>0.3743985</v>
       </c>
       <c r="E306" t="n">
@@ -7045,10 +6961,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C307" s="2" t="n">
+      <c r="C307" s="5" t="n">
         <v>19175.48</v>
       </c>
-      <c r="D307" s="3" t="n">
+      <c r="D307" s="6" t="n">
         <v>7.17927087</v>
       </c>
       <c r="E307" t="n">
@@ -7066,10 +6982,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C308" s="2" t="n">
+      <c r="C308" s="5" t="n">
         <v>22548.18</v>
       </c>
-      <c r="D308" s="3" t="n">
+      <c r="D308" s="6" t="n">
         <v>8.44200468</v>
       </c>
       <c r="E308" t="n">
@@ -7087,10 +7003,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C309" s="2" t="n">
+      <c r="C309" s="5" t="n">
         <v>3105.38</v>
       </c>
-      <c r="D309" s="3" t="n">
+      <c r="D309" s="6" t="n">
         <v>1.1626496</v>
       </c>
       <c r="E309" t="n">
@@ -7108,10 +7024,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C310" s="2" t="n">
+      <c r="C310" s="5" t="n">
         <v>9171.51</v>
       </c>
-      <c r="D310" s="3" t="n">
+      <c r="D310" s="6" t="n">
         <v>3.43379955</v>
       </c>
       <c r="E310" t="n">
@@ -7129,10 +7045,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C311" s="2" t="n">
+      <c r="C311" s="5" t="n">
         <v>195571.31</v>
       </c>
-      <c r="D311" s="3" t="n">
+      <c r="D311" s="6" t="n">
         <v>73.22160434</v>
       </c>
       <c r="E311" t="n">
@@ -7150,10 +7066,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C312" s="2" t="n">
+      <c r="C312" s="5" t="n">
         <v>27350.51</v>
       </c>
-      <c r="D312" s="3" t="n">
+      <c r="D312" s="6" t="n">
         <v>9.8197723</v>
       </c>
       <c r="E312" t="n">
@@ -7171,10 +7087,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C313" s="2" t="n">
+      <c r="C313" s="5" t="n">
         <v>21653.68</v>
       </c>
-      <c r="D313" s="3" t="n">
+      <c r="D313" s="6" t="n">
         <v>7.7744147</v>
       </c>
       <c r="E313" t="n">
@@ -7192,10 +7108,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C314" s="2" t="n">
+      <c r="C314" s="5" t="n">
         <v>30092.08</v>
       </c>
-      <c r="D314" s="3" t="n">
+      <c r="D314" s="6" t="n">
         <v>10.80409008</v>
       </c>
       <c r="E314" t="n">
@@ -7213,10 +7129,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C315" s="2" t="n">
+      <c r="C315" s="5" t="n">
         <v>199428.62</v>
       </c>
-      <c r="D315" s="3" t="n">
+      <c r="D315" s="6" t="n">
         <v>71.60172292</v>
       </c>
       <c r="E315" t="n">
@@ -7234,10 +7150,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C316" s="2" t="n">
+      <c r="C316" s="5" t="n">
         <v>18403.89</v>
       </c>
-      <c r="D316" s="3" t="n">
+      <c r="D316" s="6" t="n">
         <v>5.9503914</v>
       </c>
       <c r="E316" t="n">
@@ -7255,10 +7171,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C317" s="2" t="n">
+      <c r="C317" s="5" t="n">
         <v>88.88</v>
       </c>
-      <c r="D317" s="3" t="n">
+      <c r="D317" s="6" t="n">
         <v>0.0287369</v>
       </c>
       <c r="E317" t="n">
@@ -7276,10 +7192,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C318" s="2" t="n">
+      <c r="C318" s="5" t="n">
         <v>72445.86</v>
       </c>
-      <c r="D318" s="3" t="n">
+      <c r="D318" s="6" t="n">
         <v>23.4233753</v>
       </c>
       <c r="E318" t="n">
@@ -7297,10 +7213,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C319" s="2" t="n">
+      <c r="C319" s="5" t="n">
         <v>1021.81</v>
       </c>
-      <c r="D319" s="3" t="n">
+      <c r="D319" s="6" t="n">
         <v>0.33037415</v>
       </c>
       <c r="E319" t="n">
@@ -7318,10 +7234,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C320" s="2" t="n">
+      <c r="C320" s="5" t="n">
         <v>23146.75</v>
       </c>
-      <c r="D320" s="3" t="n">
+      <c r="D320" s="6" t="n">
         <v>7.48386467</v>
       </c>
       <c r="E320" t="n">
@@ -7339,10 +7255,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C321" s="2" t="n">
+      <c r="C321" s="5" t="n">
         <v>194181.54</v>
       </c>
-      <c r="D321" s="3" t="n">
+      <c r="D321" s="6" t="n">
         <v>62.78325757</v>
       </c>
       <c r="E321" t="n">
@@ -7360,10 +7276,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C322" s="2" t="n">
+      <c r="C322" s="5" t="n">
         <v>3620.25</v>
       </c>
-      <c r="D322" s="3" t="n">
+      <c r="D322" s="6" t="n">
         <v>1.23604851</v>
       </c>
       <c r="E322" t="n">
@@ -7381,10 +7297,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C323" s="2" t="n">
+      <c r="C323" s="5" t="n">
         <v>19747.53</v>
       </c>
-      <c r="D323" s="3" t="n">
+      <c r="D323" s="6" t="n">
         <v>6.74232582</v>
       </c>
       <c r="E323" t="n">
@@ -7402,10 +7318,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C324" s="2" t="n">
+      <c r="C324" s="5" t="n">
         <v>148.8</v>
       </c>
-      <c r="D324" s="3" t="n">
+      <c r="D324" s="6" t="n">
         <v>0.05080423</v>
       </c>
       <c r="E324" t="n">
@@ -7423,10 +7339,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C325" s="2" t="n">
+      <c r="C325" s="5" t="n">
         <v>59465.09</v>
       </c>
-      <c r="D325" s="3" t="n">
+      <c r="D325" s="6" t="n">
         <v>20.30294481</v>
       </c>
       <c r="E325" t="n">
@@ -7444,10 +7360,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C326" s="2" t="n">
+      <c r="C326" s="5" t="n">
         <v>209907.32</v>
       </c>
-      <c r="D326" s="3" t="n">
+      <c r="D326" s="6" t="n">
         <v>71.66787662</v>
       </c>
       <c r="E326" t="n">
@@ -7465,10 +7381,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C327" s="2" t="n">
+      <c r="C327" s="5" t="n">
         <v>6884.07</v>
       </c>
-      <c r="D327" s="3" t="n">
+      <c r="D327" s="6" t="n">
         <v>2.33908458</v>
       </c>
       <c r="E327" t="n">
@@ -7486,10 +7402,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C328" s="2" t="n">
+      <c r="C328" s="5" t="n">
         <v>1851.18</v>
       </c>
-      <c r="D328" s="3" t="n">
+      <c r="D328" s="6" t="n">
         <v>0.62899805</v>
       </c>
       <c r="E328" t="n">
@@ -7507,10 +7423,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C329" s="2" t="n">
+      <c r="C329" s="5" t="n">
         <v>27.27</v>
       </c>
-      <c r="D329" s="3" t="n">
+      <c r="D329" s="6" t="n">
         <v>0.009265860000000001</v>
       </c>
       <c r="E329" t="n">
@@ -7528,10 +7444,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C330" s="2" t="n">
+      <c r="C330" s="5" t="n">
         <v>48724.48</v>
       </c>
-      <c r="D330" s="3" t="n">
+      <c r="D330" s="6" t="n">
         <v>16.55571192</v>
       </c>
       <c r="E330" t="n">
@@ -7549,10 +7465,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C331" s="2" t="n">
+      <c r="C331" s="5" t="n">
         <v>236819.16</v>
       </c>
-      <c r="D331" s="3" t="n">
+      <c r="D331" s="6" t="n">
         <v>80.4669396</v>
       </c>
       <c r="E331" t="n">
@@ -7570,10 +7486,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C332" s="2" t="n">
+      <c r="C332" s="5" t="n">
         <v>1121.22</v>
       </c>
-      <c r="D332" s="3" t="n">
+      <c r="D332" s="6" t="n">
         <v>0.3654631</v>
       </c>
       <c r="E332" t="n">
@@ -7591,10 +7507,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C333" s="2" t="n">
+      <c r="C333" s="5" t="n">
         <v>44200.33</v>
       </c>
-      <c r="D333" s="3" t="n">
+      <c r="D333" s="6" t="n">
         <v>14.40715442</v>
       </c>
       <c r="E333" t="n">
@@ -7612,10 +7528,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C334" s="2" t="n">
+      <c r="C334" s="5" t="n">
         <v>1029.79</v>
       </c>
-      <c r="D334" s="3" t="n">
+      <c r="D334" s="6" t="n">
         <v>0.33566138</v>
       </c>
       <c r="E334" t="n">
@@ -7633,10 +7549,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C335" s="2" t="n">
+      <c r="C335" s="5" t="n">
         <v>47810.16</v>
       </c>
-      <c r="D335" s="3" t="n">
+      <c r="D335" s="6" t="n">
         <v>15.58378315</v>
       </c>
       <c r="E335" t="n">
@@ -7654,10 +7570,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C336" s="2" t="n">
+      <c r="C336" s="5" t="n">
         <v>212632.81</v>
       </c>
-      <c r="D336" s="3" t="n">
+      <c r="D336" s="6" t="n">
         <v>69.30793795</v>
       </c>
       <c r="E336" t="n">
@@ -7675,10 +7591,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C337" s="2" t="n">
+      <c r="C337" s="5" t="n">
         <v>6174.11</v>
       </c>
-      <c r="D337" s="3" t="n">
+      <c r="D337" s="6" t="n">
         <v>2.21572231</v>
       </c>
       <c r="E337" t="n">
@@ -7696,10 +7612,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C338" s="2" t="n">
+      <c r="C338" s="5" t="n">
         <v>41944.2</v>
       </c>
-      <c r="D338" s="3" t="n">
+      <c r="D338" s="6" t="n">
         <v>15.05264723</v>
       </c>
       <c r="E338" t="n">
@@ -7717,10 +7633,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C339" s="2" t="n">
+      <c r="C339" s="5" t="n">
         <v>77569.86</v>
       </c>
-      <c r="D339" s="3" t="n">
+      <c r="D339" s="6" t="n">
         <v>27.8377401</v>
       </c>
       <c r="E339" t="n">
@@ -7738,10 +7654,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C340" s="2" t="n">
+      <c r="C340" s="5" t="n">
         <v>152961.82</v>
       </c>
-      <c r="D340" s="3" t="n">
+      <c r="D340" s="6" t="n">
         <v>54.89389036</v>
       </c>
       <c r="E340" t="n">
@@ -7759,10 +7675,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C341" s="2" t="n">
+      <c r="C341" s="5" t="n">
         <v>4327.58</v>
       </c>
-      <c r="D341" s="3" t="n">
+      <c r="D341" s="6" t="n">
         <v>1.21146897</v>
       </c>
       <c r="E341" t="n">
@@ -7780,10 +7696,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C342" s="2" t="n">
+      <c r="C342" s="5" t="n">
         <v>28414.86</v>
       </c>
-      <c r="D342" s="3" t="n">
+      <c r="D342" s="6" t="n">
         <v>7.95449675</v>
       </c>
       <c r="E342" t="n">
@@ -7801,10 +7717,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C343" s="2" t="n">
+      <c r="C343" s="5" t="n">
         <v>57985.61</v>
       </c>
-      <c r="D343" s="3" t="n">
+      <c r="D343" s="6" t="n">
         <v>16.23257501</v>
       </c>
       <c r="E343" t="n">
@@ -7822,10 +7738,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C344" s="2" t="n">
+      <c r="C344" s="5" t="n">
         <v>164042.55</v>
       </c>
-      <c r="D344" s="3" t="n">
+      <c r="D344" s="6" t="n">
         <v>45.92230724</v>
       </c>
       <c r="E344" t="n">
@@ -7843,10 +7759,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C345" s="2" t="n">
+      <c r="C345" s="5" t="n">
         <v>102446.97</v>
       </c>
-      <c r="D345" s="3" t="n">
+      <c r="D345" s="6" t="n">
         <v>28.67915204</v>
       </c>
       <c r="E345" t="n">
@@ -7864,10 +7780,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C346" s="2" t="n">
+      <c r="C346" s="5" t="n">
         <v>6549.34</v>
       </c>
-      <c r="D346" s="3" t="n">
+      <c r="D346" s="6" t="n">
         <v>1.3658538</v>
       </c>
       <c r="E346" t="n">
@@ -7885,10 +7801,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C347" s="2" t="n">
+      <c r="C347" s="5" t="n">
         <v>70012.2</v>
       </c>
-      <c r="D347" s="3" t="n">
+      <c r="D347" s="6" t="n">
         <v>14.60092612</v>
       </c>
       <c r="E347" t="n">
@@ -7906,10 +7822,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C348" s="2" t="n">
+      <c r="C348" s="5" t="n">
         <v>131512.85</v>
       </c>
-      <c r="D348" s="3" t="n">
+      <c r="D348" s="6" t="n">
         <v>27.42678286</v>
       </c>
       <c r="E348" t="n">
@@ -7927,10 +7843,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C349" s="2" t="n">
+      <c r="C349" s="5" t="n">
         <v>271430.81</v>
       </c>
-      <c r="D349" s="3" t="n">
+      <c r="D349" s="6" t="n">
         <v>56.60643722</v>
       </c>
       <c r="E349" t="n">
@@ -7948,10 +7864,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C350" s="2" t="n">
+      <c r="C350" s="5" t="n">
         <v>15339.66</v>
       </c>
-      <c r="D350" s="3" t="n">
+      <c r="D350" s="6" t="n">
         <v>4.55580253</v>
       </c>
       <c r="E350" t="n">
@@ -7969,10 +7885,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C351" s="2" t="n">
+      <c r="C351" s="5" t="n">
         <v>24900.55</v>
       </c>
-      <c r="D351" s="3" t="n">
+      <c r="D351" s="6" t="n">
         <v>7.39533918</v>
       </c>
       <c r="E351" t="n">
@@ -7990,10 +7906,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C352" s="2" t="n">
+      <c r="C352" s="5" t="n">
         <v>7486.19</v>
       </c>
-      <c r="D352" s="3" t="n">
+      <c r="D352" s="6" t="n">
         <v>2.2233611</v>
       </c>
       <c r="E352" t="n">
@@ -8011,10 +7927,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C353" s="2" t="n">
+      <c r="C353" s="5" t="n">
         <v>75899.28</v>
       </c>
-      <c r="D353" s="3" t="n">
+      <c r="D353" s="6" t="n">
         <v>22.54170768</v>
       </c>
       <c r="E353" t="n">
@@ -8032,10 +7948,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C354" s="2" t="n">
+      <c r="C354" s="5" t="n">
         <v>213080.31</v>
       </c>
-      <c r="D354" s="3" t="n">
+      <c r="D354" s="6" t="n">
         <v>63.28378952</v>
       </c>
       <c r="E354" t="n">
@@ -8053,10 +7969,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C355" s="2" t="n">
+      <c r="C355" s="5" t="n">
         <v>99.05</v>
       </c>
-      <c r="D355" s="3" t="n">
+      <c r="D355" s="6" t="n">
         <v>0.05450467</v>
       </c>
       <c r="E355" t="n">
@@ -8074,10 +7990,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C356" s="2" t="n">
+      <c r="C356" s="5" t="n">
         <v>40317.43</v>
       </c>
-      <c r="D356" s="3" t="n">
+      <c r="D356" s="6" t="n">
         <v>22.18564427</v>
       </c>
       <c r="E356" t="n">
@@ -8095,10 +8011,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C357" s="2" t="n">
+      <c r="C357" s="5" t="n">
         <v>441.17</v>
       </c>
-      <c r="D357" s="3" t="n">
+      <c r="D357" s="6" t="n">
         <v>0.2427645</v>
       </c>
       <c r="E357" t="n">
@@ -8116,10 +8032,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C358" s="2" t="n">
+      <c r="C358" s="5" t="n">
         <v>15478.5</v>
       </c>
-      <c r="D358" s="3" t="n">
+      <c r="D358" s="6" t="n">
         <v>8.517420250000001</v>
       </c>
       <c r="E358" t="n">
@@ -8137,10 +8053,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C359" s="2" t="n">
+      <c r="C359" s="5" t="n">
         <v>125391.41</v>
       </c>
-      <c r="D359" s="3" t="n">
+      <c r="D359" s="6" t="n">
         <v>68.99966630999999</v>
       </c>
       <c r="E359" t="n">
@@ -8158,10 +8074,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C360" s="2" t="n">
+      <c r="C360" s="5" t="n">
         <v>1078.53</v>
       </c>
-      <c r="D360" s="3" t="n">
+      <c r="D360" s="6" t="n">
         <v>0.2616409</v>
       </c>
       <c r="E360" t="n">
@@ -8179,10 +8095,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C361" s="2" t="n">
+      <c r="C361" s="5" t="n">
         <v>18773.2</v>
       </c>
-      <c r="D361" s="3" t="n">
+      <c r="D361" s="6" t="n">
         <v>4.55419596</v>
       </c>
       <c r="E361" t="n">
@@ -8200,10 +8116,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C362" s="2" t="n">
+      <c r="C362" s="5" t="n">
         <v>131529.74</v>
       </c>
-      <c r="D362" s="3" t="n">
+      <c r="D362" s="6" t="n">
         <v>31.90783723</v>
       </c>
       <c r="E362" t="n">
@@ -8221,10 +8137,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C363" s="2" t="n">
+      <c r="C363" s="5" t="n">
         <v>260836.19</v>
       </c>
-      <c r="D363" s="3" t="n">
+      <c r="D363" s="6" t="n">
         <v>63.27632591</v>
       </c>
       <c r="E363" t="n">
@@ -8242,10 +8158,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C364" s="2" t="n">
+      <c r="C364" s="5" t="n">
         <v>101597</v>
       </c>
-      <c r="D364" s="3" t="n">
+      <c r="D364" s="6" t="n">
         <v>23.3811176</v>
       </c>
       <c r="E364" t="n">
@@ -8263,10 +8179,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C365" s="2" t="n">
+      <c r="C365" s="5" t="n">
         <v>28150.66</v>
       </c>
-      <c r="D365" s="3" t="n">
+      <c r="D365" s="6" t="n">
         <v>6.47847763</v>
       </c>
       <c r="E365" t="n">
@@ -8284,10 +8200,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C366" s="2" t="n">
+      <c r="C366" s="5" t="n">
         <v>40.94</v>
       </c>
-      <c r="D366" s="3" t="n">
+      <c r="D366" s="6" t="n">
         <v>0.00942176</v>
       </c>
       <c r="E366" t="n">
@@ -8305,10 +8221,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C367" s="2" t="n">
+      <c r="C367" s="5" t="n">
         <v>39974.48</v>
       </c>
-      <c r="D367" s="3" t="n">
+      <c r="D367" s="6" t="n">
         <v>9.19956316</v>
       </c>
       <c r="E367" t="n">
@@ -8326,10 +8242,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C368" s="2" t="n">
+      <c r="C368" s="5" t="n">
         <v>264762.77</v>
       </c>
-      <c r="D368" s="3" t="n">
+      <c r="D368" s="6" t="n">
         <v>60.93141985</v>
       </c>
       <c r="E368" t="n">
@@ -8347,10 +8263,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C369" s="2" t="n">
+      <c r="C369" s="5" t="n">
         <v>4391.2</v>
       </c>
-      <c r="D369" s="3" t="n">
+      <c r="D369" s="6" t="n">
         <v>1.20491459</v>
       </c>
       <c r="E369" t="n">
@@ -8368,10 +8284,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C370" s="2" t="n">
+      <c r="C370" s="5" t="n">
         <v>65068.55</v>
       </c>
-      <c r="D370" s="3" t="n">
+      <c r="D370" s="6" t="n">
         <v>17.85435532</v>
       </c>
       <c r="E370" t="n">
@@ -8389,10 +8305,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C371" s="2" t="n">
+      <c r="C371" s="5" t="n">
         <v>121692.04</v>
       </c>
-      <c r="D371" s="3" t="n">
+      <c r="D371" s="6" t="n">
         <v>33.3914452</v>
       </c>
       <c r="E371" t="n">
@@ -8410,10 +8326,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C372" s="2" t="n">
+      <c r="C372" s="5" t="n">
         <v>173288.98</v>
       </c>
-      <c r="D372" s="3" t="n">
+      <c r="D372" s="6" t="n">
         <v>47.54928489</v>
       </c>
       <c r="E372" t="n">
@@ -8431,10 +8347,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C373" s="2" t="n">
+      <c r="C373" s="5" t="n">
         <v>17775.38</v>
       </c>
-      <c r="D373" s="3" t="n">
+      <c r="D373" s="6" t="n">
         <v>7.37116189</v>
       </c>
       <c r="E373" t="n">
@@ -8452,10 +8368,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C374" s="2" t="n">
+      <c r="C374" s="5" t="n">
         <v>29163.77</v>
       </c>
-      <c r="D374" s="3" t="n">
+      <c r="D374" s="6" t="n">
         <v>12.09374259</v>
       </c>
       <c r="E374" t="n">
@@ -8473,10 +8389,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C375" s="2" t="n">
+      <c r="C375" s="5" t="n">
         <v>52107.99</v>
       </c>
-      <c r="D375" s="3" t="n">
+      <c r="D375" s="6" t="n">
         <v>21.60833863</v>
       </c>
       <c r="E375" t="n">
@@ -8494,10 +8410,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C376" s="2" t="n">
+      <c r="C376" s="5" t="n">
         <v>142100.46</v>
       </c>
-      <c r="D376" s="3" t="n">
+      <c r="D376" s="6" t="n">
         <v>58.92675689</v>
       </c>
       <c r="E376" t="n">

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -69,11 +69,11 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -477,24 +477,129 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>251254.3</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>87.96878287</v>
+      </c>
+      <c r="E2" t="n">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>19199.2</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>6.72199543</v>
+      </c>
+      <c r="E3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>3.50118517</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>4643.79</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>1.62587687</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>520.28</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0.18215966</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="4" t="n">
+      <c r="C7" s="5" t="n">
+        <v>285617.57</v>
+      </c>
+      <c r="D7" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>0</v>
+      <c r="E7" s="4" t="n">
+        <v>257</v>
       </c>
     </row>
   </sheetData>
@@ -508,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E376"/>
+  <dimension ref="A1:E381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -556,10 +661,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C2" s="5" t="n">
+      <c r="C2" s="2" t="n">
         <v>948.86</v>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="D2" s="3" t="n">
         <v>0.19126904</v>
       </c>
       <c r="E2" t="n">
@@ -577,10 +682,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" s="2" t="n">
         <v>461123.2</v>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="3" t="n">
         <v>92.95216732</v>
       </c>
       <c r="E3" t="n">
@@ -598,10 +703,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="2" t="n">
         <v>333</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="3" t="n">
         <v>0.06712538</v>
       </c>
       <c r="E4" t="n">
@@ -619,10 +724,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="2" t="n">
         <v>33681.49</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="3" t="n">
         <v>6.78943825</v>
       </c>
       <c r="E5" t="n">
@@ -640,10 +745,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="2" t="n">
         <v>3947.95</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="3" t="n">
         <v>0.94921987</v>
       </c>
       <c r="E6" t="n">
@@ -661,10 +766,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="2" t="n">
         <v>316928.34</v>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="3" t="n">
         <v>76.20022474</v>
       </c>
       <c r="E7" t="n">
@@ -682,10 +787,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="2" t="n">
         <v>28879.81</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="3" t="n">
         <v>6.94367696</v>
       </c>
       <c r="E8" t="n">
@@ -703,10 +808,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="2" t="n">
         <v>66159.13</v>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="3" t="n">
         <v>15.90687843</v>
       </c>
       <c r="E9" t="n">
@@ -724,10 +829,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="2" t="n">
         <v>672.72</v>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="3" t="n">
         <v>0.12167625</v>
       </c>
       <c r="E10" t="n">
@@ -745,10 +850,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="2" t="n">
         <v>506109.58</v>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="3" t="n">
         <v>91.54108388</v>
       </c>
       <c r="E11" t="n">
@@ -766,10 +871,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C12" s="2" t="n">
         <v>13144.61</v>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="3" t="n">
         <v>2.37749273</v>
       </c>
       <c r="E12" t="n">
@@ -787,10 +892,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C13" s="2" t="n">
         <v>32950.07</v>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="3" t="n">
         <v>5.95974714</v>
       </c>
       <c r="E13" t="n">
@@ -808,10 +913,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C14" s="5" t="n">
+      <c r="C14" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="3" t="n">
         <v>0.00340356</v>
       </c>
       <c r="E14" t="n">
@@ -829,10 +934,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C15" s="2" t="n">
         <v>3803.45</v>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="3" t="n">
         <v>1.43836189</v>
       </c>
       <c r="E15" t="n">
@@ -850,10 +955,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C16" s="5" t="n">
+      <c r="C16" s="2" t="n">
         <v>229609.87</v>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D16" s="3" t="n">
         <v>86.83224112000001</v>
       </c>
       <c r="E16" t="n">
@@ -871,10 +976,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C17" s="5" t="n">
+      <c r="C17" s="2" t="n">
         <v>884.04</v>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="D17" s="3" t="n">
         <v>0.33432001</v>
       </c>
       <c r="E17" t="n">
@@ -892,10 +997,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C18" s="5" t="n">
+      <c r="C18" s="2" t="n">
         <v>30122.92</v>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D18" s="3" t="n">
         <v>11.39167342</v>
       </c>
       <c r="E18" t="n">
@@ -913,10 +1018,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C19" s="5" t="n">
+      <c r="C19" s="2" t="n">
         <v>23268.18</v>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D19" s="3" t="n">
         <v>4.17124226</v>
       </c>
       <c r="E19" t="n">
@@ -934,10 +1039,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C20" s="5" t="n">
+      <c r="C20" s="2" t="n">
         <v>451338.15</v>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="D20" s="3" t="n">
         <v>80.91052954</v>
       </c>
       <c r="E20" t="n">
@@ -955,10 +1060,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C21" s="5" t="n">
+      <c r="C21" s="2" t="n">
         <v>20229.42</v>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D21" s="3" t="n">
         <v>3.62648955</v>
       </c>
       <c r="E21" t="n">
@@ -976,10 +1081,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C22" s="5" t="n">
+      <c r="C22" s="2" t="n">
         <v>62988</v>
       </c>
-      <c r="D22" s="6" t="n">
+      <c r="D22" s="3" t="n">
         <v>11.29173865</v>
       </c>
       <c r="E22" t="n">
@@ -997,10 +1102,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C23" s="5" t="n">
+      <c r="C23" s="2" t="n">
         <v>103.09</v>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="D23" s="3" t="n">
         <v>0.02902112</v>
       </c>
       <c r="E23" t="n">
@@ -1018,10 +1123,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C24" s="5" t="n">
+      <c r="C24" s="2" t="n">
         <v>283.13</v>
       </c>
-      <c r="D24" s="6" t="n">
+      <c r="D24" s="3" t="n">
         <v>0.07970463</v>
       </c>
       <c r="E24" t="n">
@@ -1039,10 +1144,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C25" s="5" t="n">
+      <c r="C25" s="2" t="n">
         <v>341584.75</v>
       </c>
-      <c r="D25" s="6" t="n">
+      <c r="D25" s="3" t="n">
         <v>96.16036696</v>
       </c>
       <c r="E25" t="n">
@@ -1060,10 +1165,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C26" s="5" t="n">
+      <c r="C26" s="2" t="n">
         <v>13253.08</v>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="D26" s="3" t="n">
         <v>3.7309073</v>
       </c>
       <c r="E26" t="n">
@@ -1081,10 +1186,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C27" s="5" t="n">
+      <c r="C27" s="2" t="n">
         <v>366675.1</v>
       </c>
-      <c r="D27" s="6" t="n">
+      <c r="D27" s="3" t="n">
         <v>88.88052623</v>
       </c>
       <c r="E27" t="n">
@@ -1102,10 +1207,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C28" s="5" t="n">
+      <c r="C28" s="2" t="n">
         <v>10967.83</v>
       </c>
-      <c r="D28" s="6" t="n">
+      <c r="D28" s="3" t="n">
         <v>2.65855659</v>
       </c>
       <c r="E28" t="n">
@@ -1123,10 +1228,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C29" s="5" t="n">
+      <c r="C29" s="2" t="n">
         <v>34905.37</v>
       </c>
-      <c r="D29" s="6" t="n">
+      <c r="D29" s="3" t="n">
         <v>8.460917179999999</v>
       </c>
       <c r="E29" t="n">
@@ -1144,10 +1249,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C30" s="5" t="n">
+      <c r="C30" s="2" t="n">
         <v>431085.81</v>
       </c>
-      <c r="D30" s="6" t="n">
+      <c r="D30" s="3" t="n">
         <v>81.83421629999999</v>
       </c>
       <c r="E30" t="n">
@@ -1165,10 +1270,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C31" s="5" t="n">
+      <c r="C31" s="2" t="n">
         <v>1633.45</v>
       </c>
-      <c r="D31" s="6" t="n">
+      <c r="D31" s="3" t="n">
         <v>0.31008235</v>
       </c>
       <c r="E31" t="n">
@@ -1186,10 +1291,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C32" s="5" t="n">
+      <c r="C32" s="2" t="n">
         <v>94060.16</v>
       </c>
-      <c r="D32" s="6" t="n">
+      <c r="D32" s="3" t="n">
         <v>17.85570135</v>
       </c>
       <c r="E32" t="n">
@@ -1207,10 +1312,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C33" s="5" t="n">
+      <c r="C33" s="2" t="n">
         <v>321805.16</v>
       </c>
-      <c r="D33" s="6" t="n">
+      <c r="D33" s="3" t="n">
         <v>78.53984421</v>
       </c>
       <c r="E33" t="n">
@@ -1228,10 +1333,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C34" s="5" t="n">
+      <c r="C34" s="2" t="n">
         <v>81063.48</v>
       </c>
-      <c r="D34" s="6" t="n">
+      <c r="D34" s="3" t="n">
         <v>19.78437229</v>
       </c>
       <c r="E34" t="n">
@@ -1249,10 +1354,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C35" s="5" t="n">
+      <c r="C35" s="2" t="n">
         <v>6866.27</v>
       </c>
-      <c r="D35" s="6" t="n">
+      <c r="D35" s="3" t="n">
         <v>1.6757835</v>
       </c>
       <c r="E35" t="n">
@@ -1270,10 +1375,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C36" s="5" t="n">
+      <c r="C36" s="2" t="n">
         <v>352851.14</v>
       </c>
-      <c r="D36" s="6" t="n">
+      <c r="D36" s="3" t="n">
         <v>94.15474251000001</v>
       </c>
       <c r="E36" t="n">
@@ -1291,10 +1396,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C37" s="5" t="n">
+      <c r="C37" s="2" t="n">
         <v>576.49</v>
       </c>
-      <c r="D37" s="6" t="n">
+      <c r="D37" s="3" t="n">
         <v>0.1538305</v>
       </c>
       <c r="E37" t="n">
@@ -1312,10 +1417,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C38" s="5" t="n">
+      <c r="C38" s="2" t="n">
         <v>21329</v>
       </c>
-      <c r="D38" s="6" t="n">
+      <c r="D38" s="3" t="n">
         <v>5.69142699</v>
       </c>
       <c r="E38" t="n">
@@ -1333,10 +1438,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C39" s="5" t="n">
+      <c r="C39" s="2" t="n">
         <v>83.52</v>
       </c>
-      <c r="D39" s="6" t="n">
+      <c r="D39" s="3" t="n">
         <v>0.01466719</v>
       </c>
       <c r="E39" t="n">
@@ -1354,10 +1459,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C40" s="5" t="n">
+      <c r="C40" s="2" t="n">
         <v>509873.13</v>
       </c>
-      <c r="D40" s="6" t="n">
+      <c r="D40" s="3" t="n">
         <v>89.54027855</v>
       </c>
       <c r="E40" t="n">
@@ -1375,10 +1480,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C41" s="5" t="n">
+      <c r="C41" s="2" t="n">
         <v>8520.23</v>
       </c>
-      <c r="D41" s="6" t="n">
+      <c r="D41" s="3" t="n">
         <v>1.49626196</v>
       </c>
       <c r="E41" t="n">
@@ -1396,10 +1501,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C42" s="5" t="n">
+      <c r="C42" s="2" t="n">
         <v>50957.5</v>
       </c>
-      <c r="D42" s="6" t="n">
+      <c r="D42" s="3" t="n">
         <v>8.94879231</v>
       </c>
       <c r="E42" t="n">
@@ -1417,10 +1522,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C43" s="5" t="n">
+      <c r="C43" s="2" t="n">
         <v>9326.15</v>
       </c>
-      <c r="D43" s="6" t="n">
+      <c r="D43" s="3" t="n">
         <v>1.62650962</v>
       </c>
       <c r="E43" t="n">
@@ -1438,10 +1543,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C44" s="5" t="n">
+      <c r="C44" s="2" t="n">
         <v>510341.61</v>
       </c>
-      <c r="D44" s="6" t="n">
+      <c r="D44" s="3" t="n">
         <v>89.00516713</v>
       </c>
       <c r="E44" t="n">
@@ -1459,10 +1564,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C45" s="5" t="n">
+      <c r="C45" s="2" t="n">
         <v>2517.04</v>
       </c>
-      <c r="D45" s="6" t="n">
+      <c r="D45" s="3" t="n">
         <v>0.43897962</v>
       </c>
       <c r="E45" t="n">
@@ -1480,10 +1585,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C46" s="5" t="n">
+      <c r="C46" s="2" t="n">
         <v>51199.45</v>
       </c>
-      <c r="D46" s="6" t="n">
+      <c r="D46" s="3" t="n">
         <v>8.92934363</v>
       </c>
       <c r="E46" t="n">
@@ -1501,10 +1606,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="C47" s="5" t="n">
+      <c r="C47" s="2" t="n">
         <v>850</v>
       </c>
-      <c r="D47" s="6" t="n">
+      <c r="D47" s="3" t="n">
         <v>0.25302704</v>
       </c>
       <c r="E47" t="n">
@@ -1522,10 +1627,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C48" s="5" t="n">
+      <c r="C48" s="2" t="n">
         <v>1223.36</v>
       </c>
-      <c r="D48" s="6" t="n">
+      <c r="D48" s="3" t="n">
         <v>0.36416843</v>
       </c>
       <c r="E48" t="n">
@@ -1543,10 +1648,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C49" s="5" t="n">
+      <c r="C49" s="2" t="n">
         <v>270843.56</v>
       </c>
-      <c r="D49" s="6" t="n">
+      <c r="D49" s="3" t="n">
         <v>80.62440645</v>
       </c>
       <c r="E49" t="n">
@@ -1564,10 +1669,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C50" s="5" t="n">
+      <c r="C50" s="2" t="n">
         <v>612.64</v>
       </c>
-      <c r="D50" s="6" t="n">
+      <c r="D50" s="3" t="n">
         <v>0.18236999</v>
       </c>
       <c r="E50" t="n">
@@ -1585,10 +1690,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C51" s="5" t="n">
+      <c r="C51" s="2" t="n">
         <v>62402.91</v>
       </c>
-      <c r="D51" s="6" t="n">
+      <c r="D51" s="3" t="n">
         <v>18.57602809</v>
       </c>
       <c r="E51" t="n">
@@ -1606,10 +1711,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C52" s="5" t="n">
+      <c r="C52" s="2" t="n">
         <v>555930.41</v>
       </c>
-      <c r="D52" s="6" t="n">
+      <c r="D52" s="3" t="n">
         <v>91.1452503</v>
       </c>
       <c r="E52" t="n">
@@ -1627,10 +1732,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C53" s="5" t="n">
+      <c r="C53" s="2" t="n">
         <v>1590.9</v>
       </c>
-      <c r="D53" s="6" t="n">
+      <c r="D53" s="3" t="n">
         <v>0.26082937</v>
       </c>
       <c r="E53" t="n">
@@ -1648,10 +1753,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C54" s="5" t="n">
+      <c r="C54" s="2" t="n">
         <v>52417.67</v>
       </c>
-      <c r="D54" s="6" t="n">
+      <c r="D54" s="3" t="n">
         <v>8.59392033</v>
       </c>
       <c r="E54" t="n">
@@ -1669,10 +1774,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C55" s="5" t="n">
+      <c r="C55" s="2" t="n">
         <v>10.55</v>
       </c>
-      <c r="D55" s="6" t="n">
+      <c r="D55" s="3" t="n">
         <v>0.00287103</v>
       </c>
       <c r="E55" t="n">
@@ -1690,10 +1795,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C56" s="5" t="n">
+      <c r="C56" s="2" t="n">
         <v>319888.32</v>
       </c>
-      <c r="D56" s="6" t="n">
+      <c r="D56" s="3" t="n">
         <v>87.05305848</v>
       </c>
       <c r="E56" t="n">
@@ -1711,10 +1816,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C57" s="5" t="n">
+      <c r="C57" s="2" t="n">
         <v>1278.17</v>
       </c>
-      <c r="D57" s="6" t="n">
+      <c r="D57" s="3" t="n">
         <v>0.34783579</v>
       </c>
       <c r="E57" t="n">
@@ -1732,10 +1837,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C58" s="5" t="n">
+      <c r="C58" s="2" t="n">
         <v>46286.58</v>
       </c>
-      <c r="D58" s="6" t="n">
+      <c r="D58" s="3" t="n">
         <v>12.5962347</v>
       </c>
       <c r="E58" t="n">
@@ -1753,10 +1858,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C59" s="5" t="n">
+      <c r="C59" s="2" t="n">
         <v>354.29</v>
       </c>
-      <c r="D59" s="6" t="n">
+      <c r="D59" s="3" t="n">
         <v>0.1171275</v>
       </c>
       <c r="E59" t="n">
@@ -1774,10 +1879,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C60" s="5" t="n">
+      <c r="C60" s="2" t="n">
         <v>121.49</v>
       </c>
-      <c r="D60" s="6" t="n">
+      <c r="D60" s="3" t="n">
         <v>0.04016433</v>
       </c>
       <c r="E60" t="n">
@@ -1795,10 +1900,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C61" s="5" t="n">
+      <c r="C61" s="2" t="n">
         <v>264522.3</v>
       </c>
-      <c r="D61" s="6" t="n">
+      <c r="D61" s="3" t="n">
         <v>87.4504938</v>
       </c>
       <c r="E61" t="n">
@@ -1816,10 +1921,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C62" s="5" t="n">
+      <c r="C62" s="2" t="n">
         <v>1149.77</v>
       </c>
-      <c r="D62" s="6" t="n">
+      <c r="D62" s="3" t="n">
         <v>0.38011145</v>
       </c>
       <c r="E62" t="n">
@@ -1837,10 +1942,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C63" s="5" t="n">
+      <c r="C63" s="2" t="n">
         <v>36334.49</v>
       </c>
-      <c r="D63" s="6" t="n">
+      <c r="D63" s="3" t="n">
         <v>12.01210292</v>
       </c>
       <c r="E63" t="n">
@@ -1858,10 +1963,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C64" s="5" t="n">
+      <c r="C64" s="2" t="n">
         <v>4545.45</v>
       </c>
-      <c r="D64" s="6" t="n">
+      <c r="D64" s="3" t="n">
         <v>1.24043036</v>
       </c>
       <c r="E64" t="n">
@@ -1879,10 +1984,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C65" s="5" t="n">
+      <c r="C65" s="2" t="n">
         <v>874</v>
       </c>
-      <c r="D65" s="6" t="n">
+      <c r="D65" s="3" t="n">
         <v>0.23851019</v>
       </c>
       <c r="E65" t="n">
@@ -1900,10 +2005,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C66" s="5" t="n">
+      <c r="C66" s="2" t="n">
         <v>284866.12</v>
       </c>
-      <c r="D66" s="6" t="n">
+      <c r="D66" s="3" t="n">
         <v>77.73852608</v>
       </c>
       <c r="E66" t="n">
@@ -1921,10 +2026,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C67" s="5" t="n">
+      <c r="C67" s="2" t="n">
         <v>1590.95</v>
       </c>
-      <c r="D67" s="6" t="n">
+      <c r="D67" s="3" t="n">
         <v>0.43416222</v>
       </c>
       <c r="E67" t="n">
@@ -1942,10 +2047,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C68" s="5" t="n">
+      <c r="C68" s="2" t="n">
         <v>74564.85000000001</v>
       </c>
-      <c r="D68" s="6" t="n">
+      <c r="D68" s="3" t="n">
         <v>20.34837115</v>
       </c>
       <c r="E68" t="n">
@@ -1963,10 +2068,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C69" s="5" t="n">
+      <c r="C69" s="2" t="n">
         <v>442814.15</v>
       </c>
-      <c r="D69" s="6" t="n">
+      <c r="D69" s="3" t="n">
         <v>80.48822254</v>
       </c>
       <c r="E69" t="n">
@@ -1984,10 +2089,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C70" s="5" t="n">
+      <c r="C70" s="2" t="n">
         <v>914.39</v>
       </c>
-      <c r="D70" s="6" t="n">
+      <c r="D70" s="3" t="n">
         <v>0.16620432</v>
       </c>
       <c r="E70" t="n">
@@ -2005,10 +2110,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C71" s="5" t="n">
+      <c r="C71" s="2" t="n">
         <v>106431.64</v>
       </c>
-      <c r="D71" s="6" t="n">
+      <c r="D71" s="3" t="n">
         <v>19.34557314</v>
       </c>
       <c r="E71" t="n">
@@ -2026,10 +2131,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C72" s="5" t="n">
+      <c r="C72" s="2" t="n">
         <v>166</v>
       </c>
-      <c r="D72" s="6" t="n">
+      <c r="D72" s="3" t="n">
         <v>0.02878159</v>
       </c>
       <c r="E72" t="n">
@@ -2047,10 +2152,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C73" s="5" t="n">
+      <c r="C73" s="2" t="n">
         <v>81.83</v>
       </c>
-      <c r="D73" s="6" t="n">
+      <c r="D73" s="3" t="n">
         <v>0.01418794</v>
       </c>
       <c r="E73" t="n">
@@ -2068,10 +2173,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C74" s="5" t="n">
+      <c r="C74" s="2" t="n">
         <v>528120.33</v>
       </c>
-      <c r="D74" s="6" t="n">
+      <c r="D74" s="3" t="n">
         <v>91.56712743999999</v>
       </c>
       <c r="E74" t="n">
@@ -2089,10 +2194,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C75" s="5" t="n">
+      <c r="C75" s="2" t="n">
         <v>567.3200000000001</v>
       </c>
-      <c r="D75" s="6" t="n">
+      <c r="D75" s="3" t="n">
         <v>0.09836369</v>
       </c>
       <c r="E75" t="n">
@@ -2110,10 +2215,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C76" s="5" t="n">
+      <c r="C76" s="2" t="n">
         <v>47822.08</v>
       </c>
-      <c r="D76" s="6" t="n">
+      <c r="D76" s="3" t="n">
         <v>8.29153934</v>
       </c>
       <c r="E76" t="n">
@@ -2131,10 +2236,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C77" s="5" t="n">
+      <c r="C77" s="2" t="n">
         <v>2157.29</v>
       </c>
-      <c r="D77" s="6" t="n">
+      <c r="D77" s="3" t="n">
         <v>1.00708473</v>
       </c>
       <c r="E77" t="n">
@@ -2152,10 +2257,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C78" s="5" t="n">
+      <c r="C78" s="2" t="n">
         <v>177127.26</v>
       </c>
-      <c r="D78" s="6" t="n">
+      <c r="D78" s="3" t="n">
         <v>82.68807579999999</v>
       </c>
       <c r="E78" t="n">
@@ -2173,10 +2278,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C79" s="5" t="n">
+      <c r="C79" s="2" t="n">
         <v>826.1799999999999</v>
       </c>
-      <c r="D79" s="6" t="n">
+      <c r="D79" s="3" t="n">
         <v>0.38568448</v>
       </c>
       <c r="E79" t="n">
@@ -2194,10 +2299,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C80" s="5" t="n">
+      <c r="C80" s="2" t="n">
         <v>34100.64</v>
       </c>
-      <c r="D80" s="6" t="n">
+      <c r="D80" s="3" t="n">
         <v>15.91915499</v>
       </c>
       <c r="E80" t="n">
@@ -2215,10 +2320,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C81" s="5" t="n">
+      <c r="C81" s="2" t="n">
         <v>54.12</v>
       </c>
-      <c r="D81" s="6" t="n">
+      <c r="D81" s="3" t="n">
         <v>0.01747125</v>
       </c>
       <c r="E81" t="n">
@@ -2236,10 +2341,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C82" s="5" t="n">
+      <c r="C82" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="D82" s="6" t="n">
+      <c r="D82" s="3" t="n">
         <v>0.0213064</v>
       </c>
       <c r="E82" t="n">
@@ -2257,10 +2362,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C83" s="5" t="n">
+      <c r="C83" s="2" t="n">
         <v>21771.31</v>
       </c>
-      <c r="D83" s="6" t="n">
+      <c r="D83" s="3" t="n">
         <v>7.02830778</v>
       </c>
       <c r="E83" t="n">
@@ -2278,10 +2383,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C84" s="5" t="n">
+      <c r="C84" s="2" t="n">
         <v>214416.2</v>
       </c>
-      <c r="D84" s="6" t="n">
+      <c r="D84" s="3" t="n">
         <v>69.21875842999999</v>
       </c>
       <c r="E84" t="n">
@@ -2299,10 +2404,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C85" s="5" t="n">
+      <c r="C85" s="2" t="n">
         <v>9060.450000000001</v>
       </c>
-      <c r="D85" s="6" t="n">
+      <c r="D85" s="3" t="n">
         <v>2.92493338</v>
       </c>
       <c r="E85" t="n">
@@ -2320,10 +2425,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C86" s="5" t="n">
+      <c r="C86" s="2" t="n">
         <v>64397.95</v>
       </c>
-      <c r="D86" s="6" t="n">
+      <c r="D86" s="3" t="n">
         <v>20.78922276</v>
       </c>
       <c r="E86" t="n">
@@ -2341,10 +2446,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C87" s="5" t="n">
+      <c r="C87" s="2" t="n">
         <v>1067.9</v>
       </c>
-      <c r="D87" s="6" t="n">
+      <c r="D87" s="3" t="n">
         <v>0.29681338</v>
       </c>
       <c r="E87" t="n">
@@ -2362,10 +2467,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C88" s="5" t="n">
+      <c r="C88" s="2" t="n">
         <v>260988.37</v>
       </c>
-      <c r="D88" s="6" t="n">
+      <c r="D88" s="3" t="n">
         <v>72.53941456</v>
       </c>
       <c r="E88" t="n">
@@ -2383,10 +2488,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C89" s="5" t="n">
+      <c r="C89" s="2" t="n">
         <v>7522.28</v>
       </c>
-      <c r="D89" s="6" t="n">
+      <c r="D89" s="3" t="n">
         <v>2.09075135</v>
       </c>
       <c r="E89" t="n">
@@ -2404,10 +2509,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C90" s="5" t="n">
+      <c r="C90" s="2" t="n">
         <v>90209.81</v>
       </c>
-      <c r="D90" s="6" t="n">
+      <c r="D90" s="3" t="n">
         <v>25.07302071</v>
       </c>
       <c r="E90" t="n">
@@ -2425,10 +2530,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C91" s="5" t="n">
+      <c r="C91" s="2" t="n">
         <v>11124.49</v>
       </c>
-      <c r="D91" s="6" t="n">
+      <c r="D91" s="3" t="n">
         <v>3.35098295</v>
       </c>
       <c r="E91" t="n">
@@ -2446,10 +2551,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C92" s="5" t="n">
+      <c r="C92" s="2" t="n">
         <v>201888.41</v>
       </c>
-      <c r="D92" s="6" t="n">
+      <c r="D92" s="3" t="n">
         <v>60.81398972</v>
       </c>
       <c r="E92" t="n">
@@ -2467,10 +2572,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C93" s="5" t="n">
+      <c r="C93" s="2" t="n">
         <v>15503.87</v>
       </c>
-      <c r="D93" s="6" t="n">
+      <c r="D93" s="3" t="n">
         <v>4.67016502</v>
       </c>
       <c r="E93" t="n">
@@ -2488,10 +2593,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C94" s="5" t="n">
+      <c r="C94" s="2" t="n">
         <v>103460.15</v>
       </c>
-      <c r="D94" s="6" t="n">
+      <c r="D94" s="3" t="n">
         <v>31.1648623</v>
       </c>
       <c r="E94" t="n">
@@ -2509,10 +2614,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C95" s="5" t="n">
+      <c r="C95" s="2" t="n">
         <v>1029.41</v>
       </c>
-      <c r="D95" s="6" t="n">
+      <c r="D95" s="3" t="n">
         <v>0.31513536</v>
       </c>
       <c r="E95" t="n">
@@ -2530,10 +2635,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C96" s="5" t="n">
+      <c r="C96" s="2" t="n">
         <v>1848</v>
       </c>
-      <c r="D96" s="6" t="n">
+      <c r="D96" s="3" t="n">
         <v>0.56573196</v>
       </c>
       <c r="E96" t="n">
@@ -2551,10 +2656,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C97" s="5" t="n">
+      <c r="C97" s="2" t="n">
         <v>126297.98</v>
       </c>
-      <c r="D97" s="6" t="n">
+      <c r="D97" s="3" t="n">
         <v>38.66385499</v>
       </c>
       <c r="E97" t="n">
@@ -2572,10 +2677,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C98" s="5" t="n">
+      <c r="C98" s="2" t="n">
         <v>23680.09</v>
       </c>
-      <c r="D98" s="6" t="n">
+      <c r="D98" s="3" t="n">
         <v>7.24923364</v>
       </c>
       <c r="E98" t="n">
@@ -2593,10 +2698,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C99" s="5" t="n">
+      <c r="C99" s="2" t="n">
         <v>173800.98</v>
       </c>
-      <c r="D99" s="6" t="n">
+      <c r="D99" s="3" t="n">
         <v>53.20604405</v>
       </c>
       <c r="E99" t="n">
@@ -2614,10 +2719,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C100" s="5" t="n">
+      <c r="C100" s="2" t="n">
         <v>856.11</v>
       </c>
-      <c r="D100" s="6" t="n">
+      <c r="D100" s="3" t="n">
         <v>0.22747196</v>
       </c>
       <c r="E100" t="n">
@@ -2635,10 +2740,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C101" s="5" t="n">
+      <c r="C101" s="2" t="n">
         <v>9.68</v>
       </c>
-      <c r="D101" s="6" t="n">
+      <c r="D101" s="3" t="n">
         <v>0.00257202</v>
       </c>
       <c r="E101" t="n">
@@ -2656,10 +2761,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C102" s="5" t="n">
+      <c r="C102" s="2" t="n">
         <v>296012.79</v>
       </c>
-      <c r="D102" s="6" t="n">
+      <c r="D102" s="3" t="n">
         <v>78.65181887</v>
       </c>
       <c r="E102" t="n">
@@ -2677,10 +2782,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C103" s="5" t="n">
+      <c r="C103" s="2" t="n">
         <v>3709.15</v>
       </c>
-      <c r="D103" s="6" t="n">
+      <c r="D103" s="3" t="n">
         <v>0.98553645</v>
       </c>
       <c r="E103" t="n">
@@ -2698,10 +2803,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C104" s="5" t="n">
+      <c r="C104" s="2" t="n">
         <v>75770.75</v>
       </c>
-      <c r="D104" s="6" t="n">
+      <c r="D104" s="3" t="n">
         <v>20.13260071</v>
       </c>
       <c r="E104" t="n">
@@ -2719,10 +2824,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C105" s="5" t="n">
+      <c r="C105" s="2" t="n">
         <v>363.62</v>
       </c>
-      <c r="D105" s="6" t="n">
+      <c r="D105" s="3" t="n">
         <v>0.09792976</v>
       </c>
       <c r="E105" t="n">
@@ -2740,10 +2845,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C106" s="5" t="n">
+      <c r="C106" s="2" t="n">
         <v>303265.05</v>
       </c>
-      <c r="D106" s="6" t="n">
+      <c r="D106" s="3" t="n">
         <v>81.67502655</v>
       </c>
       <c r="E106" t="n">
@@ -2761,10 +2866,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C107" s="5" t="n">
+      <c r="C107" s="2" t="n">
         <v>829.42</v>
       </c>
-      <c r="D107" s="6" t="n">
+      <c r="D107" s="3" t="n">
         <v>0.22337853</v>
       </c>
       <c r="E107" t="n">
@@ -2782,10 +2887,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C108" s="5" t="n">
+      <c r="C108" s="2" t="n">
         <v>66848.86</v>
       </c>
-      <c r="D108" s="6" t="n">
+      <c r="D108" s="3" t="n">
         <v>18.00366516</v>
       </c>
       <c r="E108" t="n">
@@ -2803,10 +2908,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C109" s="5" t="n">
+      <c r="C109" s="2" t="n">
         <v>174192.16</v>
       </c>
-      <c r="D109" s="6" t="n">
+      <c r="D109" s="3" t="n">
         <v>66.86566559000001</v>
       </c>
       <c r="E109" t="n">
@@ -2824,10 +2929,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C110" s="5" t="n">
+      <c r="C110" s="2" t="n">
         <v>19438.25</v>
       </c>
-      <c r="D110" s="6" t="n">
+      <c r="D110" s="3" t="n">
         <v>7.461596</v>
       </c>
       <c r="E110" t="n">
@@ -2845,10 +2950,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C111" s="5" t="n">
+      <c r="C111" s="2" t="n">
         <v>66880.21000000001</v>
       </c>
-      <c r="D111" s="6" t="n">
+      <c r="D111" s="3" t="n">
         <v>25.67273841</v>
       </c>
       <c r="E111" t="n">
@@ -2866,10 +2971,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C112" s="5" t="n">
+      <c r="C112" s="2" t="n">
         <v>1885.29</v>
       </c>
-      <c r="D112" s="6" t="n">
+      <c r="D112" s="3" t="n">
         <v>0.5105483200000001</v>
       </c>
       <c r="E112" t="n">
@@ -2887,10 +2992,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C113" s="5" t="n">
+      <c r="C113" s="2" t="n">
         <v>642.63</v>
       </c>
-      <c r="D113" s="6" t="n">
+      <c r="D113" s="3" t="n">
         <v>0.17402822</v>
       </c>
       <c r="E113" t="n">
@@ -2908,10 +3013,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C114" s="5" t="n">
+      <c r="C114" s="2" t="n">
         <v>2177.75</v>
       </c>
-      <c r="D114" s="6" t="n">
+      <c r="D114" s="3" t="n">
         <v>0.58974832</v>
       </c>
       <c r="E114" t="n">
@@ -2929,10 +3034,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C115" s="5" t="n">
+      <c r="C115" s="2" t="n">
         <v>202289.9</v>
       </c>
-      <c r="D115" s="6" t="n">
+      <c r="D115" s="3" t="n">
         <v>54.78137012</v>
       </c>
       <c r="E115" t="n">
@@ -2950,10 +3055,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C116" s="5" t="n">
+      <c r="C116" s="2" t="n">
         <v>30328.46</v>
       </c>
-      <c r="D116" s="6" t="n">
+      <c r="D116" s="3" t="n">
         <v>8.213136649999999</v>
       </c>
       <c r="E116" t="n">
@@ -2971,10 +3076,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C117" s="5" t="n">
+      <c r="C117" s="2" t="n">
         <v>131943.66</v>
       </c>
-      <c r="D117" s="6" t="n">
+      <c r="D117" s="3" t="n">
         <v>35.73116836</v>
       </c>
       <c r="E117" t="n">
@@ -2992,10 +3097,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C118" s="5" t="n">
+      <c r="C118" s="2" t="n">
         <v>101.72</v>
       </c>
-      <c r="D118" s="6" t="n">
+      <c r="D118" s="3" t="n">
         <v>0.03804713</v>
       </c>
       <c r="E118" t="n">
@@ -3013,10 +3118,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C119" s="5" t="n">
+      <c r="C119" s="2" t="n">
         <v>58</v>
       </c>
-      <c r="D119" s="6" t="n">
+      <c r="D119" s="3" t="n">
         <v>0.02169419</v>
       </c>
       <c r="E119" t="n">
@@ -3034,10 +3139,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C120" s="5" t="n">
+      <c r="C120" s="2" t="n">
         <v>167439.3</v>
       </c>
-      <c r="D120" s="6" t="n">
+      <c r="D120" s="3" t="n">
         <v>62.62863161</v>
       </c>
       <c r="E120" t="n">
@@ -3055,10 +3160,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C121" s="5" t="n">
+      <c r="C121" s="2" t="n">
         <v>7300.3</v>
       </c>
-      <c r="D121" s="6" t="n">
+      <c r="D121" s="3" t="n">
         <v>2.73058833</v>
       </c>
       <c r="E121" t="n">
@@ -3076,10 +3181,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C122" s="5" t="n">
+      <c r="C122" s="2" t="n">
         <v>92453.32000000001</v>
       </c>
-      <c r="D122" s="6" t="n">
+      <c r="D122" s="3" t="n">
         <v>34.58103874</v>
       </c>
       <c r="E122" t="n">
@@ -3097,10 +3202,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C123" s="5" t="n">
+      <c r="C123" s="2" t="n">
         <v>1475.74</v>
       </c>
-      <c r="D123" s="6" t="n">
+      <c r="D123" s="3" t="n">
         <v>0.33417908</v>
       </c>
       <c r="E123" t="n">
@@ -3118,10 +3223,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C124" s="5" t="n">
+      <c r="C124" s="2" t="n">
         <v>2209.05</v>
       </c>
-      <c r="D124" s="6" t="n">
+      <c r="D124" s="3" t="n">
         <v>0.50023602</v>
       </c>
       <c r="E124" t="n">
@@ -3139,10 +3244,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C125" s="5" t="n">
+      <c r="C125" s="2" t="n">
         <v>232354.93</v>
       </c>
-      <c r="D125" s="6" t="n">
+      <c r="D125" s="3" t="n">
         <v>52.61642084</v>
       </c>
       <c r="E125" t="n">
@@ -3160,10 +3265,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C126" s="5" t="n">
+      <c r="C126" s="2" t="n">
         <v>11084.31</v>
       </c>
-      <c r="D126" s="6" t="n">
+      <c r="D126" s="3" t="n">
         <v>2.51002516</v>
       </c>
       <c r="E126" t="n">
@@ -3181,10 +3286,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C127" s="5" t="n">
+      <c r="C127" s="2" t="n">
         <v>194477.52</v>
       </c>
-      <c r="D127" s="6" t="n">
+      <c r="D127" s="3" t="n">
         <v>44.0391389</v>
       </c>
       <c r="E127" t="n">
@@ -3202,10 +3307,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C128" s="5" t="n">
+      <c r="C128" s="2" t="n">
         <v>2990.78</v>
       </c>
-      <c r="D128" s="6" t="n">
+      <c r="D128" s="3" t="n">
         <v>0.63513389</v>
       </c>
       <c r="E128" t="n">
@@ -3223,10 +3328,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C129" s="5" t="n">
+      <c r="C129" s="2" t="n">
         <v>847.45</v>
       </c>
-      <c r="D129" s="6" t="n">
+      <c r="D129" s="3" t="n">
         <v>0.17996784</v>
       </c>
       <c r="E129" t="n">
@@ -3244,10 +3349,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C130" s="5" t="n">
+      <c r="C130" s="2" t="n">
         <v>211.86</v>
       </c>
-      <c r="D130" s="6" t="n">
+      <c r="D130" s="3" t="n">
         <v>0.04499143</v>
       </c>
       <c r="E130" t="n">
@@ -3265,10 +3370,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C131" s="5" t="n">
+      <c r="C131" s="2" t="n">
         <v>222684.94</v>
       </c>
-      <c r="D131" s="6" t="n">
+      <c r="D131" s="3" t="n">
         <v>47.29025603</v>
       </c>
       <c r="E131" t="n">
@@ -3286,10 +3391,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C132" s="5" t="n">
+      <c r="C132" s="2" t="n">
         <v>10642.51</v>
       </c>
-      <c r="D132" s="6" t="n">
+      <c r="D132" s="3" t="n">
         <v>2.26008558</v>
       </c>
       <c r="E132" t="n">
@@ -3307,10 +3412,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C133" s="5" t="n">
+      <c r="C133" s="2" t="n">
         <v>233512.15</v>
       </c>
-      <c r="D133" s="6" t="n">
+      <c r="D133" s="3" t="n">
         <v>49.58956523</v>
       </c>
       <c r="E133" t="n">
@@ -3328,10 +3433,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C134" s="5" t="n">
+      <c r="C134" s="2" t="n">
         <v>2894.67</v>
       </c>
-      <c r="D134" s="6" t="n">
+      <c r="D134" s="3" t="n">
         <v>0.84868485</v>
       </c>
       <c r="E134" t="n">
@@ -3349,10 +3454,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C135" s="5" t="n">
+      <c r="C135" s="2" t="n">
         <v>2112.75</v>
       </c>
-      <c r="D135" s="6" t="n">
+      <c r="D135" s="3" t="n">
         <v>0.61943465</v>
       </c>
       <c r="E135" t="n">
@@ -3370,10 +3475,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C136" s="5" t="n">
+      <c r="C136" s="2" t="n">
         <v>133738.48</v>
       </c>
-      <c r="D136" s="6" t="n">
+      <c r="D136" s="3" t="n">
         <v>39.21062549</v>
       </c>
       <c r="E136" t="n">
@@ -3391,10 +3496,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C137" s="5" t="n">
+      <c r="C137" s="2" t="n">
         <v>9278.84</v>
       </c>
-      <c r="D137" s="6" t="n">
+      <c r="D137" s="3" t="n">
         <v>2.72045204</v>
       </c>
       <c r="E137" t="n">
@@ -3412,10 +3517,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C138" s="5" t="n">
+      <c r="C138" s="2" t="n">
         <v>193052.4</v>
       </c>
-      <c r="D138" s="6" t="n">
+      <c r="D138" s="3" t="n">
         <v>56.60080297</v>
       </c>
       <c r="E138" t="n">
@@ -3433,10 +3538,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C139" s="5" t="n">
+      <c r="C139" s="2" t="n">
         <v>138.16</v>
       </c>
-      <c r="D139" s="6" t="n">
+      <c r="D139" s="3" t="n">
         <v>0.04037037</v>
       </c>
       <c r="E139" t="n">
@@ -3454,10 +3559,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C140" s="5" t="n">
+      <c r="C140" s="2" t="n">
         <v>165616.96</v>
       </c>
-      <c r="D140" s="6" t="n">
+      <c r="D140" s="3" t="n">
         <v>48.39329811</v>
       </c>
       <c r="E140" t="n">
@@ -3475,10 +3580,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C141" s="5" t="n">
+      <c r="C141" s="2" t="n">
         <v>14589.85</v>
       </c>
-      <c r="D141" s="6" t="n">
+      <c r="D141" s="3" t="n">
         <v>4.26315614</v>
       </c>
       <c r="E141" t="n">
@@ -3496,10 +3601,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C142" s="5" t="n">
+      <c r="C142" s="2" t="n">
         <v>161886.22</v>
       </c>
-      <c r="D142" s="6" t="n">
+      <c r="D142" s="3" t="n">
         <v>47.30317538</v>
       </c>
       <c r="E142" t="n">
@@ -3517,10 +3622,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C143" s="5" t="n">
+      <c r="C143" s="2" t="n">
         <v>39179.97</v>
       </c>
-      <c r="D143" s="6" t="n">
+      <c r="D143" s="3" t="n">
         <v>6.57522763</v>
       </c>
       <c r="E143" t="n">
@@ -3538,10 +3643,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C144" s="5" t="n">
+      <c r="C144" s="2" t="n">
         <v>142325.87</v>
       </c>
-      <c r="D144" s="6" t="n">
+      <c r="D144" s="3" t="n">
         <v>23.88529122</v>
       </c>
       <c r="E144" t="n">
@@ -3559,10 +3664,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C145" s="5" t="n">
+      <c r="C145" s="2" t="n">
         <v>16620.71</v>
       </c>
-      <c r="D145" s="6" t="n">
+      <c r="D145" s="3" t="n">
         <v>2.78930667</v>
       </c>
       <c r="E145" t="n">
@@ -3580,10 +3685,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C146" s="5" t="n">
+      <c r="C146" s="2" t="n">
         <v>397745.9</v>
       </c>
-      <c r="D146" s="6" t="n">
+      <c r="D146" s="3" t="n">
         <v>66.75017447</v>
       </c>
       <c r="E146" t="n">
@@ -3601,10 +3706,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C147" s="5" t="n">
+      <c r="C147" s="2" t="n">
         <v>1244.23</v>
       </c>
-      <c r="D147" s="6" t="n">
+      <c r="D147" s="3" t="n">
         <v>0.42616348</v>
       </c>
       <c r="E147" t="n">
@@ -3622,10 +3727,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C148" s="5" t="n">
+      <c r="C148" s="2" t="n">
         <v>4545.45</v>
       </c>
-      <c r="D148" s="6" t="n">
+      <c r="D148" s="3" t="n">
         <v>1.55687034</v>
       </c>
       <c r="E148" t="n">
@@ -3643,10 +3748,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C149" s="5" t="n">
+      <c r="C149" s="2" t="n">
         <v>54421.47</v>
       </c>
-      <c r="D149" s="6" t="n">
+      <c r="D149" s="3" t="n">
         <v>18.63999655</v>
       </c>
       <c r="E149" t="n">
@@ -3664,10 +3769,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C150" s="5" t="n">
+      <c r="C150" s="2" t="n">
         <v>231749.58</v>
       </c>
-      <c r="D150" s="6" t="n">
+      <c r="D150" s="3" t="n">
         <v>79.37696964</v>
       </c>
       <c r="E150" t="n">
@@ -3685,10 +3790,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C151" s="5" t="n">
+      <c r="C151" s="2" t="n">
         <v>29.6</v>
       </c>
-      <c r="D151" s="6" t="n">
+      <c r="D151" s="3" t="n">
         <v>0.00689719</v>
       </c>
       <c r="E151" t="n">
@@ -3706,10 +3811,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C152" s="5" t="n">
+      <c r="C152" s="2" t="n">
         <v>309.27</v>
       </c>
-      <c r="D152" s="6" t="n">
+      <c r="D152" s="3" t="n">
         <v>0.07206398</v>
       </c>
       <c r="E152" t="n">
@@ -3727,10 +3832,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C153" s="5" t="n">
+      <c r="C153" s="2" t="n">
         <v>3725.16</v>
       </c>
-      <c r="D153" s="6" t="n">
+      <c r="D153" s="3" t="n">
         <v>0.8680113</v>
       </c>
       <c r="E153" t="n">
@@ -3748,10 +3853,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C154" s="5" t="n">
+      <c r="C154" s="2" t="n">
         <v>8.109999999999999</v>
       </c>
-      <c r="D154" s="6" t="n">
+      <c r="D154" s="3" t="n">
         <v>0.00188974</v>
       </c>
       <c r="E154" t="n">
@@ -3769,10 +3874,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C155" s="5" t="n">
+      <c r="C155" s="2" t="n">
         <v>163136.27</v>
       </c>
-      <c r="D155" s="6" t="n">
+      <c r="D155" s="3" t="n">
         <v>38.01289779</v>
       </c>
       <c r="E155" t="n">
@@ -3790,10 +3895,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C156" s="5" t="n">
+      <c r="C156" s="2" t="n">
         <v>261951.9</v>
       </c>
-      <c r="D156" s="6" t="n">
+      <c r="D156" s="3" t="n">
         <v>61.03824</v>
       </c>
       <c r="E156" t="n">
@@ -3811,10 +3916,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C157" s="5" t="n">
+      <c r="C157" s="2" t="n">
         <v>55.55</v>
       </c>
-      <c r="D157" s="6" t="n">
+      <c r="D157" s="3" t="n">
         <v>0.01644298</v>
       </c>
       <c r="E157" t="n">
@@ -3832,10 +3937,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C158" s="5" t="n">
+      <c r="C158" s="2" t="n">
         <v>91.41</v>
       </c>
-      <c r="D158" s="6" t="n">
+      <c r="D158" s="3" t="n">
         <v>0.02705766</v>
       </c>
       <c r="E158" t="n">
@@ -3853,10 +3958,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C159" s="5" t="n">
+      <c r="C159" s="2" t="n">
         <v>5382.13</v>
       </c>
-      <c r="D159" s="6" t="n">
+      <c r="D159" s="3" t="n">
         <v>1.59312834</v>
       </c>
       <c r="E159" t="n">
@@ -3874,10 +3979,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C160" s="5" t="n">
+      <c r="C160" s="2" t="n">
         <v>909.09</v>
       </c>
-      <c r="D160" s="6" t="n">
+      <c r="D160" s="3" t="n">
         <v>0.26909366</v>
       </c>
       <c r="E160" t="n">
@@ -3895,10 +4000,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C161" s="5" t="n">
+      <c r="C161" s="2" t="n">
         <v>32670.17</v>
       </c>
-      <c r="D161" s="6" t="n">
+      <c r="D161" s="3" t="n">
         <v>9.670478749999999</v>
       </c>
       <c r="E161" t="n">
@@ -3916,10 +4021,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C162" s="5" t="n">
+      <c r="C162" s="2" t="n">
         <v>298725.7</v>
       </c>
-      <c r="D162" s="6" t="n">
+      <c r="D162" s="3" t="n">
         <v>88.42379861000001</v>
       </c>
       <c r="E162" t="n">
@@ -3937,10 +4042,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C163" s="5" t="n">
+      <c r="C163" s="2" t="n">
         <v>287.66</v>
       </c>
-      <c r="D163" s="6" t="n">
+      <c r="D163" s="3" t="n">
         <v>0.08204844999999999</v>
       </c>
       <c r="E163" t="n">
@@ -3958,10 +4063,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C164" s="5" t="n">
+      <c r="C164" s="2" t="n">
         <v>9919.66</v>
       </c>
-      <c r="D164" s="6" t="n">
+      <c r="D164" s="3" t="n">
         <v>2.82935676</v>
       </c>
       <c r="E164" t="n">
@@ -3979,10 +4084,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C165" s="5" t="n">
+      <c r="C165" s="2" t="n">
         <v>1385.01</v>
       </c>
-      <c r="D165" s="6" t="n">
+      <c r="D165" s="3" t="n">
         <v>0.39504251</v>
       </c>
       <c r="E165" t="n">
@@ -4000,10 +4105,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C166" s="5" t="n">
+      <c r="C166" s="2" t="n">
         <v>69940.2</v>
       </c>
-      <c r="D166" s="6" t="n">
+      <c r="D166" s="3" t="n">
         <v>19.94884679</v>
       </c>
       <c r="E166" t="n">
@@ -4021,10 +4126,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C167" s="5" t="n">
+      <c r="C167" s="2" t="n">
         <v>269065.18</v>
       </c>
-      <c r="D167" s="6" t="n">
+      <c r="D167" s="3" t="n">
         <v>76.74470549</v>
       </c>
       <c r="E167" t="n">
@@ -4042,10 +4147,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C168" s="5" t="n">
+      <c r="C168" s="2" t="n">
         <v>580.2</v>
       </c>
-      <c r="D168" s="6" t="n">
+      <c r="D168" s="3" t="n">
         <v>0.1561468</v>
       </c>
       <c r="E168" t="n">
@@ -4063,10 +4168,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C169" s="5" t="n">
+      <c r="C169" s="2" t="n">
         <v>98.44</v>
       </c>
-      <c r="D169" s="6" t="n">
+      <c r="D169" s="3" t="n">
         <v>0.02649275</v>
       </c>
       <c r="E169" t="n">
@@ -4084,10 +4189,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C170" s="5" t="n">
+      <c r="C170" s="2" t="n">
         <v>172.72</v>
       </c>
-      <c r="D170" s="6" t="n">
+      <c r="D170" s="3" t="n">
         <v>0.04648341</v>
       </c>
       <c r="E170" t="n">
@@ -4105,10 +4210,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C171" s="5" t="n">
+      <c r="C171" s="2" t="n">
         <v>3342.15</v>
       </c>
-      <c r="D171" s="6" t="n">
+      <c r="D171" s="3" t="n">
         <v>0.89945887</v>
       </c>
       <c r="E171" t="n">
@@ -4126,10 +4231,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C172" s="5" t="n">
+      <c r="C172" s="2" t="n">
         <v>7627.33</v>
       </c>
-      <c r="D172" s="6" t="n">
+      <c r="D172" s="3" t="n">
         <v>2.05271147</v>
       </c>
       <c r="E172" t="n">
@@ -4147,10 +4252,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C173" s="5" t="n">
+      <c r="C173" s="2" t="n">
         <v>359752.57</v>
       </c>
-      <c r="D173" s="6" t="n">
+      <c r="D173" s="3" t="n">
         <v>96.81870670000001</v>
       </c>
       <c r="E173" t="n">
@@ -4168,10 +4273,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C174" s="5" t="n">
+      <c r="C174" s="2" t="n">
         <v>61.94</v>
       </c>
-      <c r="D174" s="6" t="n">
+      <c r="D174" s="3" t="n">
         <v>0.02167129</v>
       </c>
       <c r="E174" t="n">
@@ -4189,10 +4294,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C175" s="5" t="n">
+      <c r="C175" s="2" t="n">
         <v>222</v>
       </c>
-      <c r="D175" s="6" t="n">
+      <c r="D175" s="3" t="n">
         <v>0.07767236</v>
       </c>
       <c r="E175" t="n">
@@ -4210,10 +4315,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C176" s="5" t="n">
+      <c r="C176" s="2" t="n">
         <v>10426.45</v>
       </c>
-      <c r="D176" s="6" t="n">
+      <c r="D176" s="3" t="n">
         <v>3.64795946</v>
       </c>
       <c r="E176" t="n">
@@ -4231,10 +4336,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C177" s="5" t="n">
+      <c r="C177" s="2" t="n">
         <v>36051.27</v>
       </c>
-      <c r="D177" s="6" t="n">
+      <c r="D177" s="3" t="n">
         <v>12.61345632</v>
       </c>
       <c r="E177" t="n">
@@ -4252,10 +4357,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C178" s="5" t="n">
+      <c r="C178" s="2" t="n">
         <v>239054.29</v>
       </c>
-      <c r="D178" s="6" t="n">
+      <c r="D178" s="3" t="n">
         <v>83.63924057</v>
       </c>
       <c r="E178" t="n">
@@ -4273,10 +4378,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C179" s="5" t="n">
+      <c r="C179" s="2" t="n">
         <v>1971.96</v>
       </c>
-      <c r="D179" s="6" t="n">
+      <c r="D179" s="3" t="n">
         <v>0.29536296</v>
       </c>
       <c r="E179" t="n">
@@ -4294,10 +4399,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C180" s="5" t="n">
+      <c r="C180" s="2" t="n">
         <v>970.1799999999999</v>
       </c>
-      <c r="D180" s="6" t="n">
+      <c r="D180" s="3" t="n">
         <v>0.14531493</v>
       </c>
       <c r="E180" t="n">
@@ -4315,10 +4420,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C181" s="5" t="n">
+      <c r="C181" s="2" t="n">
         <v>23400.38</v>
       </c>
-      <c r="D181" s="6" t="n">
+      <c r="D181" s="3" t="n">
         <v>3.50494199</v>
       </c>
       <c r="E181" t="n">
@@ -4336,10 +4441,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C182" s="5" t="n">
+      <c r="C182" s="2" t="n">
         <v>158698.51</v>
       </c>
-      <c r="D182" s="6" t="n">
+      <c r="D182" s="3" t="n">
         <v>23.77008715</v>
       </c>
       <c r="E182" t="n">
@@ -4357,10 +4462,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C183" s="5" t="n">
+      <c r="C183" s="2" t="n">
         <v>482598.55</v>
       </c>
-      <c r="D183" s="6" t="n">
+      <c r="D183" s="3" t="n">
         <v>72.28429297</v>
       </c>
       <c r="E183" t="n">
@@ -4378,10 +4483,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C184" s="5" t="n">
+      <c r="C184" s="2" t="n">
         <v>349.42</v>
       </c>
-      <c r="D184" s="6" t="n">
+      <c r="D184" s="3" t="n">
         <v>0.0757804</v>
       </c>
       <c r="E184" t="n">
@@ -4399,10 +4504,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C185" s="5" t="n">
+      <c r="C185" s="2" t="n">
         <v>5203.15</v>
       </c>
-      <c r="D185" s="6" t="n">
+      <c r="D185" s="3" t="n">
         <v>1.12843225</v>
       </c>
       <c r="E185" t="n">
@@ -4420,10 +4525,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C186" s="5" t="n">
+      <c r="C186" s="2" t="n">
         <v>43002.78</v>
       </c>
-      <c r="D186" s="6" t="n">
+      <c r="D186" s="3" t="n">
         <v>9.326220449999999</v>
       </c>
       <c r="E186" t="n">
@@ -4441,10 +4546,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C187" s="5" t="n">
+      <c r="C187" s="2" t="n">
         <v>412540.12</v>
       </c>
-      <c r="D187" s="6" t="n">
+      <c r="D187" s="3" t="n">
         <v>89.4695669</v>
       </c>
       <c r="E187" t="n">
@@ -4462,10 +4567,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C188" s="5" t="n">
+      <c r="C188" s="2" t="n">
         <v>1231.47</v>
       </c>
-      <c r="D188" s="6" t="n">
+      <c r="D188" s="3" t="n">
         <v>0.34199572</v>
       </c>
       <c r="E188" t="n">
@@ -4483,10 +4588,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C189" s="5" t="n">
+      <c r="C189" s="2" t="n">
         <v>484.18</v>
       </c>
-      <c r="D189" s="6" t="n">
+      <c r="D189" s="3" t="n">
         <v>0.13446328</v>
       </c>
       <c r="E189" t="n">
@@ -4504,10 +4609,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C190" s="5" t="n">
+      <c r="C190" s="2" t="n">
         <v>29461.66</v>
       </c>
-      <c r="D190" s="6" t="n">
+      <c r="D190" s="3" t="n">
         <v>8.18189784</v>
       </c>
       <c r="E190" t="n">
@@ -4525,10 +4630,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C191" s="5" t="n">
+      <c r="C191" s="2" t="n">
         <v>328906.14</v>
       </c>
-      <c r="D191" s="6" t="n">
+      <c r="D191" s="3" t="n">
         <v>91.34164317</v>
       </c>
       <c r="E191" t="n">
@@ -4546,10 +4651,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C192" s="5" t="n">
+      <c r="C192" s="2" t="n">
         <v>23.47</v>
       </c>
-      <c r="D192" s="6" t="n">
+      <c r="D192" s="3" t="n">
         <v>0.00471838</v>
       </c>
       <c r="E192" t="n">
@@ -4567,10 +4672,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C193" s="5" t="n">
+      <c r="C193" s="2" t="n">
         <v>13128.29</v>
       </c>
-      <c r="D193" s="6" t="n">
+      <c r="D193" s="3" t="n">
         <v>2.63929312</v>
       </c>
       <c r="E193" t="n">
@@ -4588,10 +4693,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C194" s="5" t="n">
+      <c r="C194" s="2" t="n">
         <v>42522.52</v>
       </c>
-      <c r="D194" s="6" t="n">
+      <c r="D194" s="3" t="n">
         <v>8.548668129999999</v>
       </c>
       <c r="E194" t="n">
@@ -4609,10 +4714,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C195" s="5" t="n">
+      <c r="C195" s="2" t="n">
         <v>441742.62</v>
       </c>
-      <c r="D195" s="6" t="n">
+      <c r="D195" s="3" t="n">
         <v>88.80732037999999</v>
       </c>
       <c r="E195" t="n">
@@ -4630,10 +4735,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C196" s="5" t="n">
+      <c r="C196" s="2" t="n">
         <v>14510.35</v>
       </c>
-      <c r="D196" s="6" t="n">
+      <c r="D196" s="3" t="n">
         <v>2.82318771</v>
       </c>
       <c r="E196" t="n">
@@ -4651,10 +4756,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C197" s="5" t="n">
+      <c r="C197" s="2" t="n">
         <v>29796.3</v>
       </c>
-      <c r="D197" s="6" t="n">
+      <c r="D197" s="3" t="n">
         <v>5.79727904</v>
       </c>
       <c r="E197" t="n">
@@ -4672,10 +4777,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C198" s="5" t="n">
+      <c r="C198" s="2" t="n">
         <v>489.48</v>
       </c>
-      <c r="D198" s="6" t="n">
+      <c r="D198" s="3" t="n">
         <v>0.09523505</v>
       </c>
       <c r="E198" t="n">
@@ -4693,10 +4798,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C199" s="5" t="n">
+      <c r="C199" s="2" t="n">
         <v>45623.94</v>
       </c>
-      <c r="D199" s="6" t="n">
+      <c r="D199" s="3" t="n">
         <v>8.876763589999999</v>
       </c>
       <c r="E199" t="n">
@@ -4714,10 +4819,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C200" s="5" t="n">
+      <c r="C200" s="2" t="n">
         <v>423550.36</v>
       </c>
-      <c r="D200" s="6" t="n">
+      <c r="D200" s="3" t="n">
         <v>82.40753461</v>
       </c>
       <c r="E200" t="n">
@@ -4735,10 +4840,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C201" s="5" t="n">
+      <c r="C201" s="2" t="n">
         <v>2894.83</v>
       </c>
-      <c r="D201" s="6" t="n">
+      <c r="D201" s="3" t="n">
         <v>0.57425271</v>
       </c>
       <c r="E201" t="n">
@@ -4756,10 +4861,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C202" s="5" t="n">
+      <c r="C202" s="2" t="n">
         <v>19389.84</v>
       </c>
-      <c r="D202" s="6" t="n">
+      <c r="D202" s="3" t="n">
         <v>3.84639792</v>
       </c>
       <c r="E202" t="n">
@@ -4777,10 +4882,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C203" s="5" t="n">
+      <c r="C203" s="2" t="n">
         <v>7103.09</v>
       </c>
-      <c r="D203" s="6" t="n">
+      <c r="D203" s="3" t="n">
         <v>1.40905292</v>
       </c>
       <c r="E203" t="n">
@@ -4798,10 +4903,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C204" s="5" t="n">
+      <c r="C204" s="2" t="n">
         <v>71555.96000000001</v>
       </c>
-      <c r="D204" s="6" t="n">
+      <c r="D204" s="3" t="n">
         <v>14.19468627</v>
       </c>
       <c r="E204" t="n">
@@ -4819,10 +4924,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C205" s="5" t="n">
+      <c r="C205" s="2" t="n">
         <v>403160.13</v>
       </c>
-      <c r="D205" s="6" t="n">
+      <c r="D205" s="3" t="n">
         <v>79.97561018</v>
       </c>
       <c r="E205" t="n">
@@ -4840,10 +4945,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C206" s="5" t="n">
+      <c r="C206" s="2" t="n">
         <v>13873.76</v>
       </c>
-      <c r="D206" s="6" t="n">
+      <c r="D206" s="3" t="n">
         <v>4.61749343</v>
       </c>
       <c r="E206" t="n">
@@ -4861,10 +4966,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C207" s="5" t="n">
+      <c r="C207" s="2" t="n">
         <v>5637.21</v>
       </c>
-      <c r="D207" s="6" t="n">
+      <c r="D207" s="3" t="n">
         <v>1.87618786</v>
       </c>
       <c r="E207" t="n">
@@ -4882,10 +4987,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C208" s="5" t="n">
+      <c r="C208" s="2" t="n">
         <v>1363.63</v>
       </c>
-      <c r="D208" s="6" t="n">
+      <c r="D208" s="3" t="n">
         <v>0.45384615</v>
       </c>
       <c r="E208" t="n">
@@ -4903,10 +5008,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C209" s="5" t="n">
+      <c r="C209" s="2" t="n">
         <v>35429.67</v>
       </c>
-      <c r="D209" s="6" t="n">
+      <c r="D209" s="3" t="n">
         <v>11.79177587</v>
       </c>
       <c r="E209" t="n">
@@ -4924,10 +5029,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C210" s="5" t="n">
+      <c r="C210" s="2" t="n">
         <v>244156.58</v>
       </c>
-      <c r="D210" s="6" t="n">
+      <c r="D210" s="3" t="n">
         <v>81.26069669</v>
       </c>
       <c r="E210" t="n">
@@ -4945,10 +5050,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C211" s="5" t="n">
+      <c r="C211" s="2" t="n">
         <v>3194.31</v>
       </c>
-      <c r="D211" s="6" t="n">
+      <c r="D211" s="3" t="n">
         <v>0.86754762</v>
       </c>
       <c r="E211" t="n">
@@ -4966,10 +5071,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C212" s="5" t="n">
+      <c r="C212" s="2" t="n">
         <v>53332.81</v>
       </c>
-      <c r="D212" s="6" t="n">
+      <c r="D212" s="3" t="n">
         <v>14.48474085</v>
       </c>
       <c r="E212" t="n">
@@ -4987,10 +5092,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C213" s="5" t="n">
+      <c r="C213" s="2" t="n">
         <v>5480.02</v>
       </c>
-      <c r="D213" s="6" t="n">
+      <c r="D213" s="3" t="n">
         <v>1.48832716</v>
       </c>
       <c r="E213" t="n">
@@ -5008,10 +5113,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C214" s="5" t="n">
+      <c r="C214" s="2" t="n">
         <v>54619.67</v>
       </c>
-      <c r="D214" s="6" t="n">
+      <c r="D214" s="3" t="n">
         <v>14.83424116</v>
       </c>
       <c r="E214" t="n">
@@ -5029,10 +5134,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C215" s="5" t="n">
+      <c r="C215" s="2" t="n">
         <v>251573.15</v>
       </c>
-      <c r="D215" s="6" t="n">
+      <c r="D215" s="3" t="n">
         <v>68.32514322</v>
       </c>
       <c r="E215" t="n">
@@ -5050,10 +5155,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C216" s="5" t="n">
+      <c r="C216" s="2" t="n">
         <v>892</v>
       </c>
-      <c r="D216" s="6" t="n">
+      <c r="D216" s="3" t="n">
         <v>0.30548187</v>
       </c>
       <c r="E216" t="n">
@@ -5071,10 +5176,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C217" s="5" t="n">
+      <c r="C217" s="2" t="n">
         <v>7918.09</v>
       </c>
-      <c r="D217" s="6" t="n">
+      <c r="D217" s="3" t="n">
         <v>2.71169611</v>
       </c>
       <c r="E217" t="n">
@@ -5092,10 +5197,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C218" s="5" t="n">
+      <c r="C218" s="2" t="n">
         <v>37.66</v>
       </c>
-      <c r="D218" s="6" t="n">
+      <c r="D218" s="3" t="n">
         <v>0.01289736</v>
       </c>
       <c r="E218" t="n">
@@ -5113,10 +5218,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C219" s="5" t="n">
+      <c r="C219" s="2" t="n">
         <v>14209.15</v>
       </c>
-      <c r="D219" s="6" t="n">
+      <c r="D219" s="3" t="n">
         <v>4.86618576</v>
       </c>
       <c r="E219" t="n">
@@ -5134,10 +5239,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C220" s="5" t="n">
+      <c r="C220" s="2" t="n">
         <v>268940.79</v>
       </c>
-      <c r="D220" s="6" t="n">
+      <c r="D220" s="3" t="n">
         <v>92.1037389</v>
       </c>
       <c r="E220" t="n">
@@ -5155,10 +5260,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C221" s="5" t="n">
+      <c r="C221" s="2" t="n">
         <v>287</v>
       </c>
-      <c r="D221" s="6" t="n">
+      <c r="D221" s="3" t="n">
         <v>0.07919683</v>
       </c>
       <c r="E221" t="n">
@@ -5176,10 +5281,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C222" s="5" t="n">
+      <c r="C222" s="2" t="n">
         <v>17982.75</v>
       </c>
-      <c r="D222" s="6" t="n">
+      <c r="D222" s="3" t="n">
         <v>4.96228879</v>
       </c>
       <c r="E222" t="n">
@@ -5197,10 +5302,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C223" s="5" t="n">
+      <c r="C223" s="2" t="n">
         <v>2603.68</v>
       </c>
-      <c r="D223" s="6" t="n">
+      <c r="D223" s="3" t="n">
         <v>0.7184781</v>
       </c>
       <c r="E223" t="n">
@@ -5218,10 +5323,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C224" s="5" t="n">
+      <c r="C224" s="2" t="n">
         <v>34911.64</v>
       </c>
-      <c r="D224" s="6" t="n">
+      <c r="D224" s="3" t="n">
         <v>9.6337679</v>
       </c>
       <c r="E224" t="n">
@@ -5239,10 +5344,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C225" s="5" t="n">
+      <c r="C225" s="2" t="n">
         <v>306603.15</v>
       </c>
-      <c r="D225" s="6" t="n">
+      <c r="D225" s="3" t="n">
         <v>84.60626838</v>
       </c>
       <c r="E225" t="n">
@@ -5260,10 +5365,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C226" s="5" t="n">
+      <c r="C226" s="2" t="n">
         <v>1099.13</v>
       </c>
-      <c r="D226" s="6" t="n">
+      <c r="D226" s="3" t="n">
         <v>0.35003695</v>
       </c>
       <c r="E226" t="n">
@@ -5281,10 +5386,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C227" s="5" t="n">
+      <c r="C227" s="2" t="n">
         <v>1908.13</v>
       </c>
-      <c r="D227" s="6" t="n">
+      <c r="D227" s="3" t="n">
         <v>0.60767699</v>
       </c>
       <c r="E227" t="n">
@@ -5302,10 +5407,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C228" s="5" t="n">
+      <c r="C228" s="2" t="n">
         <v>1788.1</v>
       </c>
-      <c r="D228" s="6" t="n">
+      <c r="D228" s="3" t="n">
         <v>0.56945136</v>
       </c>
       <c r="E228" t="n">
@@ -5323,10 +5428,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C229" s="5" t="n">
+      <c r="C229" s="2" t="n">
         <v>54065.52</v>
       </c>
-      <c r="D229" s="6" t="n">
+      <c r="D229" s="3" t="n">
         <v>17.21809968</v>
       </c>
       <c r="E229" t="n">
@@ -5344,10 +5449,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C230" s="5" t="n">
+      <c r="C230" s="2" t="n">
         <v>255143.11</v>
       </c>
-      <c r="D230" s="6" t="n">
+      <c r="D230" s="3" t="n">
         <v>81.25473501</v>
       </c>
       <c r="E230" t="n">
@@ -5365,10 +5470,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C231" s="5" t="n">
+      <c r="C231" s="2" t="n">
         <v>2988.23</v>
       </c>
-      <c r="D231" s="6" t="n">
+      <c r="D231" s="3" t="n">
         <v>1.09502707</v>
       </c>
       <c r="E231" t="n">
@@ -5386,10 +5491,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C232" s="5" t="n">
+      <c r="C232" s="2" t="n">
         <v>89030.31</v>
       </c>
-      <c r="D232" s="6" t="n">
+      <c r="D232" s="3" t="n">
         <v>32.62486479</v>
       </c>
       <c r="E232" t="n">
@@ -5407,10 +5512,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C233" s="5" t="n">
+      <c r="C233" s="2" t="n">
         <v>180872.43</v>
       </c>
-      <c r="D233" s="6" t="n">
+      <c r="D233" s="3" t="n">
         <v>66.28010813</v>
       </c>
       <c r="E233" t="n">
@@ -5428,10 +5533,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C234" s="5" t="n">
+      <c r="C234" s="2" t="n">
         <v>232.92</v>
       </c>
-      <c r="D234" s="6" t="n">
+      <c r="D234" s="3" t="n">
         <v>0.10614272</v>
       </c>
       <c r="E234" t="n">
@@ -5449,10 +5554,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C235" s="5" t="n">
+      <c r="C235" s="2" t="n">
         <v>27443.48</v>
       </c>
-      <c r="D235" s="6" t="n">
+      <c r="D235" s="3" t="n">
         <v>12.50612011</v>
       </c>
       <c r="E235" t="n">
@@ -5470,10 +5575,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C236" s="5" t="n">
+      <c r="C236" s="2" t="n">
         <v>66453.41</v>
       </c>
-      <c r="D236" s="6" t="n">
+      <c r="D236" s="3" t="n">
         <v>30.28312471</v>
       </c>
       <c r="E236" t="n">
@@ -5491,10 +5596,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C237" s="5" t="n">
+      <c r="C237" s="2" t="n">
         <v>125310.59</v>
       </c>
-      <c r="D237" s="6" t="n">
+      <c r="D237" s="3" t="n">
         <v>57.10461246</v>
       </c>
       <c r="E237" t="n">
@@ -5512,10 +5617,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C238" s="5" t="n">
+      <c r="C238" s="2" t="n">
         <v>12206.63</v>
       </c>
-      <c r="D238" s="6" t="n">
+      <c r="D238" s="3" t="n">
         <v>2.80910278</v>
       </c>
       <c r="E238" t="n">
@@ -5533,10 +5638,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C239" s="5" t="n">
+      <c r="C239" s="2" t="n">
         <v>14439.81</v>
       </c>
-      <c r="D239" s="6" t="n">
+      <c r="D239" s="3" t="n">
         <v>3.32302285</v>
       </c>
       <c r="E239" t="n">
@@ -5554,10 +5659,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C240" s="5" t="n">
+      <c r="C240" s="2" t="n">
         <v>73404.17</v>
       </c>
-      <c r="D240" s="6" t="n">
+      <c r="D240" s="3" t="n">
         <v>16.89244764</v>
       </c>
       <c r="E240" t="n">
@@ -5575,10 +5680,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C241" s="5" t="n">
+      <c r="C241" s="2" t="n">
         <v>334487.78</v>
       </c>
-      <c r="D241" s="6" t="n">
+      <c r="D241" s="3" t="n">
         <v>76.97542673</v>
       </c>
       <c r="E241" t="n">
@@ -5596,10 +5701,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C242" s="5" t="n">
+      <c r="C242" s="2" t="n">
         <v>4414.12</v>
       </c>
-      <c r="D242" s="6" t="n">
+      <c r="D242" s="3" t="n">
         <v>2.02734127</v>
       </c>
       <c r="E242" t="n">
@@ -5617,10 +5722,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C243" s="5" t="n">
+      <c r="C243" s="2" t="n">
         <v>206.75</v>
       </c>
-      <c r="D243" s="6" t="n">
+      <c r="D243" s="3" t="n">
         <v>0.09495727</v>
       </c>
       <c r="E243" t="n">
@@ -5638,10 +5743,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C244" s="5" t="n">
+      <c r="C244" s="2" t="n">
         <v>6938.86</v>
       </c>
-      <c r="D244" s="6" t="n">
+      <c r="D244" s="3" t="n">
         <v>3.18691771</v>
       </c>
       <c r="E244" t="n">
@@ -5659,10 +5764,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C245" s="5" t="n">
+      <c r="C245" s="2" t="n">
         <v>206169.77</v>
       </c>
-      <c r="D245" s="6" t="n">
+      <c r="D245" s="3" t="n">
         <v>94.69078374999999</v>
       </c>
       <c r="E245" t="n">
@@ -5680,10 +5785,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C246" s="5" t="n">
+      <c r="C246" s="2" t="n">
         <v>45195.76</v>
       </c>
-      <c r="D246" s="6" t="n">
+      <c r="D246" s="3" t="n">
         <v>10.41762819</v>
       </c>
       <c r="E246" t="n">
@@ -5701,10 +5806,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C247" s="5" t="n">
+      <c r="C247" s="2" t="n">
         <v>9882.6</v>
       </c>
-      <c r="D247" s="6" t="n">
+      <c r="D247" s="3" t="n">
         <v>2.2779405</v>
       </c>
       <c r="E247" t="n">
@@ -5722,10 +5827,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C248" s="5" t="n">
+      <c r="C248" s="2" t="n">
         <v>305.19</v>
       </c>
-      <c r="D248" s="6" t="n">
+      <c r="D248" s="3" t="n">
         <v>0.07034633</v>
       </c>
       <c r="E248" t="n">
@@ -5743,10 +5848,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C249" s="5" t="n">
+      <c r="C249" s="2" t="n">
         <v>9384.76</v>
       </c>
-      <c r="D249" s="6" t="n">
+      <c r="D249" s="3" t="n">
         <v>2.16318832</v>
       </c>
       <c r="E249" t="n">
@@ -5764,10 +5869,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C250" s="5" t="n">
+      <c r="C250" s="2" t="n">
         <v>369070.94</v>
       </c>
-      <c r="D250" s="6" t="n">
+      <c r="D250" s="3" t="n">
         <v>85.07089664999999</v>
       </c>
       <c r="E250" t="n">
@@ -5785,10 +5890,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C251" s="5" t="n">
+      <c r="C251" s="2" t="n">
         <v>387.59</v>
       </c>
-      <c r="D251" s="6" t="n">
+      <c r="D251" s="3" t="n">
         <v>0.10977502</v>
       </c>
       <c r="E251" t="n">
@@ -5806,10 +5911,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C252" s="5" t="n">
+      <c r="C252" s="2" t="n">
         <v>3000</v>
       </c>
-      <c r="D252" s="6" t="n">
+      <c r="D252" s="3" t="n">
         <v>0.84967379</v>
       </c>
       <c r="E252" t="n">
@@ -5827,10 +5932,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C253" s="5" t="n">
+      <c r="C253" s="2" t="n">
         <v>114879.27</v>
       </c>
-      <c r="D253" s="6" t="n">
+      <c r="D253" s="3" t="n">
         <v>32.53663482</v>
       </c>
       <c r="E253" t="n">
@@ -5848,10 +5953,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C254" s="5" t="n">
+      <c r="C254" s="2" t="n">
         <v>234809.82</v>
       </c>
-      <c r="D254" s="6" t="n">
+      <c r="D254" s="3" t="n">
         <v>66.50391637</v>
       </c>
       <c r="E254" t="n">
@@ -5869,10 +5974,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C255" s="5" t="n">
+      <c r="C255" s="2" t="n">
         <v>8859.66</v>
       </c>
-      <c r="D255" s="6" t="n">
+      <c r="D255" s="3" t="n">
         <v>5.34081687</v>
       </c>
       <c r="E255" t="n">
@@ -5890,10 +5995,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C256" s="5" t="n">
+      <c r="C256" s="2" t="n">
         <v>1006.9</v>
       </c>
-      <c r="D256" s="6" t="n">
+      <c r="D256" s="3" t="n">
         <v>0.6069836199999999</v>
       </c>
       <c r="E256" t="n">
@@ -5911,10 +6016,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C257" s="5" t="n">
+      <c r="C257" s="2" t="n">
         <v>1000</v>
       </c>
-      <c r="D257" s="6" t="n">
+      <c r="D257" s="3" t="n">
         <v>0.60282413</v>
       </c>
       <c r="E257" t="n">
@@ -5932,10 +6037,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C258" s="5" t="n">
+      <c r="C258" s="2" t="n">
         <v>51121.7</v>
       </c>
-      <c r="D258" s="6" t="n">
+      <c r="D258" s="3" t="n">
         <v>30.81739456</v>
       </c>
       <c r="E258" t="n">
@@ -5953,10 +6058,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C259" s="5" t="n">
+      <c r="C259" s="2" t="n">
         <v>103897.6</v>
       </c>
-      <c r="D259" s="6" t="n">
+      <c r="D259" s="3" t="n">
         <v>62.63198081</v>
       </c>
       <c r="E259" t="n">
@@ -5974,10 +6079,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C260" s="5" t="n">
+      <c r="C260" s="2" t="n">
         <v>7692.3</v>
       </c>
-      <c r="D260" s="6" t="n">
+      <c r="D260" s="3" t="n">
         <v>6.29078176</v>
       </c>
       <c r="E260" t="n">
@@ -5995,10 +6100,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C261" s="5" t="n">
+      <c r="C261" s="2" t="n">
         <v>1882.73</v>
       </c>
-      <c r="D261" s="6" t="n">
+      <c r="D261" s="3" t="n">
         <v>1.5397012</v>
       </c>
       <c r="E261" t="n">
@@ -6016,10 +6121,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C262" s="5" t="n">
+      <c r="C262" s="2" t="n">
         <v>14869.63</v>
       </c>
-      <c r="D262" s="6" t="n">
+      <c r="D262" s="3" t="n">
         <v>12.1604198</v>
       </c>
       <c r="E262" t="n">
@@ -6037,10 +6142,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C263" s="5" t="n">
+      <c r="C263" s="2" t="n">
         <v>97834.25999999999</v>
       </c>
-      <c r="D263" s="6" t="n">
+      <c r="D263" s="3" t="n">
         <v>80.00909722999999</v>
       </c>
       <c r="E263" t="n">
@@ -6058,10 +6163,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C264" s="5" t="n">
+      <c r="C264" s="2" t="n">
         <v>3303.59</v>
       </c>
-      <c r="D264" s="6" t="n">
+      <c r="D264" s="3" t="n">
         <v>1.27093949</v>
       </c>
       <c r="E264" t="n">
@@ -6079,10 +6184,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C265" s="5" t="n">
+      <c r="C265" s="2" t="n">
         <v>18435.53</v>
       </c>
-      <c r="D265" s="6" t="n">
+      <c r="D265" s="3" t="n">
         <v>7.09241858</v>
       </c>
       <c r="E265" t="n">
@@ -6100,10 +6205,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C266" s="5" t="n">
+      <c r="C266" s="2" t="n">
         <v>2222.22</v>
       </c>
-      <c r="D266" s="6" t="n">
+      <c r="D266" s="3" t="n">
         <v>0.8549206</v>
       </c>
       <c r="E266" t="n">
@@ -6121,10 +6226,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C267" s="5" t="n">
+      <c r="C267" s="2" t="n">
         <v>50871.54</v>
       </c>
-      <c r="D267" s="6" t="n">
+      <c r="D267" s="3" t="n">
         <v>19.571027</v>
       </c>
       <c r="E267" t="n">
@@ -6142,10 +6247,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C268" s="5" t="n">
+      <c r="C268" s="2" t="n">
         <v>185100.03</v>
       </c>
-      <c r="D268" s="6" t="n">
+      <c r="D268" s="3" t="n">
         <v>71.21069433</v>
       </c>
       <c r="E268" t="n">
@@ -6163,10 +6268,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C269" s="5" t="n">
+      <c r="C269" s="2" t="n">
         <v>26854.86</v>
       </c>
-      <c r="D269" s="6" t="n">
+      <c r="D269" s="3" t="n">
         <v>6.60466391</v>
       </c>
       <c r="E269" t="n">
@@ -6184,10 +6289,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="C270" s="5" t="n">
+      <c r="C270" s="2" t="n">
         <v>554.28</v>
       </c>
-      <c r="D270" s="6" t="n">
+      <c r="D270" s="3" t="n">
         <v>0.1363192</v>
       </c>
       <c r="E270" t="n">
@@ -6205,10 +6310,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C271" s="5" t="n">
+      <c r="C271" s="2" t="n">
         <v>487.8</v>
       </c>
-      <c r="D271" s="6" t="n">
+      <c r="D271" s="3" t="n">
         <v>0.11996916</v>
       </c>
       <c r="E271" t="n">
@@ -6226,10 +6331,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C272" s="5" t="n">
+      <c r="C272" s="2" t="n">
         <v>12206.22</v>
       </c>
-      <c r="D272" s="6" t="n">
+      <c r="D272" s="3" t="n">
         <v>3.00198849</v>
       </c>
       <c r="E272" t="n">
@@ -6247,10 +6352,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C273" s="5" t="n">
+      <c r="C273" s="2" t="n">
         <v>28370.02</v>
       </c>
-      <c r="D273" s="6" t="n">
+      <c r="D273" s="3" t="n">
         <v>6.97730121</v>
       </c>
       <c r="E273" t="n">
@@ -6268,10 +6373,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C274" s="5" t="n">
+      <c r="C274" s="2" t="n">
         <v>338131.31</v>
       </c>
-      <c r="D274" s="6" t="n">
+      <c r="D274" s="3" t="n">
         <v>83.15975802</v>
       </c>
       <c r="E274" t="n">
@@ -6289,10 +6394,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C275" s="5" t="n">
+      <c r="C275" s="2" t="n">
         <v>19985.78</v>
       </c>
-      <c r="D275" s="6" t="n">
+      <c r="D275" s="3" t="n">
         <v>7.97052191</v>
       </c>
       <c r="E275" t="n">
@@ -6310,10 +6415,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="C276" s="5" t="n">
+      <c r="C276" s="2" t="n">
         <v>2222.22</v>
       </c>
-      <c r="D276" s="6" t="n">
+      <c r="D276" s="3" t="n">
         <v>0.88624278</v>
       </c>
       <c r="E276" t="n">
@@ -6331,10 +6436,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C277" s="5" t="n">
+      <c r="C277" s="2" t="n">
         <v>4445.7</v>
       </c>
-      <c r="D277" s="6" t="n">
+      <c r="D277" s="3" t="n">
         <v>1.77298806</v>
       </c>
       <c r="E277" t="n">
@@ -6352,10 +6457,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C278" s="5" t="n">
+      <c r="C278" s="2" t="n">
         <v>50514.02</v>
       </c>
-      <c r="D278" s="6" t="n">
+      <c r="D278" s="3" t="n">
         <v>20.14547858</v>
       </c>
       <c r="E278" t="n">
@@ -6373,10 +6478,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C279" s="5" t="n">
+      <c r="C279" s="2" t="n">
         <v>173578.47</v>
       </c>
-      <c r="D279" s="6" t="n">
+      <c r="D279" s="3" t="n">
         <v>69.22476868</v>
       </c>
       <c r="E279" t="n">
@@ -6394,10 +6499,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C280" s="5" t="n">
+      <c r="C280" s="2" t="n">
         <v>40560.99</v>
       </c>
-      <c r="D280" s="6" t="n">
+      <c r="D280" s="3" t="n">
         <v>8.644859670000001</v>
       </c>
       <c r="E280" t="n">
@@ -6415,10 +6520,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C281" s="5" t="n">
+      <c r="C281" s="2" t="n">
         <v>6836.42</v>
       </c>
-      <c r="D281" s="6" t="n">
+      <c r="D281" s="3" t="n">
         <v>1.45706235</v>
       </c>
       <c r="E281" t="n">
@@ -6436,10 +6541,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C282" s="5" t="n">
+      <c r="C282" s="2" t="n">
         <v>34873.15</v>
       </c>
-      <c r="D282" s="6" t="n">
+      <c r="D282" s="3" t="n">
         <v>7.43259689</v>
       </c>
       <c r="E282" t="n">
@@ -6457,10 +6562,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C283" s="5" t="n">
+      <c r="C283" s="2" t="n">
         <v>386921.44</v>
       </c>
-      <c r="D283" s="6" t="n">
+      <c r="D283" s="3" t="n">
         <v>82.46548108</v>
       </c>
       <c r="E283" t="n">
@@ -6478,10 +6583,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="C284" s="5" t="n">
+      <c r="C284" s="2" t="n">
         <v>2062.08</v>
       </c>
-      <c r="D284" s="6" t="n">
+      <c r="D284" s="3" t="n">
         <v>0.67843969</v>
       </c>
       <c r="E284" t="n">
@@ -6499,10 +6604,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C285" s="5" t="n">
+      <c r="C285" s="2" t="n">
         <v>67302.87</v>
       </c>
-      <c r="D285" s="6" t="n">
+      <c r="D285" s="3" t="n">
         <v>22.14314601</v>
       </c>
       <c r="E285" t="n">
@@ -6520,10 +6625,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C286" s="5" t="n">
+      <c r="C286" s="2" t="n">
         <v>37.83</v>
       </c>
-      <c r="D286" s="6" t="n">
+      <c r="D286" s="3" t="n">
         <v>0.01244635</v>
       </c>
       <c r="E286" t="n">
@@ -6541,10 +6646,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C287" s="5" t="n">
+      <c r="C287" s="2" t="n">
         <v>82048.36</v>
       </c>
-      <c r="D287" s="6" t="n">
+      <c r="D287" s="3" t="n">
         <v>26.99452216</v>
       </c>
       <c r="E287" t="n">
@@ -6562,10 +6667,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C288" s="5" t="n">
+      <c r="C288" s="2" t="n">
         <v>152493.34</v>
       </c>
-      <c r="D288" s="6" t="n">
+      <c r="D288" s="3" t="n">
         <v>50.17144579</v>
       </c>
       <c r="E288" t="n">
@@ -6583,10 +6688,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C289" s="5" t="n">
+      <c r="C289" s="2" t="n">
         <v>16850.05</v>
       </c>
-      <c r="D289" s="6" t="n">
+      <c r="D289" s="3" t="n">
         <v>8.3557591</v>
       </c>
       <c r="E289" t="n">
@@ -6604,10 +6709,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C290" s="5" t="n">
+      <c r="C290" s="2" t="n">
         <v>1221.31</v>
       </c>
-      <c r="D290" s="6" t="n">
+      <c r="D290" s="3" t="n">
         <v>0.60563453</v>
       </c>
       <c r="E290" t="n">
@@ -6625,10 +6730,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C291" s="5" t="n">
+      <c r="C291" s="2" t="n">
         <v>542.72</v>
       </c>
-      <c r="D291" s="6" t="n">
+      <c r="D291" s="3" t="n">
         <v>0.26912903</v>
       </c>
       <c r="E291" t="n">
@@ -6646,10 +6751,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C292" s="5" t="n">
+      <c r="C292" s="2" t="n">
         <v>1989.87</v>
       </c>
-      <c r="D292" s="6" t="n">
+      <c r="D292" s="3" t="n">
         <v>0.98675519</v>
       </c>
       <c r="E292" t="n">
@@ -6667,10 +6772,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C293" s="5" t="n">
+      <c r="C293" s="2" t="n">
         <v>181053.97</v>
       </c>
-      <c r="D293" s="6" t="n">
+      <c r="D293" s="3" t="n">
         <v>89.78272215</v>
       </c>
       <c r="E293" t="n">
@@ -6688,10 +6793,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C294" s="5" t="n">
+      <c r="C294" s="2" t="n">
         <v>2791.46</v>
       </c>
-      <c r="D294" s="6" t="n">
+      <c r="D294" s="3" t="n">
         <v>1.6215349</v>
       </c>
       <c r="E294" t="n">
@@ -6709,10 +6814,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C295" s="5" t="n">
+      <c r="C295" s="2" t="n">
         <v>6752.82</v>
       </c>
-      <c r="D295" s="6" t="n">
+      <c r="D295" s="3" t="n">
         <v>3.92265455</v>
       </c>
       <c r="E295" t="n">
@@ -6730,10 +6835,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C296" s="5" t="n">
+      <c r="C296" s="2" t="n">
         <v>42038.15</v>
       </c>
-      <c r="D296" s="6" t="n">
+      <c r="D296" s="3" t="n">
         <v>24.41959662</v>
       </c>
       <c r="E296" t="n">
@@ -6751,10 +6856,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C297" s="5" t="n">
+      <c r="C297" s="2" t="n">
         <v>120566.81</v>
       </c>
-      <c r="D297" s="6" t="n">
+      <c r="D297" s="3" t="n">
         <v>70.03621393</v>
       </c>
       <c r="E297" t="n">
@@ -6772,10 +6877,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C298" s="5" t="n">
+      <c r="C298" s="2" t="n">
         <v>360</v>
       </c>
-      <c r="D298" s="6" t="n">
+      <c r="D298" s="3" t="n">
         <v>0.13798773</v>
       </c>
       <c r="E298" t="n">
@@ -6793,10 +6898,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C299" s="5" t="n">
+      <c r="C299" s="2" t="n">
         <v>9364.209999999999</v>
       </c>
-      <c r="D299" s="6" t="n">
+      <c r="D299" s="3" t="n">
         <v>3.58929456</v>
       </c>
       <c r="E299" t="n">
@@ -6814,10 +6919,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C300" s="5" t="n">
+      <c r="C300" s="2" t="n">
         <v>4780.88</v>
       </c>
-      <c r="D300" s="6" t="n">
+      <c r="D300" s="3" t="n">
         <v>1.83250766</v>
       </c>
       <c r="E300" t="n">
@@ -6835,10 +6940,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C301" s="5" t="n">
+      <c r="C301" s="2" t="n">
         <v>246387.68</v>
       </c>
-      <c r="D301" s="6" t="n">
+      <c r="D301" s="3" t="n">
         <v>94.44021005</v>
       </c>
       <c r="E301" t="n">
@@ -6856,10 +6961,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C302" s="5" t="n">
+      <c r="C302" s="2" t="n">
         <v>6057.75</v>
       </c>
-      <c r="D302" s="6" t="n">
+      <c r="D302" s="3" t="n">
         <v>2.33727832</v>
       </c>
       <c r="E302" t="n">
@@ -6877,10 +6982,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C303" s="5" t="n">
+      <c r="C303" s="2" t="n">
         <v>48766.63</v>
       </c>
-      <c r="D303" s="6" t="n">
+      <c r="D303" s="3" t="n">
         <v>18.81576278</v>
       </c>
       <c r="E303" t="n">
@@ -6898,10 +7003,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C304" s="5" t="n">
+      <c r="C304" s="2" t="n">
         <v>204355.28</v>
       </c>
-      <c r="D304" s="6" t="n">
+      <c r="D304" s="3" t="n">
         <v>78.8469589</v>
       </c>
       <c r="E304" t="n">
@@ -6919,10 +7024,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C305" s="5" t="n">
+      <c r="C305" s="2" t="n">
         <v>16523.23</v>
       </c>
-      <c r="D305" s="6" t="n">
+      <c r="D305" s="3" t="n">
         <v>6.18627246</v>
       </c>
       <c r="E305" t="n">
@@ -6940,10 +7045,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="C306" s="5" t="n">
+      <c r="C306" s="2" t="n">
         <v>1000</v>
       </c>
-      <c r="D306" s="6" t="n">
+      <c r="D306" s="3" t="n">
         <v>0.3743985</v>
       </c>
       <c r="E306" t="n">
@@ -6961,10 +7066,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C307" s="5" t="n">
+      <c r="C307" s="2" t="n">
         <v>19175.48</v>
       </c>
-      <c r="D307" s="6" t="n">
+      <c r="D307" s="3" t="n">
         <v>7.17927087</v>
       </c>
       <c r="E307" t="n">
@@ -6982,10 +7087,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C308" s="5" t="n">
+      <c r="C308" s="2" t="n">
         <v>22548.18</v>
       </c>
-      <c r="D308" s="6" t="n">
+      <c r="D308" s="3" t="n">
         <v>8.44200468</v>
       </c>
       <c r="E308" t="n">
@@ -7003,10 +7108,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C309" s="5" t="n">
+      <c r="C309" s="2" t="n">
         <v>3105.38</v>
       </c>
-      <c r="D309" s="6" t="n">
+      <c r="D309" s="3" t="n">
         <v>1.1626496</v>
       </c>
       <c r="E309" t="n">
@@ -7024,10 +7129,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C310" s="5" t="n">
+      <c r="C310" s="2" t="n">
         <v>9171.51</v>
       </c>
-      <c r="D310" s="6" t="n">
+      <c r="D310" s="3" t="n">
         <v>3.43379955</v>
       </c>
       <c r="E310" t="n">
@@ -7045,10 +7150,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C311" s="5" t="n">
+      <c r="C311" s="2" t="n">
         <v>195571.31</v>
       </c>
-      <c r="D311" s="6" t="n">
+      <c r="D311" s="3" t="n">
         <v>73.22160434</v>
       </c>
       <c r="E311" t="n">
@@ -7066,10 +7171,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C312" s="5" t="n">
+      <c r="C312" s="2" t="n">
         <v>27350.51</v>
       </c>
-      <c r="D312" s="6" t="n">
+      <c r="D312" s="3" t="n">
         <v>9.8197723</v>
       </c>
       <c r="E312" t="n">
@@ -7087,10 +7192,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C313" s="5" t="n">
+      <c r="C313" s="2" t="n">
         <v>21653.68</v>
       </c>
-      <c r="D313" s="6" t="n">
+      <c r="D313" s="3" t="n">
         <v>7.7744147</v>
       </c>
       <c r="E313" t="n">
@@ -7108,10 +7213,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C314" s="5" t="n">
+      <c r="C314" s="2" t="n">
         <v>30092.08</v>
       </c>
-      <c r="D314" s="6" t="n">
+      <c r="D314" s="3" t="n">
         <v>10.80409008</v>
       </c>
       <c r="E314" t="n">
@@ -7129,10 +7234,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C315" s="5" t="n">
+      <c r="C315" s="2" t="n">
         <v>199428.62</v>
       </c>
-      <c r="D315" s="6" t="n">
+      <c r="D315" s="3" t="n">
         <v>71.60172292</v>
       </c>
       <c r="E315" t="n">
@@ -7150,10 +7255,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C316" s="5" t="n">
+      <c r="C316" s="2" t="n">
         <v>18403.89</v>
       </c>
-      <c r="D316" s="6" t="n">
+      <c r="D316" s="3" t="n">
         <v>5.9503914</v>
       </c>
       <c r="E316" t="n">
@@ -7171,10 +7276,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C317" s="5" t="n">
+      <c r="C317" s="2" t="n">
         <v>88.88</v>
       </c>
-      <c r="D317" s="6" t="n">
+      <c r="D317" s="3" t="n">
         <v>0.0287369</v>
       </c>
       <c r="E317" t="n">
@@ -7192,10 +7297,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C318" s="5" t="n">
+      <c r="C318" s="2" t="n">
         <v>72445.86</v>
       </c>
-      <c r="D318" s="6" t="n">
+      <c r="D318" s="3" t="n">
         <v>23.4233753</v>
       </c>
       <c r="E318" t="n">
@@ -7213,10 +7318,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C319" s="5" t="n">
+      <c r="C319" s="2" t="n">
         <v>1021.81</v>
       </c>
-      <c r="D319" s="6" t="n">
+      <c r="D319" s="3" t="n">
         <v>0.33037415</v>
       </c>
       <c r="E319" t="n">
@@ -7234,10 +7339,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C320" s="5" t="n">
+      <c r="C320" s="2" t="n">
         <v>23146.75</v>
       </c>
-      <c r="D320" s="6" t="n">
+      <c r="D320" s="3" t="n">
         <v>7.48386467</v>
       </c>
       <c r="E320" t="n">
@@ -7255,10 +7360,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C321" s="5" t="n">
+      <c r="C321" s="2" t="n">
         <v>194181.54</v>
       </c>
-      <c r="D321" s="6" t="n">
+      <c r="D321" s="3" t="n">
         <v>62.78325757</v>
       </c>
       <c r="E321" t="n">
@@ -7276,10 +7381,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C322" s="5" t="n">
+      <c r="C322" s="2" t="n">
         <v>3620.25</v>
       </c>
-      <c r="D322" s="6" t="n">
+      <c r="D322" s="3" t="n">
         <v>1.23604851</v>
       </c>
       <c r="E322" t="n">
@@ -7297,10 +7402,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C323" s="5" t="n">
+      <c r="C323" s="2" t="n">
         <v>19747.53</v>
       </c>
-      <c r="D323" s="6" t="n">
+      <c r="D323" s="3" t="n">
         <v>6.74232582</v>
       </c>
       <c r="E323" t="n">
@@ -7318,10 +7423,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C324" s="5" t="n">
+      <c r="C324" s="2" t="n">
         <v>148.8</v>
       </c>
-      <c r="D324" s="6" t="n">
+      <c r="D324" s="3" t="n">
         <v>0.05080423</v>
       </c>
       <c r="E324" t="n">
@@ -7339,10 +7444,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C325" s="5" t="n">
+      <c r="C325" s="2" t="n">
         <v>59465.09</v>
       </c>
-      <c r="D325" s="6" t="n">
+      <c r="D325" s="3" t="n">
         <v>20.30294481</v>
       </c>
       <c r="E325" t="n">
@@ -7360,10 +7465,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C326" s="5" t="n">
+      <c r="C326" s="2" t="n">
         <v>209907.32</v>
       </c>
-      <c r="D326" s="6" t="n">
+      <c r="D326" s="3" t="n">
         <v>71.66787662</v>
       </c>
       <c r="E326" t="n">
@@ -7381,10 +7486,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C327" s="5" t="n">
+      <c r="C327" s="2" t="n">
         <v>6884.07</v>
       </c>
-      <c r="D327" s="6" t="n">
+      <c r="D327" s="3" t="n">
         <v>2.33908458</v>
       </c>
       <c r="E327" t="n">
@@ -7402,10 +7507,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C328" s="5" t="n">
+      <c r="C328" s="2" t="n">
         <v>1851.18</v>
       </c>
-      <c r="D328" s="6" t="n">
+      <c r="D328" s="3" t="n">
         <v>0.62899805</v>
       </c>
       <c r="E328" t="n">
@@ -7423,10 +7528,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C329" s="5" t="n">
+      <c r="C329" s="2" t="n">
         <v>27.27</v>
       </c>
-      <c r="D329" s="6" t="n">
+      <c r="D329" s="3" t="n">
         <v>0.009265860000000001</v>
       </c>
       <c r="E329" t="n">
@@ -7444,10 +7549,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C330" s="5" t="n">
+      <c r="C330" s="2" t="n">
         <v>48724.48</v>
       </c>
-      <c r="D330" s="6" t="n">
+      <c r="D330" s="3" t="n">
         <v>16.55571192</v>
       </c>
       <c r="E330" t="n">
@@ -7465,10 +7570,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C331" s="5" t="n">
+      <c r="C331" s="2" t="n">
         <v>236819.16</v>
       </c>
-      <c r="D331" s="6" t="n">
+      <c r="D331" s="3" t="n">
         <v>80.4669396</v>
       </c>
       <c r="E331" t="n">
@@ -7486,10 +7591,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C332" s="5" t="n">
+      <c r="C332" s="2" t="n">
         <v>1121.22</v>
       </c>
-      <c r="D332" s="6" t="n">
+      <c r="D332" s="3" t="n">
         <v>0.3654631</v>
       </c>
       <c r="E332" t="n">
@@ -7507,10 +7612,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C333" s="5" t="n">
+      <c r="C333" s="2" t="n">
         <v>44200.33</v>
       </c>
-      <c r="D333" s="6" t="n">
+      <c r="D333" s="3" t="n">
         <v>14.40715442</v>
       </c>
       <c r="E333" t="n">
@@ -7528,10 +7633,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C334" s="5" t="n">
+      <c r="C334" s="2" t="n">
         <v>1029.79</v>
       </c>
-      <c r="D334" s="6" t="n">
+      <c r="D334" s="3" t="n">
         <v>0.33566138</v>
       </c>
       <c r="E334" t="n">
@@ -7549,10 +7654,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C335" s="5" t="n">
+      <c r="C335" s="2" t="n">
         <v>47810.16</v>
       </c>
-      <c r="D335" s="6" t="n">
+      <c r="D335" s="3" t="n">
         <v>15.58378315</v>
       </c>
       <c r="E335" t="n">
@@ -7570,10 +7675,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C336" s="5" t="n">
+      <c r="C336" s="2" t="n">
         <v>212632.81</v>
       </c>
-      <c r="D336" s="6" t="n">
+      <c r="D336" s="3" t="n">
         <v>69.30793795</v>
       </c>
       <c r="E336" t="n">
@@ -7591,10 +7696,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C337" s="5" t="n">
+      <c r="C337" s="2" t="n">
         <v>6174.11</v>
       </c>
-      <c r="D337" s="6" t="n">
+      <c r="D337" s="3" t="n">
         <v>2.21572231</v>
       </c>
       <c r="E337" t="n">
@@ -7612,10 +7717,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C338" s="5" t="n">
+      <c r="C338" s="2" t="n">
         <v>41944.2</v>
       </c>
-      <c r="D338" s="6" t="n">
+      <c r="D338" s="3" t="n">
         <v>15.05264723</v>
       </c>
       <c r="E338" t="n">
@@ -7633,10 +7738,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C339" s="5" t="n">
+      <c r="C339" s="2" t="n">
         <v>77569.86</v>
       </c>
-      <c r="D339" s="6" t="n">
+      <c r="D339" s="3" t="n">
         <v>27.8377401</v>
       </c>
       <c r="E339" t="n">
@@ -7654,10 +7759,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C340" s="5" t="n">
+      <c r="C340" s="2" t="n">
         <v>152961.82</v>
       </c>
-      <c r="D340" s="6" t="n">
+      <c r="D340" s="3" t="n">
         <v>54.89389036</v>
       </c>
       <c r="E340" t="n">
@@ -7675,10 +7780,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C341" s="5" t="n">
+      <c r="C341" s="2" t="n">
         <v>4327.58</v>
       </c>
-      <c r="D341" s="6" t="n">
+      <c r="D341" s="3" t="n">
         <v>1.21146897</v>
       </c>
       <c r="E341" t="n">
@@ -7696,10 +7801,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C342" s="5" t="n">
+      <c r="C342" s="2" t="n">
         <v>28414.86</v>
       </c>
-      <c r="D342" s="6" t="n">
+      <c r="D342" s="3" t="n">
         <v>7.95449675</v>
       </c>
       <c r="E342" t="n">
@@ -7717,10 +7822,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C343" s="5" t="n">
+      <c r="C343" s="2" t="n">
         <v>57985.61</v>
       </c>
-      <c r="D343" s="6" t="n">
+      <c r="D343" s="3" t="n">
         <v>16.23257501</v>
       </c>
       <c r="E343" t="n">
@@ -7738,10 +7843,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C344" s="5" t="n">
+      <c r="C344" s="2" t="n">
         <v>164042.55</v>
       </c>
-      <c r="D344" s="6" t="n">
+      <c r="D344" s="3" t="n">
         <v>45.92230724</v>
       </c>
       <c r="E344" t="n">
@@ -7759,10 +7864,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C345" s="5" t="n">
+      <c r="C345" s="2" t="n">
         <v>102446.97</v>
       </c>
-      <c r="D345" s="6" t="n">
+      <c r="D345" s="3" t="n">
         <v>28.67915204</v>
       </c>
       <c r="E345" t="n">
@@ -7780,10 +7885,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C346" s="5" t="n">
+      <c r="C346" s="2" t="n">
         <v>6549.34</v>
       </c>
-      <c r="D346" s="6" t="n">
+      <c r="D346" s="3" t="n">
         <v>1.3658538</v>
       </c>
       <c r="E346" t="n">
@@ -7801,10 +7906,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C347" s="5" t="n">
+      <c r="C347" s="2" t="n">
         <v>70012.2</v>
       </c>
-      <c r="D347" s="6" t="n">
+      <c r="D347" s="3" t="n">
         <v>14.60092612</v>
       </c>
       <c r="E347" t="n">
@@ -7822,10 +7927,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C348" s="5" t="n">
+      <c r="C348" s="2" t="n">
         <v>131512.85</v>
       </c>
-      <c r="D348" s="6" t="n">
+      <c r="D348" s="3" t="n">
         <v>27.42678286</v>
       </c>
       <c r="E348" t="n">
@@ -7843,10 +7948,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C349" s="5" t="n">
+      <c r="C349" s="2" t="n">
         <v>271430.81</v>
       </c>
-      <c r="D349" s="6" t="n">
+      <c r="D349" s="3" t="n">
         <v>56.60643722</v>
       </c>
       <c r="E349" t="n">
@@ -7864,10 +7969,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C350" s="5" t="n">
+      <c r="C350" s="2" t="n">
         <v>15339.66</v>
       </c>
-      <c r="D350" s="6" t="n">
+      <c r="D350" s="3" t="n">
         <v>4.55580253</v>
       </c>
       <c r="E350" t="n">
@@ -7885,10 +7990,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C351" s="5" t="n">
+      <c r="C351" s="2" t="n">
         <v>24900.55</v>
       </c>
-      <c r="D351" s="6" t="n">
+      <c r="D351" s="3" t="n">
         <v>7.39533918</v>
       </c>
       <c r="E351" t="n">
@@ -7906,10 +8011,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C352" s="5" t="n">
+      <c r="C352" s="2" t="n">
         <v>7486.19</v>
       </c>
-      <c r="D352" s="6" t="n">
+      <c r="D352" s="3" t="n">
         <v>2.2233611</v>
       </c>
       <c r="E352" t="n">
@@ -7927,10 +8032,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C353" s="5" t="n">
+      <c r="C353" s="2" t="n">
         <v>75899.28</v>
       </c>
-      <c r="D353" s="6" t="n">
+      <c r="D353" s="3" t="n">
         <v>22.54170768</v>
       </c>
       <c r="E353" t="n">
@@ -7948,10 +8053,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C354" s="5" t="n">
+      <c r="C354" s="2" t="n">
         <v>213080.31</v>
       </c>
-      <c r="D354" s="6" t="n">
+      <c r="D354" s="3" t="n">
         <v>63.28378952</v>
       </c>
       <c r="E354" t="n">
@@ -7969,10 +8074,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C355" s="5" t="n">
+      <c r="C355" s="2" t="n">
         <v>99.05</v>
       </c>
-      <c r="D355" s="6" t="n">
+      <c r="D355" s="3" t="n">
         <v>0.05450467</v>
       </c>
       <c r="E355" t="n">
@@ -7990,10 +8095,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C356" s="5" t="n">
+      <c r="C356" s="2" t="n">
         <v>40317.43</v>
       </c>
-      <c r="D356" s="6" t="n">
+      <c r="D356" s="3" t="n">
         <v>22.18564427</v>
       </c>
       <c r="E356" t="n">
@@ -8011,10 +8116,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C357" s="5" t="n">
+      <c r="C357" s="2" t="n">
         <v>441.17</v>
       </c>
-      <c r="D357" s="6" t="n">
+      <c r="D357" s="3" t="n">
         <v>0.2427645</v>
       </c>
       <c r="E357" t="n">
@@ -8032,10 +8137,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C358" s="5" t="n">
+      <c r="C358" s="2" t="n">
         <v>15478.5</v>
       </c>
-      <c r="D358" s="6" t="n">
+      <c r="D358" s="3" t="n">
         <v>8.517420250000001</v>
       </c>
       <c r="E358" t="n">
@@ -8053,10 +8158,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C359" s="5" t="n">
+      <c r="C359" s="2" t="n">
         <v>125391.41</v>
       </c>
-      <c r="D359" s="6" t="n">
+      <c r="D359" s="3" t="n">
         <v>68.99966630999999</v>
       </c>
       <c r="E359" t="n">
@@ -8074,10 +8179,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C360" s="5" t="n">
+      <c r="C360" s="2" t="n">
         <v>1078.53</v>
       </c>
-      <c r="D360" s="6" t="n">
+      <c r="D360" s="3" t="n">
         <v>0.2616409</v>
       </c>
       <c r="E360" t="n">
@@ -8095,10 +8200,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C361" s="5" t="n">
+      <c r="C361" s="2" t="n">
         <v>18773.2</v>
       </c>
-      <c r="D361" s="6" t="n">
+      <c r="D361" s="3" t="n">
         <v>4.55419596</v>
       </c>
       <c r="E361" t="n">
@@ -8116,10 +8221,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C362" s="5" t="n">
+      <c r="C362" s="2" t="n">
         <v>131529.74</v>
       </c>
-      <c r="D362" s="6" t="n">
+      <c r="D362" s="3" t="n">
         <v>31.90783723</v>
       </c>
       <c r="E362" t="n">
@@ -8137,10 +8242,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C363" s="5" t="n">
+      <c r="C363" s="2" t="n">
         <v>260836.19</v>
       </c>
-      <c r="D363" s="6" t="n">
+      <c r="D363" s="3" t="n">
         <v>63.27632591</v>
       </c>
       <c r="E363" t="n">
@@ -8158,10 +8263,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C364" s="5" t="n">
+      <c r="C364" s="2" t="n">
         <v>101597</v>
       </c>
-      <c r="D364" s="6" t="n">
+      <c r="D364" s="3" t="n">
         <v>23.3811176</v>
       </c>
       <c r="E364" t="n">
@@ -8179,10 +8284,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C365" s="5" t="n">
+      <c r="C365" s="2" t="n">
         <v>28150.66</v>
       </c>
-      <c r="D365" s="6" t="n">
+      <c r="D365" s="3" t="n">
         <v>6.47847763</v>
       </c>
       <c r="E365" t="n">
@@ -8200,10 +8305,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C366" s="5" t="n">
+      <c r="C366" s="2" t="n">
         <v>40.94</v>
       </c>
-      <c r="D366" s="6" t="n">
+      <c r="D366" s="3" t="n">
         <v>0.00942176</v>
       </c>
       <c r="E366" t="n">
@@ -8221,10 +8326,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C367" s="5" t="n">
+      <c r="C367" s="2" t="n">
         <v>39974.48</v>
       </c>
-      <c r="D367" s="6" t="n">
+      <c r="D367" s="3" t="n">
         <v>9.19956316</v>
       </c>
       <c r="E367" t="n">
@@ -8242,10 +8347,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C368" s="5" t="n">
+      <c r="C368" s="2" t="n">
         <v>264762.77</v>
       </c>
-      <c r="D368" s="6" t="n">
+      <c r="D368" s="3" t="n">
         <v>60.93141985</v>
       </c>
       <c r="E368" t="n">
@@ -8263,10 +8368,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C369" s="5" t="n">
+      <c r="C369" s="2" t="n">
         <v>4391.2</v>
       </c>
-      <c r="D369" s="6" t="n">
+      <c r="D369" s="3" t="n">
         <v>1.20491459</v>
       </c>
       <c r="E369" t="n">
@@ -8284,10 +8389,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C370" s="5" t="n">
+      <c r="C370" s="2" t="n">
         <v>65068.55</v>
       </c>
-      <c r="D370" s="6" t="n">
+      <c r="D370" s="3" t="n">
         <v>17.85435532</v>
       </c>
       <c r="E370" t="n">
@@ -8305,10 +8410,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C371" s="5" t="n">
+      <c r="C371" s="2" t="n">
         <v>121692.04</v>
       </c>
-      <c r="D371" s="6" t="n">
+      <c r="D371" s="3" t="n">
         <v>33.3914452</v>
       </c>
       <c r="E371" t="n">
@@ -8326,10 +8431,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C372" s="5" t="n">
+      <c r="C372" s="2" t="n">
         <v>173288.98</v>
       </c>
-      <c r="D372" s="6" t="n">
+      <c r="D372" s="3" t="n">
         <v>47.54928489</v>
       </c>
       <c r="E372" t="n">
@@ -8347,10 +8452,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C373" s="5" t="n">
+      <c r="C373" s="2" t="n">
         <v>17775.38</v>
       </c>
-      <c r="D373" s="6" t="n">
+      <c r="D373" s="3" t="n">
         <v>7.37116189</v>
       </c>
       <c r="E373" t="n">
@@ -8368,10 +8473,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C374" s="5" t="n">
+      <c r="C374" s="2" t="n">
         <v>29163.77</v>
       </c>
-      <c r="D374" s="6" t="n">
+      <c r="D374" s="3" t="n">
         <v>12.09374259</v>
       </c>
       <c r="E374" t="n">
@@ -8389,10 +8494,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C375" s="5" t="n">
+      <c r="C375" s="2" t="n">
         <v>52107.99</v>
       </c>
-      <c r="D375" s="6" t="n">
+      <c r="D375" s="3" t="n">
         <v>21.60833863</v>
       </c>
       <c r="E375" t="n">
@@ -8410,14 +8515,119 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C376" s="5" t="n">
+      <c r="C376" s="2" t="n">
         <v>142100.46</v>
       </c>
-      <c r="D376" s="6" t="n">
+      <c r="D376" s="3" t="n">
         <v>58.92675689</v>
       </c>
       <c r="E376" t="n">
         <v>172</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C377" s="2" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D377" s="3" t="n">
+        <v>3.50118517</v>
+      </c>
+      <c r="E377" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C378" s="2" t="n">
+        <v>4643.79</v>
+      </c>
+      <c r="D378" s="3" t="n">
+        <v>1.62587687</v>
+      </c>
+      <c r="E378" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C379" s="2" t="n">
+        <v>520.28</v>
+      </c>
+      <c r="D379" s="3" t="n">
+        <v>0.18215966</v>
+      </c>
+      <c r="E379" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C380" s="2" t="n">
+        <v>19199.2</v>
+      </c>
+      <c r="D380" s="3" t="n">
+        <v>6.72199543</v>
+      </c>
+      <c r="E380" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C381" s="2" t="n">
+        <v>251254.3</v>
+      </c>
+      <c r="D381" s="3" t="n">
+        <v>87.96878287</v>
+      </c>
+      <c r="E381" t="n">
+        <v>223</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>251254.3</v>
+        <v>162348.21</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>87.96878287</v>
+        <v>77.44570976999999</v>
       </c>
       <c r="E2" t="n">
-        <v>223</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,97 +509,76 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>19199.2</v>
+        <v>41002.83</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>6.72199543</v>
+        <v>19.55976769</v>
       </c>
       <c r="E3" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Business/Economy</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>10000</v>
+        <v>3564.2</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>3.50118517</v>
+        <v>1.70024664</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Business/Economy</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>4643.79</v>
+        <v>2713.17</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1.62587687</v>
+        <v>1.2942759</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Sports</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>520.28</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0.18215966</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
-        <v>285617.57</v>
-      </c>
-      <c r="D7" s="6" t="n">
+      <c r="C6" s="5" t="n">
+        <v>209628.41</v>
+      </c>
+      <c r="D6" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E7" s="4" t="n">
-        <v>257</v>
+      <c r="E6" s="4" t="n">
+        <v>186</v>
       </c>
     </row>
   </sheetData>
@@ -613,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E381"/>
+  <dimension ref="A1:E385"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8630,6 +8609,90 @@
         <v>223</v>
       </c>
     </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C382" s="2" t="n">
+        <v>2713.17</v>
+      </c>
+      <c r="D382" s="3" t="n">
+        <v>1.2942759</v>
+      </c>
+      <c r="E382" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C383" s="2" t="n">
+        <v>3564.2</v>
+      </c>
+      <c r="D383" s="3" t="n">
+        <v>1.70024664</v>
+      </c>
+      <c r="E383" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C384" s="2" t="n">
+        <v>41002.83</v>
+      </c>
+      <c r="D384" s="3" t="n">
+        <v>19.55976769</v>
+      </c>
+      <c r="E384" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C385" s="2" t="n">
+        <v>162348.21</v>
+      </c>
+      <c r="D385" s="3" t="n">
+        <v>77.44570976999999</v>
+      </c>
+      <c r="E385" t="n">
+        <v>159</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,61 +488,61 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>162348.21</v>
+        <v>142029.22</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>77.44570976999999</v>
+        <v>70.27903101</v>
       </c>
       <c r="E2" t="n">
-        <v>159</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tech &amp; Science</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>41002.83</v>
+        <v>42513.88</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>19.55976769</v>
+        <v>21.03675772</v>
       </c>
       <c r="E3" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Tech &amp; Science</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>3564.2</v>
+        <v>15613.89</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1.70024664</v>
+        <v>7.7260796</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,34 +551,55 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2713.17</v>
+        <v>1485.87</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1.2942759</v>
+        <v>0.73523958</v>
       </c>
       <c r="E5" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>450.45</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0.22289209</v>
+      </c>
+      <c r="E6" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n">
-        <v>209628.41</v>
-      </c>
-      <c r="D6" s="6" t="n">
+      <c r="C7" s="5" t="n">
+        <v>202093.31</v>
+      </c>
+      <c r="D7" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>186</v>
+      <c r="E7" s="4" t="n">
+        <v>192</v>
       </c>
     </row>
   </sheetData>
@@ -592,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E385"/>
+  <dimension ref="A1:E390"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8693,6 +8714,111 @@
         <v>159</v>
       </c>
     </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C386" s="2" t="n">
+        <v>1485.87</v>
+      </c>
+      <c r="D386" s="3" t="n">
+        <v>0.73523958</v>
+      </c>
+      <c r="E386" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C387" s="2" t="n">
+        <v>42513.88</v>
+      </c>
+      <c r="D387" s="3" t="n">
+        <v>21.03675772</v>
+      </c>
+      <c r="E387" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C388" s="2" t="n">
+        <v>450.45</v>
+      </c>
+      <c r="D388" s="3" t="n">
+        <v>0.22289209</v>
+      </c>
+      <c r="E388" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C389" s="2" t="n">
+        <v>15613.89</v>
+      </c>
+      <c r="D389" s="3" t="n">
+        <v>7.7260796</v>
+      </c>
+      <c r="E389" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C390" s="2" t="n">
+        <v>142029.22</v>
+      </c>
+      <c r="D390" s="3" t="n">
+        <v>70.27903101</v>
+      </c>
+      <c r="E390" t="n">
+        <v>142</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,118 +488,97 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>142029.22</v>
+        <v>158088.34</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>70.27903101</v>
+        <v>59.39210384</v>
       </c>
       <c r="E2" t="n">
-        <v>142</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Tech &amp; Science</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>42513.88</v>
+        <v>40536.38</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>21.03675772</v>
+        <v>15.22908578</v>
       </c>
       <c r="E3" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tech &amp; Science</t>
+          <t>Business/Economy</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>15613.89</v>
+        <v>35429.86</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>7.7260796</v>
+        <v>13.31062066</v>
       </c>
       <c r="E4" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Business/Economy</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1485.87</v>
+        <v>32122.79</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.73523958</v>
+        <v>12.06818972</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Sports</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>450.45</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0.22289209</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
-        <v>202093.31</v>
-      </c>
-      <c r="D7" s="6" t="n">
+      <c r="C6" s="5" t="n">
+        <v>266177.37</v>
+      </c>
+      <c r="D6" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E7" s="4" t="n">
-        <v>192</v>
+      <c r="E6" s="4" t="n">
+        <v>282</v>
       </c>
     </row>
   </sheetData>
@@ -613,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E390"/>
+  <dimension ref="A1:E394"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8819,6 +8798,90 @@
         <v>142</v>
       </c>
     </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C391" s="2" t="n">
+        <v>35429.86</v>
+      </c>
+      <c r="D391" s="3" t="n">
+        <v>13.31062066</v>
+      </c>
+      <c r="E391" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C392" s="2" t="n">
+        <v>32122.79</v>
+      </c>
+      <c r="D392" s="3" t="n">
+        <v>12.06818972</v>
+      </c>
+      <c r="E392" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C393" s="2" t="n">
+        <v>40536.38</v>
+      </c>
+      <c r="D393" s="3" t="n">
+        <v>15.22908578</v>
+      </c>
+      <c r="E393" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C394" s="2" t="n">
+        <v>158088.34</v>
+      </c>
+      <c r="D394" s="3" t="n">
+        <v>59.39210384</v>
+      </c>
+      <c r="E394" t="n">
+        <v>193</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -479,49 +479,49 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Unclassified</t>
+          <t>Tech &amp; Science</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>158088.34</v>
+        <v>158704.71</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>59.39210384</v>
+        <v>50.67424116</v>
       </c>
       <c r="E2" t="n">
-        <v>193</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tech &amp; Science</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>40536.38</v>
+        <v>120794.19</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>15.22908578</v>
+        <v>38.56945339</v>
       </c>
       <c r="E3" t="n">
-        <v>36</v>
+        <v>154</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>35429.86</v>
+        <v>18675.56</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13.31062066</v>
+        <v>5.96308598</v>
       </c>
       <c r="E4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>32122.79</v>
+        <v>15011.7</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>12.06818972</v>
+        <v>4.79321947</v>
       </c>
       <c r="E5" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -572,13 +572,13 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>266177.37</v>
+        <v>313186.16</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>282</v>
+        <v>252</v>
       </c>
     </row>
   </sheetData>
@@ -592,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E394"/>
+  <dimension ref="A1:E398"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8882,6 +8882,90 @@
         <v>193</v>
       </c>
     </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C395" s="2" t="n">
+        <v>18675.56</v>
+      </c>
+      <c r="D395" s="3" t="n">
+        <v>5.96308598</v>
+      </c>
+      <c r="E395" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C396" s="2" t="n">
+        <v>15011.7</v>
+      </c>
+      <c r="D396" s="3" t="n">
+        <v>4.79321947</v>
+      </c>
+      <c r="E396" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C397" s="2" t="n">
+        <v>158704.71</v>
+      </c>
+      <c r="D397" s="3" t="n">
+        <v>50.67424116</v>
+      </c>
+      <c r="E397" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C398" s="2" t="n">
+        <v>120794.19</v>
+      </c>
+      <c r="D398" s="3" t="n">
+        <v>38.56945339</v>
+      </c>
+      <c r="E398" t="n">
+        <v>154</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,106 +479,127 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tech &amp; Science</t>
+          <t>Unclassified</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>158704.71</v>
+        <v>209165.12</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>50.67424116</v>
+        <v>67.4821278</v>
       </c>
       <c r="E2" t="n">
-        <v>71</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Unclassified</t>
+          <t>Tech &amp; Science</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>120794.19</v>
+        <v>97008.50999999999</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>38.56945339</v>
+        <v>31.29747766</v>
       </c>
       <c r="E3" t="n">
-        <v>154</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Business/Economy</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>18675.56</v>
+        <v>2850.15</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>5.96308598</v>
+        <v>0.91953279</v>
       </c>
       <c r="E4" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Business/Economy</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>15011.7</v>
+        <v>925.92</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>4.79321947</v>
+        <v>0.29872596</v>
       </c>
       <c r="E5" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0.00213578</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n">
-        <v>313186.16</v>
-      </c>
-      <c r="D6" s="6" t="n">
+      <c r="C7" s="5" t="n">
+        <v>309956.32</v>
+      </c>
+      <c r="D7" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>252</v>
+      <c r="E7" s="4" t="n">
+        <v>262</v>
       </c>
     </row>
   </sheetData>
@@ -592,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E398"/>
+  <dimension ref="A1:E403"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -8966,6 +8987,111 @@
         <v>154</v>
       </c>
     </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C399" s="2" t="n">
+        <v>925.92</v>
+      </c>
+      <c r="D399" s="3" t="n">
+        <v>0.29872596</v>
+      </c>
+      <c r="E399" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C400" s="2" t="n">
+        <v>2850.15</v>
+      </c>
+      <c r="D400" s="3" t="n">
+        <v>0.91953279</v>
+      </c>
+      <c r="E400" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C401" s="2" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="D401" s="3" t="n">
+        <v>0.00213578</v>
+      </c>
+      <c r="E401" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C402" s="2" t="n">
+        <v>97008.50999999999</v>
+      </c>
+      <c r="D402" s="3" t="n">
+        <v>31.29747766</v>
+      </c>
+      <c r="E402" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C403" s="2" t="n">
+        <v>209165.12</v>
+      </c>
+      <c r="D403" s="3" t="n">
+        <v>67.4821278</v>
+      </c>
+      <c r="E403" t="n">
+        <v>189</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,103 +488,103 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>209165.12</v>
+        <v>434509.4</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>67.4821278</v>
+        <v>78.41404713</v>
       </c>
       <c r="E2" t="n">
-        <v>189</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tech &amp; Science</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>97008.50999999999</v>
+        <v>68317.38</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>31.29747766</v>
+        <v>12.32894445</v>
       </c>
       <c r="E3" t="n">
-        <v>68</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Tech &amp; Science</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2850.15</v>
+        <v>36483.28</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.91953279</v>
+        <v>6.58398101</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Business/Economy</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>925.92</v>
+        <v>13257.43</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.29872596</v>
+        <v>2.39251151</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Business/Economy</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>6.62</v>
+        <v>1554.4</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.00213578</v>
+        <v>0.2805159</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>309956.32</v>
+        <v>554121.89</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>262</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>
@@ -613,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E403"/>
+  <dimension ref="A1:E408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9092,6 +9092,111 @@
         <v>189</v>
       </c>
     </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C404" s="2" t="n">
+        <v>1554.4</v>
+      </c>
+      <c r="D404" s="3" t="n">
+        <v>0.2805159</v>
+      </c>
+      <c r="E404" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C405" s="2" t="n">
+        <v>13257.43</v>
+      </c>
+      <c r="D405" s="3" t="n">
+        <v>2.39251151</v>
+      </c>
+      <c r="E405" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C406" s="2" t="n">
+        <v>68317.38</v>
+      </c>
+      <c r="D406" s="3" t="n">
+        <v>12.32894445</v>
+      </c>
+      <c r="E406" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C407" s="2" t="n">
+        <v>36483.28</v>
+      </c>
+      <c r="D407" s="3" t="n">
+        <v>6.58398101</v>
+      </c>
+      <c r="E407" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C408" s="2" t="n">
+        <v>434509.4</v>
+      </c>
+      <c r="D408" s="3" t="n">
+        <v>78.41404713</v>
+      </c>
+      <c r="E408" t="n">
+        <v>166</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,31 +488,31 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>434509.4</v>
+        <v>215229.17</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>78.41404713</v>
+        <v>64.98832014</v>
       </c>
       <c r="E2" t="n">
-        <v>166</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Business/Economy</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>68317.38</v>
+        <v>84045.97</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>12.32894445</v>
+        <v>25.37763076</v>
       </c>
       <c r="E3" t="n">
         <v>5</v>
@@ -521,7 +521,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,19 +530,19 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>36483.28</v>
+        <v>26688.17</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>6.58398101</v>
+        <v>8.05847709</v>
       </c>
       <c r="E4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,40 +551,40 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>13257.43</v>
+        <v>3679.54</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>2.39251151</v>
+        <v>1.11103492</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Business/Economy</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1554.4</v>
+        <v>1538.46</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.2805159</v>
+        <v>0.46453708</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>554121.89</v>
+        <v>331181.31</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>199</v>
+        <v>229</v>
       </c>
     </row>
   </sheetData>
@@ -613,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E408"/>
+  <dimension ref="A1:E413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9197,6 +9197,111 @@
         <v>166</v>
       </c>
     </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C409" s="2" t="n">
+        <v>84045.97</v>
+      </c>
+      <c r="D409" s="3" t="n">
+        <v>25.37763076</v>
+      </c>
+      <c r="E409" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C410" s="2" t="n">
+        <v>3679.54</v>
+      </c>
+      <c r="D410" s="3" t="n">
+        <v>1.11103492</v>
+      </c>
+      <c r="E410" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C411" s="2" t="n">
+        <v>1538.46</v>
+      </c>
+      <c r="D411" s="3" t="n">
+        <v>0.46453708</v>
+      </c>
+      <c r="E411" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C412" s="2" t="n">
+        <v>26688.17</v>
+      </c>
+      <c r="D412" s="3" t="n">
+        <v>8.05847709</v>
+      </c>
+      <c r="E412" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C413" s="2" t="n">
+        <v>215229.17</v>
+      </c>
+      <c r="D413" s="3" t="n">
+        <v>64.98832014</v>
+      </c>
+      <c r="E413" t="n">
+        <v>192</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,82 +488,82 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>215229.17</v>
+        <v>203124.98</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>64.98832014</v>
+        <v>84.63662850999999</v>
       </c>
       <c r="E2" t="n">
-        <v>192</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Business/Economy</t>
+          <t>Tech &amp; Science</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>84045.97</v>
+        <v>25240.28</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>25.37763076</v>
+        <v>10.51693495</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tech &amp; Science</t>
+          <t>Business/Economy</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>26688.17</v>
+        <v>6028.33</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>8.05847709</v>
+        <v>2.51184038</v>
       </c>
       <c r="E4" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>3679.54</v>
+        <v>3112.84</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1.11103492</v>
+        <v>1.29703537</v>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -572,34 +572,55 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1538.46</v>
+        <v>2022.83</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.46453708</v>
+        <v>0.84285798</v>
       </c>
       <c r="E6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>467.28</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0.19470281</v>
+      </c>
+      <c r="E7" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
-        <v>331181.31</v>
-      </c>
-      <c r="D7" s="6" t="n">
+      <c r="C8" s="5" t="n">
+        <v>239996.54</v>
+      </c>
+      <c r="D8" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E7" s="4" t="n">
-        <v>229</v>
+      <c r="E8" s="4" t="n">
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -613,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E413"/>
+  <dimension ref="A1:E419"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9302,6 +9323,132 @@
         <v>192</v>
       </c>
     </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C414" s="2" t="n">
+        <v>6028.33</v>
+      </c>
+      <c r="D414" s="3" t="n">
+        <v>2.51184038</v>
+      </c>
+      <c r="E414" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C415" s="2" t="n">
+        <v>3112.84</v>
+      </c>
+      <c r="D415" s="3" t="n">
+        <v>1.29703537</v>
+      </c>
+      <c r="E415" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C416" s="2" t="n">
+        <v>467.28</v>
+      </c>
+      <c r="D416" s="3" t="n">
+        <v>0.19470281</v>
+      </c>
+      <c r="E416" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C417" s="2" t="n">
+        <v>2022.83</v>
+      </c>
+      <c r="D417" s="3" t="n">
+        <v>0.84285798</v>
+      </c>
+      <c r="E417" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C418" s="2" t="n">
+        <v>25240.28</v>
+      </c>
+      <c r="D418" s="3" t="n">
+        <v>10.51693495</v>
+      </c>
+      <c r="E418" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C419" s="2" t="n">
+        <v>203124.98</v>
+      </c>
+      <c r="D419" s="3" t="n">
+        <v>84.63662850999999</v>
+      </c>
+      <c r="E419" t="n">
+        <v>149</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>203124.98</v>
+        <v>160658.86</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>84.63662850999999</v>
+        <v>76.2366936</v>
       </c>
       <c r="E2" t="n">
-        <v>149</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,103 +509,103 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>25240.28</v>
+        <v>36763.78</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>10.51693495</v>
+        <v>17.4453437</v>
       </c>
       <c r="E3" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Business/Economy</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>6028.33</v>
+        <v>4783.33</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2.51184038</v>
+        <v>2.2698111</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Business/Economy</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>3112.84</v>
+        <v>4052.09</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1.29703537</v>
+        <v>1.92281922</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>2022.83</v>
+        <v>3694.66</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.84285798</v>
+        <v>1.75320964</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>467.28</v>
+        <v>784.2</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.19470281</v>
+        <v>0.37212274</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -614,13 +614,13 @@
         </is>
       </c>
       <c r="C8" s="5" t="n">
-        <v>239996.54</v>
+        <v>210736.92</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>182</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E419"/>
+  <dimension ref="A1:E425"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9449,6 +9449,132 @@
         <v>149</v>
       </c>
     </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C420" s="2" t="n">
+        <v>4052.09</v>
+      </c>
+      <c r="D420" s="3" t="n">
+        <v>1.92281922</v>
+      </c>
+      <c r="E420" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C421" s="2" t="n">
+        <v>4783.33</v>
+      </c>
+      <c r="D421" s="3" t="n">
+        <v>2.2698111</v>
+      </c>
+      <c r="E421" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C422" s="2" t="n">
+        <v>3694.66</v>
+      </c>
+      <c r="D422" s="3" t="n">
+        <v>1.75320964</v>
+      </c>
+      <c r="E422" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C423" s="2" t="n">
+        <v>784.2</v>
+      </c>
+      <c r="D423" s="3" t="n">
+        <v>0.37212274</v>
+      </c>
+      <c r="E423" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C424" s="2" t="n">
+        <v>36763.78</v>
+      </c>
+      <c r="D424" s="3" t="n">
+        <v>17.4453437</v>
+      </c>
+      <c r="E424" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C425" s="2" t="n">
+        <v>160658.86</v>
+      </c>
+      <c r="D425" s="3" t="n">
+        <v>76.2366936</v>
+      </c>
+      <c r="E425" t="n">
+        <v>122</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,61 +488,61 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>160658.86</v>
+        <v>184753.69</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>76.2366936</v>
+        <v>82.03607473</v>
       </c>
       <c r="E2" t="n">
-        <v>122</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tech &amp; Science</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>36763.78</v>
+        <v>31634.55</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>17.4453437</v>
+        <v>14.04667104</v>
       </c>
       <c r="E3" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Tech &amp; Science</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>4783.33</v>
+        <v>8138.08</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>2.2698111</v>
+        <v>3.61354698</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,76 +551,55 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>4052.09</v>
+        <v>632.91</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1.92281922</v>
+        <v>0.28103066</v>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>3694.66</v>
+        <v>51.07</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1.75320964</v>
+        <v>0.02267658</v>
       </c>
       <c r="E6" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Sports</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>784.2</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>0.37212274</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n">
-        <v>210736.92</v>
-      </c>
-      <c r="D8" s="6" t="n">
+      <c r="C7" s="5" t="n">
+        <v>225210.3</v>
+      </c>
+      <c r="D7" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E8" s="4" t="n">
-        <v>159</v>
+      <c r="E7" s="4" t="n">
+        <v>260</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E425"/>
+  <dimension ref="A1:E430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9575,6 +9554,111 @@
         <v>122</v>
       </c>
     </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C426" s="2" t="n">
+        <v>632.91</v>
+      </c>
+      <c r="D426" s="3" t="n">
+        <v>0.28103066</v>
+      </c>
+      <c r="E426" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C427" s="2" t="n">
+        <v>31634.55</v>
+      </c>
+      <c r="D427" s="3" t="n">
+        <v>14.04667104</v>
+      </c>
+      <c r="E427" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C428" s="2" t="n">
+        <v>51.07</v>
+      </c>
+      <c r="D428" s="3" t="n">
+        <v>0.02267658</v>
+      </c>
+      <c r="E428" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C429" s="2" t="n">
+        <v>8138.08</v>
+      </c>
+      <c r="D429" s="3" t="n">
+        <v>3.61354698</v>
+      </c>
+      <c r="E429" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C430" s="2" t="n">
+        <v>184753.69</v>
+      </c>
+      <c r="D430" s="3" t="n">
+        <v>82.03607473</v>
+      </c>
+      <c r="E430" t="n">
+        <v>214</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,61 +488,61 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>184753.69</v>
+        <v>196643.56</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>82.03607473</v>
+        <v>65.40597252000001</v>
       </c>
       <c r="E2" t="n">
-        <v>214</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Tech &amp; Science</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>31634.55</v>
+        <v>90262.50999999999</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>14.04667104</v>
+        <v>30.02237779</v>
       </c>
       <c r="E3" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tech &amp; Science</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>8138.08</v>
+        <v>13374.33</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>3.61354698</v>
+        <v>4.44846025</v>
       </c>
       <c r="E4" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,55 +551,34 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>632.91</v>
+        <v>370.37</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.28103066</v>
+        <v>0.12318944</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Sports</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>51.07</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0.02267658</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
-        <v>225210.3</v>
-      </c>
-      <c r="D7" s="6" t="n">
+      <c r="C6" s="5" t="n">
+        <v>300650.77</v>
+      </c>
+      <c r="D6" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E7" s="4" t="n">
-        <v>260</v>
+      <c r="E6" s="4" t="n">
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -613,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E430"/>
+  <dimension ref="A1:E434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9659,6 +9638,90 @@
         <v>214</v>
       </c>
     </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C431" s="2" t="n">
+        <v>370.37</v>
+      </c>
+      <c r="D431" s="3" t="n">
+        <v>0.12318944</v>
+      </c>
+      <c r="E431" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C432" s="2" t="n">
+        <v>13374.33</v>
+      </c>
+      <c r="D432" s="3" t="n">
+        <v>4.44846025</v>
+      </c>
+      <c r="E432" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C433" s="2" t="n">
+        <v>90262.50999999999</v>
+      </c>
+      <c r="D433" s="3" t="n">
+        <v>30.02237779</v>
+      </c>
+      <c r="E433" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C434" s="2" t="n">
+        <v>196643.56</v>
+      </c>
+      <c r="D434" s="3" t="n">
+        <v>65.40597252000001</v>
+      </c>
+      <c r="E434" t="n">
+        <v>143</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>196643.56</v>
+        <v>240538.18</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>65.40597252000001</v>
+        <v>76.18569598000001</v>
       </c>
       <c r="E2" t="n">
-        <v>143</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>90262.50999999999</v>
+        <v>69638.25999999999</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>30.02237779</v>
+        <v>22.05653716</v>
       </c>
       <c r="E3" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,55 +530,76 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>13374.33</v>
+        <v>5137.53</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>4.44846025</v>
+        <v>1.62721069</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>387.7</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0.12279628</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
-        <v>370.37</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>0.12318944</v>
-      </c>
-      <c r="E5" t="n">
+      <c r="C6" s="2" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0.00775989</v>
+      </c>
+      <c r="E6" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n">
-        <v>300650.77</v>
-      </c>
-      <c r="D6" s="6" t="n">
+      <c r="C7" s="5" t="n">
+        <v>315726.17</v>
+      </c>
+      <c r="D7" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>177</v>
+      <c r="E7" s="4" t="n">
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -592,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E434"/>
+  <dimension ref="A1:E439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9722,6 +9743,111 @@
         <v>143</v>
       </c>
     </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C435" s="2" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="D435" s="3" t="n">
+        <v>0.00775989</v>
+      </c>
+      <c r="E435" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C436" s="2" t="n">
+        <v>5137.53</v>
+      </c>
+      <c r="D436" s="3" t="n">
+        <v>1.62721069</v>
+      </c>
+      <c r="E436" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C437" s="2" t="n">
+        <v>387.7</v>
+      </c>
+      <c r="D437" s="3" t="n">
+        <v>0.12279628</v>
+      </c>
+      <c r="E437" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C438" s="2" t="n">
+        <v>69638.25999999999</v>
+      </c>
+      <c r="D438" s="3" t="n">
+        <v>22.05653716</v>
+      </c>
+      <c r="E438" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C439" s="2" t="n">
+        <v>240538.18</v>
+      </c>
+      <c r="D439" s="3" t="n">
+        <v>76.18569598000001</v>
+      </c>
+      <c r="E439" t="n">
+        <v>182</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>240538.18</v>
+        <v>158577.73</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>76.18569598000001</v>
+        <v>70.25950666</v>
       </c>
       <c r="E2" t="n">
-        <v>182</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,73 +509,73 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>69638.25999999999</v>
+        <v>44798.68</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.05653716</v>
+        <v>19.84851943</v>
       </c>
       <c r="E3" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Business/Economy</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>5137.53</v>
+        <v>11292.41</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1.62721069</v>
+        <v>5.00321928</v>
       </c>
       <c r="E4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>387.7</v>
+        <v>5806.79</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.12279628</v>
+        <v>2.57275849</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Business/Economy</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>24.5</v>
+        <v>5227.27</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.00775989</v>
+        <v>2.31599615</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>315726.17</v>
+        <v>225702.88</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>230</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -613,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E439"/>
+  <dimension ref="A1:E444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9848,6 +9848,111 @@
         <v>182</v>
       </c>
     </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C440" s="2" t="n">
+        <v>11292.41</v>
+      </c>
+      <c r="D440" s="3" t="n">
+        <v>5.00321928</v>
+      </c>
+      <c r="E440" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C441" s="2" t="n">
+        <v>5806.79</v>
+      </c>
+      <c r="D441" s="3" t="n">
+        <v>2.57275849</v>
+      </c>
+      <c r="E441" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C442" s="2" t="n">
+        <v>5227.27</v>
+      </c>
+      <c r="D442" s="3" t="n">
+        <v>2.31599615</v>
+      </c>
+      <c r="E442" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C443" s="2" t="n">
+        <v>44798.68</v>
+      </c>
+      <c r="D443" s="3" t="n">
+        <v>19.84851943</v>
+      </c>
+      <c r="E443" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C444" s="2" t="n">
+        <v>158577.73</v>
+      </c>
+      <c r="D444" s="3" t="n">
+        <v>70.25950666</v>
+      </c>
+      <c r="E444" t="n">
+        <v>114</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>158577.73</v>
+        <v>476360.36</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>70.25950666</v>
+        <v>89.5635712</v>
       </c>
       <c r="E2" t="n">
-        <v>114</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,73 +509,73 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>44798.68</v>
+        <v>27839.02</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>19.84851943</v>
+        <v>5.23419298</v>
       </c>
       <c r="E3" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Business/Economy</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>11292.41</v>
+        <v>27501.45</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>5.00321928</v>
+        <v>5.17072427</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>5806.79</v>
+        <v>162.95</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>2.57275849</v>
+        <v>0.03063728</v>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Business/Economy</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>5227.27</v>
+        <v>4.65</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2.31599615</v>
+        <v>0.00087428</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>225702.88</v>
+        <v>531868.4300000001</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>170</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -613,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E444"/>
+  <dimension ref="A1:E449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9953,6 +9953,111 @@
         <v>114</v>
       </c>
     </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C445" s="2" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="D445" s="3" t="n">
+        <v>0.00087428</v>
+      </c>
+      <c r="E445" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C446" s="2" t="n">
+        <v>27501.45</v>
+      </c>
+      <c r="D446" s="3" t="n">
+        <v>5.17072427</v>
+      </c>
+      <c r="E446" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C447" s="2" t="n">
+        <v>162.95</v>
+      </c>
+      <c r="D447" s="3" t="n">
+        <v>0.03063728</v>
+      </c>
+      <c r="E447" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C448" s="2" t="n">
+        <v>27839.02</v>
+      </c>
+      <c r="D448" s="3" t="n">
+        <v>5.23419298</v>
+      </c>
+      <c r="E448" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C449" s="2" t="n">
+        <v>476360.36</v>
+      </c>
+      <c r="D449" s="3" t="n">
+        <v>89.5635712</v>
+      </c>
+      <c r="E449" t="n">
+        <v>145</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>476360.36</v>
+        <v>83966.32000000001</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>89.5635712</v>
+        <v>78.88263399</v>
       </c>
       <c r="E2" t="n">
-        <v>145</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,97 +509,76 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>27839.02</v>
+        <v>19728.18</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>5.23419298</v>
+        <v>18.53375023</v>
       </c>
       <c r="E3" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>27501.45</v>
+        <v>1928.09</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>5.17072427</v>
+        <v>1.81135505</v>
       </c>
       <c r="E4" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>162.95</v>
+        <v>822.03</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.03063728</v>
+        <v>0.77226073</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Business/Economy</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0.00087428</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
-        <v>531868.4300000001</v>
-      </c>
-      <c r="D7" s="6" t="n">
+      <c r="C6" s="5" t="n">
+        <v>106444.62</v>
+      </c>
+      <c r="D6" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E7" s="4" t="n">
-        <v>185</v>
+      <c r="E6" s="4" t="n">
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -613,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E449"/>
+  <dimension ref="A1:E453"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10058,6 +10037,90 @@
         <v>145</v>
       </c>
     </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C450" s="2" t="n">
+        <v>822.03</v>
+      </c>
+      <c r="D450" s="3" t="n">
+        <v>0.77226073</v>
+      </c>
+      <c r="E450" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C451" s="2" t="n">
+        <v>1928.09</v>
+      </c>
+      <c r="D451" s="3" t="n">
+        <v>1.81135505</v>
+      </c>
+      <c r="E451" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C452" s="2" t="n">
+        <v>19728.18</v>
+      </c>
+      <c r="D452" s="3" t="n">
+        <v>18.53375023</v>
+      </c>
+      <c r="E452" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C453" s="2" t="n">
+        <v>83966.32000000001</v>
+      </c>
+      <c r="D453" s="3" t="n">
+        <v>78.88263399</v>
+      </c>
+      <c r="E453" t="n">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,97 +488,76 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>83966.32000000001</v>
+        <v>47873.33</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>78.88263399</v>
+        <v>69.55978129</v>
       </c>
       <c r="E2" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tech &amp; Science</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>19728.18</v>
+        <v>11929.86</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>18.53375023</v>
+        <v>17.33404491</v>
       </c>
       <c r="E3" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Tech &amp; Science</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1928.09</v>
+        <v>9020.1</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1.81135505</v>
+        <v>13.1061738</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Geopolitics</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>822.03</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>0.77226073</v>
-      </c>
-      <c r="E5" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n">
-        <v>106444.62</v>
-      </c>
-      <c r="D6" s="6" t="n">
+      <c r="C5" s="5" t="n">
+        <v>68823.28999999999</v>
+      </c>
+      <c r="D5" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>114</v>
+      <c r="E5" s="4" t="n">
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -592,7 +571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E453"/>
+  <dimension ref="A1:E456"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10121,6 +10100,69 @@
         <v>100</v>
       </c>
     </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C454" s="2" t="n">
+        <v>11929.86</v>
+      </c>
+      <c r="D454" s="3" t="n">
+        <v>17.33404491</v>
+      </c>
+      <c r="E454" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C455" s="2" t="n">
+        <v>9020.1</v>
+      </c>
+      <c r="D455" s="3" t="n">
+        <v>13.1061738</v>
+      </c>
+      <c r="E455" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C456" s="2" t="n">
+        <v>47873.33</v>
+      </c>
+      <c r="D456" s="3" t="n">
+        <v>69.55978129</v>
+      </c>
+      <c r="E456" t="n">
+        <v>101</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,76 +488,118 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>47873.33</v>
+        <v>104120.71</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>69.55978129</v>
+        <v>68.72963976</v>
       </c>
       <c r="E2" t="n">
-        <v>101</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Tech &amp; Science</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>11929.86</v>
+        <v>27605.06</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>17.33404491</v>
+        <v>18.22198321</v>
       </c>
       <c r="E3" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tech &amp; Science</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>9020.1</v>
+        <v>10214.3</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>13.1061738</v>
+        <v>6.74241618</v>
       </c>
       <c r="E4" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-25</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>9530.34</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>6.29093708</v>
+      </c>
+      <c r="E5" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>22.76</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0.01502378</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n">
-        <v>68823.28999999999</v>
-      </c>
-      <c r="D5" s="6" t="n">
+      <c r="C7" s="5" t="n">
+        <v>151493.17</v>
+      </c>
+      <c r="D7" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E5" s="4" t="n">
-        <v>130</v>
+      <c r="E7" s="4" t="n">
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -571,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E456"/>
+  <dimension ref="A1:E461"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10163,6 +10205,111 @@
         <v>101</v>
       </c>
     </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C457" s="2" t="n">
+        <v>22.76</v>
+      </c>
+      <c r="D457" s="3" t="n">
+        <v>0.01502378</v>
+      </c>
+      <c r="E457" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C458" s="2" t="n">
+        <v>9530.34</v>
+      </c>
+      <c r="D458" s="3" t="n">
+        <v>6.29093708</v>
+      </c>
+      <c r="E458" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C459" s="2" t="n">
+        <v>10214.3</v>
+      </c>
+      <c r="D459" s="3" t="n">
+        <v>6.74241618</v>
+      </c>
+      <c r="E459" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C460" s="2" t="n">
+        <v>27605.06</v>
+      </c>
+      <c r="D460" s="3" t="n">
+        <v>18.22198321</v>
+      </c>
+      <c r="E460" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C461" s="2" t="n">
+        <v>104120.71</v>
+      </c>
+      <c r="D461" s="3" t="n">
+        <v>68.72963976</v>
+      </c>
+      <c r="E461" t="n">
+        <v>144</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>104120.71</v>
+        <v>151007.13</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>68.72963976</v>
+        <v>76.11251842999999</v>
       </c>
       <c r="E2" t="n">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,82 +509,82 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>27605.06</v>
+        <v>45400.43</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>18.22198321</v>
+        <v>22.8832974</v>
       </c>
       <c r="E3" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>10214.3</v>
+        <v>769.23</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>6.74241618</v>
+        <v>0.38771701</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Geopolitics</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>9530.34</v>
+        <v>701.92</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>6.29093708</v>
+        <v>0.35379057</v>
       </c>
       <c r="E5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Business/Economy</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>22.76</v>
+        <v>521.15</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0.01502378</v>
+        <v>0.2626766</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>151493.17</v>
+        <v>198399.86</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>100</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>178</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -613,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E461"/>
+  <dimension ref="A1:E466"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10310,6 +10310,111 @@
         <v>144</v>
       </c>
     </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C462" s="2" t="n">
+        <v>769.23</v>
+      </c>
+      <c r="D462" s="3" t="n">
+        <v>0.38771701</v>
+      </c>
+      <c r="E462" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C463" s="2" t="n">
+        <v>521.15</v>
+      </c>
+      <c r="D463" s="3" t="n">
+        <v>0.2626766</v>
+      </c>
+      <c r="E463" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="C464" s="2" t="n">
+        <v>701.92</v>
+      </c>
+      <c r="D464" s="3" t="n">
+        <v>0.35379057</v>
+      </c>
+      <c r="E464" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C465" s="2" t="n">
+        <v>45400.43</v>
+      </c>
+      <c r="D465" s="3" t="n">
+        <v>22.8832974</v>
+      </c>
+      <c r="E465" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C466" s="2" t="n">
+        <v>151007.13</v>
+      </c>
+      <c r="D466" s="3" t="n">
+        <v>76.11251842999999</v>
+      </c>
+      <c r="E466" t="n">
+        <v>151</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>151007.13</v>
+        <v>112223.75</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>76.11251842999999</v>
+        <v>64.35672067</v>
       </c>
       <c r="E2" t="n">
-        <v>151</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,97 +509,76 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>45400.43</v>
+        <v>45149.15</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>22.8832974</v>
+        <v>25.89158922</v>
       </c>
       <c r="E3" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Business/Economy</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>769.23</v>
+        <v>16710.66</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0.38771701</v>
+        <v>9.58302746</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Geopolitics</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>701.92</v>
+        <v>294.11</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0.35379057</v>
+        <v>0.16866265</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Geopolitics</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>521.15</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0.2626766</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
-        <v>198399.86</v>
-      </c>
-      <c r="D7" s="6" t="n">
+      <c r="C6" s="5" t="n">
+        <v>174377.67</v>
+      </c>
+      <c r="D6" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E7" s="4" t="n">
-        <v>194</v>
+      <c r="E6" s="4" t="n">
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -613,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E466"/>
+  <dimension ref="A1:E470"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10415,6 +10394,90 @@
         <v>151</v>
       </c>
     </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C467" s="2" t="n">
+        <v>16710.66</v>
+      </c>
+      <c r="D467" s="3" t="n">
+        <v>9.58302746</v>
+      </c>
+      <c r="E467" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C468" s="2" t="n">
+        <v>294.11</v>
+      </c>
+      <c r="D468" s="3" t="n">
+        <v>0.16866265</v>
+      </c>
+      <c r="E468" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C469" s="2" t="n">
+        <v>45149.15</v>
+      </c>
+      <c r="D469" s="3" t="n">
+        <v>25.89158922</v>
+      </c>
+      <c r="E469" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C470" s="2" t="n">
+        <v>112223.75</v>
+      </c>
+      <c r="D470" s="3" t="n">
+        <v>64.35672067</v>
+      </c>
+      <c r="E470" t="n">
+        <v>120</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -69,11 +69,11 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -477,108 +477,24 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Unclassified</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>112223.75</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>64.35672067</v>
-      </c>
-      <c r="E2" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Tech &amp; Science</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>45149.15</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>25.89158922</v>
-      </c>
-      <c r="E3" t="n">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Business/Economy</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>16710.66</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>9.58302746</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Geopolitics</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>294.11</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>0.16866265</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-28</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n">
-        <v>174377.67</v>
-      </c>
-      <c r="D6" s="6" t="n">
+      <c r="C2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>176</v>
+      <c r="E2" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -640,10 +556,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="5" t="n">
         <v>948.86</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="6" t="n">
         <v>0.19126904</v>
       </c>
       <c r="E2" t="n">
@@ -661,10 +577,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="5" t="n">
         <v>461123.2</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="6" t="n">
         <v>92.95216732</v>
       </c>
       <c r="E3" t="n">
@@ -682,10 +598,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" s="5" t="n">
         <v>333</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="6" t="n">
         <v>0.06712538</v>
       </c>
       <c r="E4" t="n">
@@ -703,10 +619,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" s="5" t="n">
         <v>33681.49</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="6" t="n">
         <v>6.78943825</v>
       </c>
       <c r="E5" t="n">
@@ -724,10 +640,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" s="5" t="n">
         <v>3947.95</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="6" t="n">
         <v>0.94921987</v>
       </c>
       <c r="E6" t="n">
@@ -745,10 +661,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" s="5" t="n">
         <v>316928.34</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="6" t="n">
         <v>76.20022474</v>
       </c>
       <c r="E7" t="n">
@@ -766,10 +682,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="C8" s="5" t="n">
         <v>28879.81</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="6" t="n">
         <v>6.94367696</v>
       </c>
       <c r="E8" t="n">
@@ -787,10 +703,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n">
+      <c r="C9" s="5" t="n">
         <v>66159.13</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" s="6" t="n">
         <v>15.90687843</v>
       </c>
       <c r="E9" t="n">
@@ -808,10 +724,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n">
+      <c r="C10" s="5" t="n">
         <v>672.72</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D10" s="6" t="n">
         <v>0.12167625</v>
       </c>
       <c r="E10" t="n">
@@ -829,10 +745,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n">
+      <c r="C11" s="5" t="n">
         <v>506109.58</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="D11" s="6" t="n">
         <v>91.54108388</v>
       </c>
       <c r="E11" t="n">
@@ -850,10 +766,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C12" s="2" t="n">
+      <c r="C12" s="5" t="n">
         <v>13144.61</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" s="6" t="n">
         <v>2.37749273</v>
       </c>
       <c r="E12" t="n">
@@ -871,10 +787,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n">
+      <c r="C13" s="5" t="n">
         <v>32950.07</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" s="6" t="n">
         <v>5.95974714</v>
       </c>
       <c r="E13" t="n">
@@ -892,10 +808,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
+      <c r="C14" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D14" s="6" t="n">
         <v>0.00340356</v>
       </c>
       <c r="E14" t="n">
@@ -913,10 +829,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n">
+      <c r="C15" s="5" t="n">
         <v>3803.45</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="D15" s="6" t="n">
         <v>1.43836189</v>
       </c>
       <c r="E15" t="n">
@@ -934,10 +850,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n">
+      <c r="C16" s="5" t="n">
         <v>229609.87</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D16" s="6" t="n">
         <v>86.83224112000001</v>
       </c>
       <c r="E16" t="n">
@@ -955,10 +871,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C17" s="2" t="n">
+      <c r="C17" s="5" t="n">
         <v>884.04</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="D17" s="6" t="n">
         <v>0.33432001</v>
       </c>
       <c r="E17" t="n">
@@ -976,10 +892,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C18" s="2" t="n">
+      <c r="C18" s="5" t="n">
         <v>30122.92</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="D18" s="6" t="n">
         <v>11.39167342</v>
       </c>
       <c r="E18" t="n">
@@ -997,10 +913,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C19" s="2" t="n">
+      <c r="C19" s="5" t="n">
         <v>23268.18</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="D19" s="6" t="n">
         <v>4.17124226</v>
       </c>
       <c r="E19" t="n">
@@ -1018,10 +934,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C20" s="2" t="n">
+      <c r="C20" s="5" t="n">
         <v>451338.15</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="D20" s="6" t="n">
         <v>80.91052954</v>
       </c>
       <c r="E20" t="n">
@@ -1039,10 +955,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C21" s="2" t="n">
+      <c r="C21" s="5" t="n">
         <v>20229.42</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="D21" s="6" t="n">
         <v>3.62648955</v>
       </c>
       <c r="E21" t="n">
@@ -1060,10 +976,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C22" s="2" t="n">
+      <c r="C22" s="5" t="n">
         <v>62988</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="D22" s="6" t="n">
         <v>11.29173865</v>
       </c>
       <c r="E22" t="n">
@@ -1081,10 +997,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C23" s="2" t="n">
+      <c r="C23" s="5" t="n">
         <v>103.09</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="D23" s="6" t="n">
         <v>0.02902112</v>
       </c>
       <c r="E23" t="n">
@@ -1102,10 +1018,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C24" s="2" t="n">
+      <c r="C24" s="5" t="n">
         <v>283.13</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="D24" s="6" t="n">
         <v>0.07970463</v>
       </c>
       <c r="E24" t="n">
@@ -1123,10 +1039,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C25" s="2" t="n">
+      <c r="C25" s="5" t="n">
         <v>341584.75</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="D25" s="6" t="n">
         <v>96.16036696</v>
       </c>
       <c r="E25" t="n">
@@ -1144,10 +1060,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C26" s="2" t="n">
+      <c r="C26" s="5" t="n">
         <v>13253.08</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="D26" s="6" t="n">
         <v>3.7309073</v>
       </c>
       <c r="E26" t="n">
@@ -1165,10 +1081,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C27" s="2" t="n">
+      <c r="C27" s="5" t="n">
         <v>366675.1</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="D27" s="6" t="n">
         <v>88.88052623</v>
       </c>
       <c r="E27" t="n">
@@ -1186,10 +1102,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C28" s="2" t="n">
+      <c r="C28" s="5" t="n">
         <v>10967.83</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="D28" s="6" t="n">
         <v>2.65855659</v>
       </c>
       <c r="E28" t="n">
@@ -1207,10 +1123,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C29" s="2" t="n">
+      <c r="C29" s="5" t="n">
         <v>34905.37</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="D29" s="6" t="n">
         <v>8.460917179999999</v>
       </c>
       <c r="E29" t="n">
@@ -1228,10 +1144,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C30" s="2" t="n">
+      <c r="C30" s="5" t="n">
         <v>431085.81</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="D30" s="6" t="n">
         <v>81.83421629999999</v>
       </c>
       <c r="E30" t="n">
@@ -1249,10 +1165,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C31" s="2" t="n">
+      <c r="C31" s="5" t="n">
         <v>1633.45</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="D31" s="6" t="n">
         <v>0.31008235</v>
       </c>
       <c r="E31" t="n">
@@ -1270,10 +1186,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C32" s="2" t="n">
+      <c r="C32" s="5" t="n">
         <v>94060.16</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="D32" s="6" t="n">
         <v>17.85570135</v>
       </c>
       <c r="E32" t="n">
@@ -1291,10 +1207,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C33" s="2" t="n">
+      <c r="C33" s="5" t="n">
         <v>321805.16</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="D33" s="6" t="n">
         <v>78.53984421</v>
       </c>
       <c r="E33" t="n">
@@ -1312,10 +1228,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C34" s="2" t="n">
+      <c r="C34" s="5" t="n">
         <v>81063.48</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="D34" s="6" t="n">
         <v>19.78437229</v>
       </c>
       <c r="E34" t="n">
@@ -1333,10 +1249,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C35" s="2" t="n">
+      <c r="C35" s="5" t="n">
         <v>6866.27</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="D35" s="6" t="n">
         <v>1.6757835</v>
       </c>
       <c r="E35" t="n">
@@ -1354,10 +1270,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C36" s="2" t="n">
+      <c r="C36" s="5" t="n">
         <v>352851.14</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="D36" s="6" t="n">
         <v>94.15474251000001</v>
       </c>
       <c r="E36" t="n">
@@ -1375,10 +1291,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C37" s="2" t="n">
+      <c r="C37" s="5" t="n">
         <v>576.49</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="D37" s="6" t="n">
         <v>0.1538305</v>
       </c>
       <c r="E37" t="n">
@@ -1396,10 +1312,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C38" s="2" t="n">
+      <c r="C38" s="5" t="n">
         <v>21329</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="D38" s="6" t="n">
         <v>5.69142699</v>
       </c>
       <c r="E38" t="n">
@@ -1417,10 +1333,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C39" s="2" t="n">
+      <c r="C39" s="5" t="n">
         <v>83.52</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="D39" s="6" t="n">
         <v>0.01466719</v>
       </c>
       <c r="E39" t="n">
@@ -1438,10 +1354,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C40" s="2" t="n">
+      <c r="C40" s="5" t="n">
         <v>509873.13</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="D40" s="6" t="n">
         <v>89.54027855</v>
       </c>
       <c r="E40" t="n">
@@ -1459,10 +1375,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C41" s="2" t="n">
+      <c r="C41" s="5" t="n">
         <v>8520.23</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="D41" s="6" t="n">
         <v>1.49626196</v>
       </c>
       <c r="E41" t="n">
@@ -1480,10 +1396,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C42" s="2" t="n">
+      <c r="C42" s="5" t="n">
         <v>50957.5</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="D42" s="6" t="n">
         <v>8.94879231</v>
       </c>
       <c r="E42" t="n">
@@ -1501,10 +1417,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C43" s="2" t="n">
+      <c r="C43" s="5" t="n">
         <v>9326.15</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="D43" s="6" t="n">
         <v>1.62650962</v>
       </c>
       <c r="E43" t="n">
@@ -1522,10 +1438,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C44" s="2" t="n">
+      <c r="C44" s="5" t="n">
         <v>510341.61</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="D44" s="6" t="n">
         <v>89.00516713</v>
       </c>
       <c r="E44" t="n">
@@ -1543,10 +1459,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C45" s="2" t="n">
+      <c r="C45" s="5" t="n">
         <v>2517.04</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="D45" s="6" t="n">
         <v>0.43897962</v>
       </c>
       <c r="E45" t="n">
@@ -1564,10 +1480,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C46" s="2" t="n">
+      <c r="C46" s="5" t="n">
         <v>51199.45</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="D46" s="6" t="n">
         <v>8.92934363</v>
       </c>
       <c r="E46" t="n">
@@ -1585,10 +1501,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="C47" s="2" t="n">
+      <c r="C47" s="5" t="n">
         <v>850</v>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="D47" s="6" t="n">
         <v>0.25302704</v>
       </c>
       <c r="E47" t="n">
@@ -1606,10 +1522,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C48" s="2" t="n">
+      <c r="C48" s="5" t="n">
         <v>1223.36</v>
       </c>
-      <c r="D48" s="3" t="n">
+      <c r="D48" s="6" t="n">
         <v>0.36416843</v>
       </c>
       <c r="E48" t="n">
@@ -1627,10 +1543,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C49" s="2" t="n">
+      <c r="C49" s="5" t="n">
         <v>270843.56</v>
       </c>
-      <c r="D49" s="3" t="n">
+      <c r="D49" s="6" t="n">
         <v>80.62440645</v>
       </c>
       <c r="E49" t="n">
@@ -1648,10 +1564,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C50" s="2" t="n">
+      <c r="C50" s="5" t="n">
         <v>612.64</v>
       </c>
-      <c r="D50" s="3" t="n">
+      <c r="D50" s="6" t="n">
         <v>0.18236999</v>
       </c>
       <c r="E50" t="n">
@@ -1669,10 +1585,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C51" s="2" t="n">
+      <c r="C51" s="5" t="n">
         <v>62402.91</v>
       </c>
-      <c r="D51" s="3" t="n">
+      <c r="D51" s="6" t="n">
         <v>18.57602809</v>
       </c>
       <c r="E51" t="n">
@@ -1690,10 +1606,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C52" s="2" t="n">
+      <c r="C52" s="5" t="n">
         <v>555930.41</v>
       </c>
-      <c r="D52" s="3" t="n">
+      <c r="D52" s="6" t="n">
         <v>91.1452503</v>
       </c>
       <c r="E52" t="n">
@@ -1711,10 +1627,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C53" s="2" t="n">
+      <c r="C53" s="5" t="n">
         <v>1590.9</v>
       </c>
-      <c r="D53" s="3" t="n">
+      <c r="D53" s="6" t="n">
         <v>0.26082937</v>
       </c>
       <c r="E53" t="n">
@@ -1732,10 +1648,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C54" s="2" t="n">
+      <c r="C54" s="5" t="n">
         <v>52417.67</v>
       </c>
-      <c r="D54" s="3" t="n">
+      <c r="D54" s="6" t="n">
         <v>8.59392033</v>
       </c>
       <c r="E54" t="n">
@@ -1753,10 +1669,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C55" s="2" t="n">
+      <c r="C55" s="5" t="n">
         <v>10.55</v>
       </c>
-      <c r="D55" s="3" t="n">
+      <c r="D55" s="6" t="n">
         <v>0.00287103</v>
       </c>
       <c r="E55" t="n">
@@ -1774,10 +1690,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C56" s="2" t="n">
+      <c r="C56" s="5" t="n">
         <v>319888.32</v>
       </c>
-      <c r="D56" s="3" t="n">
+      <c r="D56" s="6" t="n">
         <v>87.05305848</v>
       </c>
       <c r="E56" t="n">
@@ -1795,10 +1711,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C57" s="2" t="n">
+      <c r="C57" s="5" t="n">
         <v>1278.17</v>
       </c>
-      <c r="D57" s="3" t="n">
+      <c r="D57" s="6" t="n">
         <v>0.34783579</v>
       </c>
       <c r="E57" t="n">
@@ -1816,10 +1732,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C58" s="2" t="n">
+      <c r="C58" s="5" t="n">
         <v>46286.58</v>
       </c>
-      <c r="D58" s="3" t="n">
+      <c r="D58" s="6" t="n">
         <v>12.5962347</v>
       </c>
       <c r="E58" t="n">
@@ -1837,10 +1753,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C59" s="2" t="n">
+      <c r="C59" s="5" t="n">
         <v>354.29</v>
       </c>
-      <c r="D59" s="3" t="n">
+      <c r="D59" s="6" t="n">
         <v>0.1171275</v>
       </c>
       <c r="E59" t="n">
@@ -1858,10 +1774,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C60" s="2" t="n">
+      <c r="C60" s="5" t="n">
         <v>121.49</v>
       </c>
-      <c r="D60" s="3" t="n">
+      <c r="D60" s="6" t="n">
         <v>0.04016433</v>
       </c>
       <c r="E60" t="n">
@@ -1879,10 +1795,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C61" s="2" t="n">
+      <c r="C61" s="5" t="n">
         <v>264522.3</v>
       </c>
-      <c r="D61" s="3" t="n">
+      <c r="D61" s="6" t="n">
         <v>87.4504938</v>
       </c>
       <c r="E61" t="n">
@@ -1900,10 +1816,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C62" s="2" t="n">
+      <c r="C62" s="5" t="n">
         <v>1149.77</v>
       </c>
-      <c r="D62" s="3" t="n">
+      <c r="D62" s="6" t="n">
         <v>0.38011145</v>
       </c>
       <c r="E62" t="n">
@@ -1921,10 +1837,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C63" s="2" t="n">
+      <c r="C63" s="5" t="n">
         <v>36334.49</v>
       </c>
-      <c r="D63" s="3" t="n">
+      <c r="D63" s="6" t="n">
         <v>12.01210292</v>
       </c>
       <c r="E63" t="n">
@@ -1942,10 +1858,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C64" s="2" t="n">
+      <c r="C64" s="5" t="n">
         <v>4545.45</v>
       </c>
-      <c r="D64" s="3" t="n">
+      <c r="D64" s="6" t="n">
         <v>1.24043036</v>
       </c>
       <c r="E64" t="n">
@@ -1963,10 +1879,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C65" s="2" t="n">
+      <c r="C65" s="5" t="n">
         <v>874</v>
       </c>
-      <c r="D65" s="3" t="n">
+      <c r="D65" s="6" t="n">
         <v>0.23851019</v>
       </c>
       <c r="E65" t="n">
@@ -1984,10 +1900,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C66" s="2" t="n">
+      <c r="C66" s="5" t="n">
         <v>284866.12</v>
       </c>
-      <c r="D66" s="3" t="n">
+      <c r="D66" s="6" t="n">
         <v>77.73852608</v>
       </c>
       <c r="E66" t="n">
@@ -2005,10 +1921,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C67" s="2" t="n">
+      <c r="C67" s="5" t="n">
         <v>1590.95</v>
       </c>
-      <c r="D67" s="3" t="n">
+      <c r="D67" s="6" t="n">
         <v>0.43416222</v>
       </c>
       <c r="E67" t="n">
@@ -2026,10 +1942,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C68" s="2" t="n">
+      <c r="C68" s="5" t="n">
         <v>74564.85000000001</v>
       </c>
-      <c r="D68" s="3" t="n">
+      <c r="D68" s="6" t="n">
         <v>20.34837115</v>
       </c>
       <c r="E68" t="n">
@@ -2047,10 +1963,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C69" s="2" t="n">
+      <c r="C69" s="5" t="n">
         <v>442814.15</v>
       </c>
-      <c r="D69" s="3" t="n">
+      <c r="D69" s="6" t="n">
         <v>80.48822254</v>
       </c>
       <c r="E69" t="n">
@@ -2068,10 +1984,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C70" s="2" t="n">
+      <c r="C70" s="5" t="n">
         <v>914.39</v>
       </c>
-      <c r="D70" s="3" t="n">
+      <c r="D70" s="6" t="n">
         <v>0.16620432</v>
       </c>
       <c r="E70" t="n">
@@ -2089,10 +2005,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C71" s="2" t="n">
+      <c r="C71" s="5" t="n">
         <v>106431.64</v>
       </c>
-      <c r="D71" s="3" t="n">
+      <c r="D71" s="6" t="n">
         <v>19.34557314</v>
       </c>
       <c r="E71" t="n">
@@ -2110,10 +2026,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C72" s="2" t="n">
+      <c r="C72" s="5" t="n">
         <v>166</v>
       </c>
-      <c r="D72" s="3" t="n">
+      <c r="D72" s="6" t="n">
         <v>0.02878159</v>
       </c>
       <c r="E72" t="n">
@@ -2131,10 +2047,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C73" s="2" t="n">
+      <c r="C73" s="5" t="n">
         <v>81.83</v>
       </c>
-      <c r="D73" s="3" t="n">
+      <c r="D73" s="6" t="n">
         <v>0.01418794</v>
       </c>
       <c r="E73" t="n">
@@ -2152,10 +2068,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C74" s="2" t="n">
+      <c r="C74" s="5" t="n">
         <v>528120.33</v>
       </c>
-      <c r="D74" s="3" t="n">
+      <c r="D74" s="6" t="n">
         <v>91.56712743999999</v>
       </c>
       <c r="E74" t="n">
@@ -2173,10 +2089,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C75" s="2" t="n">
+      <c r="C75" s="5" t="n">
         <v>567.3200000000001</v>
       </c>
-      <c r="D75" s="3" t="n">
+      <c r="D75" s="6" t="n">
         <v>0.09836369</v>
       </c>
       <c r="E75" t="n">
@@ -2194,10 +2110,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C76" s="2" t="n">
+      <c r="C76" s="5" t="n">
         <v>47822.08</v>
       </c>
-      <c r="D76" s="3" t="n">
+      <c r="D76" s="6" t="n">
         <v>8.29153934</v>
       </c>
       <c r="E76" t="n">
@@ -2215,10 +2131,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C77" s="2" t="n">
+      <c r="C77" s="5" t="n">
         <v>2157.29</v>
       </c>
-      <c r="D77" s="3" t="n">
+      <c r="D77" s="6" t="n">
         <v>1.00708473</v>
       </c>
       <c r="E77" t="n">
@@ -2236,10 +2152,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C78" s="2" t="n">
+      <c r="C78" s="5" t="n">
         <v>177127.26</v>
       </c>
-      <c r="D78" s="3" t="n">
+      <c r="D78" s="6" t="n">
         <v>82.68807579999999</v>
       </c>
       <c r="E78" t="n">
@@ -2257,10 +2173,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C79" s="2" t="n">
+      <c r="C79" s="5" t="n">
         <v>826.1799999999999</v>
       </c>
-      <c r="D79" s="3" t="n">
+      <c r="D79" s="6" t="n">
         <v>0.38568448</v>
       </c>
       <c r="E79" t="n">
@@ -2278,10 +2194,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C80" s="2" t="n">
+      <c r="C80" s="5" t="n">
         <v>34100.64</v>
       </c>
-      <c r="D80" s="3" t="n">
+      <c r="D80" s="6" t="n">
         <v>15.91915499</v>
       </c>
       <c r="E80" t="n">
@@ -2299,10 +2215,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C81" s="2" t="n">
+      <c r="C81" s="5" t="n">
         <v>54.12</v>
       </c>
-      <c r="D81" s="3" t="n">
+      <c r="D81" s="6" t="n">
         <v>0.01747125</v>
       </c>
       <c r="E81" t="n">
@@ -2320,10 +2236,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C82" s="2" t="n">
+      <c r="C82" s="5" t="n">
         <v>66</v>
       </c>
-      <c r="D82" s="3" t="n">
+      <c r="D82" s="6" t="n">
         <v>0.0213064</v>
       </c>
       <c r="E82" t="n">
@@ -2341,10 +2257,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C83" s="2" t="n">
+      <c r="C83" s="5" t="n">
         <v>21771.31</v>
       </c>
-      <c r="D83" s="3" t="n">
+      <c r="D83" s="6" t="n">
         <v>7.02830778</v>
       </c>
       <c r="E83" t="n">
@@ -2362,10 +2278,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C84" s="2" t="n">
+      <c r="C84" s="5" t="n">
         <v>214416.2</v>
       </c>
-      <c r="D84" s="3" t="n">
+      <c r="D84" s="6" t="n">
         <v>69.21875842999999</v>
       </c>
       <c r="E84" t="n">
@@ -2383,10 +2299,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C85" s="2" t="n">
+      <c r="C85" s="5" t="n">
         <v>9060.450000000001</v>
       </c>
-      <c r="D85" s="3" t="n">
+      <c r="D85" s="6" t="n">
         <v>2.92493338</v>
       </c>
       <c r="E85" t="n">
@@ -2404,10 +2320,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C86" s="2" t="n">
+      <c r="C86" s="5" t="n">
         <v>64397.95</v>
       </c>
-      <c r="D86" s="3" t="n">
+      <c r="D86" s="6" t="n">
         <v>20.78922276</v>
       </c>
       <c r="E86" t="n">
@@ -2425,10 +2341,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C87" s="2" t="n">
+      <c r="C87" s="5" t="n">
         <v>1067.9</v>
       </c>
-      <c r="D87" s="3" t="n">
+      <c r="D87" s="6" t="n">
         <v>0.29681338</v>
       </c>
       <c r="E87" t="n">
@@ -2446,10 +2362,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C88" s="2" t="n">
+      <c r="C88" s="5" t="n">
         <v>260988.37</v>
       </c>
-      <c r="D88" s="3" t="n">
+      <c r="D88" s="6" t="n">
         <v>72.53941456</v>
       </c>
       <c r="E88" t="n">
@@ -2467,10 +2383,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C89" s="2" t="n">
+      <c r="C89" s="5" t="n">
         <v>7522.28</v>
       </c>
-      <c r="D89" s="3" t="n">
+      <c r="D89" s="6" t="n">
         <v>2.09075135</v>
       </c>
       <c r="E89" t="n">
@@ -2488,10 +2404,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C90" s="2" t="n">
+      <c r="C90" s="5" t="n">
         <v>90209.81</v>
       </c>
-      <c r="D90" s="3" t="n">
+      <c r="D90" s="6" t="n">
         <v>25.07302071</v>
       </c>
       <c r="E90" t="n">
@@ -2509,10 +2425,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C91" s="2" t="n">
+      <c r="C91" s="5" t="n">
         <v>11124.49</v>
       </c>
-      <c r="D91" s="3" t="n">
+      <c r="D91" s="6" t="n">
         <v>3.35098295</v>
       </c>
       <c r="E91" t="n">
@@ -2530,10 +2446,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C92" s="2" t="n">
+      <c r="C92" s="5" t="n">
         <v>201888.41</v>
       </c>
-      <c r="D92" s="3" t="n">
+      <c r="D92" s="6" t="n">
         <v>60.81398972</v>
       </c>
       <c r="E92" t="n">
@@ -2551,10 +2467,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C93" s="2" t="n">
+      <c r="C93" s="5" t="n">
         <v>15503.87</v>
       </c>
-      <c r="D93" s="3" t="n">
+      <c r="D93" s="6" t="n">
         <v>4.67016502</v>
       </c>
       <c r="E93" t="n">
@@ -2572,10 +2488,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C94" s="2" t="n">
+      <c r="C94" s="5" t="n">
         <v>103460.15</v>
       </c>
-      <c r="D94" s="3" t="n">
+      <c r="D94" s="6" t="n">
         <v>31.1648623</v>
       </c>
       <c r="E94" t="n">
@@ -2593,10 +2509,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C95" s="2" t="n">
+      <c r="C95" s="5" t="n">
         <v>1029.41</v>
       </c>
-      <c r="D95" s="3" t="n">
+      <c r="D95" s="6" t="n">
         <v>0.31513536</v>
       </c>
       <c r="E95" t="n">
@@ -2614,10 +2530,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C96" s="2" t="n">
+      <c r="C96" s="5" t="n">
         <v>1848</v>
       </c>
-      <c r="D96" s="3" t="n">
+      <c r="D96" s="6" t="n">
         <v>0.56573196</v>
       </c>
       <c r="E96" t="n">
@@ -2635,10 +2551,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C97" s="2" t="n">
+      <c r="C97" s="5" t="n">
         <v>126297.98</v>
       </c>
-      <c r="D97" s="3" t="n">
+      <c r="D97" s="6" t="n">
         <v>38.66385499</v>
       </c>
       <c r="E97" t="n">
@@ -2656,10 +2572,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C98" s="2" t="n">
+      <c r="C98" s="5" t="n">
         <v>23680.09</v>
       </c>
-      <c r="D98" s="3" t="n">
+      <c r="D98" s="6" t="n">
         <v>7.24923364</v>
       </c>
       <c r="E98" t="n">
@@ -2677,10 +2593,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C99" s="2" t="n">
+      <c r="C99" s="5" t="n">
         <v>173800.98</v>
       </c>
-      <c r="D99" s="3" t="n">
+      <c r="D99" s="6" t="n">
         <v>53.20604405</v>
       </c>
       <c r="E99" t="n">
@@ -2698,10 +2614,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C100" s="2" t="n">
+      <c r="C100" s="5" t="n">
         <v>856.11</v>
       </c>
-      <c r="D100" s="3" t="n">
+      <c r="D100" s="6" t="n">
         <v>0.22747196</v>
       </c>
       <c r="E100" t="n">
@@ -2719,10 +2635,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C101" s="2" t="n">
+      <c r="C101" s="5" t="n">
         <v>9.68</v>
       </c>
-      <c r="D101" s="3" t="n">
+      <c r="D101" s="6" t="n">
         <v>0.00257202</v>
       </c>
       <c r="E101" t="n">
@@ -2740,10 +2656,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C102" s="2" t="n">
+      <c r="C102" s="5" t="n">
         <v>296012.79</v>
       </c>
-      <c r="D102" s="3" t="n">
+      <c r="D102" s="6" t="n">
         <v>78.65181887</v>
       </c>
       <c r="E102" t="n">
@@ -2761,10 +2677,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C103" s="2" t="n">
+      <c r="C103" s="5" t="n">
         <v>3709.15</v>
       </c>
-      <c r="D103" s="3" t="n">
+      <c r="D103" s="6" t="n">
         <v>0.98553645</v>
       </c>
       <c r="E103" t="n">
@@ -2782,10 +2698,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C104" s="2" t="n">
+      <c r="C104" s="5" t="n">
         <v>75770.75</v>
       </c>
-      <c r="D104" s="3" t="n">
+      <c r="D104" s="6" t="n">
         <v>20.13260071</v>
       </c>
       <c r="E104" t="n">
@@ -2803,10 +2719,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C105" s="2" t="n">
+      <c r="C105" s="5" t="n">
         <v>363.62</v>
       </c>
-      <c r="D105" s="3" t="n">
+      <c r="D105" s="6" t="n">
         <v>0.09792976</v>
       </c>
       <c r="E105" t="n">
@@ -2824,10 +2740,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C106" s="2" t="n">
+      <c r="C106" s="5" t="n">
         <v>303265.05</v>
       </c>
-      <c r="D106" s="3" t="n">
+      <c r="D106" s="6" t="n">
         <v>81.67502655</v>
       </c>
       <c r="E106" t="n">
@@ -2845,10 +2761,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C107" s="2" t="n">
+      <c r="C107" s="5" t="n">
         <v>829.42</v>
       </c>
-      <c r="D107" s="3" t="n">
+      <c r="D107" s="6" t="n">
         <v>0.22337853</v>
       </c>
       <c r="E107" t="n">
@@ -2866,10 +2782,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C108" s="2" t="n">
+      <c r="C108" s="5" t="n">
         <v>66848.86</v>
       </c>
-      <c r="D108" s="3" t="n">
+      <c r="D108" s="6" t="n">
         <v>18.00366516</v>
       </c>
       <c r="E108" t="n">
@@ -2887,10 +2803,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C109" s="2" t="n">
+      <c r="C109" s="5" t="n">
         <v>174192.16</v>
       </c>
-      <c r="D109" s="3" t="n">
+      <c r="D109" s="6" t="n">
         <v>66.86566559000001</v>
       </c>
       <c r="E109" t="n">
@@ -2908,10 +2824,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C110" s="2" t="n">
+      <c r="C110" s="5" t="n">
         <v>19438.25</v>
       </c>
-      <c r="D110" s="3" t="n">
+      <c r="D110" s="6" t="n">
         <v>7.461596</v>
       </c>
       <c r="E110" t="n">
@@ -2929,10 +2845,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C111" s="2" t="n">
+      <c r="C111" s="5" t="n">
         <v>66880.21000000001</v>
       </c>
-      <c r="D111" s="3" t="n">
+      <c r="D111" s="6" t="n">
         <v>25.67273841</v>
       </c>
       <c r="E111" t="n">
@@ -2950,10 +2866,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C112" s="2" t="n">
+      <c r="C112" s="5" t="n">
         <v>1885.29</v>
       </c>
-      <c r="D112" s="3" t="n">
+      <c r="D112" s="6" t="n">
         <v>0.5105483200000001</v>
       </c>
       <c r="E112" t="n">
@@ -2971,10 +2887,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C113" s="2" t="n">
+      <c r="C113" s="5" t="n">
         <v>642.63</v>
       </c>
-      <c r="D113" s="3" t="n">
+      <c r="D113" s="6" t="n">
         <v>0.17402822</v>
       </c>
       <c r="E113" t="n">
@@ -2992,10 +2908,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C114" s="2" t="n">
+      <c r="C114" s="5" t="n">
         <v>2177.75</v>
       </c>
-      <c r="D114" s="3" t="n">
+      <c r="D114" s="6" t="n">
         <v>0.58974832</v>
       </c>
       <c r="E114" t="n">
@@ -3013,10 +2929,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C115" s="2" t="n">
+      <c r="C115" s="5" t="n">
         <v>202289.9</v>
       </c>
-      <c r="D115" s="3" t="n">
+      <c r="D115" s="6" t="n">
         <v>54.78137012</v>
       </c>
       <c r="E115" t="n">
@@ -3034,10 +2950,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C116" s="2" t="n">
+      <c r="C116" s="5" t="n">
         <v>30328.46</v>
       </c>
-      <c r="D116" s="3" t="n">
+      <c r="D116" s="6" t="n">
         <v>8.213136649999999</v>
       </c>
       <c r="E116" t="n">
@@ -3055,10 +2971,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C117" s="2" t="n">
+      <c r="C117" s="5" t="n">
         <v>131943.66</v>
       </c>
-      <c r="D117" s="3" t="n">
+      <c r="D117" s="6" t="n">
         <v>35.73116836</v>
       </c>
       <c r="E117" t="n">
@@ -3076,10 +2992,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C118" s="2" t="n">
+      <c r="C118" s="5" t="n">
         <v>101.72</v>
       </c>
-      <c r="D118" s="3" t="n">
+      <c r="D118" s="6" t="n">
         <v>0.03804713</v>
       </c>
       <c r="E118" t="n">
@@ -3097,10 +3013,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C119" s="2" t="n">
+      <c r="C119" s="5" t="n">
         <v>58</v>
       </c>
-      <c r="D119" s="3" t="n">
+      <c r="D119" s="6" t="n">
         <v>0.02169419</v>
       </c>
       <c r="E119" t="n">
@@ -3118,10 +3034,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C120" s="2" t="n">
+      <c r="C120" s="5" t="n">
         <v>167439.3</v>
       </c>
-      <c r="D120" s="3" t="n">
+      <c r="D120" s="6" t="n">
         <v>62.62863161</v>
       </c>
       <c r="E120" t="n">
@@ -3139,10 +3055,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C121" s="2" t="n">
+      <c r="C121" s="5" t="n">
         <v>7300.3</v>
       </c>
-      <c r="D121" s="3" t="n">
+      <c r="D121" s="6" t="n">
         <v>2.73058833</v>
       </c>
       <c r="E121" t="n">
@@ -3160,10 +3076,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C122" s="2" t="n">
+      <c r="C122" s="5" t="n">
         <v>92453.32000000001</v>
       </c>
-      <c r="D122" s="3" t="n">
+      <c r="D122" s="6" t="n">
         <v>34.58103874</v>
       </c>
       <c r="E122" t="n">
@@ -3181,10 +3097,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C123" s="2" t="n">
+      <c r="C123" s="5" t="n">
         <v>1475.74</v>
       </c>
-      <c r="D123" s="3" t="n">
+      <c r="D123" s="6" t="n">
         <v>0.33417908</v>
       </c>
       <c r="E123" t="n">
@@ -3202,10 +3118,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C124" s="2" t="n">
+      <c r="C124" s="5" t="n">
         <v>2209.05</v>
       </c>
-      <c r="D124" s="3" t="n">
+      <c r="D124" s="6" t="n">
         <v>0.50023602</v>
       </c>
       <c r="E124" t="n">
@@ -3223,10 +3139,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C125" s="2" t="n">
+      <c r="C125" s="5" t="n">
         <v>232354.93</v>
       </c>
-      <c r="D125" s="3" t="n">
+      <c r="D125" s="6" t="n">
         <v>52.61642084</v>
       </c>
       <c r="E125" t="n">
@@ -3244,10 +3160,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C126" s="2" t="n">
+      <c r="C126" s="5" t="n">
         <v>11084.31</v>
       </c>
-      <c r="D126" s="3" t="n">
+      <c r="D126" s="6" t="n">
         <v>2.51002516</v>
       </c>
       <c r="E126" t="n">
@@ -3265,10 +3181,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C127" s="2" t="n">
+      <c r="C127" s="5" t="n">
         <v>194477.52</v>
       </c>
-      <c r="D127" s="3" t="n">
+      <c r="D127" s="6" t="n">
         <v>44.0391389</v>
       </c>
       <c r="E127" t="n">
@@ -3286,10 +3202,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C128" s="2" t="n">
+      <c r="C128" s="5" t="n">
         <v>2990.78</v>
       </c>
-      <c r="D128" s="3" t="n">
+      <c r="D128" s="6" t="n">
         <v>0.63513389</v>
       </c>
       <c r="E128" t="n">
@@ -3307,10 +3223,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C129" s="2" t="n">
+      <c r="C129" s="5" t="n">
         <v>847.45</v>
       </c>
-      <c r="D129" s="3" t="n">
+      <c r="D129" s="6" t="n">
         <v>0.17996784</v>
       </c>
       <c r="E129" t="n">
@@ -3328,10 +3244,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C130" s="2" t="n">
+      <c r="C130" s="5" t="n">
         <v>211.86</v>
       </c>
-      <c r="D130" s="3" t="n">
+      <c r="D130" s="6" t="n">
         <v>0.04499143</v>
       </c>
       <c r="E130" t="n">
@@ -3349,10 +3265,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C131" s="2" t="n">
+      <c r="C131" s="5" t="n">
         <v>222684.94</v>
       </c>
-      <c r="D131" s="3" t="n">
+      <c r="D131" s="6" t="n">
         <v>47.29025603</v>
       </c>
       <c r="E131" t="n">
@@ -3370,10 +3286,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C132" s="2" t="n">
+      <c r="C132" s="5" t="n">
         <v>10642.51</v>
       </c>
-      <c r="D132" s="3" t="n">
+      <c r="D132" s="6" t="n">
         <v>2.26008558</v>
       </c>
       <c r="E132" t="n">
@@ -3391,10 +3307,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C133" s="2" t="n">
+      <c r="C133" s="5" t="n">
         <v>233512.15</v>
       </c>
-      <c r="D133" s="3" t="n">
+      <c r="D133" s="6" t="n">
         <v>49.58956523</v>
       </c>
       <c r="E133" t="n">
@@ -3412,10 +3328,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C134" s="2" t="n">
+      <c r="C134" s="5" t="n">
         <v>2894.67</v>
       </c>
-      <c r="D134" s="3" t="n">
+      <c r="D134" s="6" t="n">
         <v>0.84868485</v>
       </c>
       <c r="E134" t="n">
@@ -3433,10 +3349,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C135" s="2" t="n">
+      <c r="C135" s="5" t="n">
         <v>2112.75</v>
       </c>
-      <c r="D135" s="3" t="n">
+      <c r="D135" s="6" t="n">
         <v>0.61943465</v>
       </c>
       <c r="E135" t="n">
@@ -3454,10 +3370,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C136" s="2" t="n">
+      <c r="C136" s="5" t="n">
         <v>133738.48</v>
       </c>
-      <c r="D136" s="3" t="n">
+      <c r="D136" s="6" t="n">
         <v>39.21062549</v>
       </c>
       <c r="E136" t="n">
@@ -3475,10 +3391,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C137" s="2" t="n">
+      <c r="C137" s="5" t="n">
         <v>9278.84</v>
       </c>
-      <c r="D137" s="3" t="n">
+      <c r="D137" s="6" t="n">
         <v>2.72045204</v>
       </c>
       <c r="E137" t="n">
@@ -3496,10 +3412,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C138" s="2" t="n">
+      <c r="C138" s="5" t="n">
         <v>193052.4</v>
       </c>
-      <c r="D138" s="3" t="n">
+      <c r="D138" s="6" t="n">
         <v>56.60080297</v>
       </c>
       <c r="E138" t="n">
@@ -3517,10 +3433,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C139" s="2" t="n">
+      <c r="C139" s="5" t="n">
         <v>138.16</v>
       </c>
-      <c r="D139" s="3" t="n">
+      <c r="D139" s="6" t="n">
         <v>0.04037037</v>
       </c>
       <c r="E139" t="n">
@@ -3538,10 +3454,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C140" s="2" t="n">
+      <c r="C140" s="5" t="n">
         <v>165616.96</v>
       </c>
-      <c r="D140" s="3" t="n">
+      <c r="D140" s="6" t="n">
         <v>48.39329811</v>
       </c>
       <c r="E140" t="n">
@@ -3559,10 +3475,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C141" s="2" t="n">
+      <c r="C141" s="5" t="n">
         <v>14589.85</v>
       </c>
-      <c r="D141" s="3" t="n">
+      <c r="D141" s="6" t="n">
         <v>4.26315614</v>
       </c>
       <c r="E141" t="n">
@@ -3580,10 +3496,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C142" s="2" t="n">
+      <c r="C142" s="5" t="n">
         <v>161886.22</v>
       </c>
-      <c r="D142" s="3" t="n">
+      <c r="D142" s="6" t="n">
         <v>47.30317538</v>
       </c>
       <c r="E142" t="n">
@@ -3601,10 +3517,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C143" s="2" t="n">
+      <c r="C143" s="5" t="n">
         <v>39179.97</v>
       </c>
-      <c r="D143" s="3" t="n">
+      <c r="D143" s="6" t="n">
         <v>6.57522763</v>
       </c>
       <c r="E143" t="n">
@@ -3622,10 +3538,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C144" s="2" t="n">
+      <c r="C144" s="5" t="n">
         <v>142325.87</v>
       </c>
-      <c r="D144" s="3" t="n">
+      <c r="D144" s="6" t="n">
         <v>23.88529122</v>
       </c>
       <c r="E144" t="n">
@@ -3643,10 +3559,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C145" s="2" t="n">
+      <c r="C145" s="5" t="n">
         <v>16620.71</v>
       </c>
-      <c r="D145" s="3" t="n">
+      <c r="D145" s="6" t="n">
         <v>2.78930667</v>
       </c>
       <c r="E145" t="n">
@@ -3664,10 +3580,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C146" s="2" t="n">
+      <c r="C146" s="5" t="n">
         <v>397745.9</v>
       </c>
-      <c r="D146" s="3" t="n">
+      <c r="D146" s="6" t="n">
         <v>66.75017447</v>
       </c>
       <c r="E146" t="n">
@@ -3685,10 +3601,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C147" s="2" t="n">
+      <c r="C147" s="5" t="n">
         <v>1244.23</v>
       </c>
-      <c r="D147" s="3" t="n">
+      <c r="D147" s="6" t="n">
         <v>0.42616348</v>
       </c>
       <c r="E147" t="n">
@@ -3706,10 +3622,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C148" s="2" t="n">
+      <c r="C148" s="5" t="n">
         <v>4545.45</v>
       </c>
-      <c r="D148" s="3" t="n">
+      <c r="D148" s="6" t="n">
         <v>1.55687034</v>
       </c>
       <c r="E148" t="n">
@@ -3727,10 +3643,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C149" s="2" t="n">
+      <c r="C149" s="5" t="n">
         <v>54421.47</v>
       </c>
-      <c r="D149" s="3" t="n">
+      <c r="D149" s="6" t="n">
         <v>18.63999655</v>
       </c>
       <c r="E149" t="n">
@@ -3748,10 +3664,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C150" s="2" t="n">
+      <c r="C150" s="5" t="n">
         <v>231749.58</v>
       </c>
-      <c r="D150" s="3" t="n">
+      <c r="D150" s="6" t="n">
         <v>79.37696964</v>
       </c>
       <c r="E150" t="n">
@@ -3769,10 +3685,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C151" s="2" t="n">
+      <c r="C151" s="5" t="n">
         <v>29.6</v>
       </c>
-      <c r="D151" s="3" t="n">
+      <c r="D151" s="6" t="n">
         <v>0.00689719</v>
       </c>
       <c r="E151" t="n">
@@ -3790,10 +3706,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C152" s="2" t="n">
+      <c r="C152" s="5" t="n">
         <v>309.27</v>
       </c>
-      <c r="D152" s="3" t="n">
+      <c r="D152" s="6" t="n">
         <v>0.07206398</v>
       </c>
       <c r="E152" t="n">
@@ -3811,10 +3727,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C153" s="2" t="n">
+      <c r="C153" s="5" t="n">
         <v>3725.16</v>
       </c>
-      <c r="D153" s="3" t="n">
+      <c r="D153" s="6" t="n">
         <v>0.8680113</v>
       </c>
       <c r="E153" t="n">
@@ -3832,10 +3748,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C154" s="2" t="n">
+      <c r="C154" s="5" t="n">
         <v>8.109999999999999</v>
       </c>
-      <c r="D154" s="3" t="n">
+      <c r="D154" s="6" t="n">
         <v>0.00188974</v>
       </c>
       <c r="E154" t="n">
@@ -3853,10 +3769,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C155" s="2" t="n">
+      <c r="C155" s="5" t="n">
         <v>163136.27</v>
       </c>
-      <c r="D155" s="3" t="n">
+      <c r="D155" s="6" t="n">
         <v>38.01289779</v>
       </c>
       <c r="E155" t="n">
@@ -3874,10 +3790,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C156" s="2" t="n">
+      <c r="C156" s="5" t="n">
         <v>261951.9</v>
       </c>
-      <c r="D156" s="3" t="n">
+      <c r="D156" s="6" t="n">
         <v>61.03824</v>
       </c>
       <c r="E156" t="n">
@@ -3895,10 +3811,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C157" s="2" t="n">
+      <c r="C157" s="5" t="n">
         <v>55.55</v>
       </c>
-      <c r="D157" s="3" t="n">
+      <c r="D157" s="6" t="n">
         <v>0.01644298</v>
       </c>
       <c r="E157" t="n">
@@ -3916,10 +3832,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C158" s="2" t="n">
+      <c r="C158" s="5" t="n">
         <v>91.41</v>
       </c>
-      <c r="D158" s="3" t="n">
+      <c r="D158" s="6" t="n">
         <v>0.02705766</v>
       </c>
       <c r="E158" t="n">
@@ -3937,10 +3853,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C159" s="2" t="n">
+      <c r="C159" s="5" t="n">
         <v>5382.13</v>
       </c>
-      <c r="D159" s="3" t="n">
+      <c r="D159" s="6" t="n">
         <v>1.59312834</v>
       </c>
       <c r="E159" t="n">
@@ -3958,10 +3874,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C160" s="2" t="n">
+      <c r="C160" s="5" t="n">
         <v>909.09</v>
       </c>
-      <c r="D160" s="3" t="n">
+      <c r="D160" s="6" t="n">
         <v>0.26909366</v>
       </c>
       <c r="E160" t="n">
@@ -3979,10 +3895,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C161" s="2" t="n">
+      <c r="C161" s="5" t="n">
         <v>32670.17</v>
       </c>
-      <c r="D161" s="3" t="n">
+      <c r="D161" s="6" t="n">
         <v>9.670478749999999</v>
       </c>
       <c r="E161" t="n">
@@ -4000,10 +3916,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C162" s="2" t="n">
+      <c r="C162" s="5" t="n">
         <v>298725.7</v>
       </c>
-      <c r="D162" s="3" t="n">
+      <c r="D162" s="6" t="n">
         <v>88.42379861000001</v>
       </c>
       <c r="E162" t="n">
@@ -4021,10 +3937,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C163" s="2" t="n">
+      <c r="C163" s="5" t="n">
         <v>287.66</v>
       </c>
-      <c r="D163" s="3" t="n">
+      <c r="D163" s="6" t="n">
         <v>0.08204844999999999</v>
       </c>
       <c r="E163" t="n">
@@ -4042,10 +3958,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C164" s="2" t="n">
+      <c r="C164" s="5" t="n">
         <v>9919.66</v>
       </c>
-      <c r="D164" s="3" t="n">
+      <c r="D164" s="6" t="n">
         <v>2.82935676</v>
       </c>
       <c r="E164" t="n">
@@ -4063,10 +3979,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C165" s="2" t="n">
+      <c r="C165" s="5" t="n">
         <v>1385.01</v>
       </c>
-      <c r="D165" s="3" t="n">
+      <c r="D165" s="6" t="n">
         <v>0.39504251</v>
       </c>
       <c r="E165" t="n">
@@ -4084,10 +4000,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C166" s="2" t="n">
+      <c r="C166" s="5" t="n">
         <v>69940.2</v>
       </c>
-      <c r="D166" s="3" t="n">
+      <c r="D166" s="6" t="n">
         <v>19.94884679</v>
       </c>
       <c r="E166" t="n">
@@ -4105,10 +4021,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C167" s="2" t="n">
+      <c r="C167" s="5" t="n">
         <v>269065.18</v>
       </c>
-      <c r="D167" s="3" t="n">
+      <c r="D167" s="6" t="n">
         <v>76.74470549</v>
       </c>
       <c r="E167" t="n">
@@ -4126,10 +4042,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C168" s="2" t="n">
+      <c r="C168" s="5" t="n">
         <v>580.2</v>
       </c>
-      <c r="D168" s="3" t="n">
+      <c r="D168" s="6" t="n">
         <v>0.1561468</v>
       </c>
       <c r="E168" t="n">
@@ -4147,10 +4063,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C169" s="2" t="n">
+      <c r="C169" s="5" t="n">
         <v>98.44</v>
       </c>
-      <c r="D169" s="3" t="n">
+      <c r="D169" s="6" t="n">
         <v>0.02649275</v>
       </c>
       <c r="E169" t="n">
@@ -4168,10 +4084,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C170" s="2" t="n">
+      <c r="C170" s="5" t="n">
         <v>172.72</v>
       </c>
-      <c r="D170" s="3" t="n">
+      <c r="D170" s="6" t="n">
         <v>0.04648341</v>
       </c>
       <c r="E170" t="n">
@@ -4189,10 +4105,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C171" s="2" t="n">
+      <c r="C171" s="5" t="n">
         <v>3342.15</v>
       </c>
-      <c r="D171" s="3" t="n">
+      <c r="D171" s="6" t="n">
         <v>0.89945887</v>
       </c>
       <c r="E171" t="n">
@@ -4210,10 +4126,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C172" s="2" t="n">
+      <c r="C172" s="5" t="n">
         <v>7627.33</v>
       </c>
-      <c r="D172" s="3" t="n">
+      <c r="D172" s="6" t="n">
         <v>2.05271147</v>
       </c>
       <c r="E172" t="n">
@@ -4231,10 +4147,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C173" s="2" t="n">
+      <c r="C173" s="5" t="n">
         <v>359752.57</v>
       </c>
-      <c r="D173" s="3" t="n">
+      <c r="D173" s="6" t="n">
         <v>96.81870670000001</v>
       </c>
       <c r="E173" t="n">
@@ -4252,10 +4168,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C174" s="2" t="n">
+      <c r="C174" s="5" t="n">
         <v>61.94</v>
       </c>
-      <c r="D174" s="3" t="n">
+      <c r="D174" s="6" t="n">
         <v>0.02167129</v>
       </c>
       <c r="E174" t="n">
@@ -4273,10 +4189,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C175" s="2" t="n">
+      <c r="C175" s="5" t="n">
         <v>222</v>
       </c>
-      <c r="D175" s="3" t="n">
+      <c r="D175" s="6" t="n">
         <v>0.07767236</v>
       </c>
       <c r="E175" t="n">
@@ -4294,10 +4210,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C176" s="2" t="n">
+      <c r="C176" s="5" t="n">
         <v>10426.45</v>
       </c>
-      <c r="D176" s="3" t="n">
+      <c r="D176" s="6" t="n">
         <v>3.64795946</v>
       </c>
       <c r="E176" t="n">
@@ -4315,10 +4231,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C177" s="2" t="n">
+      <c r="C177" s="5" t="n">
         <v>36051.27</v>
       </c>
-      <c r="D177" s="3" t="n">
+      <c r="D177" s="6" t="n">
         <v>12.61345632</v>
       </c>
       <c r="E177" t="n">
@@ -4336,10 +4252,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C178" s="2" t="n">
+      <c r="C178" s="5" t="n">
         <v>239054.29</v>
       </c>
-      <c r="D178" s="3" t="n">
+      <c r="D178" s="6" t="n">
         <v>83.63924057</v>
       </c>
       <c r="E178" t="n">
@@ -4357,10 +4273,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C179" s="2" t="n">
+      <c r="C179" s="5" t="n">
         <v>1971.96</v>
       </c>
-      <c r="D179" s="3" t="n">
+      <c r="D179" s="6" t="n">
         <v>0.29536296</v>
       </c>
       <c r="E179" t="n">
@@ -4378,10 +4294,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C180" s="2" t="n">
+      <c r="C180" s="5" t="n">
         <v>970.1799999999999</v>
       </c>
-      <c r="D180" s="3" t="n">
+      <c r="D180" s="6" t="n">
         <v>0.14531493</v>
       </c>
       <c r="E180" t="n">
@@ -4399,10 +4315,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C181" s="2" t="n">
+      <c r="C181" s="5" t="n">
         <v>23400.38</v>
       </c>
-      <c r="D181" s="3" t="n">
+      <c r="D181" s="6" t="n">
         <v>3.50494199</v>
       </c>
       <c r="E181" t="n">
@@ -4420,10 +4336,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C182" s="2" t="n">
+      <c r="C182" s="5" t="n">
         <v>158698.51</v>
       </c>
-      <c r="D182" s="3" t="n">
+      <c r="D182" s="6" t="n">
         <v>23.77008715</v>
       </c>
       <c r="E182" t="n">
@@ -4441,10 +4357,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C183" s="2" t="n">
+      <c r="C183" s="5" t="n">
         <v>482598.55</v>
       </c>
-      <c r="D183" s="3" t="n">
+      <c r="D183" s="6" t="n">
         <v>72.28429297</v>
       </c>
       <c r="E183" t="n">
@@ -4462,10 +4378,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C184" s="2" t="n">
+      <c r="C184" s="5" t="n">
         <v>349.42</v>
       </c>
-      <c r="D184" s="3" t="n">
+      <c r="D184" s="6" t="n">
         <v>0.0757804</v>
       </c>
       <c r="E184" t="n">
@@ -4483,10 +4399,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C185" s="2" t="n">
+      <c r="C185" s="5" t="n">
         <v>5203.15</v>
       </c>
-      <c r="D185" s="3" t="n">
+      <c r="D185" s="6" t="n">
         <v>1.12843225</v>
       </c>
       <c r="E185" t="n">
@@ -4504,10 +4420,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C186" s="2" t="n">
+      <c r="C186" s="5" t="n">
         <v>43002.78</v>
       </c>
-      <c r="D186" s="3" t="n">
+      <c r="D186" s="6" t="n">
         <v>9.326220449999999</v>
       </c>
       <c r="E186" t="n">
@@ -4525,10 +4441,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C187" s="2" t="n">
+      <c r="C187" s="5" t="n">
         <v>412540.12</v>
       </c>
-      <c r="D187" s="3" t="n">
+      <c r="D187" s="6" t="n">
         <v>89.4695669</v>
       </c>
       <c r="E187" t="n">
@@ -4546,10 +4462,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C188" s="2" t="n">
+      <c r="C188" s="5" t="n">
         <v>1231.47</v>
       </c>
-      <c r="D188" s="3" t="n">
+      <c r="D188" s="6" t="n">
         <v>0.34199572</v>
       </c>
       <c r="E188" t="n">
@@ -4567,10 +4483,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C189" s="2" t="n">
+      <c r="C189" s="5" t="n">
         <v>484.18</v>
       </c>
-      <c r="D189" s="3" t="n">
+      <c r="D189" s="6" t="n">
         <v>0.13446328</v>
       </c>
       <c r="E189" t="n">
@@ -4588,10 +4504,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C190" s="2" t="n">
+      <c r="C190" s="5" t="n">
         <v>29461.66</v>
       </c>
-      <c r="D190" s="3" t="n">
+      <c r="D190" s="6" t="n">
         <v>8.18189784</v>
       </c>
       <c r="E190" t="n">
@@ -4609,10 +4525,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C191" s="2" t="n">
+      <c r="C191" s="5" t="n">
         <v>328906.14</v>
       </c>
-      <c r="D191" s="3" t="n">
+      <c r="D191" s="6" t="n">
         <v>91.34164317</v>
       </c>
       <c r="E191" t="n">
@@ -4630,10 +4546,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C192" s="2" t="n">
+      <c r="C192" s="5" t="n">
         <v>23.47</v>
       </c>
-      <c r="D192" s="3" t="n">
+      <c r="D192" s="6" t="n">
         <v>0.00471838</v>
       </c>
       <c r="E192" t="n">
@@ -4651,10 +4567,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C193" s="2" t="n">
+      <c r="C193" s="5" t="n">
         <v>13128.29</v>
       </c>
-      <c r="D193" s="3" t="n">
+      <c r="D193" s="6" t="n">
         <v>2.63929312</v>
       </c>
       <c r="E193" t="n">
@@ -4672,10 +4588,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C194" s="2" t="n">
+      <c r="C194" s="5" t="n">
         <v>42522.52</v>
       </c>
-      <c r="D194" s="3" t="n">
+      <c r="D194" s="6" t="n">
         <v>8.548668129999999</v>
       </c>
       <c r="E194" t="n">
@@ -4693,10 +4609,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C195" s="2" t="n">
+      <c r="C195" s="5" t="n">
         <v>441742.62</v>
       </c>
-      <c r="D195" s="3" t="n">
+      <c r="D195" s="6" t="n">
         <v>88.80732037999999</v>
       </c>
       <c r="E195" t="n">
@@ -4714,10 +4630,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C196" s="2" t="n">
+      <c r="C196" s="5" t="n">
         <v>14510.35</v>
       </c>
-      <c r="D196" s="3" t="n">
+      <c r="D196" s="6" t="n">
         <v>2.82318771</v>
       </c>
       <c r="E196" t="n">
@@ -4735,10 +4651,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C197" s="2" t="n">
+      <c r="C197" s="5" t="n">
         <v>29796.3</v>
       </c>
-      <c r="D197" s="3" t="n">
+      <c r="D197" s="6" t="n">
         <v>5.79727904</v>
       </c>
       <c r="E197" t="n">
@@ -4756,10 +4672,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C198" s="2" t="n">
+      <c r="C198" s="5" t="n">
         <v>489.48</v>
       </c>
-      <c r="D198" s="3" t="n">
+      <c r="D198" s="6" t="n">
         <v>0.09523505</v>
       </c>
       <c r="E198" t="n">
@@ -4777,10 +4693,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C199" s="2" t="n">
+      <c r="C199" s="5" t="n">
         <v>45623.94</v>
       </c>
-      <c r="D199" s="3" t="n">
+      <c r="D199" s="6" t="n">
         <v>8.876763589999999</v>
       </c>
       <c r="E199" t="n">
@@ -4798,10 +4714,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C200" s="2" t="n">
+      <c r="C200" s="5" t="n">
         <v>423550.36</v>
       </c>
-      <c r="D200" s="3" t="n">
+      <c r="D200" s="6" t="n">
         <v>82.40753461</v>
       </c>
       <c r="E200" t="n">
@@ -4819,10 +4735,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C201" s="2" t="n">
+      <c r="C201" s="5" t="n">
         <v>2894.83</v>
       </c>
-      <c r="D201" s="3" t="n">
+      <c r="D201" s="6" t="n">
         <v>0.57425271</v>
       </c>
       <c r="E201" t="n">
@@ -4840,10 +4756,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C202" s="2" t="n">
+      <c r="C202" s="5" t="n">
         <v>19389.84</v>
       </c>
-      <c r="D202" s="3" t="n">
+      <c r="D202" s="6" t="n">
         <v>3.84639792</v>
       </c>
       <c r="E202" t="n">
@@ -4861,10 +4777,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C203" s="2" t="n">
+      <c r="C203" s="5" t="n">
         <v>7103.09</v>
       </c>
-      <c r="D203" s="3" t="n">
+      <c r="D203" s="6" t="n">
         <v>1.40905292</v>
       </c>
       <c r="E203" t="n">
@@ -4882,10 +4798,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C204" s="2" t="n">
+      <c r="C204" s="5" t="n">
         <v>71555.96000000001</v>
       </c>
-      <c r="D204" s="3" t="n">
+      <c r="D204" s="6" t="n">
         <v>14.19468627</v>
       </c>
       <c r="E204" t="n">
@@ -4903,10 +4819,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C205" s="2" t="n">
+      <c r="C205" s="5" t="n">
         <v>403160.13</v>
       </c>
-      <c r="D205" s="3" t="n">
+      <c r="D205" s="6" t="n">
         <v>79.97561018</v>
       </c>
       <c r="E205" t="n">
@@ -4924,10 +4840,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C206" s="2" t="n">
+      <c r="C206" s="5" t="n">
         <v>13873.76</v>
       </c>
-      <c r="D206" s="3" t="n">
+      <c r="D206" s="6" t="n">
         <v>4.61749343</v>
       </c>
       <c r="E206" t="n">
@@ -4945,10 +4861,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C207" s="2" t="n">
+      <c r="C207" s="5" t="n">
         <v>5637.21</v>
       </c>
-      <c r="D207" s="3" t="n">
+      <c r="D207" s="6" t="n">
         <v>1.87618786</v>
       </c>
       <c r="E207" t="n">
@@ -4966,10 +4882,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C208" s="2" t="n">
+      <c r="C208" s="5" t="n">
         <v>1363.63</v>
       </c>
-      <c r="D208" s="3" t="n">
+      <c r="D208" s="6" t="n">
         <v>0.45384615</v>
       </c>
       <c r="E208" t="n">
@@ -4987,10 +4903,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C209" s="2" t="n">
+      <c r="C209" s="5" t="n">
         <v>35429.67</v>
       </c>
-      <c r="D209" s="3" t="n">
+      <c r="D209" s="6" t="n">
         <v>11.79177587</v>
       </c>
       <c r="E209" t="n">
@@ -5008,10 +4924,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C210" s="2" t="n">
+      <c r="C210" s="5" t="n">
         <v>244156.58</v>
       </c>
-      <c r="D210" s="3" t="n">
+      <c r="D210" s="6" t="n">
         <v>81.26069669</v>
       </c>
       <c r="E210" t="n">
@@ -5029,10 +4945,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C211" s="2" t="n">
+      <c r="C211" s="5" t="n">
         <v>3194.31</v>
       </c>
-      <c r="D211" s="3" t="n">
+      <c r="D211" s="6" t="n">
         <v>0.86754762</v>
       </c>
       <c r="E211" t="n">
@@ -5050,10 +4966,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C212" s="2" t="n">
+      <c r="C212" s="5" t="n">
         <v>53332.81</v>
       </c>
-      <c r="D212" s="3" t="n">
+      <c r="D212" s="6" t="n">
         <v>14.48474085</v>
       </c>
       <c r="E212" t="n">
@@ -5071,10 +4987,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C213" s="2" t="n">
+      <c r="C213" s="5" t="n">
         <v>5480.02</v>
       </c>
-      <c r="D213" s="3" t="n">
+      <c r="D213" s="6" t="n">
         <v>1.48832716</v>
       </c>
       <c r="E213" t="n">
@@ -5092,10 +5008,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C214" s="2" t="n">
+      <c r="C214" s="5" t="n">
         <v>54619.67</v>
       </c>
-      <c r="D214" s="3" t="n">
+      <c r="D214" s="6" t="n">
         <v>14.83424116</v>
       </c>
       <c r="E214" t="n">
@@ -5113,10 +5029,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C215" s="2" t="n">
+      <c r="C215" s="5" t="n">
         <v>251573.15</v>
       </c>
-      <c r="D215" s="3" t="n">
+      <c r="D215" s="6" t="n">
         <v>68.32514322</v>
       </c>
       <c r="E215" t="n">
@@ -5134,10 +5050,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C216" s="2" t="n">
+      <c r="C216" s="5" t="n">
         <v>892</v>
       </c>
-      <c r="D216" s="3" t="n">
+      <c r="D216" s="6" t="n">
         <v>0.30548187</v>
       </c>
       <c r="E216" t="n">
@@ -5155,10 +5071,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C217" s="2" t="n">
+      <c r="C217" s="5" t="n">
         <v>7918.09</v>
       </c>
-      <c r="D217" s="3" t="n">
+      <c r="D217" s="6" t="n">
         <v>2.71169611</v>
       </c>
       <c r="E217" t="n">
@@ -5176,10 +5092,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C218" s="2" t="n">
+      <c r="C218" s="5" t="n">
         <v>37.66</v>
       </c>
-      <c r="D218" s="3" t="n">
+      <c r="D218" s="6" t="n">
         <v>0.01289736</v>
       </c>
       <c r="E218" t="n">
@@ -5197,10 +5113,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C219" s="2" t="n">
+      <c r="C219" s="5" t="n">
         <v>14209.15</v>
       </c>
-      <c r="D219" s="3" t="n">
+      <c r="D219" s="6" t="n">
         <v>4.86618576</v>
       </c>
       <c r="E219" t="n">
@@ -5218,10 +5134,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C220" s="2" t="n">
+      <c r="C220" s="5" t="n">
         <v>268940.79</v>
       </c>
-      <c r="D220" s="3" t="n">
+      <c r="D220" s="6" t="n">
         <v>92.1037389</v>
       </c>
       <c r="E220" t="n">
@@ -5239,10 +5155,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C221" s="2" t="n">
+      <c r="C221" s="5" t="n">
         <v>287</v>
       </c>
-      <c r="D221" s="3" t="n">
+      <c r="D221" s="6" t="n">
         <v>0.07919683</v>
       </c>
       <c r="E221" t="n">
@@ -5260,10 +5176,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C222" s="2" t="n">
+      <c r="C222" s="5" t="n">
         <v>17982.75</v>
       </c>
-      <c r="D222" s="3" t="n">
+      <c r="D222" s="6" t="n">
         <v>4.96228879</v>
       </c>
       <c r="E222" t="n">
@@ -5281,10 +5197,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C223" s="2" t="n">
+      <c r="C223" s="5" t="n">
         <v>2603.68</v>
       </c>
-      <c r="D223" s="3" t="n">
+      <c r="D223" s="6" t="n">
         <v>0.7184781</v>
       </c>
       <c r="E223" t="n">
@@ -5302,10 +5218,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C224" s="2" t="n">
+      <c r="C224" s="5" t="n">
         <v>34911.64</v>
       </c>
-      <c r="D224" s="3" t="n">
+      <c r="D224" s="6" t="n">
         <v>9.6337679</v>
       </c>
       <c r="E224" t="n">
@@ -5323,10 +5239,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C225" s="2" t="n">
+      <c r="C225" s="5" t="n">
         <v>306603.15</v>
       </c>
-      <c r="D225" s="3" t="n">
+      <c r="D225" s="6" t="n">
         <v>84.60626838</v>
       </c>
       <c r="E225" t="n">
@@ -5344,10 +5260,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C226" s="2" t="n">
+      <c r="C226" s="5" t="n">
         <v>1099.13</v>
       </c>
-      <c r="D226" s="3" t="n">
+      <c r="D226" s="6" t="n">
         <v>0.35003695</v>
       </c>
       <c r="E226" t="n">
@@ -5365,10 +5281,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C227" s="2" t="n">
+      <c r="C227" s="5" t="n">
         <v>1908.13</v>
       </c>
-      <c r="D227" s="3" t="n">
+      <c r="D227" s="6" t="n">
         <v>0.60767699</v>
       </c>
       <c r="E227" t="n">
@@ -5386,10 +5302,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C228" s="2" t="n">
+      <c r="C228" s="5" t="n">
         <v>1788.1</v>
       </c>
-      <c r="D228" s="3" t="n">
+      <c r="D228" s="6" t="n">
         <v>0.56945136</v>
       </c>
       <c r="E228" t="n">
@@ -5407,10 +5323,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C229" s="2" t="n">
+      <c r="C229" s="5" t="n">
         <v>54065.52</v>
       </c>
-      <c r="D229" s="3" t="n">
+      <c r="D229" s="6" t="n">
         <v>17.21809968</v>
       </c>
       <c r="E229" t="n">
@@ -5428,10 +5344,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C230" s="2" t="n">
+      <c r="C230" s="5" t="n">
         <v>255143.11</v>
       </c>
-      <c r="D230" s="3" t="n">
+      <c r="D230" s="6" t="n">
         <v>81.25473501</v>
       </c>
       <c r="E230" t="n">
@@ -5449,10 +5365,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C231" s="2" t="n">
+      <c r="C231" s="5" t="n">
         <v>2988.23</v>
       </c>
-      <c r="D231" s="3" t="n">
+      <c r="D231" s="6" t="n">
         <v>1.09502707</v>
       </c>
       <c r="E231" t="n">
@@ -5470,10 +5386,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C232" s="2" t="n">
+      <c r="C232" s="5" t="n">
         <v>89030.31</v>
       </c>
-      <c r="D232" s="3" t="n">
+      <c r="D232" s="6" t="n">
         <v>32.62486479</v>
       </c>
       <c r="E232" t="n">
@@ -5491,10 +5407,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C233" s="2" t="n">
+      <c r="C233" s="5" t="n">
         <v>180872.43</v>
       </c>
-      <c r="D233" s="3" t="n">
+      <c r="D233" s="6" t="n">
         <v>66.28010813</v>
       </c>
       <c r="E233" t="n">
@@ -5512,10 +5428,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C234" s="2" t="n">
+      <c r="C234" s="5" t="n">
         <v>232.92</v>
       </c>
-      <c r="D234" s="3" t="n">
+      <c r="D234" s="6" t="n">
         <v>0.10614272</v>
       </c>
       <c r="E234" t="n">
@@ -5533,10 +5449,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C235" s="2" t="n">
+      <c r="C235" s="5" t="n">
         <v>27443.48</v>
       </c>
-      <c r="D235" s="3" t="n">
+      <c r="D235" s="6" t="n">
         <v>12.50612011</v>
       </c>
       <c r="E235" t="n">
@@ -5554,10 +5470,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C236" s="2" t="n">
+      <c r="C236" s="5" t="n">
         <v>66453.41</v>
       </c>
-      <c r="D236" s="3" t="n">
+      <c r="D236" s="6" t="n">
         <v>30.28312471</v>
       </c>
       <c r="E236" t="n">
@@ -5575,10 +5491,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C237" s="2" t="n">
+      <c r="C237" s="5" t="n">
         <v>125310.59</v>
       </c>
-      <c r="D237" s="3" t="n">
+      <c r="D237" s="6" t="n">
         <v>57.10461246</v>
       </c>
       <c r="E237" t="n">
@@ -5596,10 +5512,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C238" s="2" t="n">
+      <c r="C238" s="5" t="n">
         <v>12206.63</v>
       </c>
-      <c r="D238" s="3" t="n">
+      <c r="D238" s="6" t="n">
         <v>2.80910278</v>
       </c>
       <c r="E238" t="n">
@@ -5617,10 +5533,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C239" s="2" t="n">
+      <c r="C239" s="5" t="n">
         <v>14439.81</v>
       </c>
-      <c r="D239" s="3" t="n">
+      <c r="D239" s="6" t="n">
         <v>3.32302285</v>
       </c>
       <c r="E239" t="n">
@@ -5638,10 +5554,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C240" s="2" t="n">
+      <c r="C240" s="5" t="n">
         <v>73404.17</v>
       </c>
-      <c r="D240" s="3" t="n">
+      <c r="D240" s="6" t="n">
         <v>16.89244764</v>
       </c>
       <c r="E240" t="n">
@@ -5659,10 +5575,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C241" s="2" t="n">
+      <c r="C241" s="5" t="n">
         <v>334487.78</v>
       </c>
-      <c r="D241" s="3" t="n">
+      <c r="D241" s="6" t="n">
         <v>76.97542673</v>
       </c>
       <c r="E241" t="n">
@@ -5680,10 +5596,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C242" s="2" t="n">
+      <c r="C242" s="5" t="n">
         <v>4414.12</v>
       </c>
-      <c r="D242" s="3" t="n">
+      <c r="D242" s="6" t="n">
         <v>2.02734127</v>
       </c>
       <c r="E242" t="n">
@@ -5701,10 +5617,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C243" s="2" t="n">
+      <c r="C243" s="5" t="n">
         <v>206.75</v>
       </c>
-      <c r="D243" s="3" t="n">
+      <c r="D243" s="6" t="n">
         <v>0.09495727</v>
       </c>
       <c r="E243" t="n">
@@ -5722,10 +5638,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C244" s="2" t="n">
+      <c r="C244" s="5" t="n">
         <v>6938.86</v>
       </c>
-      <c r="D244" s="3" t="n">
+      <c r="D244" s="6" t="n">
         <v>3.18691771</v>
       </c>
       <c r="E244" t="n">
@@ -5743,10 +5659,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C245" s="2" t="n">
+      <c r="C245" s="5" t="n">
         <v>206169.77</v>
       </c>
-      <c r="D245" s="3" t="n">
+      <c r="D245" s="6" t="n">
         <v>94.69078374999999</v>
       </c>
       <c r="E245" t="n">
@@ -5764,10 +5680,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C246" s="2" t="n">
+      <c r="C246" s="5" t="n">
         <v>45195.76</v>
       </c>
-      <c r="D246" s="3" t="n">
+      <c r="D246" s="6" t="n">
         <v>10.41762819</v>
       </c>
       <c r="E246" t="n">
@@ -5785,10 +5701,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C247" s="2" t="n">
+      <c r="C247" s="5" t="n">
         <v>9882.6</v>
       </c>
-      <c r="D247" s="3" t="n">
+      <c r="D247" s="6" t="n">
         <v>2.2779405</v>
       </c>
       <c r="E247" t="n">
@@ -5806,10 +5722,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C248" s="2" t="n">
+      <c r="C248" s="5" t="n">
         <v>305.19</v>
       </c>
-      <c r="D248" s="3" t="n">
+      <c r="D248" s="6" t="n">
         <v>0.07034633</v>
       </c>
       <c r="E248" t="n">
@@ -5827,10 +5743,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C249" s="2" t="n">
+      <c r="C249" s="5" t="n">
         <v>9384.76</v>
       </c>
-      <c r="D249" s="3" t="n">
+      <c r="D249" s="6" t="n">
         <v>2.16318832</v>
       </c>
       <c r="E249" t="n">
@@ -5848,10 +5764,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C250" s="2" t="n">
+      <c r="C250" s="5" t="n">
         <v>369070.94</v>
       </c>
-      <c r="D250" s="3" t="n">
+      <c r="D250" s="6" t="n">
         <v>85.07089664999999</v>
       </c>
       <c r="E250" t="n">
@@ -5869,10 +5785,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C251" s="2" t="n">
+      <c r="C251" s="5" t="n">
         <v>387.59</v>
       </c>
-      <c r="D251" s="3" t="n">
+      <c r="D251" s="6" t="n">
         <v>0.10977502</v>
       </c>
       <c r="E251" t="n">
@@ -5890,10 +5806,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C252" s="2" t="n">
+      <c r="C252" s="5" t="n">
         <v>3000</v>
       </c>
-      <c r="D252" s="3" t="n">
+      <c r="D252" s="6" t="n">
         <v>0.84967379</v>
       </c>
       <c r="E252" t="n">
@@ -5911,10 +5827,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C253" s="2" t="n">
+      <c r="C253" s="5" t="n">
         <v>114879.27</v>
       </c>
-      <c r="D253" s="3" t="n">
+      <c r="D253" s="6" t="n">
         <v>32.53663482</v>
       </c>
       <c r="E253" t="n">
@@ -5932,10 +5848,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C254" s="2" t="n">
+      <c r="C254" s="5" t="n">
         <v>234809.82</v>
       </c>
-      <c r="D254" s="3" t="n">
+      <c r="D254" s="6" t="n">
         <v>66.50391637</v>
       </c>
       <c r="E254" t="n">
@@ -5953,10 +5869,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C255" s="2" t="n">
+      <c r="C255" s="5" t="n">
         <v>8859.66</v>
       </c>
-      <c r="D255" s="3" t="n">
+      <c r="D255" s="6" t="n">
         <v>5.34081687</v>
       </c>
       <c r="E255" t="n">
@@ -5974,10 +5890,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C256" s="2" t="n">
+      <c r="C256" s="5" t="n">
         <v>1006.9</v>
       </c>
-      <c r="D256" s="3" t="n">
+      <c r="D256" s="6" t="n">
         <v>0.6069836199999999</v>
       </c>
       <c r="E256" t="n">
@@ -5995,10 +5911,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C257" s="2" t="n">
+      <c r="C257" s="5" t="n">
         <v>1000</v>
       </c>
-      <c r="D257" s="3" t="n">
+      <c r="D257" s="6" t="n">
         <v>0.60282413</v>
       </c>
       <c r="E257" t="n">
@@ -6016,10 +5932,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C258" s="2" t="n">
+      <c r="C258" s="5" t="n">
         <v>51121.7</v>
       </c>
-      <c r="D258" s="3" t="n">
+      <c r="D258" s="6" t="n">
         <v>30.81739456</v>
       </c>
       <c r="E258" t="n">
@@ -6037,10 +5953,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C259" s="2" t="n">
+      <c r="C259" s="5" t="n">
         <v>103897.6</v>
       </c>
-      <c r="D259" s="3" t="n">
+      <c r="D259" s="6" t="n">
         <v>62.63198081</v>
       </c>
       <c r="E259" t="n">
@@ -6058,10 +5974,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C260" s="2" t="n">
+      <c r="C260" s="5" t="n">
         <v>7692.3</v>
       </c>
-      <c r="D260" s="3" t="n">
+      <c r="D260" s="6" t="n">
         <v>6.29078176</v>
       </c>
       <c r="E260" t="n">
@@ -6079,10 +5995,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C261" s="2" t="n">
+      <c r="C261" s="5" t="n">
         <v>1882.73</v>
       </c>
-      <c r="D261" s="3" t="n">
+      <c r="D261" s="6" t="n">
         <v>1.5397012</v>
       </c>
       <c r="E261" t="n">
@@ -6100,10 +6016,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C262" s="2" t="n">
+      <c r="C262" s="5" t="n">
         <v>14869.63</v>
       </c>
-      <c r="D262" s="3" t="n">
+      <c r="D262" s="6" t="n">
         <v>12.1604198</v>
       </c>
       <c r="E262" t="n">
@@ -6121,10 +6037,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C263" s="2" t="n">
+      <c r="C263" s="5" t="n">
         <v>97834.25999999999</v>
       </c>
-      <c r="D263" s="3" t="n">
+      <c r="D263" s="6" t="n">
         <v>80.00909722999999</v>
       </c>
       <c r="E263" t="n">
@@ -6142,10 +6058,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C264" s="2" t="n">
+      <c r="C264" s="5" t="n">
         <v>3303.59</v>
       </c>
-      <c r="D264" s="3" t="n">
+      <c r="D264" s="6" t="n">
         <v>1.27093949</v>
       </c>
       <c r="E264" t="n">
@@ -6163,10 +6079,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C265" s="2" t="n">
+      <c r="C265" s="5" t="n">
         <v>18435.53</v>
       </c>
-      <c r="D265" s="3" t="n">
+      <c r="D265" s="6" t="n">
         <v>7.09241858</v>
       </c>
       <c r="E265" t="n">
@@ -6184,10 +6100,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C266" s="2" t="n">
+      <c r="C266" s="5" t="n">
         <v>2222.22</v>
       </c>
-      <c r="D266" s="3" t="n">
+      <c r="D266" s="6" t="n">
         <v>0.8549206</v>
       </c>
       <c r="E266" t="n">
@@ -6205,10 +6121,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C267" s="2" t="n">
+      <c r="C267" s="5" t="n">
         <v>50871.54</v>
       </c>
-      <c r="D267" s="3" t="n">
+      <c r="D267" s="6" t="n">
         <v>19.571027</v>
       </c>
       <c r="E267" t="n">
@@ -6226,10 +6142,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C268" s="2" t="n">
+      <c r="C268" s="5" t="n">
         <v>185100.03</v>
       </c>
-      <c r="D268" s="3" t="n">
+      <c r="D268" s="6" t="n">
         <v>71.21069433</v>
       </c>
       <c r="E268" t="n">
@@ -6247,10 +6163,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C269" s="2" t="n">
+      <c r="C269" s="5" t="n">
         <v>26854.86</v>
       </c>
-      <c r="D269" s="3" t="n">
+      <c r="D269" s="6" t="n">
         <v>6.60466391</v>
       </c>
       <c r="E269" t="n">
@@ -6268,10 +6184,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="C270" s="2" t="n">
+      <c r="C270" s="5" t="n">
         <v>554.28</v>
       </c>
-      <c r="D270" s="3" t="n">
+      <c r="D270" s="6" t="n">
         <v>0.1363192</v>
       </c>
       <c r="E270" t="n">
@@ -6289,10 +6205,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C271" s="2" t="n">
+      <c r="C271" s="5" t="n">
         <v>487.8</v>
       </c>
-      <c r="D271" s="3" t="n">
+      <c r="D271" s="6" t="n">
         <v>0.11996916</v>
       </c>
       <c r="E271" t="n">
@@ -6310,10 +6226,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C272" s="2" t="n">
+      <c r="C272" s="5" t="n">
         <v>12206.22</v>
       </c>
-      <c r="D272" s="3" t="n">
+      <c r="D272" s="6" t="n">
         <v>3.00198849</v>
       </c>
       <c r="E272" t="n">
@@ -6331,10 +6247,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C273" s="2" t="n">
+      <c r="C273" s="5" t="n">
         <v>28370.02</v>
       </c>
-      <c r="D273" s="3" t="n">
+      <c r="D273" s="6" t="n">
         <v>6.97730121</v>
       </c>
       <c r="E273" t="n">
@@ -6352,10 +6268,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C274" s="2" t="n">
+      <c r="C274" s="5" t="n">
         <v>338131.31</v>
       </c>
-      <c r="D274" s="3" t="n">
+      <c r="D274" s="6" t="n">
         <v>83.15975802</v>
       </c>
       <c r="E274" t="n">
@@ -6373,10 +6289,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C275" s="2" t="n">
+      <c r="C275" s="5" t="n">
         <v>19985.78</v>
       </c>
-      <c r="D275" s="3" t="n">
+      <c r="D275" s="6" t="n">
         <v>7.97052191</v>
       </c>
       <c r="E275" t="n">
@@ -6394,10 +6310,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="C276" s="2" t="n">
+      <c r="C276" s="5" t="n">
         <v>2222.22</v>
       </c>
-      <c r="D276" s="3" t="n">
+      <c r="D276" s="6" t="n">
         <v>0.88624278</v>
       </c>
       <c r="E276" t="n">
@@ -6415,10 +6331,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C277" s="2" t="n">
+      <c r="C277" s="5" t="n">
         <v>4445.7</v>
       </c>
-      <c r="D277" s="3" t="n">
+      <c r="D277" s="6" t="n">
         <v>1.77298806</v>
       </c>
       <c r="E277" t="n">
@@ -6436,10 +6352,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C278" s="2" t="n">
+      <c r="C278" s="5" t="n">
         <v>50514.02</v>
       </c>
-      <c r="D278" s="3" t="n">
+      <c r="D278" s="6" t="n">
         <v>20.14547858</v>
       </c>
       <c r="E278" t="n">
@@ -6457,10 +6373,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C279" s="2" t="n">
+      <c r="C279" s="5" t="n">
         <v>173578.47</v>
       </c>
-      <c r="D279" s="3" t="n">
+      <c r="D279" s="6" t="n">
         <v>69.22476868</v>
       </c>
       <c r="E279" t="n">
@@ -6478,10 +6394,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C280" s="2" t="n">
+      <c r="C280" s="5" t="n">
         <v>40560.99</v>
       </c>
-      <c r="D280" s="3" t="n">
+      <c r="D280" s="6" t="n">
         <v>8.644859670000001</v>
       </c>
       <c r="E280" t="n">
@@ -6499,10 +6415,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C281" s="2" t="n">
+      <c r="C281" s="5" t="n">
         <v>6836.42</v>
       </c>
-      <c r="D281" s="3" t="n">
+      <c r="D281" s="6" t="n">
         <v>1.45706235</v>
       </c>
       <c r="E281" t="n">
@@ -6520,10 +6436,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C282" s="2" t="n">
+      <c r="C282" s="5" t="n">
         <v>34873.15</v>
       </c>
-      <c r="D282" s="3" t="n">
+      <c r="D282" s="6" t="n">
         <v>7.43259689</v>
       </c>
       <c r="E282" t="n">
@@ -6541,10 +6457,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C283" s="2" t="n">
+      <c r="C283" s="5" t="n">
         <v>386921.44</v>
       </c>
-      <c r="D283" s="3" t="n">
+      <c r="D283" s="6" t="n">
         <v>82.46548108</v>
       </c>
       <c r="E283" t="n">
@@ -6562,10 +6478,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="C284" s="2" t="n">
+      <c r="C284" s="5" t="n">
         <v>2062.08</v>
       </c>
-      <c r="D284" s="3" t="n">
+      <c r="D284" s="6" t="n">
         <v>0.67843969</v>
       </c>
       <c r="E284" t="n">
@@ -6583,10 +6499,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C285" s="2" t="n">
+      <c r="C285" s="5" t="n">
         <v>67302.87</v>
       </c>
-      <c r="D285" s="3" t="n">
+      <c r="D285" s="6" t="n">
         <v>22.14314601</v>
       </c>
       <c r="E285" t="n">
@@ -6604,10 +6520,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C286" s="2" t="n">
+      <c r="C286" s="5" t="n">
         <v>37.83</v>
       </c>
-      <c r="D286" s="3" t="n">
+      <c r="D286" s="6" t="n">
         <v>0.01244635</v>
       </c>
       <c r="E286" t="n">
@@ -6625,10 +6541,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C287" s="2" t="n">
+      <c r="C287" s="5" t="n">
         <v>82048.36</v>
       </c>
-      <c r="D287" s="3" t="n">
+      <c r="D287" s="6" t="n">
         <v>26.99452216</v>
       </c>
       <c r="E287" t="n">
@@ -6646,10 +6562,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C288" s="2" t="n">
+      <c r="C288" s="5" t="n">
         <v>152493.34</v>
       </c>
-      <c r="D288" s="3" t="n">
+      <c r="D288" s="6" t="n">
         <v>50.17144579</v>
       </c>
       <c r="E288" t="n">
@@ -6667,10 +6583,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C289" s="2" t="n">
+      <c r="C289" s="5" t="n">
         <v>16850.05</v>
       </c>
-      <c r="D289" s="3" t="n">
+      <c r="D289" s="6" t="n">
         <v>8.3557591</v>
       </c>
       <c r="E289" t="n">
@@ -6688,10 +6604,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C290" s="2" t="n">
+      <c r="C290" s="5" t="n">
         <v>1221.31</v>
       </c>
-      <c r="D290" s="3" t="n">
+      <c r="D290" s="6" t="n">
         <v>0.60563453</v>
       </c>
       <c r="E290" t="n">
@@ -6709,10 +6625,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C291" s="2" t="n">
+      <c r="C291" s="5" t="n">
         <v>542.72</v>
       </c>
-      <c r="D291" s="3" t="n">
+      <c r="D291" s="6" t="n">
         <v>0.26912903</v>
       </c>
       <c r="E291" t="n">
@@ -6730,10 +6646,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C292" s="2" t="n">
+      <c r="C292" s="5" t="n">
         <v>1989.87</v>
       </c>
-      <c r="D292" s="3" t="n">
+      <c r="D292" s="6" t="n">
         <v>0.98675519</v>
       </c>
       <c r="E292" t="n">
@@ -6751,10 +6667,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C293" s="2" t="n">
+      <c r="C293" s="5" t="n">
         <v>181053.97</v>
       </c>
-      <c r="D293" s="3" t="n">
+      <c r="D293" s="6" t="n">
         <v>89.78272215</v>
       </c>
       <c r="E293" t="n">
@@ -6772,10 +6688,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C294" s="2" t="n">
+      <c r="C294" s="5" t="n">
         <v>2791.46</v>
       </c>
-      <c r="D294" s="3" t="n">
+      <c r="D294" s="6" t="n">
         <v>1.6215349</v>
       </c>
       <c r="E294" t="n">
@@ -6793,10 +6709,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C295" s="2" t="n">
+      <c r="C295" s="5" t="n">
         <v>6752.82</v>
       </c>
-      <c r="D295" s="3" t="n">
+      <c r="D295" s="6" t="n">
         <v>3.92265455</v>
       </c>
       <c r="E295" t="n">
@@ -6814,10 +6730,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C296" s="2" t="n">
+      <c r="C296" s="5" t="n">
         <v>42038.15</v>
       </c>
-      <c r="D296" s="3" t="n">
+      <c r="D296" s="6" t="n">
         <v>24.41959662</v>
       </c>
       <c r="E296" t="n">
@@ -6835,10 +6751,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C297" s="2" t="n">
+      <c r="C297" s="5" t="n">
         <v>120566.81</v>
       </c>
-      <c r="D297" s="3" t="n">
+      <c r="D297" s="6" t="n">
         <v>70.03621393</v>
       </c>
       <c r="E297" t="n">
@@ -6856,10 +6772,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C298" s="2" t="n">
+      <c r="C298" s="5" t="n">
         <v>360</v>
       </c>
-      <c r="D298" s="3" t="n">
+      <c r="D298" s="6" t="n">
         <v>0.13798773</v>
       </c>
       <c r="E298" t="n">
@@ -6877,10 +6793,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C299" s="2" t="n">
+      <c r="C299" s="5" t="n">
         <v>9364.209999999999</v>
       </c>
-      <c r="D299" s="3" t="n">
+      <c r="D299" s="6" t="n">
         <v>3.58929456</v>
       </c>
       <c r="E299" t="n">
@@ -6898,10 +6814,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C300" s="2" t="n">
+      <c r="C300" s="5" t="n">
         <v>4780.88</v>
       </c>
-      <c r="D300" s="3" t="n">
+      <c r="D300" s="6" t="n">
         <v>1.83250766</v>
       </c>
       <c r="E300" t="n">
@@ -6919,10 +6835,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C301" s="2" t="n">
+      <c r="C301" s="5" t="n">
         <v>246387.68</v>
       </c>
-      <c r="D301" s="3" t="n">
+      <c r="D301" s="6" t="n">
         <v>94.44021005</v>
       </c>
       <c r="E301" t="n">
@@ -6940,10 +6856,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C302" s="2" t="n">
+      <c r="C302" s="5" t="n">
         <v>6057.75</v>
       </c>
-      <c r="D302" s="3" t="n">
+      <c r="D302" s="6" t="n">
         <v>2.33727832</v>
       </c>
       <c r="E302" t="n">
@@ -6961,10 +6877,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C303" s="2" t="n">
+      <c r="C303" s="5" t="n">
         <v>48766.63</v>
       </c>
-      <c r="D303" s="3" t="n">
+      <c r="D303" s="6" t="n">
         <v>18.81576278</v>
       </c>
       <c r="E303" t="n">
@@ -6982,10 +6898,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C304" s="2" t="n">
+      <c r="C304" s="5" t="n">
         <v>204355.28</v>
       </c>
-      <c r="D304" s="3" t="n">
+      <c r="D304" s="6" t="n">
         <v>78.8469589</v>
       </c>
       <c r="E304" t="n">
@@ -7003,10 +6919,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C305" s="2" t="n">
+      <c r="C305" s="5" t="n">
         <v>16523.23</v>
       </c>
-      <c r="D305" s="3" t="n">
+      <c r="D305" s="6" t="n">
         <v>6.18627246</v>
       </c>
       <c r="E305" t="n">
@@ -7024,10 +6940,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="C306" s="2" t="n">
+      <c r="C306" s="5" t="n">
         <v>1000</v>
       </c>
-      <c r="D306" s="3" t="n">
+      <c r="D306" s="6" t="n">
         <v>0.3743985</v>
       </c>
       <c r="E306" t="n">
@@ -7045,10 +6961,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C307" s="2" t="n">
+      <c r="C307" s="5" t="n">
         <v>19175.48</v>
       </c>
-      <c r="D307" s="3" t="n">
+      <c r="D307" s="6" t="n">
         <v>7.17927087</v>
       </c>
       <c r="E307" t="n">
@@ -7066,10 +6982,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C308" s="2" t="n">
+      <c r="C308" s="5" t="n">
         <v>22548.18</v>
       </c>
-      <c r="D308" s="3" t="n">
+      <c r="D308" s="6" t="n">
         <v>8.44200468</v>
       </c>
       <c r="E308" t="n">
@@ -7087,10 +7003,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C309" s="2" t="n">
+      <c r="C309" s="5" t="n">
         <v>3105.38</v>
       </c>
-      <c r="D309" s="3" t="n">
+      <c r="D309" s="6" t="n">
         <v>1.1626496</v>
       </c>
       <c r="E309" t="n">
@@ -7108,10 +7024,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C310" s="2" t="n">
+      <c r="C310" s="5" t="n">
         <v>9171.51</v>
       </c>
-      <c r="D310" s="3" t="n">
+      <c r="D310" s="6" t="n">
         <v>3.43379955</v>
       </c>
       <c r="E310" t="n">
@@ -7129,10 +7045,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C311" s="2" t="n">
+      <c r="C311" s="5" t="n">
         <v>195571.31</v>
       </c>
-      <c r="D311" s="3" t="n">
+      <c r="D311" s="6" t="n">
         <v>73.22160434</v>
       </c>
       <c r="E311" t="n">
@@ -7150,10 +7066,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C312" s="2" t="n">
+      <c r="C312" s="5" t="n">
         <v>27350.51</v>
       </c>
-      <c r="D312" s="3" t="n">
+      <c r="D312" s="6" t="n">
         <v>9.8197723</v>
       </c>
       <c r="E312" t="n">
@@ -7171,10 +7087,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C313" s="2" t="n">
+      <c r="C313" s="5" t="n">
         <v>21653.68</v>
       </c>
-      <c r="D313" s="3" t="n">
+      <c r="D313" s="6" t="n">
         <v>7.7744147</v>
       </c>
       <c r="E313" t="n">
@@ -7192,10 +7108,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C314" s="2" t="n">
+      <c r="C314" s="5" t="n">
         <v>30092.08</v>
       </c>
-      <c r="D314" s="3" t="n">
+      <c r="D314" s="6" t="n">
         <v>10.80409008</v>
       </c>
       <c r="E314" t="n">
@@ -7213,10 +7129,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C315" s="2" t="n">
+      <c r="C315" s="5" t="n">
         <v>199428.62</v>
       </c>
-      <c r="D315" s="3" t="n">
+      <c r="D315" s="6" t="n">
         <v>71.60172292</v>
       </c>
       <c r="E315" t="n">
@@ -7234,10 +7150,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C316" s="2" t="n">
+      <c r="C316" s="5" t="n">
         <v>18403.89</v>
       </c>
-      <c r="D316" s="3" t="n">
+      <c r="D316" s="6" t="n">
         <v>5.9503914</v>
       </c>
       <c r="E316" t="n">
@@ -7255,10 +7171,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C317" s="2" t="n">
+      <c r="C317" s="5" t="n">
         <v>88.88</v>
       </c>
-      <c r="D317" s="3" t="n">
+      <c r="D317" s="6" t="n">
         <v>0.0287369</v>
       </c>
       <c r="E317" t="n">
@@ -7276,10 +7192,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C318" s="2" t="n">
+      <c r="C318" s="5" t="n">
         <v>72445.86</v>
       </c>
-      <c r="D318" s="3" t="n">
+      <c r="D318" s="6" t="n">
         <v>23.4233753</v>
       </c>
       <c r="E318" t="n">
@@ -7297,10 +7213,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C319" s="2" t="n">
+      <c r="C319" s="5" t="n">
         <v>1021.81</v>
       </c>
-      <c r="D319" s="3" t="n">
+      <c r="D319" s="6" t="n">
         <v>0.33037415</v>
       </c>
       <c r="E319" t="n">
@@ -7318,10 +7234,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C320" s="2" t="n">
+      <c r="C320" s="5" t="n">
         <v>23146.75</v>
       </c>
-      <c r="D320" s="3" t="n">
+      <c r="D320" s="6" t="n">
         <v>7.48386467</v>
       </c>
       <c r="E320" t="n">
@@ -7339,10 +7255,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C321" s="2" t="n">
+      <c r="C321" s="5" t="n">
         <v>194181.54</v>
       </c>
-      <c r="D321" s="3" t="n">
+      <c r="D321" s="6" t="n">
         <v>62.78325757</v>
       </c>
       <c r="E321" t="n">
@@ -7360,10 +7276,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C322" s="2" t="n">
+      <c r="C322" s="5" t="n">
         <v>3620.25</v>
       </c>
-      <c r="D322" s="3" t="n">
+      <c r="D322" s="6" t="n">
         <v>1.23604851</v>
       </c>
       <c r="E322" t="n">
@@ -7381,10 +7297,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C323" s="2" t="n">
+      <c r="C323" s="5" t="n">
         <v>19747.53</v>
       </c>
-      <c r="D323" s="3" t="n">
+      <c r="D323" s="6" t="n">
         <v>6.74232582</v>
       </c>
       <c r="E323" t="n">
@@ -7402,10 +7318,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C324" s="2" t="n">
+      <c r="C324" s="5" t="n">
         <v>148.8</v>
       </c>
-      <c r="D324" s="3" t="n">
+      <c r="D324" s="6" t="n">
         <v>0.05080423</v>
       </c>
       <c r="E324" t="n">
@@ -7423,10 +7339,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C325" s="2" t="n">
+      <c r="C325" s="5" t="n">
         <v>59465.09</v>
       </c>
-      <c r="D325" s="3" t="n">
+      <c r="D325" s="6" t="n">
         <v>20.30294481</v>
       </c>
       <c r="E325" t="n">
@@ -7444,10 +7360,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C326" s="2" t="n">
+      <c r="C326" s="5" t="n">
         <v>209907.32</v>
       </c>
-      <c r="D326" s="3" t="n">
+      <c r="D326" s="6" t="n">
         <v>71.66787662</v>
       </c>
       <c r="E326" t="n">
@@ -7465,10 +7381,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C327" s="2" t="n">
+      <c r="C327" s="5" t="n">
         <v>6884.07</v>
       </c>
-      <c r="D327" s="3" t="n">
+      <c r="D327" s="6" t="n">
         <v>2.33908458</v>
       </c>
       <c r="E327" t="n">
@@ -7486,10 +7402,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C328" s="2" t="n">
+      <c r="C328" s="5" t="n">
         <v>1851.18</v>
       </c>
-      <c r="D328" s="3" t="n">
+      <c r="D328" s="6" t="n">
         <v>0.62899805</v>
       </c>
       <c r="E328" t="n">
@@ -7507,10 +7423,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C329" s="2" t="n">
+      <c r="C329" s="5" t="n">
         <v>27.27</v>
       </c>
-      <c r="D329" s="3" t="n">
+      <c r="D329" s="6" t="n">
         <v>0.009265860000000001</v>
       </c>
       <c r="E329" t="n">
@@ -7528,10 +7444,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C330" s="2" t="n">
+      <c r="C330" s="5" t="n">
         <v>48724.48</v>
       </c>
-      <c r="D330" s="3" t="n">
+      <c r="D330" s="6" t="n">
         <v>16.55571192</v>
       </c>
       <c r="E330" t="n">
@@ -7549,10 +7465,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C331" s="2" t="n">
+      <c r="C331" s="5" t="n">
         <v>236819.16</v>
       </c>
-      <c r="D331" s="3" t="n">
+      <c r="D331" s="6" t="n">
         <v>80.4669396</v>
       </c>
       <c r="E331" t="n">
@@ -7570,10 +7486,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C332" s="2" t="n">
+      <c r="C332" s="5" t="n">
         <v>1121.22</v>
       </c>
-      <c r="D332" s="3" t="n">
+      <c r="D332" s="6" t="n">
         <v>0.3654631</v>
       </c>
       <c r="E332" t="n">
@@ -7591,10 +7507,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C333" s="2" t="n">
+      <c r="C333" s="5" t="n">
         <v>44200.33</v>
       </c>
-      <c r="D333" s="3" t="n">
+      <c r="D333" s="6" t="n">
         <v>14.40715442</v>
       </c>
       <c r="E333" t="n">
@@ -7612,10 +7528,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C334" s="2" t="n">
+      <c r="C334" s="5" t="n">
         <v>1029.79</v>
       </c>
-      <c r="D334" s="3" t="n">
+      <c r="D334" s="6" t="n">
         <v>0.33566138</v>
       </c>
       <c r="E334" t="n">
@@ -7633,10 +7549,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C335" s="2" t="n">
+      <c r="C335" s="5" t="n">
         <v>47810.16</v>
       </c>
-      <c r="D335" s="3" t="n">
+      <c r="D335" s="6" t="n">
         <v>15.58378315</v>
       </c>
       <c r="E335" t="n">
@@ -7654,10 +7570,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C336" s="2" t="n">
+      <c r="C336" s="5" t="n">
         <v>212632.81</v>
       </c>
-      <c r="D336" s="3" t="n">
+      <c r="D336" s="6" t="n">
         <v>69.30793795</v>
       </c>
       <c r="E336" t="n">
@@ -7675,10 +7591,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C337" s="2" t="n">
+      <c r="C337" s="5" t="n">
         <v>6174.11</v>
       </c>
-      <c r="D337" s="3" t="n">
+      <c r="D337" s="6" t="n">
         <v>2.21572231</v>
       </c>
       <c r="E337" t="n">
@@ -7696,10 +7612,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C338" s="2" t="n">
+      <c r="C338" s="5" t="n">
         <v>41944.2</v>
       </c>
-      <c r="D338" s="3" t="n">
+      <c r="D338" s="6" t="n">
         <v>15.05264723</v>
       </c>
       <c r="E338" t="n">
@@ -7717,10 +7633,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C339" s="2" t="n">
+      <c r="C339" s="5" t="n">
         <v>77569.86</v>
       </c>
-      <c r="D339" s="3" t="n">
+      <c r="D339" s="6" t="n">
         <v>27.8377401</v>
       </c>
       <c r="E339" t="n">
@@ -7738,10 +7654,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C340" s="2" t="n">
+      <c r="C340" s="5" t="n">
         <v>152961.82</v>
       </c>
-      <c r="D340" s="3" t="n">
+      <c r="D340" s="6" t="n">
         <v>54.89389036</v>
       </c>
       <c r="E340" t="n">
@@ -7759,10 +7675,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C341" s="2" t="n">
+      <c r="C341" s="5" t="n">
         <v>4327.58</v>
       </c>
-      <c r="D341" s="3" t="n">
+      <c r="D341" s="6" t="n">
         <v>1.21146897</v>
       </c>
       <c r="E341" t="n">
@@ -7780,10 +7696,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C342" s="2" t="n">
+      <c r="C342" s="5" t="n">
         <v>28414.86</v>
       </c>
-      <c r="D342" s="3" t="n">
+      <c r="D342" s="6" t="n">
         <v>7.95449675</v>
       </c>
       <c r="E342" t="n">
@@ -7801,10 +7717,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C343" s="2" t="n">
+      <c r="C343" s="5" t="n">
         <v>57985.61</v>
       </c>
-      <c r="D343" s="3" t="n">
+      <c r="D343" s="6" t="n">
         <v>16.23257501</v>
       </c>
       <c r="E343" t="n">
@@ -7822,10 +7738,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C344" s="2" t="n">
+      <c r="C344" s="5" t="n">
         <v>164042.55</v>
       </c>
-      <c r="D344" s="3" t="n">
+      <c r="D344" s="6" t="n">
         <v>45.92230724</v>
       </c>
       <c r="E344" t="n">
@@ -7843,10 +7759,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C345" s="2" t="n">
+      <c r="C345" s="5" t="n">
         <v>102446.97</v>
       </c>
-      <c r="D345" s="3" t="n">
+      <c r="D345" s="6" t="n">
         <v>28.67915204</v>
       </c>
       <c r="E345" t="n">
@@ -7864,10 +7780,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C346" s="2" t="n">
+      <c r="C346" s="5" t="n">
         <v>6549.34</v>
       </c>
-      <c r="D346" s="3" t="n">
+      <c r="D346" s="6" t="n">
         <v>1.3658538</v>
       </c>
       <c r="E346" t="n">
@@ -7885,10 +7801,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C347" s="2" t="n">
+      <c r="C347" s="5" t="n">
         <v>70012.2</v>
       </c>
-      <c r="D347" s="3" t="n">
+      <c r="D347" s="6" t="n">
         <v>14.60092612</v>
       </c>
       <c r="E347" t="n">
@@ -7906,10 +7822,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C348" s="2" t="n">
+      <c r="C348" s="5" t="n">
         <v>131512.85</v>
       </c>
-      <c r="D348" s="3" t="n">
+      <c r="D348" s="6" t="n">
         <v>27.42678286</v>
       </c>
       <c r="E348" t="n">
@@ -7927,10 +7843,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C349" s="2" t="n">
+      <c r="C349" s="5" t="n">
         <v>271430.81</v>
       </c>
-      <c r="D349" s="3" t="n">
+      <c r="D349" s="6" t="n">
         <v>56.60643722</v>
       </c>
       <c r="E349" t="n">
@@ -7948,10 +7864,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C350" s="2" t="n">
+      <c r="C350" s="5" t="n">
         <v>15339.66</v>
       </c>
-      <c r="D350" s="3" t="n">
+      <c r="D350" s="6" t="n">
         <v>4.55580253</v>
       </c>
       <c r="E350" t="n">
@@ -7969,10 +7885,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C351" s="2" t="n">
+      <c r="C351" s="5" t="n">
         <v>24900.55</v>
       </c>
-      <c r="D351" s="3" t="n">
+      <c r="D351" s="6" t="n">
         <v>7.39533918</v>
       </c>
       <c r="E351" t="n">
@@ -7990,10 +7906,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C352" s="2" t="n">
+      <c r="C352" s="5" t="n">
         <v>7486.19</v>
       </c>
-      <c r="D352" s="3" t="n">
+      <c r="D352" s="6" t="n">
         <v>2.2233611</v>
       </c>
       <c r="E352" t="n">
@@ -8011,10 +7927,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C353" s="2" t="n">
+      <c r="C353" s="5" t="n">
         <v>75899.28</v>
       </c>
-      <c r="D353" s="3" t="n">
+      <c r="D353" s="6" t="n">
         <v>22.54170768</v>
       </c>
       <c r="E353" t="n">
@@ -8032,10 +7948,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C354" s="2" t="n">
+      <c r="C354" s="5" t="n">
         <v>213080.31</v>
       </c>
-      <c r="D354" s="3" t="n">
+      <c r="D354" s="6" t="n">
         <v>63.28378952</v>
       </c>
       <c r="E354" t="n">
@@ -8053,10 +7969,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C355" s="2" t="n">
+      <c r="C355" s="5" t="n">
         <v>99.05</v>
       </c>
-      <c r="D355" s="3" t="n">
+      <c r="D355" s="6" t="n">
         <v>0.05450467</v>
       </c>
       <c r="E355" t="n">
@@ -8074,10 +7990,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C356" s="2" t="n">
+      <c r="C356" s="5" t="n">
         <v>40317.43</v>
       </c>
-      <c r="D356" s="3" t="n">
+      <c r="D356" s="6" t="n">
         <v>22.18564427</v>
       </c>
       <c r="E356" t="n">
@@ -8095,10 +8011,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C357" s="2" t="n">
+      <c r="C357" s="5" t="n">
         <v>441.17</v>
       </c>
-      <c r="D357" s="3" t="n">
+      <c r="D357" s="6" t="n">
         <v>0.2427645</v>
       </c>
       <c r="E357" t="n">
@@ -8116,10 +8032,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C358" s="2" t="n">
+      <c r="C358" s="5" t="n">
         <v>15478.5</v>
       </c>
-      <c r="D358" s="3" t="n">
+      <c r="D358" s="6" t="n">
         <v>8.517420250000001</v>
       </c>
       <c r="E358" t="n">
@@ -8137,10 +8053,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C359" s="2" t="n">
+      <c r="C359" s="5" t="n">
         <v>125391.41</v>
       </c>
-      <c r="D359" s="3" t="n">
+      <c r="D359" s="6" t="n">
         <v>68.99966630999999</v>
       </c>
       <c r="E359" t="n">
@@ -8158,10 +8074,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C360" s="2" t="n">
+      <c r="C360" s="5" t="n">
         <v>1078.53</v>
       </c>
-      <c r="D360" s="3" t="n">
+      <c r="D360" s="6" t="n">
         <v>0.2616409</v>
       </c>
       <c r="E360" t="n">
@@ -8179,10 +8095,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C361" s="2" t="n">
+      <c r="C361" s="5" t="n">
         <v>18773.2</v>
       </c>
-      <c r="D361" s="3" t="n">
+      <c r="D361" s="6" t="n">
         <v>4.55419596</v>
       </c>
       <c r="E361" t="n">
@@ -8200,10 +8116,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C362" s="2" t="n">
+      <c r="C362" s="5" t="n">
         <v>131529.74</v>
       </c>
-      <c r="D362" s="3" t="n">
+      <c r="D362" s="6" t="n">
         <v>31.90783723</v>
       </c>
       <c r="E362" t="n">
@@ -8221,10 +8137,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C363" s="2" t="n">
+      <c r="C363" s="5" t="n">
         <v>260836.19</v>
       </c>
-      <c r="D363" s="3" t="n">
+      <c r="D363" s="6" t="n">
         <v>63.27632591</v>
       </c>
       <c r="E363" t="n">
@@ -8242,10 +8158,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C364" s="2" t="n">
+      <c r="C364" s="5" t="n">
         <v>101597</v>
       </c>
-      <c r="D364" s="3" t="n">
+      <c r="D364" s="6" t="n">
         <v>23.3811176</v>
       </c>
       <c r="E364" t="n">
@@ -8263,10 +8179,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C365" s="2" t="n">
+      <c r="C365" s="5" t="n">
         <v>28150.66</v>
       </c>
-      <c r="D365" s="3" t="n">
+      <c r="D365" s="6" t="n">
         <v>6.47847763</v>
       </c>
       <c r="E365" t="n">
@@ -8284,10 +8200,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C366" s="2" t="n">
+      <c r="C366" s="5" t="n">
         <v>40.94</v>
       </c>
-      <c r="D366" s="3" t="n">
+      <c r="D366" s="6" t="n">
         <v>0.00942176</v>
       </c>
       <c r="E366" t="n">
@@ -8305,10 +8221,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C367" s="2" t="n">
+      <c r="C367" s="5" t="n">
         <v>39974.48</v>
       </c>
-      <c r="D367" s="3" t="n">
+      <c r="D367" s="6" t="n">
         <v>9.19956316</v>
       </c>
       <c r="E367" t="n">
@@ -8326,10 +8242,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C368" s="2" t="n">
+      <c r="C368" s="5" t="n">
         <v>264762.77</v>
       </c>
-      <c r="D368" s="3" t="n">
+      <c r="D368" s="6" t="n">
         <v>60.93141985</v>
       </c>
       <c r="E368" t="n">
@@ -8347,10 +8263,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C369" s="2" t="n">
+      <c r="C369" s="5" t="n">
         <v>4391.2</v>
       </c>
-      <c r="D369" s="3" t="n">
+      <c r="D369" s="6" t="n">
         <v>1.20491459</v>
       </c>
       <c r="E369" t="n">
@@ -8368,10 +8284,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C370" s="2" t="n">
+      <c r="C370" s="5" t="n">
         <v>65068.55</v>
       </c>
-      <c r="D370" s="3" t="n">
+      <c r="D370" s="6" t="n">
         <v>17.85435532</v>
       </c>
       <c r="E370" t="n">
@@ -8389,10 +8305,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C371" s="2" t="n">
+      <c r="C371" s="5" t="n">
         <v>121692.04</v>
       </c>
-      <c r="D371" s="3" t="n">
+      <c r="D371" s="6" t="n">
         <v>33.3914452</v>
       </c>
       <c r="E371" t="n">
@@ -8410,10 +8326,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C372" s="2" t="n">
+      <c r="C372" s="5" t="n">
         <v>173288.98</v>
       </c>
-      <c r="D372" s="3" t="n">
+      <c r="D372" s="6" t="n">
         <v>47.54928489</v>
       </c>
       <c r="E372" t="n">
@@ -8431,10 +8347,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C373" s="2" t="n">
+      <c r="C373" s="5" t="n">
         <v>17775.38</v>
       </c>
-      <c r="D373" s="3" t="n">
+      <c r="D373" s="6" t="n">
         <v>7.37116189</v>
       </c>
       <c r="E373" t="n">
@@ -8452,10 +8368,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C374" s="2" t="n">
+      <c r="C374" s="5" t="n">
         <v>29163.77</v>
       </c>
-      <c r="D374" s="3" t="n">
+      <c r="D374" s="6" t="n">
         <v>12.09374259</v>
       </c>
       <c r="E374" t="n">
@@ -8473,10 +8389,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C375" s="2" t="n">
+      <c r="C375" s="5" t="n">
         <v>52107.99</v>
       </c>
-      <c r="D375" s="3" t="n">
+      <c r="D375" s="6" t="n">
         <v>21.60833863</v>
       </c>
       <c r="E375" t="n">
@@ -8494,10 +8410,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C376" s="2" t="n">
+      <c r="C376" s="5" t="n">
         <v>142100.46</v>
       </c>
-      <c r="D376" s="3" t="n">
+      <c r="D376" s="6" t="n">
         <v>58.92675689</v>
       </c>
       <c r="E376" t="n">
@@ -8515,10 +8431,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C377" s="2" t="n">
+      <c r="C377" s="5" t="n">
         <v>10000</v>
       </c>
-      <c r="D377" s="3" t="n">
+      <c r="D377" s="6" t="n">
         <v>3.50118517</v>
       </c>
       <c r="E377" t="n">
@@ -8536,10 +8452,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C378" s="2" t="n">
+      <c r="C378" s="5" t="n">
         <v>4643.79</v>
       </c>
-      <c r="D378" s="3" t="n">
+      <c r="D378" s="6" t="n">
         <v>1.62587687</v>
       </c>
       <c r="E378" t="n">
@@ -8557,10 +8473,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C379" s="2" t="n">
+      <c r="C379" s="5" t="n">
         <v>520.28</v>
       </c>
-      <c r="D379" s="3" t="n">
+      <c r="D379" s="6" t="n">
         <v>0.18215966</v>
       </c>
       <c r="E379" t="n">
@@ -8578,10 +8494,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C380" s="2" t="n">
+      <c r="C380" s="5" t="n">
         <v>19199.2</v>
       </c>
-      <c r="D380" s="3" t="n">
+      <c r="D380" s="6" t="n">
         <v>6.72199543</v>
       </c>
       <c r="E380" t="n">
@@ -8599,10 +8515,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C381" s="2" t="n">
+      <c r="C381" s="5" t="n">
         <v>251254.3</v>
       </c>
-      <c r="D381" s="3" t="n">
+      <c r="D381" s="6" t="n">
         <v>87.96878287</v>
       </c>
       <c r="E381" t="n">
@@ -8620,10 +8536,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C382" s="2" t="n">
+      <c r="C382" s="5" t="n">
         <v>2713.17</v>
       </c>
-      <c r="D382" s="3" t="n">
+      <c r="D382" s="6" t="n">
         <v>1.2942759</v>
       </c>
       <c r="E382" t="n">
@@ -8641,10 +8557,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C383" s="2" t="n">
+      <c r="C383" s="5" t="n">
         <v>3564.2</v>
       </c>
-      <c r="D383" s="3" t="n">
+      <c r="D383" s="6" t="n">
         <v>1.70024664</v>
       </c>
       <c r="E383" t="n">
@@ -8662,10 +8578,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C384" s="2" t="n">
+      <c r="C384" s="5" t="n">
         <v>41002.83</v>
       </c>
-      <c r="D384" s="3" t="n">
+      <c r="D384" s="6" t="n">
         <v>19.55976769</v>
       </c>
       <c r="E384" t="n">
@@ -8683,10 +8599,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C385" s="2" t="n">
+      <c r="C385" s="5" t="n">
         <v>162348.21</v>
       </c>
-      <c r="D385" s="3" t="n">
+      <c r="D385" s="6" t="n">
         <v>77.44570976999999</v>
       </c>
       <c r="E385" t="n">
@@ -8704,10 +8620,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C386" s="2" t="n">
+      <c r="C386" s="5" t="n">
         <v>1485.87</v>
       </c>
-      <c r="D386" s="3" t="n">
+      <c r="D386" s="6" t="n">
         <v>0.73523958</v>
       </c>
       <c r="E386" t="n">
@@ -8725,10 +8641,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C387" s="2" t="n">
+      <c r="C387" s="5" t="n">
         <v>42513.88</v>
       </c>
-      <c r="D387" s="3" t="n">
+      <c r="D387" s="6" t="n">
         <v>21.03675772</v>
       </c>
       <c r="E387" t="n">
@@ -8746,10 +8662,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C388" s="2" t="n">
+      <c r="C388" s="5" t="n">
         <v>450.45</v>
       </c>
-      <c r="D388" s="3" t="n">
+      <c r="D388" s="6" t="n">
         <v>0.22289209</v>
       </c>
       <c r="E388" t="n">
@@ -8767,10 +8683,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C389" s="2" t="n">
+      <c r="C389" s="5" t="n">
         <v>15613.89</v>
       </c>
-      <c r="D389" s="3" t="n">
+      <c r="D389" s="6" t="n">
         <v>7.7260796</v>
       </c>
       <c r="E389" t="n">
@@ -8788,10 +8704,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C390" s="2" t="n">
+      <c r="C390" s="5" t="n">
         <v>142029.22</v>
       </c>
-      <c r="D390" s="3" t="n">
+      <c r="D390" s="6" t="n">
         <v>70.27903101</v>
       </c>
       <c r="E390" t="n">
@@ -8809,10 +8725,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C391" s="2" t="n">
+      <c r="C391" s="5" t="n">
         <v>35429.86</v>
       </c>
-      <c r="D391" s="3" t="n">
+      <c r="D391" s="6" t="n">
         <v>13.31062066</v>
       </c>
       <c r="E391" t="n">
@@ -8830,10 +8746,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C392" s="2" t="n">
+      <c r="C392" s="5" t="n">
         <v>32122.79</v>
       </c>
-      <c r="D392" s="3" t="n">
+      <c r="D392" s="6" t="n">
         <v>12.06818972</v>
       </c>
       <c r="E392" t="n">
@@ -8851,10 +8767,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C393" s="2" t="n">
+      <c r="C393" s="5" t="n">
         <v>40536.38</v>
       </c>
-      <c r="D393" s="3" t="n">
+      <c r="D393" s="6" t="n">
         <v>15.22908578</v>
       </c>
       <c r="E393" t="n">
@@ -8872,10 +8788,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C394" s="2" t="n">
+      <c r="C394" s="5" t="n">
         <v>158088.34</v>
       </c>
-      <c r="D394" s="3" t="n">
+      <c r="D394" s="6" t="n">
         <v>59.39210384</v>
       </c>
       <c r="E394" t="n">
@@ -8893,10 +8809,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C395" s="2" t="n">
+      <c r="C395" s="5" t="n">
         <v>18675.56</v>
       </c>
-      <c r="D395" s="3" t="n">
+      <c r="D395" s="6" t="n">
         <v>5.96308598</v>
       </c>
       <c r="E395" t="n">
@@ -8914,10 +8830,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C396" s="2" t="n">
+      <c r="C396" s="5" t="n">
         <v>15011.7</v>
       </c>
-      <c r="D396" s="3" t="n">
+      <c r="D396" s="6" t="n">
         <v>4.79321947</v>
       </c>
       <c r="E396" t="n">
@@ -8935,10 +8851,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C397" s="2" t="n">
+      <c r="C397" s="5" t="n">
         <v>158704.71</v>
       </c>
-      <c r="D397" s="3" t="n">
+      <c r="D397" s="6" t="n">
         <v>50.67424116</v>
       </c>
       <c r="E397" t="n">
@@ -8956,10 +8872,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C398" s="2" t="n">
+      <c r="C398" s="5" t="n">
         <v>120794.19</v>
       </c>
-      <c r="D398" s="3" t="n">
+      <c r="D398" s="6" t="n">
         <v>38.56945339</v>
       </c>
       <c r="E398" t="n">
@@ -8977,10 +8893,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C399" s="2" t="n">
+      <c r="C399" s="5" t="n">
         <v>925.92</v>
       </c>
-      <c r="D399" s="3" t="n">
+      <c r="D399" s="6" t="n">
         <v>0.29872596</v>
       </c>
       <c r="E399" t="n">
@@ -8998,10 +8914,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C400" s="2" t="n">
+      <c r="C400" s="5" t="n">
         <v>2850.15</v>
       </c>
-      <c r="D400" s="3" t="n">
+      <c r="D400" s="6" t="n">
         <v>0.91953279</v>
       </c>
       <c r="E400" t="n">
@@ -9019,10 +8935,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C401" s="2" t="n">
+      <c r="C401" s="5" t="n">
         <v>6.62</v>
       </c>
-      <c r="D401" s="3" t="n">
+      <c r="D401" s="6" t="n">
         <v>0.00213578</v>
       </c>
       <c r="E401" t="n">
@@ -9040,10 +8956,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C402" s="2" t="n">
+      <c r="C402" s="5" t="n">
         <v>97008.50999999999</v>
       </c>
-      <c r="D402" s="3" t="n">
+      <c r="D402" s="6" t="n">
         <v>31.29747766</v>
       </c>
       <c r="E402" t="n">
@@ -9061,10 +8977,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C403" s="2" t="n">
+      <c r="C403" s="5" t="n">
         <v>209165.12</v>
       </c>
-      <c r="D403" s="3" t="n">
+      <c r="D403" s="6" t="n">
         <v>67.4821278</v>
       </c>
       <c r="E403" t="n">
@@ -9082,10 +8998,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C404" s="2" t="n">
+      <c r="C404" s="5" t="n">
         <v>1554.4</v>
       </c>
-      <c r="D404" s="3" t="n">
+      <c r="D404" s="6" t="n">
         <v>0.2805159</v>
       </c>
       <c r="E404" t="n">
@@ -9103,10 +9019,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C405" s="2" t="n">
+      <c r="C405" s="5" t="n">
         <v>13257.43</v>
       </c>
-      <c r="D405" s="3" t="n">
+      <c r="D405" s="6" t="n">
         <v>2.39251151</v>
       </c>
       <c r="E405" t="n">
@@ -9124,10 +9040,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C406" s="2" t="n">
+      <c r="C406" s="5" t="n">
         <v>68317.38</v>
       </c>
-      <c r="D406" s="3" t="n">
+      <c r="D406" s="6" t="n">
         <v>12.32894445</v>
       </c>
       <c r="E406" t="n">
@@ -9145,10 +9061,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C407" s="2" t="n">
+      <c r="C407" s="5" t="n">
         <v>36483.28</v>
       </c>
-      <c r="D407" s="3" t="n">
+      <c r="D407" s="6" t="n">
         <v>6.58398101</v>
       </c>
       <c r="E407" t="n">
@@ -9166,10 +9082,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C408" s="2" t="n">
+      <c r="C408" s="5" t="n">
         <v>434509.4</v>
       </c>
-      <c r="D408" s="3" t="n">
+      <c r="D408" s="6" t="n">
         <v>78.41404713</v>
       </c>
       <c r="E408" t="n">
@@ -9187,10 +9103,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C409" s="2" t="n">
+      <c r="C409" s="5" t="n">
         <v>84045.97</v>
       </c>
-      <c r="D409" s="3" t="n">
+      <c r="D409" s="6" t="n">
         <v>25.37763076</v>
       </c>
       <c r="E409" t="n">
@@ -9208,10 +9124,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C410" s="2" t="n">
+      <c r="C410" s="5" t="n">
         <v>3679.54</v>
       </c>
-      <c r="D410" s="3" t="n">
+      <c r="D410" s="6" t="n">
         <v>1.11103492</v>
       </c>
       <c r="E410" t="n">
@@ -9229,10 +9145,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C411" s="2" t="n">
+      <c r="C411" s="5" t="n">
         <v>1538.46</v>
       </c>
-      <c r="D411" s="3" t="n">
+      <c r="D411" s="6" t="n">
         <v>0.46453708</v>
       </c>
       <c r="E411" t="n">
@@ -9250,10 +9166,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C412" s="2" t="n">
+      <c r="C412" s="5" t="n">
         <v>26688.17</v>
       </c>
-      <c r="D412" s="3" t="n">
+      <c r="D412" s="6" t="n">
         <v>8.05847709</v>
       </c>
       <c r="E412" t="n">
@@ -9271,10 +9187,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C413" s="2" t="n">
+      <c r="C413" s="5" t="n">
         <v>215229.17</v>
       </c>
-      <c r="D413" s="3" t="n">
+      <c r="D413" s="6" t="n">
         <v>64.98832014</v>
       </c>
       <c r="E413" t="n">
@@ -9292,10 +9208,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C414" s="2" t="n">
+      <c r="C414" s="5" t="n">
         <v>6028.33</v>
       </c>
-      <c r="D414" s="3" t="n">
+      <c r="D414" s="6" t="n">
         <v>2.51184038</v>
       </c>
       <c r="E414" t="n">
@@ -9313,10 +9229,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="C415" s="2" t="n">
+      <c r="C415" s="5" t="n">
         <v>3112.84</v>
       </c>
-      <c r="D415" s="3" t="n">
+      <c r="D415" s="6" t="n">
         <v>1.29703537</v>
       </c>
       <c r="E415" t="n">
@@ -9334,10 +9250,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C416" s="2" t="n">
+      <c r="C416" s="5" t="n">
         <v>467.28</v>
       </c>
-      <c r="D416" s="3" t="n">
+      <c r="D416" s="6" t="n">
         <v>0.19470281</v>
       </c>
       <c r="E416" t="n">
@@ -9355,10 +9271,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C417" s="2" t="n">
+      <c r="C417" s="5" t="n">
         <v>2022.83</v>
       </c>
-      <c r="D417" s="3" t="n">
+      <c r="D417" s="6" t="n">
         <v>0.84285798</v>
       </c>
       <c r="E417" t="n">
@@ -9376,10 +9292,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C418" s="2" t="n">
+      <c r="C418" s="5" t="n">
         <v>25240.28</v>
       </c>
-      <c r="D418" s="3" t="n">
+      <c r="D418" s="6" t="n">
         <v>10.51693495</v>
       </c>
       <c r="E418" t="n">
@@ -9397,10 +9313,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C419" s="2" t="n">
+      <c r="C419" s="5" t="n">
         <v>203124.98</v>
       </c>
-      <c r="D419" s="3" t="n">
+      <c r="D419" s="6" t="n">
         <v>84.63662850999999</v>
       </c>
       <c r="E419" t="n">
@@ -9418,10 +9334,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C420" s="2" t="n">
+      <c r="C420" s="5" t="n">
         <v>4052.09</v>
       </c>
-      <c r="D420" s="3" t="n">
+      <c r="D420" s="6" t="n">
         <v>1.92281922</v>
       </c>
       <c r="E420" t="n">
@@ -9439,10 +9355,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="C421" s="2" t="n">
+      <c r="C421" s="5" t="n">
         <v>4783.33</v>
       </c>
-      <c r="D421" s="3" t="n">
+      <c r="D421" s="6" t="n">
         <v>2.2698111</v>
       </c>
       <c r="E421" t="n">
@@ -9460,10 +9376,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C422" s="2" t="n">
+      <c r="C422" s="5" t="n">
         <v>3694.66</v>
       </c>
-      <c r="D422" s="3" t="n">
+      <c r="D422" s="6" t="n">
         <v>1.75320964</v>
       </c>
       <c r="E422" t="n">
@@ -9481,10 +9397,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C423" s="2" t="n">
+      <c r="C423" s="5" t="n">
         <v>784.2</v>
       </c>
-      <c r="D423" s="3" t="n">
+      <c r="D423" s="6" t="n">
         <v>0.37212274</v>
       </c>
       <c r="E423" t="n">
@@ -9502,10 +9418,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C424" s="2" t="n">
+      <c r="C424" s="5" t="n">
         <v>36763.78</v>
       </c>
-      <c r="D424" s="3" t="n">
+      <c r="D424" s="6" t="n">
         <v>17.4453437</v>
       </c>
       <c r="E424" t="n">
@@ -9523,10 +9439,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C425" s="2" t="n">
+      <c r="C425" s="5" t="n">
         <v>160658.86</v>
       </c>
-      <c r="D425" s="3" t="n">
+      <c r="D425" s="6" t="n">
         <v>76.2366936</v>
       </c>
       <c r="E425" t="n">
@@ -9544,10 +9460,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C426" s="2" t="n">
+      <c r="C426" s="5" t="n">
         <v>632.91</v>
       </c>
-      <c r="D426" s="3" t="n">
+      <c r="D426" s="6" t="n">
         <v>0.28103066</v>
       </c>
       <c r="E426" t="n">
@@ -9565,10 +9481,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C427" s="2" t="n">
+      <c r="C427" s="5" t="n">
         <v>31634.55</v>
       </c>
-      <c r="D427" s="3" t="n">
+      <c r="D427" s="6" t="n">
         <v>14.04667104</v>
       </c>
       <c r="E427" t="n">
@@ -9586,10 +9502,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C428" s="2" t="n">
+      <c r="C428" s="5" t="n">
         <v>51.07</v>
       </c>
-      <c r="D428" s="3" t="n">
+      <c r="D428" s="6" t="n">
         <v>0.02267658</v>
       </c>
       <c r="E428" t="n">
@@ -9607,10 +9523,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C429" s="2" t="n">
+      <c r="C429" s="5" t="n">
         <v>8138.08</v>
       </c>
-      <c r="D429" s="3" t="n">
+      <c r="D429" s="6" t="n">
         <v>3.61354698</v>
       </c>
       <c r="E429" t="n">
@@ -9628,10 +9544,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C430" s="2" t="n">
+      <c r="C430" s="5" t="n">
         <v>184753.69</v>
       </c>
-      <c r="D430" s="3" t="n">
+      <c r="D430" s="6" t="n">
         <v>82.03607473</v>
       </c>
       <c r="E430" t="n">
@@ -9649,10 +9565,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C431" s="2" t="n">
+      <c r="C431" s="5" t="n">
         <v>370.37</v>
       </c>
-      <c r="D431" s="3" t="n">
+      <c r="D431" s="6" t="n">
         <v>0.12318944</v>
       </c>
       <c r="E431" t="n">
@@ -9670,10 +9586,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C432" s="2" t="n">
+      <c r="C432" s="5" t="n">
         <v>13374.33</v>
       </c>
-      <c r="D432" s="3" t="n">
+      <c r="D432" s="6" t="n">
         <v>4.44846025</v>
       </c>
       <c r="E432" t="n">
@@ -9691,10 +9607,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C433" s="2" t="n">
+      <c r="C433" s="5" t="n">
         <v>90262.50999999999</v>
       </c>
-      <c r="D433" s="3" t="n">
+      <c r="D433" s="6" t="n">
         <v>30.02237779</v>
       </c>
       <c r="E433" t="n">
@@ -9712,10 +9628,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C434" s="2" t="n">
+      <c r="C434" s="5" t="n">
         <v>196643.56</v>
       </c>
-      <c r="D434" s="3" t="n">
+      <c r="D434" s="6" t="n">
         <v>65.40597252000001</v>
       </c>
       <c r="E434" t="n">
@@ -9733,10 +9649,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C435" s="2" t="n">
+      <c r="C435" s="5" t="n">
         <v>24.5</v>
       </c>
-      <c r="D435" s="3" t="n">
+      <c r="D435" s="6" t="n">
         <v>0.00775989</v>
       </c>
       <c r="E435" t="n">
@@ -9754,10 +9670,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C436" s="2" t="n">
+      <c r="C436" s="5" t="n">
         <v>5137.53</v>
       </c>
-      <c r="D436" s="3" t="n">
+      <c r="D436" s="6" t="n">
         <v>1.62721069</v>
       </c>
       <c r="E436" t="n">
@@ -9775,10 +9691,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C437" s="2" t="n">
+      <c r="C437" s="5" t="n">
         <v>387.7</v>
       </c>
-      <c r="D437" s="3" t="n">
+      <c r="D437" s="6" t="n">
         <v>0.12279628</v>
       </c>
       <c r="E437" t="n">
@@ -9796,10 +9712,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C438" s="2" t="n">
+      <c r="C438" s="5" t="n">
         <v>69638.25999999999</v>
       </c>
-      <c r="D438" s="3" t="n">
+      <c r="D438" s="6" t="n">
         <v>22.05653716</v>
       </c>
       <c r="E438" t="n">
@@ -9817,10 +9733,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C439" s="2" t="n">
+      <c r="C439" s="5" t="n">
         <v>240538.18</v>
       </c>
-      <c r="D439" s="3" t="n">
+      <c r="D439" s="6" t="n">
         <v>76.18569598000001</v>
       </c>
       <c r="E439" t="n">
@@ -9838,10 +9754,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C440" s="2" t="n">
+      <c r="C440" s="5" t="n">
         <v>11292.41</v>
       </c>
-      <c r="D440" s="3" t="n">
+      <c r="D440" s="6" t="n">
         <v>5.00321928</v>
       </c>
       <c r="E440" t="n">
@@ -9859,10 +9775,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C441" s="2" t="n">
+      <c r="C441" s="5" t="n">
         <v>5806.79</v>
       </c>
-      <c r="D441" s="3" t="n">
+      <c r="D441" s="6" t="n">
         <v>2.57275849</v>
       </c>
       <c r="E441" t="n">
@@ -9880,10 +9796,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C442" s="2" t="n">
+      <c r="C442" s="5" t="n">
         <v>5227.27</v>
       </c>
-      <c r="D442" s="3" t="n">
+      <c r="D442" s="6" t="n">
         <v>2.31599615</v>
       </c>
       <c r="E442" t="n">
@@ -9901,10 +9817,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C443" s="2" t="n">
+      <c r="C443" s="5" t="n">
         <v>44798.68</v>
       </c>
-      <c r="D443" s="3" t="n">
+      <c r="D443" s="6" t="n">
         <v>19.84851943</v>
       </c>
       <c r="E443" t="n">
@@ -9922,10 +9838,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C444" s="2" t="n">
+      <c r="C444" s="5" t="n">
         <v>158577.73</v>
       </c>
-      <c r="D444" s="3" t="n">
+      <c r="D444" s="6" t="n">
         <v>70.25950666</v>
       </c>
       <c r="E444" t="n">
@@ -9943,10 +9859,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C445" s="2" t="n">
+      <c r="C445" s="5" t="n">
         <v>4.65</v>
       </c>
-      <c r="D445" s="3" t="n">
+      <c r="D445" s="6" t="n">
         <v>0.00087428</v>
       </c>
       <c r="E445" t="n">
@@ -9964,10 +9880,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C446" s="2" t="n">
+      <c r="C446" s="5" t="n">
         <v>27501.45</v>
       </c>
-      <c r="D446" s="3" t="n">
+      <c r="D446" s="6" t="n">
         <v>5.17072427</v>
       </c>
       <c r="E446" t="n">
@@ -9985,10 +9901,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C447" s="2" t="n">
+      <c r="C447" s="5" t="n">
         <v>162.95</v>
       </c>
-      <c r="D447" s="3" t="n">
+      <c r="D447" s="6" t="n">
         <v>0.03063728</v>
       </c>
       <c r="E447" t="n">
@@ -10006,10 +9922,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C448" s="2" t="n">
+      <c r="C448" s="5" t="n">
         <v>27839.02</v>
       </c>
-      <c r="D448" s="3" t="n">
+      <c r="D448" s="6" t="n">
         <v>5.23419298</v>
       </c>
       <c r="E448" t="n">
@@ -10027,10 +9943,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C449" s="2" t="n">
+      <c r="C449" s="5" t="n">
         <v>476360.36</v>
       </c>
-      <c r="D449" s="3" t="n">
+      <c r="D449" s="6" t="n">
         <v>89.5635712</v>
       </c>
       <c r="E449" t="n">
@@ -10048,10 +9964,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C450" s="2" t="n">
+      <c r="C450" s="5" t="n">
         <v>822.03</v>
       </c>
-      <c r="D450" s="3" t="n">
+      <c r="D450" s="6" t="n">
         <v>0.77226073</v>
       </c>
       <c r="E450" t="n">
@@ -10069,10 +9985,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C451" s="2" t="n">
+      <c r="C451" s="5" t="n">
         <v>1928.09</v>
       </c>
-      <c r="D451" s="3" t="n">
+      <c r="D451" s="6" t="n">
         <v>1.81135505</v>
       </c>
       <c r="E451" t="n">
@@ -10090,10 +10006,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C452" s="2" t="n">
+      <c r="C452" s="5" t="n">
         <v>19728.18</v>
       </c>
-      <c r="D452" s="3" t="n">
+      <c r="D452" s="6" t="n">
         <v>18.53375023</v>
       </c>
       <c r="E452" t="n">
@@ -10111,10 +10027,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C453" s="2" t="n">
+      <c r="C453" s="5" t="n">
         <v>83966.32000000001</v>
       </c>
-      <c r="D453" s="3" t="n">
+      <c r="D453" s="6" t="n">
         <v>78.88263399</v>
       </c>
       <c r="E453" t="n">
@@ -10132,10 +10048,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C454" s="2" t="n">
+      <c r="C454" s="5" t="n">
         <v>11929.86</v>
       </c>
-      <c r="D454" s="3" t="n">
+      <c r="D454" s="6" t="n">
         <v>17.33404491</v>
       </c>
       <c r="E454" t="n">
@@ -10153,10 +10069,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C455" s="2" t="n">
+      <c r="C455" s="5" t="n">
         <v>9020.1</v>
       </c>
-      <c r="D455" s="3" t="n">
+      <c r="D455" s="6" t="n">
         <v>13.1061738</v>
       </c>
       <c r="E455" t="n">
@@ -10174,10 +10090,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C456" s="2" t="n">
+      <c r="C456" s="5" t="n">
         <v>47873.33</v>
       </c>
-      <c r="D456" s="3" t="n">
+      <c r="D456" s="6" t="n">
         <v>69.55978129</v>
       </c>
       <c r="E456" t="n">
@@ -10195,10 +10111,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C457" s="2" t="n">
+      <c r="C457" s="5" t="n">
         <v>22.76</v>
       </c>
-      <c r="D457" s="3" t="n">
+      <c r="D457" s="6" t="n">
         <v>0.01502378</v>
       </c>
       <c r="E457" t="n">
@@ -10216,10 +10132,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C458" s="2" t="n">
+      <c r="C458" s="5" t="n">
         <v>9530.34</v>
       </c>
-      <c r="D458" s="3" t="n">
+      <c r="D458" s="6" t="n">
         <v>6.29093708</v>
       </c>
       <c r="E458" t="n">
@@ -10237,10 +10153,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C459" s="2" t="n">
+      <c r="C459" s="5" t="n">
         <v>10214.3</v>
       </c>
-      <c r="D459" s="3" t="n">
+      <c r="D459" s="6" t="n">
         <v>6.74241618</v>
       </c>
       <c r="E459" t="n">
@@ -10258,10 +10174,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C460" s="2" t="n">
+      <c r="C460" s="5" t="n">
         <v>27605.06</v>
       </c>
-      <c r="D460" s="3" t="n">
+      <c r="D460" s="6" t="n">
         <v>18.22198321</v>
       </c>
       <c r="E460" t="n">
@@ -10279,10 +10195,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C461" s="2" t="n">
+      <c r="C461" s="5" t="n">
         <v>104120.71</v>
       </c>
-      <c r="D461" s="3" t="n">
+      <c r="D461" s="6" t="n">
         <v>68.72963976</v>
       </c>
       <c r="E461" t="n">
@@ -10300,10 +10216,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="C462" s="2" t="n">
+      <c r="C462" s="5" t="n">
         <v>769.23</v>
       </c>
-      <c r="D462" s="3" t="n">
+      <c r="D462" s="6" t="n">
         <v>0.38771701</v>
       </c>
       <c r="E462" t="n">
@@ -10321,10 +10237,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C463" s="2" t="n">
+      <c r="C463" s="5" t="n">
         <v>521.15</v>
       </c>
-      <c r="D463" s="3" t="n">
+      <c r="D463" s="6" t="n">
         <v>0.2626766</v>
       </c>
       <c r="E463" t="n">
@@ -10342,10 +10258,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C464" s="2" t="n">
+      <c r="C464" s="5" t="n">
         <v>701.92</v>
       </c>
-      <c r="D464" s="3" t="n">
+      <c r="D464" s="6" t="n">
         <v>0.35379057</v>
       </c>
       <c r="E464" t="n">
@@ -10363,10 +10279,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C465" s="2" t="n">
+      <c r="C465" s="5" t="n">
         <v>45400.43</v>
       </c>
-      <c r="D465" s="3" t="n">
+      <c r="D465" s="6" t="n">
         <v>22.8832974</v>
       </c>
       <c r="E465" t="n">
@@ -10384,10 +10300,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C466" s="2" t="n">
+      <c r="C466" s="5" t="n">
         <v>151007.13</v>
       </c>
-      <c r="D466" s="3" t="n">
+      <c r="D466" s="6" t="n">
         <v>76.11251842999999</v>
       </c>
       <c r="E466" t="n">
@@ -10405,10 +10321,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C467" s="2" t="n">
+      <c r="C467" s="5" t="n">
         <v>16710.66</v>
       </c>
-      <c r="D467" s="3" t="n">
+      <c r="D467" s="6" t="n">
         <v>9.58302746</v>
       </c>
       <c r="E467" t="n">
@@ -10426,10 +10342,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C468" s="2" t="n">
+      <c r="C468" s="5" t="n">
         <v>294.11</v>
       </c>
-      <c r="D468" s="3" t="n">
+      <c r="D468" s="6" t="n">
         <v>0.16866265</v>
       </c>
       <c r="E468" t="n">
@@ -10447,10 +10363,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C469" s="2" t="n">
+      <c r="C469" s="5" t="n">
         <v>45149.15</v>
       </c>
-      <c r="D469" s="3" t="n">
+      <c r="D469" s="6" t="n">
         <v>25.89158922</v>
       </c>
       <c r="E469" t="n">
@@ -10468,10 +10384,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C470" s="2" t="n">
+      <c r="C470" s="5" t="n">
         <v>112223.75</v>
       </c>
-      <c r="D470" s="3" t="n">
+      <c r="D470" s="6" t="n">
         <v>64.35672067</v>
       </c>
       <c r="E470" t="n">

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -69,11 +69,11 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -477,24 +477,129 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-29</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>141354.61</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>80.28192092</v>
+      </c>
+      <c r="E2" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>29126.64</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>16.54238662</v>
+      </c>
+      <c r="E3" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>2884.61</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>1.63830548</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>2631.57</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>1.49459218</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>75.34999999999999</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0.0427948</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="4" t="n">
+      <c r="C7" s="5" t="n">
+        <v>176072.78</v>
+      </c>
+      <c r="D7" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>0</v>
+      <c r="E7" s="4" t="n">
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -508,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E470"/>
+  <dimension ref="A1:E475"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -556,10 +661,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C2" s="5" t="n">
+      <c r="C2" s="2" t="n">
         <v>948.86</v>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="D2" s="3" t="n">
         <v>0.19126904</v>
       </c>
       <c r="E2" t="n">
@@ -577,10 +682,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C3" s="5" t="n">
+      <c r="C3" s="2" t="n">
         <v>461123.2</v>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="3" t="n">
         <v>92.95216732</v>
       </c>
       <c r="E3" t="n">
@@ -598,10 +703,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="2" t="n">
         <v>333</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="3" t="n">
         <v>0.06712538</v>
       </c>
       <c r="E4" t="n">
@@ -619,10 +724,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="2" t="n">
         <v>33681.49</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="3" t="n">
         <v>6.78943825</v>
       </c>
       <c r="E5" t="n">
@@ -640,10 +745,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="2" t="n">
         <v>3947.95</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="3" t="n">
         <v>0.94921987</v>
       </c>
       <c r="E6" t="n">
@@ -661,10 +766,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="2" t="n">
         <v>316928.34</v>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="3" t="n">
         <v>76.20022474</v>
       </c>
       <c r="E7" t="n">
@@ -682,10 +787,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="2" t="n">
         <v>28879.81</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D8" s="3" t="n">
         <v>6.94367696</v>
       </c>
       <c r="E8" t="n">
@@ -703,10 +808,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="2" t="n">
         <v>66159.13</v>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="3" t="n">
         <v>15.90687843</v>
       </c>
       <c r="E9" t="n">
@@ -724,10 +829,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="2" t="n">
         <v>672.72</v>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="D10" s="3" t="n">
         <v>0.12167625</v>
       </c>
       <c r="E10" t="n">
@@ -745,10 +850,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="2" t="n">
         <v>506109.58</v>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D11" s="3" t="n">
         <v>91.54108388</v>
       </c>
       <c r="E11" t="n">
@@ -766,10 +871,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C12" s="2" t="n">
         <v>13144.61</v>
       </c>
-      <c r="D12" s="6" t="n">
+      <c r="D12" s="3" t="n">
         <v>2.37749273</v>
       </c>
       <c r="E12" t="n">
@@ -787,10 +892,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C13" s="2" t="n">
         <v>32950.07</v>
       </c>
-      <c r="D13" s="6" t="n">
+      <c r="D13" s="3" t="n">
         <v>5.95974714</v>
       </c>
       <c r="E13" t="n">
@@ -808,10 +913,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C14" s="5" t="n">
+      <c r="C14" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="3" t="n">
         <v>0.00340356</v>
       </c>
       <c r="E14" t="n">
@@ -829,10 +934,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C15" s="2" t="n">
         <v>3803.45</v>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D15" s="3" t="n">
         <v>1.43836189</v>
       </c>
       <c r="E15" t="n">
@@ -850,10 +955,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C16" s="5" t="n">
+      <c r="C16" s="2" t="n">
         <v>229609.87</v>
       </c>
-      <c r="D16" s="6" t="n">
+      <c r="D16" s="3" t="n">
         <v>86.83224112000001</v>
       </c>
       <c r="E16" t="n">
@@ -871,10 +976,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C17" s="5" t="n">
+      <c r="C17" s="2" t="n">
         <v>884.04</v>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="D17" s="3" t="n">
         <v>0.33432001</v>
       </c>
       <c r="E17" t="n">
@@ -892,10 +997,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C18" s="5" t="n">
+      <c r="C18" s="2" t="n">
         <v>30122.92</v>
       </c>
-      <c r="D18" s="6" t="n">
+      <c r="D18" s="3" t="n">
         <v>11.39167342</v>
       </c>
       <c r="E18" t="n">
@@ -913,10 +1018,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C19" s="5" t="n">
+      <c r="C19" s="2" t="n">
         <v>23268.18</v>
       </c>
-      <c r="D19" s="6" t="n">
+      <c r="D19" s="3" t="n">
         <v>4.17124226</v>
       </c>
       <c r="E19" t="n">
@@ -934,10 +1039,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C20" s="5" t="n">
+      <c r="C20" s="2" t="n">
         <v>451338.15</v>
       </c>
-      <c r="D20" s="6" t="n">
+      <c r="D20" s="3" t="n">
         <v>80.91052954</v>
       </c>
       <c r="E20" t="n">
@@ -955,10 +1060,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C21" s="5" t="n">
+      <c r="C21" s="2" t="n">
         <v>20229.42</v>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D21" s="3" t="n">
         <v>3.62648955</v>
       </c>
       <c r="E21" t="n">
@@ -976,10 +1081,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C22" s="5" t="n">
+      <c r="C22" s="2" t="n">
         <v>62988</v>
       </c>
-      <c r="D22" s="6" t="n">
+      <c r="D22" s="3" t="n">
         <v>11.29173865</v>
       </c>
       <c r="E22" t="n">
@@ -997,10 +1102,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C23" s="5" t="n">
+      <c r="C23" s="2" t="n">
         <v>103.09</v>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="D23" s="3" t="n">
         <v>0.02902112</v>
       </c>
       <c r="E23" t="n">
@@ -1018,10 +1123,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C24" s="5" t="n">
+      <c r="C24" s="2" t="n">
         <v>283.13</v>
       </c>
-      <c r="D24" s="6" t="n">
+      <c r="D24" s="3" t="n">
         <v>0.07970463</v>
       </c>
       <c r="E24" t="n">
@@ -1039,10 +1144,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C25" s="5" t="n">
+      <c r="C25" s="2" t="n">
         <v>341584.75</v>
       </c>
-      <c r="D25" s="6" t="n">
+      <c r="D25" s="3" t="n">
         <v>96.16036696</v>
       </c>
       <c r="E25" t="n">
@@ -1060,10 +1165,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C26" s="5" t="n">
+      <c r="C26" s="2" t="n">
         <v>13253.08</v>
       </c>
-      <c r="D26" s="6" t="n">
+      <c r="D26" s="3" t="n">
         <v>3.7309073</v>
       </c>
       <c r="E26" t="n">
@@ -1081,10 +1186,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C27" s="5" t="n">
+      <c r="C27" s="2" t="n">
         <v>366675.1</v>
       </c>
-      <c r="D27" s="6" t="n">
+      <c r="D27" s="3" t="n">
         <v>88.88052623</v>
       </c>
       <c r="E27" t="n">
@@ -1102,10 +1207,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C28" s="5" t="n">
+      <c r="C28" s="2" t="n">
         <v>10967.83</v>
       </c>
-      <c r="D28" s="6" t="n">
+      <c r="D28" s="3" t="n">
         <v>2.65855659</v>
       </c>
       <c r="E28" t="n">
@@ -1123,10 +1228,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C29" s="5" t="n">
+      <c r="C29" s="2" t="n">
         <v>34905.37</v>
       </c>
-      <c r="D29" s="6" t="n">
+      <c r="D29" s="3" t="n">
         <v>8.460917179999999</v>
       </c>
       <c r="E29" t="n">
@@ -1144,10 +1249,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C30" s="5" t="n">
+      <c r="C30" s="2" t="n">
         <v>431085.81</v>
       </c>
-      <c r="D30" s="6" t="n">
+      <c r="D30" s="3" t="n">
         <v>81.83421629999999</v>
       </c>
       <c r="E30" t="n">
@@ -1165,10 +1270,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C31" s="5" t="n">
+      <c r="C31" s="2" t="n">
         <v>1633.45</v>
       </c>
-      <c r="D31" s="6" t="n">
+      <c r="D31" s="3" t="n">
         <v>0.31008235</v>
       </c>
       <c r="E31" t="n">
@@ -1186,10 +1291,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C32" s="5" t="n">
+      <c r="C32" s="2" t="n">
         <v>94060.16</v>
       </c>
-      <c r="D32" s="6" t="n">
+      <c r="D32" s="3" t="n">
         <v>17.85570135</v>
       </c>
       <c r="E32" t="n">
@@ -1207,10 +1312,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C33" s="5" t="n">
+      <c r="C33" s="2" t="n">
         <v>321805.16</v>
       </c>
-      <c r="D33" s="6" t="n">
+      <c r="D33" s="3" t="n">
         <v>78.53984421</v>
       </c>
       <c r="E33" t="n">
@@ -1228,10 +1333,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C34" s="5" t="n">
+      <c r="C34" s="2" t="n">
         <v>81063.48</v>
       </c>
-      <c r="D34" s="6" t="n">
+      <c r="D34" s="3" t="n">
         <v>19.78437229</v>
       </c>
       <c r="E34" t="n">
@@ -1249,10 +1354,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C35" s="5" t="n">
+      <c r="C35" s="2" t="n">
         <v>6866.27</v>
       </c>
-      <c r="D35" s="6" t="n">
+      <c r="D35" s="3" t="n">
         <v>1.6757835</v>
       </c>
       <c r="E35" t="n">
@@ -1270,10 +1375,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C36" s="5" t="n">
+      <c r="C36" s="2" t="n">
         <v>352851.14</v>
       </c>
-      <c r="D36" s="6" t="n">
+      <c r="D36" s="3" t="n">
         <v>94.15474251000001</v>
       </c>
       <c r="E36" t="n">
@@ -1291,10 +1396,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C37" s="5" t="n">
+      <c r="C37" s="2" t="n">
         <v>576.49</v>
       </c>
-      <c r="D37" s="6" t="n">
+      <c r="D37" s="3" t="n">
         <v>0.1538305</v>
       </c>
       <c r="E37" t="n">
@@ -1312,10 +1417,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C38" s="5" t="n">
+      <c r="C38" s="2" t="n">
         <v>21329</v>
       </c>
-      <c r="D38" s="6" t="n">
+      <c r="D38" s="3" t="n">
         <v>5.69142699</v>
       </c>
       <c r="E38" t="n">
@@ -1333,10 +1438,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C39" s="5" t="n">
+      <c r="C39" s="2" t="n">
         <v>83.52</v>
       </c>
-      <c r="D39" s="6" t="n">
+      <c r="D39" s="3" t="n">
         <v>0.01466719</v>
       </c>
       <c r="E39" t="n">
@@ -1354,10 +1459,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C40" s="5" t="n">
+      <c r="C40" s="2" t="n">
         <v>509873.13</v>
       </c>
-      <c r="D40" s="6" t="n">
+      <c r="D40" s="3" t="n">
         <v>89.54027855</v>
       </c>
       <c r="E40" t="n">
@@ -1375,10 +1480,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C41" s="5" t="n">
+      <c r="C41" s="2" t="n">
         <v>8520.23</v>
       </c>
-      <c r="D41" s="6" t="n">
+      <c r="D41" s="3" t="n">
         <v>1.49626196</v>
       </c>
       <c r="E41" t="n">
@@ -1396,10 +1501,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C42" s="5" t="n">
+      <c r="C42" s="2" t="n">
         <v>50957.5</v>
       </c>
-      <c r="D42" s="6" t="n">
+      <c r="D42" s="3" t="n">
         <v>8.94879231</v>
       </c>
       <c r="E42" t="n">
@@ -1417,10 +1522,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C43" s="5" t="n">
+      <c r="C43" s="2" t="n">
         <v>9326.15</v>
       </c>
-      <c r="D43" s="6" t="n">
+      <c r="D43" s="3" t="n">
         <v>1.62650962</v>
       </c>
       <c r="E43" t="n">
@@ -1438,10 +1543,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C44" s="5" t="n">
+      <c r="C44" s="2" t="n">
         <v>510341.61</v>
       </c>
-      <c r="D44" s="6" t="n">
+      <c r="D44" s="3" t="n">
         <v>89.00516713</v>
       </c>
       <c r="E44" t="n">
@@ -1459,10 +1564,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C45" s="5" t="n">
+      <c r="C45" s="2" t="n">
         <v>2517.04</v>
       </c>
-      <c r="D45" s="6" t="n">
+      <c r="D45" s="3" t="n">
         <v>0.43897962</v>
       </c>
       <c r="E45" t="n">
@@ -1480,10 +1585,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C46" s="5" t="n">
+      <c r="C46" s="2" t="n">
         <v>51199.45</v>
       </c>
-      <c r="D46" s="6" t="n">
+      <c r="D46" s="3" t="n">
         <v>8.92934363</v>
       </c>
       <c r="E46" t="n">
@@ -1501,10 +1606,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="C47" s="5" t="n">
+      <c r="C47" s="2" t="n">
         <v>850</v>
       </c>
-      <c r="D47" s="6" t="n">
+      <c r="D47" s="3" t="n">
         <v>0.25302704</v>
       </c>
       <c r="E47" t="n">
@@ -1522,10 +1627,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C48" s="5" t="n">
+      <c r="C48" s="2" t="n">
         <v>1223.36</v>
       </c>
-      <c r="D48" s="6" t="n">
+      <c r="D48" s="3" t="n">
         <v>0.36416843</v>
       </c>
       <c r="E48" t="n">
@@ -1543,10 +1648,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C49" s="5" t="n">
+      <c r="C49" s="2" t="n">
         <v>270843.56</v>
       </c>
-      <c r="D49" s="6" t="n">
+      <c r="D49" s="3" t="n">
         <v>80.62440645</v>
       </c>
       <c r="E49" t="n">
@@ -1564,10 +1669,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C50" s="5" t="n">
+      <c r="C50" s="2" t="n">
         <v>612.64</v>
       </c>
-      <c r="D50" s="6" t="n">
+      <c r="D50" s="3" t="n">
         <v>0.18236999</v>
       </c>
       <c r="E50" t="n">
@@ -1585,10 +1690,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C51" s="5" t="n">
+      <c r="C51" s="2" t="n">
         <v>62402.91</v>
       </c>
-      <c r="D51" s="6" t="n">
+      <c r="D51" s="3" t="n">
         <v>18.57602809</v>
       </c>
       <c r="E51" t="n">
@@ -1606,10 +1711,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C52" s="5" t="n">
+      <c r="C52" s="2" t="n">
         <v>555930.41</v>
       </c>
-      <c r="D52" s="6" t="n">
+      <c r="D52" s="3" t="n">
         <v>91.1452503</v>
       </c>
       <c r="E52" t="n">
@@ -1627,10 +1732,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C53" s="5" t="n">
+      <c r="C53" s="2" t="n">
         <v>1590.9</v>
       </c>
-      <c r="D53" s="6" t="n">
+      <c r="D53" s="3" t="n">
         <v>0.26082937</v>
       </c>
       <c r="E53" t="n">
@@ -1648,10 +1753,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C54" s="5" t="n">
+      <c r="C54" s="2" t="n">
         <v>52417.67</v>
       </c>
-      <c r="D54" s="6" t="n">
+      <c r="D54" s="3" t="n">
         <v>8.59392033</v>
       </c>
       <c r="E54" t="n">
@@ -1669,10 +1774,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C55" s="5" t="n">
+      <c r="C55" s="2" t="n">
         <v>10.55</v>
       </c>
-      <c r="D55" s="6" t="n">
+      <c r="D55" s="3" t="n">
         <v>0.00287103</v>
       </c>
       <c r="E55" t="n">
@@ -1690,10 +1795,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C56" s="5" t="n">
+      <c r="C56" s="2" t="n">
         <v>319888.32</v>
       </c>
-      <c r="D56" s="6" t="n">
+      <c r="D56" s="3" t="n">
         <v>87.05305848</v>
       </c>
       <c r="E56" t="n">
@@ -1711,10 +1816,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C57" s="5" t="n">
+      <c r="C57" s="2" t="n">
         <v>1278.17</v>
       </c>
-      <c r="D57" s="6" t="n">
+      <c r="D57" s="3" t="n">
         <v>0.34783579</v>
       </c>
       <c r="E57" t="n">
@@ -1732,10 +1837,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C58" s="5" t="n">
+      <c r="C58" s="2" t="n">
         <v>46286.58</v>
       </c>
-      <c r="D58" s="6" t="n">
+      <c r="D58" s="3" t="n">
         <v>12.5962347</v>
       </c>
       <c r="E58" t="n">
@@ -1753,10 +1858,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C59" s="5" t="n">
+      <c r="C59" s="2" t="n">
         <v>354.29</v>
       </c>
-      <c r="D59" s="6" t="n">
+      <c r="D59" s="3" t="n">
         <v>0.1171275</v>
       </c>
       <c r="E59" t="n">
@@ -1774,10 +1879,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C60" s="5" t="n">
+      <c r="C60" s="2" t="n">
         <v>121.49</v>
       </c>
-      <c r="D60" s="6" t="n">
+      <c r="D60" s="3" t="n">
         <v>0.04016433</v>
       </c>
       <c r="E60" t="n">
@@ -1795,10 +1900,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C61" s="5" t="n">
+      <c r="C61" s="2" t="n">
         <v>264522.3</v>
       </c>
-      <c r="D61" s="6" t="n">
+      <c r="D61" s="3" t="n">
         <v>87.4504938</v>
       </c>
       <c r="E61" t="n">
@@ -1816,10 +1921,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C62" s="5" t="n">
+      <c r="C62" s="2" t="n">
         <v>1149.77</v>
       </c>
-      <c r="D62" s="6" t="n">
+      <c r="D62" s="3" t="n">
         <v>0.38011145</v>
       </c>
       <c r="E62" t="n">
@@ -1837,10 +1942,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C63" s="5" t="n">
+      <c r="C63" s="2" t="n">
         <v>36334.49</v>
       </c>
-      <c r="D63" s="6" t="n">
+      <c r="D63" s="3" t="n">
         <v>12.01210292</v>
       </c>
       <c r="E63" t="n">
@@ -1858,10 +1963,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C64" s="5" t="n">
+      <c r="C64" s="2" t="n">
         <v>4545.45</v>
       </c>
-      <c r="D64" s="6" t="n">
+      <c r="D64" s="3" t="n">
         <v>1.24043036</v>
       </c>
       <c r="E64" t="n">
@@ -1879,10 +1984,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C65" s="5" t="n">
+      <c r="C65" s="2" t="n">
         <v>874</v>
       </c>
-      <c r="D65" s="6" t="n">
+      <c r="D65" s="3" t="n">
         <v>0.23851019</v>
       </c>
       <c r="E65" t="n">
@@ -1900,10 +2005,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C66" s="5" t="n">
+      <c r="C66" s="2" t="n">
         <v>284866.12</v>
       </c>
-      <c r="D66" s="6" t="n">
+      <c r="D66" s="3" t="n">
         <v>77.73852608</v>
       </c>
       <c r="E66" t="n">
@@ -1921,10 +2026,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C67" s="5" t="n">
+      <c r="C67" s="2" t="n">
         <v>1590.95</v>
       </c>
-      <c r="D67" s="6" t="n">
+      <c r="D67" s="3" t="n">
         <v>0.43416222</v>
       </c>
       <c r="E67" t="n">
@@ -1942,10 +2047,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C68" s="5" t="n">
+      <c r="C68" s="2" t="n">
         <v>74564.85000000001</v>
       </c>
-      <c r="D68" s="6" t="n">
+      <c r="D68" s="3" t="n">
         <v>20.34837115</v>
       </c>
       <c r="E68" t="n">
@@ -1963,10 +2068,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C69" s="5" t="n">
+      <c r="C69" s="2" t="n">
         <v>442814.15</v>
       </c>
-      <c r="D69" s="6" t="n">
+      <c r="D69" s="3" t="n">
         <v>80.48822254</v>
       </c>
       <c r="E69" t="n">
@@ -1984,10 +2089,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C70" s="5" t="n">
+      <c r="C70" s="2" t="n">
         <v>914.39</v>
       </c>
-      <c r="D70" s="6" t="n">
+      <c r="D70" s="3" t="n">
         <v>0.16620432</v>
       </c>
       <c r="E70" t="n">
@@ -2005,10 +2110,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C71" s="5" t="n">
+      <c r="C71" s="2" t="n">
         <v>106431.64</v>
       </c>
-      <c r="D71" s="6" t="n">
+      <c r="D71" s="3" t="n">
         <v>19.34557314</v>
       </c>
       <c r="E71" t="n">
@@ -2026,10 +2131,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C72" s="5" t="n">
+      <c r="C72" s="2" t="n">
         <v>166</v>
       </c>
-      <c r="D72" s="6" t="n">
+      <c r="D72" s="3" t="n">
         <v>0.02878159</v>
       </c>
       <c r="E72" t="n">
@@ -2047,10 +2152,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C73" s="5" t="n">
+      <c r="C73" s="2" t="n">
         <v>81.83</v>
       </c>
-      <c r="D73" s="6" t="n">
+      <c r="D73" s="3" t="n">
         <v>0.01418794</v>
       </c>
       <c r="E73" t="n">
@@ -2068,10 +2173,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C74" s="5" t="n">
+      <c r="C74" s="2" t="n">
         <v>528120.33</v>
       </c>
-      <c r="D74" s="6" t="n">
+      <c r="D74" s="3" t="n">
         <v>91.56712743999999</v>
       </c>
       <c r="E74" t="n">
@@ -2089,10 +2194,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C75" s="5" t="n">
+      <c r="C75" s="2" t="n">
         <v>567.3200000000001</v>
       </c>
-      <c r="D75" s="6" t="n">
+      <c r="D75" s="3" t="n">
         <v>0.09836369</v>
       </c>
       <c r="E75" t="n">
@@ -2110,10 +2215,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C76" s="5" t="n">
+      <c r="C76" s="2" t="n">
         <v>47822.08</v>
       </c>
-      <c r="D76" s="6" t="n">
+      <c r="D76" s="3" t="n">
         <v>8.29153934</v>
       </c>
       <c r="E76" t="n">
@@ -2131,10 +2236,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C77" s="5" t="n">
+      <c r="C77" s="2" t="n">
         <v>2157.29</v>
       </c>
-      <c r="D77" s="6" t="n">
+      <c r="D77" s="3" t="n">
         <v>1.00708473</v>
       </c>
       <c r="E77" t="n">
@@ -2152,10 +2257,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C78" s="5" t="n">
+      <c r="C78" s="2" t="n">
         <v>177127.26</v>
       </c>
-      <c r="D78" s="6" t="n">
+      <c r="D78" s="3" t="n">
         <v>82.68807579999999</v>
       </c>
       <c r="E78" t="n">
@@ -2173,10 +2278,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C79" s="5" t="n">
+      <c r="C79" s="2" t="n">
         <v>826.1799999999999</v>
       </c>
-      <c r="D79" s="6" t="n">
+      <c r="D79" s="3" t="n">
         <v>0.38568448</v>
       </c>
       <c r="E79" t="n">
@@ -2194,10 +2299,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C80" s="5" t="n">
+      <c r="C80" s="2" t="n">
         <v>34100.64</v>
       </c>
-      <c r="D80" s="6" t="n">
+      <c r="D80" s="3" t="n">
         <v>15.91915499</v>
       </c>
       <c r="E80" t="n">
@@ -2215,10 +2320,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C81" s="5" t="n">
+      <c r="C81" s="2" t="n">
         <v>54.12</v>
       </c>
-      <c r="D81" s="6" t="n">
+      <c r="D81" s="3" t="n">
         <v>0.01747125</v>
       </c>
       <c r="E81" t="n">
@@ -2236,10 +2341,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C82" s="5" t="n">
+      <c r="C82" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="D82" s="6" t="n">
+      <c r="D82" s="3" t="n">
         <v>0.0213064</v>
       </c>
       <c r="E82" t="n">
@@ -2257,10 +2362,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C83" s="5" t="n">
+      <c r="C83" s="2" t="n">
         <v>21771.31</v>
       </c>
-      <c r="D83" s="6" t="n">
+      <c r="D83" s="3" t="n">
         <v>7.02830778</v>
       </c>
       <c r="E83" t="n">
@@ -2278,10 +2383,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C84" s="5" t="n">
+      <c r="C84" s="2" t="n">
         <v>214416.2</v>
       </c>
-      <c r="D84" s="6" t="n">
+      <c r="D84" s="3" t="n">
         <v>69.21875842999999</v>
       </c>
       <c r="E84" t="n">
@@ -2299,10 +2404,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C85" s="5" t="n">
+      <c r="C85" s="2" t="n">
         <v>9060.450000000001</v>
       </c>
-      <c r="D85" s="6" t="n">
+      <c r="D85" s="3" t="n">
         <v>2.92493338</v>
       </c>
       <c r="E85" t="n">
@@ -2320,10 +2425,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C86" s="5" t="n">
+      <c r="C86" s="2" t="n">
         <v>64397.95</v>
       </c>
-      <c r="D86" s="6" t="n">
+      <c r="D86" s="3" t="n">
         <v>20.78922276</v>
       </c>
       <c r="E86" t="n">
@@ -2341,10 +2446,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C87" s="5" t="n">
+      <c r="C87" s="2" t="n">
         <v>1067.9</v>
       </c>
-      <c r="D87" s="6" t="n">
+      <c r="D87" s="3" t="n">
         <v>0.29681338</v>
       </c>
       <c r="E87" t="n">
@@ -2362,10 +2467,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C88" s="5" t="n">
+      <c r="C88" s="2" t="n">
         <v>260988.37</v>
       </c>
-      <c r="D88" s="6" t="n">
+      <c r="D88" s="3" t="n">
         <v>72.53941456</v>
       </c>
       <c r="E88" t="n">
@@ -2383,10 +2488,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C89" s="5" t="n">
+      <c r="C89" s="2" t="n">
         <v>7522.28</v>
       </c>
-      <c r="D89" s="6" t="n">
+      <c r="D89" s="3" t="n">
         <v>2.09075135</v>
       </c>
       <c r="E89" t="n">
@@ -2404,10 +2509,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C90" s="5" t="n">
+      <c r="C90" s="2" t="n">
         <v>90209.81</v>
       </c>
-      <c r="D90" s="6" t="n">
+      <c r="D90" s="3" t="n">
         <v>25.07302071</v>
       </c>
       <c r="E90" t="n">
@@ -2425,10 +2530,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C91" s="5" t="n">
+      <c r="C91" s="2" t="n">
         <v>11124.49</v>
       </c>
-      <c r="D91" s="6" t="n">
+      <c r="D91" s="3" t="n">
         <v>3.35098295</v>
       </c>
       <c r="E91" t="n">
@@ -2446,10 +2551,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C92" s="5" t="n">
+      <c r="C92" s="2" t="n">
         <v>201888.41</v>
       </c>
-      <c r="D92" s="6" t="n">
+      <c r="D92" s="3" t="n">
         <v>60.81398972</v>
       </c>
       <c r="E92" t="n">
@@ -2467,10 +2572,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C93" s="5" t="n">
+      <c r="C93" s="2" t="n">
         <v>15503.87</v>
       </c>
-      <c r="D93" s="6" t="n">
+      <c r="D93" s="3" t="n">
         <v>4.67016502</v>
       </c>
       <c r="E93" t="n">
@@ -2488,10 +2593,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C94" s="5" t="n">
+      <c r="C94" s="2" t="n">
         <v>103460.15</v>
       </c>
-      <c r="D94" s="6" t="n">
+      <c r="D94" s="3" t="n">
         <v>31.1648623</v>
       </c>
       <c r="E94" t="n">
@@ -2509,10 +2614,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C95" s="5" t="n">
+      <c r="C95" s="2" t="n">
         <v>1029.41</v>
       </c>
-      <c r="D95" s="6" t="n">
+      <c r="D95" s="3" t="n">
         <v>0.31513536</v>
       </c>
       <c r="E95" t="n">
@@ -2530,10 +2635,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C96" s="5" t="n">
+      <c r="C96" s="2" t="n">
         <v>1848</v>
       </c>
-      <c r="D96" s="6" t="n">
+      <c r="D96" s="3" t="n">
         <v>0.56573196</v>
       </c>
       <c r="E96" t="n">
@@ -2551,10 +2656,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C97" s="5" t="n">
+      <c r="C97" s="2" t="n">
         <v>126297.98</v>
       </c>
-      <c r="D97" s="6" t="n">
+      <c r="D97" s="3" t="n">
         <v>38.66385499</v>
       </c>
       <c r="E97" t="n">
@@ -2572,10 +2677,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C98" s="5" t="n">
+      <c r="C98" s="2" t="n">
         <v>23680.09</v>
       </c>
-      <c r="D98" s="6" t="n">
+      <c r="D98" s="3" t="n">
         <v>7.24923364</v>
       </c>
       <c r="E98" t="n">
@@ -2593,10 +2698,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C99" s="5" t="n">
+      <c r="C99" s="2" t="n">
         <v>173800.98</v>
       </c>
-      <c r="D99" s="6" t="n">
+      <c r="D99" s="3" t="n">
         <v>53.20604405</v>
       </c>
       <c r="E99" t="n">
@@ -2614,10 +2719,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C100" s="5" t="n">
+      <c r="C100" s="2" t="n">
         <v>856.11</v>
       </c>
-      <c r="D100" s="6" t="n">
+      <c r="D100" s="3" t="n">
         <v>0.22747196</v>
       </c>
       <c r="E100" t="n">
@@ -2635,10 +2740,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C101" s="5" t="n">
+      <c r="C101" s="2" t="n">
         <v>9.68</v>
       </c>
-      <c r="D101" s="6" t="n">
+      <c r="D101" s="3" t="n">
         <v>0.00257202</v>
       </c>
       <c r="E101" t="n">
@@ -2656,10 +2761,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C102" s="5" t="n">
+      <c r="C102" s="2" t="n">
         <v>296012.79</v>
       </c>
-      <c r="D102" s="6" t="n">
+      <c r="D102" s="3" t="n">
         <v>78.65181887</v>
       </c>
       <c r="E102" t="n">
@@ -2677,10 +2782,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C103" s="5" t="n">
+      <c r="C103" s="2" t="n">
         <v>3709.15</v>
       </c>
-      <c r="D103" s="6" t="n">
+      <c r="D103" s="3" t="n">
         <v>0.98553645</v>
       </c>
       <c r="E103" t="n">
@@ -2698,10 +2803,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C104" s="5" t="n">
+      <c r="C104" s="2" t="n">
         <v>75770.75</v>
       </c>
-      <c r="D104" s="6" t="n">
+      <c r="D104" s="3" t="n">
         <v>20.13260071</v>
       </c>
       <c r="E104" t="n">
@@ -2719,10 +2824,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C105" s="5" t="n">
+      <c r="C105" s="2" t="n">
         <v>363.62</v>
       </c>
-      <c r="D105" s="6" t="n">
+      <c r="D105" s="3" t="n">
         <v>0.09792976</v>
       </c>
       <c r="E105" t="n">
@@ -2740,10 +2845,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C106" s="5" t="n">
+      <c r="C106" s="2" t="n">
         <v>303265.05</v>
       </c>
-      <c r="D106" s="6" t="n">
+      <c r="D106" s="3" t="n">
         <v>81.67502655</v>
       </c>
       <c r="E106" t="n">
@@ -2761,10 +2866,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C107" s="5" t="n">
+      <c r="C107" s="2" t="n">
         <v>829.42</v>
       </c>
-      <c r="D107" s="6" t="n">
+      <c r="D107" s="3" t="n">
         <v>0.22337853</v>
       </c>
       <c r="E107" t="n">
@@ -2782,10 +2887,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C108" s="5" t="n">
+      <c r="C108" s="2" t="n">
         <v>66848.86</v>
       </c>
-      <c r="D108" s="6" t="n">
+      <c r="D108" s="3" t="n">
         <v>18.00366516</v>
       </c>
       <c r="E108" t="n">
@@ -2803,10 +2908,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C109" s="5" t="n">
+      <c r="C109" s="2" t="n">
         <v>174192.16</v>
       </c>
-      <c r="D109" s="6" t="n">
+      <c r="D109" s="3" t="n">
         <v>66.86566559000001</v>
       </c>
       <c r="E109" t="n">
@@ -2824,10 +2929,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C110" s="5" t="n">
+      <c r="C110" s="2" t="n">
         <v>19438.25</v>
       </c>
-      <c r="D110" s="6" t="n">
+      <c r="D110" s="3" t="n">
         <v>7.461596</v>
       </c>
       <c r="E110" t="n">
@@ -2845,10 +2950,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C111" s="5" t="n">
+      <c r="C111" s="2" t="n">
         <v>66880.21000000001</v>
       </c>
-      <c r="D111" s="6" t="n">
+      <c r="D111" s="3" t="n">
         <v>25.67273841</v>
       </c>
       <c r="E111" t="n">
@@ -2866,10 +2971,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C112" s="5" t="n">
+      <c r="C112" s="2" t="n">
         <v>1885.29</v>
       </c>
-      <c r="D112" s="6" t="n">
+      <c r="D112" s="3" t="n">
         <v>0.5105483200000001</v>
       </c>
       <c r="E112" t="n">
@@ -2887,10 +2992,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C113" s="5" t="n">
+      <c r="C113" s="2" t="n">
         <v>642.63</v>
       </c>
-      <c r="D113" s="6" t="n">
+      <c r="D113" s="3" t="n">
         <v>0.17402822</v>
       </c>
       <c r="E113" t="n">
@@ -2908,10 +3013,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C114" s="5" t="n">
+      <c r="C114" s="2" t="n">
         <v>2177.75</v>
       </c>
-      <c r="D114" s="6" t="n">
+      <c r="D114" s="3" t="n">
         <v>0.58974832</v>
       </c>
       <c r="E114" t="n">
@@ -2929,10 +3034,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C115" s="5" t="n">
+      <c r="C115" s="2" t="n">
         <v>202289.9</v>
       </c>
-      <c r="D115" s="6" t="n">
+      <c r="D115" s="3" t="n">
         <v>54.78137012</v>
       </c>
       <c r="E115" t="n">
@@ -2950,10 +3055,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C116" s="5" t="n">
+      <c r="C116" s="2" t="n">
         <v>30328.46</v>
       </c>
-      <c r="D116" s="6" t="n">
+      <c r="D116" s="3" t="n">
         <v>8.213136649999999</v>
       </c>
       <c r="E116" t="n">
@@ -2971,10 +3076,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C117" s="5" t="n">
+      <c r="C117" s="2" t="n">
         <v>131943.66</v>
       </c>
-      <c r="D117" s="6" t="n">
+      <c r="D117" s="3" t="n">
         <v>35.73116836</v>
       </c>
       <c r="E117" t="n">
@@ -2992,10 +3097,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C118" s="5" t="n">
+      <c r="C118" s="2" t="n">
         <v>101.72</v>
       </c>
-      <c r="D118" s="6" t="n">
+      <c r="D118" s="3" t="n">
         <v>0.03804713</v>
       </c>
       <c r="E118" t="n">
@@ -3013,10 +3118,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C119" s="5" t="n">
+      <c r="C119" s="2" t="n">
         <v>58</v>
       </c>
-      <c r="D119" s="6" t="n">
+      <c r="D119" s="3" t="n">
         <v>0.02169419</v>
       </c>
       <c r="E119" t="n">
@@ -3034,10 +3139,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C120" s="5" t="n">
+      <c r="C120" s="2" t="n">
         <v>167439.3</v>
       </c>
-      <c r="D120" s="6" t="n">
+      <c r="D120" s="3" t="n">
         <v>62.62863161</v>
       </c>
       <c r="E120" t="n">
@@ -3055,10 +3160,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C121" s="5" t="n">
+      <c r="C121" s="2" t="n">
         <v>7300.3</v>
       </c>
-      <c r="D121" s="6" t="n">
+      <c r="D121" s="3" t="n">
         <v>2.73058833</v>
       </c>
       <c r="E121" t="n">
@@ -3076,10 +3181,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C122" s="5" t="n">
+      <c r="C122" s="2" t="n">
         <v>92453.32000000001</v>
       </c>
-      <c r="D122" s="6" t="n">
+      <c r="D122" s="3" t="n">
         <v>34.58103874</v>
       </c>
       <c r="E122" t="n">
@@ -3097,10 +3202,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C123" s="5" t="n">
+      <c r="C123" s="2" t="n">
         <v>1475.74</v>
       </c>
-      <c r="D123" s="6" t="n">
+      <c r="D123" s="3" t="n">
         <v>0.33417908</v>
       </c>
       <c r="E123" t="n">
@@ -3118,10 +3223,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C124" s="5" t="n">
+      <c r="C124" s="2" t="n">
         <v>2209.05</v>
       </c>
-      <c r="D124" s="6" t="n">
+      <c r="D124" s="3" t="n">
         <v>0.50023602</v>
       </c>
       <c r="E124" t="n">
@@ -3139,10 +3244,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C125" s="5" t="n">
+      <c r="C125" s="2" t="n">
         <v>232354.93</v>
       </c>
-      <c r="D125" s="6" t="n">
+      <c r="D125" s="3" t="n">
         <v>52.61642084</v>
       </c>
       <c r="E125" t="n">
@@ -3160,10 +3265,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C126" s="5" t="n">
+      <c r="C126" s="2" t="n">
         <v>11084.31</v>
       </c>
-      <c r="D126" s="6" t="n">
+      <c r="D126" s="3" t="n">
         <v>2.51002516</v>
       </c>
       <c r="E126" t="n">
@@ -3181,10 +3286,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C127" s="5" t="n">
+      <c r="C127" s="2" t="n">
         <v>194477.52</v>
       </c>
-      <c r="D127" s="6" t="n">
+      <c r="D127" s="3" t="n">
         <v>44.0391389</v>
       </c>
       <c r="E127" t="n">
@@ -3202,10 +3307,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C128" s="5" t="n">
+      <c r="C128" s="2" t="n">
         <v>2990.78</v>
       </c>
-      <c r="D128" s="6" t="n">
+      <c r="D128" s="3" t="n">
         <v>0.63513389</v>
       </c>
       <c r="E128" t="n">
@@ -3223,10 +3328,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C129" s="5" t="n">
+      <c r="C129" s="2" t="n">
         <v>847.45</v>
       </c>
-      <c r="D129" s="6" t="n">
+      <c r="D129" s="3" t="n">
         <v>0.17996784</v>
       </c>
       <c r="E129" t="n">
@@ -3244,10 +3349,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C130" s="5" t="n">
+      <c r="C130" s="2" t="n">
         <v>211.86</v>
       </c>
-      <c r="D130" s="6" t="n">
+      <c r="D130" s="3" t="n">
         <v>0.04499143</v>
       </c>
       <c r="E130" t="n">
@@ -3265,10 +3370,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C131" s="5" t="n">
+      <c r="C131" s="2" t="n">
         <v>222684.94</v>
       </c>
-      <c r="D131" s="6" t="n">
+      <c r="D131" s="3" t="n">
         <v>47.29025603</v>
       </c>
       <c r="E131" t="n">
@@ -3286,10 +3391,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C132" s="5" t="n">
+      <c r="C132" s="2" t="n">
         <v>10642.51</v>
       </c>
-      <c r="D132" s="6" t="n">
+      <c r="D132" s="3" t="n">
         <v>2.26008558</v>
       </c>
       <c r="E132" t="n">
@@ -3307,10 +3412,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C133" s="5" t="n">
+      <c r="C133" s="2" t="n">
         <v>233512.15</v>
       </c>
-      <c r="D133" s="6" t="n">
+      <c r="D133" s="3" t="n">
         <v>49.58956523</v>
       </c>
       <c r="E133" t="n">
@@ -3328,10 +3433,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C134" s="5" t="n">
+      <c r="C134" s="2" t="n">
         <v>2894.67</v>
       </c>
-      <c r="D134" s="6" t="n">
+      <c r="D134" s="3" t="n">
         <v>0.84868485</v>
       </c>
       <c r="E134" t="n">
@@ -3349,10 +3454,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C135" s="5" t="n">
+      <c r="C135" s="2" t="n">
         <v>2112.75</v>
       </c>
-      <c r="D135" s="6" t="n">
+      <c r="D135" s="3" t="n">
         <v>0.61943465</v>
       </c>
       <c r="E135" t="n">
@@ -3370,10 +3475,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C136" s="5" t="n">
+      <c r="C136" s="2" t="n">
         <v>133738.48</v>
       </c>
-      <c r="D136" s="6" t="n">
+      <c r="D136" s="3" t="n">
         <v>39.21062549</v>
       </c>
       <c r="E136" t="n">
@@ -3391,10 +3496,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C137" s="5" t="n">
+      <c r="C137" s="2" t="n">
         <v>9278.84</v>
       </c>
-      <c r="D137" s="6" t="n">
+      <c r="D137" s="3" t="n">
         <v>2.72045204</v>
       </c>
       <c r="E137" t="n">
@@ -3412,10 +3517,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C138" s="5" t="n">
+      <c r="C138" s="2" t="n">
         <v>193052.4</v>
       </c>
-      <c r="D138" s="6" t="n">
+      <c r="D138" s="3" t="n">
         <v>56.60080297</v>
       </c>
       <c r="E138" t="n">
@@ -3433,10 +3538,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C139" s="5" t="n">
+      <c r="C139" s="2" t="n">
         <v>138.16</v>
       </c>
-      <c r="D139" s="6" t="n">
+      <c r="D139" s="3" t="n">
         <v>0.04037037</v>
       </c>
       <c r="E139" t="n">
@@ -3454,10 +3559,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C140" s="5" t="n">
+      <c r="C140" s="2" t="n">
         <v>165616.96</v>
       </c>
-      <c r="D140" s="6" t="n">
+      <c r="D140" s="3" t="n">
         <v>48.39329811</v>
       </c>
       <c r="E140" t="n">
@@ -3475,10 +3580,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C141" s="5" t="n">
+      <c r="C141" s="2" t="n">
         <v>14589.85</v>
       </c>
-      <c r="D141" s="6" t="n">
+      <c r="D141" s="3" t="n">
         <v>4.26315614</v>
       </c>
       <c r="E141" t="n">
@@ -3496,10 +3601,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C142" s="5" t="n">
+      <c r="C142" s="2" t="n">
         <v>161886.22</v>
       </c>
-      <c r="D142" s="6" t="n">
+      <c r="D142" s="3" t="n">
         <v>47.30317538</v>
       </c>
       <c r="E142" t="n">
@@ -3517,10 +3622,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C143" s="5" t="n">
+      <c r="C143" s="2" t="n">
         <v>39179.97</v>
       </c>
-      <c r="D143" s="6" t="n">
+      <c r="D143" s="3" t="n">
         <v>6.57522763</v>
       </c>
       <c r="E143" t="n">
@@ -3538,10 +3643,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C144" s="5" t="n">
+      <c r="C144" s="2" t="n">
         <v>142325.87</v>
       </c>
-      <c r="D144" s="6" t="n">
+      <c r="D144" s="3" t="n">
         <v>23.88529122</v>
       </c>
       <c r="E144" t="n">
@@ -3559,10 +3664,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C145" s="5" t="n">
+      <c r="C145" s="2" t="n">
         <v>16620.71</v>
       </c>
-      <c r="D145" s="6" t="n">
+      <c r="D145" s="3" t="n">
         <v>2.78930667</v>
       </c>
       <c r="E145" t="n">
@@ -3580,10 +3685,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C146" s="5" t="n">
+      <c r="C146" s="2" t="n">
         <v>397745.9</v>
       </c>
-      <c r="D146" s="6" t="n">
+      <c r="D146" s="3" t="n">
         <v>66.75017447</v>
       </c>
       <c r="E146" t="n">
@@ -3601,10 +3706,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C147" s="5" t="n">
+      <c r="C147" s="2" t="n">
         <v>1244.23</v>
       </c>
-      <c r="D147" s="6" t="n">
+      <c r="D147" s="3" t="n">
         <v>0.42616348</v>
       </c>
       <c r="E147" t="n">
@@ -3622,10 +3727,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C148" s="5" t="n">
+      <c r="C148" s="2" t="n">
         <v>4545.45</v>
       </c>
-      <c r="D148" s="6" t="n">
+      <c r="D148" s="3" t="n">
         <v>1.55687034</v>
       </c>
       <c r="E148" t="n">
@@ -3643,10 +3748,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C149" s="5" t="n">
+      <c r="C149" s="2" t="n">
         <v>54421.47</v>
       </c>
-      <c r="D149" s="6" t="n">
+      <c r="D149" s="3" t="n">
         <v>18.63999655</v>
       </c>
       <c r="E149" t="n">
@@ -3664,10 +3769,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C150" s="5" t="n">
+      <c r="C150" s="2" t="n">
         <v>231749.58</v>
       </c>
-      <c r="D150" s="6" t="n">
+      <c r="D150" s="3" t="n">
         <v>79.37696964</v>
       </c>
       <c r="E150" t="n">
@@ -3685,10 +3790,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C151" s="5" t="n">
+      <c r="C151" s="2" t="n">
         <v>29.6</v>
       </c>
-      <c r="D151" s="6" t="n">
+      <c r="D151" s="3" t="n">
         <v>0.00689719</v>
       </c>
       <c r="E151" t="n">
@@ -3706,10 +3811,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C152" s="5" t="n">
+      <c r="C152" s="2" t="n">
         <v>309.27</v>
       </c>
-      <c r="D152" s="6" t="n">
+      <c r="D152" s="3" t="n">
         <v>0.07206398</v>
       </c>
       <c r="E152" t="n">
@@ -3727,10 +3832,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C153" s="5" t="n">
+      <c r="C153" s="2" t="n">
         <v>3725.16</v>
       </c>
-      <c r="D153" s="6" t="n">
+      <c r="D153" s="3" t="n">
         <v>0.8680113</v>
       </c>
       <c r="E153" t="n">
@@ -3748,10 +3853,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C154" s="5" t="n">
+      <c r="C154" s="2" t="n">
         <v>8.109999999999999</v>
       </c>
-      <c r="D154" s="6" t="n">
+      <c r="D154" s="3" t="n">
         <v>0.00188974</v>
       </c>
       <c r="E154" t="n">
@@ -3769,10 +3874,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C155" s="5" t="n">
+      <c r="C155" s="2" t="n">
         <v>163136.27</v>
       </c>
-      <c r="D155" s="6" t="n">
+      <c r="D155" s="3" t="n">
         <v>38.01289779</v>
       </c>
       <c r="E155" t="n">
@@ -3790,10 +3895,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C156" s="5" t="n">
+      <c r="C156" s="2" t="n">
         <v>261951.9</v>
       </c>
-      <c r="D156" s="6" t="n">
+      <c r="D156" s="3" t="n">
         <v>61.03824</v>
       </c>
       <c r="E156" t="n">
@@ -3811,10 +3916,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C157" s="5" t="n">
+      <c r="C157" s="2" t="n">
         <v>55.55</v>
       </c>
-      <c r="D157" s="6" t="n">
+      <c r="D157" s="3" t="n">
         <v>0.01644298</v>
       </c>
       <c r="E157" t="n">
@@ -3832,10 +3937,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C158" s="5" t="n">
+      <c r="C158" s="2" t="n">
         <v>91.41</v>
       </c>
-      <c r="D158" s="6" t="n">
+      <c r="D158" s="3" t="n">
         <v>0.02705766</v>
       </c>
       <c r="E158" t="n">
@@ -3853,10 +3958,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C159" s="5" t="n">
+      <c r="C159" s="2" t="n">
         <v>5382.13</v>
       </c>
-      <c r="D159" s="6" t="n">
+      <c r="D159" s="3" t="n">
         <v>1.59312834</v>
       </c>
       <c r="E159" t="n">
@@ -3874,10 +3979,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C160" s="5" t="n">
+      <c r="C160" s="2" t="n">
         <v>909.09</v>
       </c>
-      <c r="D160" s="6" t="n">
+      <c r="D160" s="3" t="n">
         <v>0.26909366</v>
       </c>
       <c r="E160" t="n">
@@ -3895,10 +4000,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C161" s="5" t="n">
+      <c r="C161" s="2" t="n">
         <v>32670.17</v>
       </c>
-      <c r="D161" s="6" t="n">
+      <c r="D161" s="3" t="n">
         <v>9.670478749999999</v>
       </c>
       <c r="E161" t="n">
@@ -3916,10 +4021,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C162" s="5" t="n">
+      <c r="C162" s="2" t="n">
         <v>298725.7</v>
       </c>
-      <c r="D162" s="6" t="n">
+      <c r="D162" s="3" t="n">
         <v>88.42379861000001</v>
       </c>
       <c r="E162" t="n">
@@ -3937,10 +4042,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C163" s="5" t="n">
+      <c r="C163" s="2" t="n">
         <v>287.66</v>
       </c>
-      <c r="D163" s="6" t="n">
+      <c r="D163" s="3" t="n">
         <v>0.08204844999999999</v>
       </c>
       <c r="E163" t="n">
@@ -3958,10 +4063,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C164" s="5" t="n">
+      <c r="C164" s="2" t="n">
         <v>9919.66</v>
       </c>
-      <c r="D164" s="6" t="n">
+      <c r="D164" s="3" t="n">
         <v>2.82935676</v>
       </c>
       <c r="E164" t="n">
@@ -3979,10 +4084,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C165" s="5" t="n">
+      <c r="C165" s="2" t="n">
         <v>1385.01</v>
       </c>
-      <c r="D165" s="6" t="n">
+      <c r="D165" s="3" t="n">
         <v>0.39504251</v>
       </c>
       <c r="E165" t="n">
@@ -4000,10 +4105,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C166" s="5" t="n">
+      <c r="C166" s="2" t="n">
         <v>69940.2</v>
       </c>
-      <c r="D166" s="6" t="n">
+      <c r="D166" s="3" t="n">
         <v>19.94884679</v>
       </c>
       <c r="E166" t="n">
@@ -4021,10 +4126,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C167" s="5" t="n">
+      <c r="C167" s="2" t="n">
         <v>269065.18</v>
       </c>
-      <c r="D167" s="6" t="n">
+      <c r="D167" s="3" t="n">
         <v>76.74470549</v>
       </c>
       <c r="E167" t="n">
@@ -4042,10 +4147,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C168" s="5" t="n">
+      <c r="C168" s="2" t="n">
         <v>580.2</v>
       </c>
-      <c r="D168" s="6" t="n">
+      <c r="D168" s="3" t="n">
         <v>0.1561468</v>
       </c>
       <c r="E168" t="n">
@@ -4063,10 +4168,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C169" s="5" t="n">
+      <c r="C169" s="2" t="n">
         <v>98.44</v>
       </c>
-      <c r="D169" s="6" t="n">
+      <c r="D169" s="3" t="n">
         <v>0.02649275</v>
       </c>
       <c r="E169" t="n">
@@ -4084,10 +4189,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C170" s="5" t="n">
+      <c r="C170" s="2" t="n">
         <v>172.72</v>
       </c>
-      <c r="D170" s="6" t="n">
+      <c r="D170" s="3" t="n">
         <v>0.04648341</v>
       </c>
       <c r="E170" t="n">
@@ -4105,10 +4210,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C171" s="5" t="n">
+      <c r="C171" s="2" t="n">
         <v>3342.15</v>
       </c>
-      <c r="D171" s="6" t="n">
+      <c r="D171" s="3" t="n">
         <v>0.89945887</v>
       </c>
       <c r="E171" t="n">
@@ -4126,10 +4231,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C172" s="5" t="n">
+      <c r="C172" s="2" t="n">
         <v>7627.33</v>
       </c>
-      <c r="D172" s="6" t="n">
+      <c r="D172" s="3" t="n">
         <v>2.05271147</v>
       </c>
       <c r="E172" t="n">
@@ -4147,10 +4252,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C173" s="5" t="n">
+      <c r="C173" s="2" t="n">
         <v>359752.57</v>
       </c>
-      <c r="D173" s="6" t="n">
+      <c r="D173" s="3" t="n">
         <v>96.81870670000001</v>
       </c>
       <c r="E173" t="n">
@@ -4168,10 +4273,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C174" s="5" t="n">
+      <c r="C174" s="2" t="n">
         <v>61.94</v>
       </c>
-      <c r="D174" s="6" t="n">
+      <c r="D174" s="3" t="n">
         <v>0.02167129</v>
       </c>
       <c r="E174" t="n">
@@ -4189,10 +4294,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C175" s="5" t="n">
+      <c r="C175" s="2" t="n">
         <v>222</v>
       </c>
-      <c r="D175" s="6" t="n">
+      <c r="D175" s="3" t="n">
         <v>0.07767236</v>
       </c>
       <c r="E175" t="n">
@@ -4210,10 +4315,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C176" s="5" t="n">
+      <c r="C176" s="2" t="n">
         <v>10426.45</v>
       </c>
-      <c r="D176" s="6" t="n">
+      <c r="D176" s="3" t="n">
         <v>3.64795946</v>
       </c>
       <c r="E176" t="n">
@@ -4231,10 +4336,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C177" s="5" t="n">
+      <c r="C177" s="2" t="n">
         <v>36051.27</v>
       </c>
-      <c r="D177" s="6" t="n">
+      <c r="D177" s="3" t="n">
         <v>12.61345632</v>
       </c>
       <c r="E177" t="n">
@@ -4252,10 +4357,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C178" s="5" t="n">
+      <c r="C178" s="2" t="n">
         <v>239054.29</v>
       </c>
-      <c r="D178" s="6" t="n">
+      <c r="D178" s="3" t="n">
         <v>83.63924057</v>
       </c>
       <c r="E178" t="n">
@@ -4273,10 +4378,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C179" s="5" t="n">
+      <c r="C179" s="2" t="n">
         <v>1971.96</v>
       </c>
-      <c r="D179" s="6" t="n">
+      <c r="D179" s="3" t="n">
         <v>0.29536296</v>
       </c>
       <c r="E179" t="n">
@@ -4294,10 +4399,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C180" s="5" t="n">
+      <c r="C180" s="2" t="n">
         <v>970.1799999999999</v>
       </c>
-      <c r="D180" s="6" t="n">
+      <c r="D180" s="3" t="n">
         <v>0.14531493</v>
       </c>
       <c r="E180" t="n">
@@ -4315,10 +4420,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C181" s="5" t="n">
+      <c r="C181" s="2" t="n">
         <v>23400.38</v>
       </c>
-      <c r="D181" s="6" t="n">
+      <c r="D181" s="3" t="n">
         <v>3.50494199</v>
       </c>
       <c r="E181" t="n">
@@ -4336,10 +4441,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C182" s="5" t="n">
+      <c r="C182" s="2" t="n">
         <v>158698.51</v>
       </c>
-      <c r="D182" s="6" t="n">
+      <c r="D182" s="3" t="n">
         <v>23.77008715</v>
       </c>
       <c r="E182" t="n">
@@ -4357,10 +4462,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C183" s="5" t="n">
+      <c r="C183" s="2" t="n">
         <v>482598.55</v>
       </c>
-      <c r="D183" s="6" t="n">
+      <c r="D183" s="3" t="n">
         <v>72.28429297</v>
       </c>
       <c r="E183" t="n">
@@ -4378,10 +4483,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C184" s="5" t="n">
+      <c r="C184" s="2" t="n">
         <v>349.42</v>
       </c>
-      <c r="D184" s="6" t="n">
+      <c r="D184" s="3" t="n">
         <v>0.0757804</v>
       </c>
       <c r="E184" t="n">
@@ -4399,10 +4504,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C185" s="5" t="n">
+      <c r="C185" s="2" t="n">
         <v>5203.15</v>
       </c>
-      <c r="D185" s="6" t="n">
+      <c r="D185" s="3" t="n">
         <v>1.12843225</v>
       </c>
       <c r="E185" t="n">
@@ -4420,10 +4525,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C186" s="5" t="n">
+      <c r="C186" s="2" t="n">
         <v>43002.78</v>
       </c>
-      <c r="D186" s="6" t="n">
+      <c r="D186" s="3" t="n">
         <v>9.326220449999999</v>
       </c>
       <c r="E186" t="n">
@@ -4441,10 +4546,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C187" s="5" t="n">
+      <c r="C187" s="2" t="n">
         <v>412540.12</v>
       </c>
-      <c r="D187" s="6" t="n">
+      <c r="D187" s="3" t="n">
         <v>89.4695669</v>
       </c>
       <c r="E187" t="n">
@@ -4462,10 +4567,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C188" s="5" t="n">
+      <c r="C188" s="2" t="n">
         <v>1231.47</v>
       </c>
-      <c r="D188" s="6" t="n">
+      <c r="D188" s="3" t="n">
         <v>0.34199572</v>
       </c>
       <c r="E188" t="n">
@@ -4483,10 +4588,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C189" s="5" t="n">
+      <c r="C189" s="2" t="n">
         <v>484.18</v>
       </c>
-      <c r="D189" s="6" t="n">
+      <c r="D189" s="3" t="n">
         <v>0.13446328</v>
       </c>
       <c r="E189" t="n">
@@ -4504,10 +4609,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C190" s="5" t="n">
+      <c r="C190" s="2" t="n">
         <v>29461.66</v>
       </c>
-      <c r="D190" s="6" t="n">
+      <c r="D190" s="3" t="n">
         <v>8.18189784</v>
       </c>
       <c r="E190" t="n">
@@ -4525,10 +4630,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C191" s="5" t="n">
+      <c r="C191" s="2" t="n">
         <v>328906.14</v>
       </c>
-      <c r="D191" s="6" t="n">
+      <c r="D191" s="3" t="n">
         <v>91.34164317</v>
       </c>
       <c r="E191" t="n">
@@ -4546,10 +4651,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C192" s="5" t="n">
+      <c r="C192" s="2" t="n">
         <v>23.47</v>
       </c>
-      <c r="D192" s="6" t="n">
+      <c r="D192" s="3" t="n">
         <v>0.00471838</v>
       </c>
       <c r="E192" t="n">
@@ -4567,10 +4672,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C193" s="5" t="n">
+      <c r="C193" s="2" t="n">
         <v>13128.29</v>
       </c>
-      <c r="D193" s="6" t="n">
+      <c r="D193" s="3" t="n">
         <v>2.63929312</v>
       </c>
       <c r="E193" t="n">
@@ -4588,10 +4693,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C194" s="5" t="n">
+      <c r="C194" s="2" t="n">
         <v>42522.52</v>
       </c>
-      <c r="D194" s="6" t="n">
+      <c r="D194" s="3" t="n">
         <v>8.548668129999999</v>
       </c>
       <c r="E194" t="n">
@@ -4609,10 +4714,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C195" s="5" t="n">
+      <c r="C195" s="2" t="n">
         <v>441742.62</v>
       </c>
-      <c r="D195" s="6" t="n">
+      <c r="D195" s="3" t="n">
         <v>88.80732037999999</v>
       </c>
       <c r="E195" t="n">
@@ -4630,10 +4735,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C196" s="5" t="n">
+      <c r="C196" s="2" t="n">
         <v>14510.35</v>
       </c>
-      <c r="D196" s="6" t="n">
+      <c r="D196" s="3" t="n">
         <v>2.82318771</v>
       </c>
       <c r="E196" t="n">
@@ -4651,10 +4756,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C197" s="5" t="n">
+      <c r="C197" s="2" t="n">
         <v>29796.3</v>
       </c>
-      <c r="D197" s="6" t="n">
+      <c r="D197" s="3" t="n">
         <v>5.79727904</v>
       </c>
       <c r="E197" t="n">
@@ -4672,10 +4777,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C198" s="5" t="n">
+      <c r="C198" s="2" t="n">
         <v>489.48</v>
       </c>
-      <c r="D198" s="6" t="n">
+      <c r="D198" s="3" t="n">
         <v>0.09523505</v>
       </c>
       <c r="E198" t="n">
@@ -4693,10 +4798,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C199" s="5" t="n">
+      <c r="C199" s="2" t="n">
         <v>45623.94</v>
       </c>
-      <c r="D199" s="6" t="n">
+      <c r="D199" s="3" t="n">
         <v>8.876763589999999</v>
       </c>
       <c r="E199" t="n">
@@ -4714,10 +4819,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C200" s="5" t="n">
+      <c r="C200" s="2" t="n">
         <v>423550.36</v>
       </c>
-      <c r="D200" s="6" t="n">
+      <c r="D200" s="3" t="n">
         <v>82.40753461</v>
       </c>
       <c r="E200" t="n">
@@ -4735,10 +4840,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C201" s="5" t="n">
+      <c r="C201" s="2" t="n">
         <v>2894.83</v>
       </c>
-      <c r="D201" s="6" t="n">
+      <c r="D201" s="3" t="n">
         <v>0.57425271</v>
       </c>
       <c r="E201" t="n">
@@ -4756,10 +4861,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C202" s="5" t="n">
+      <c r="C202" s="2" t="n">
         <v>19389.84</v>
       </c>
-      <c r="D202" s="6" t="n">
+      <c r="D202" s="3" t="n">
         <v>3.84639792</v>
       </c>
       <c r="E202" t="n">
@@ -4777,10 +4882,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C203" s="5" t="n">
+      <c r="C203" s="2" t="n">
         <v>7103.09</v>
       </c>
-      <c r="D203" s="6" t="n">
+      <c r="D203" s="3" t="n">
         <v>1.40905292</v>
       </c>
       <c r="E203" t="n">
@@ -4798,10 +4903,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C204" s="5" t="n">
+      <c r="C204" s="2" t="n">
         <v>71555.96000000001</v>
       </c>
-      <c r="D204" s="6" t="n">
+      <c r="D204" s="3" t="n">
         <v>14.19468627</v>
       </c>
       <c r="E204" t="n">
@@ -4819,10 +4924,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C205" s="5" t="n">
+      <c r="C205" s="2" t="n">
         <v>403160.13</v>
       </c>
-      <c r="D205" s="6" t="n">
+      <c r="D205" s="3" t="n">
         <v>79.97561018</v>
       </c>
       <c r="E205" t="n">
@@ -4840,10 +4945,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C206" s="5" t="n">
+      <c r="C206" s="2" t="n">
         <v>13873.76</v>
       </c>
-      <c r="D206" s="6" t="n">
+      <c r="D206" s="3" t="n">
         <v>4.61749343</v>
       </c>
       <c r="E206" t="n">
@@ -4861,10 +4966,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C207" s="5" t="n">
+      <c r="C207" s="2" t="n">
         <v>5637.21</v>
       </c>
-      <c r="D207" s="6" t="n">
+      <c r="D207" s="3" t="n">
         <v>1.87618786</v>
       </c>
       <c r="E207" t="n">
@@ -4882,10 +4987,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C208" s="5" t="n">
+      <c r="C208" s="2" t="n">
         <v>1363.63</v>
       </c>
-      <c r="D208" s="6" t="n">
+      <c r="D208" s="3" t="n">
         <v>0.45384615</v>
       </c>
       <c r="E208" t="n">
@@ -4903,10 +5008,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C209" s="5" t="n">
+      <c r="C209" s="2" t="n">
         <v>35429.67</v>
       </c>
-      <c r="D209" s="6" t="n">
+      <c r="D209" s="3" t="n">
         <v>11.79177587</v>
       </c>
       <c r="E209" t="n">
@@ -4924,10 +5029,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C210" s="5" t="n">
+      <c r="C210" s="2" t="n">
         <v>244156.58</v>
       </c>
-      <c r="D210" s="6" t="n">
+      <c r="D210" s="3" t="n">
         <v>81.26069669</v>
       </c>
       <c r="E210" t="n">
@@ -4945,10 +5050,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C211" s="5" t="n">
+      <c r="C211" s="2" t="n">
         <v>3194.31</v>
       </c>
-      <c r="D211" s="6" t="n">
+      <c r="D211" s="3" t="n">
         <v>0.86754762</v>
       </c>
       <c r="E211" t="n">
@@ -4966,10 +5071,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C212" s="5" t="n">
+      <c r="C212" s="2" t="n">
         <v>53332.81</v>
       </c>
-      <c r="D212" s="6" t="n">
+      <c r="D212" s="3" t="n">
         <v>14.48474085</v>
       </c>
       <c r="E212" t="n">
@@ -4987,10 +5092,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C213" s="5" t="n">
+      <c r="C213" s="2" t="n">
         <v>5480.02</v>
       </c>
-      <c r="D213" s="6" t="n">
+      <c r="D213" s="3" t="n">
         <v>1.48832716</v>
       </c>
       <c r="E213" t="n">
@@ -5008,10 +5113,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C214" s="5" t="n">
+      <c r="C214" s="2" t="n">
         <v>54619.67</v>
       </c>
-      <c r="D214" s="6" t="n">
+      <c r="D214" s="3" t="n">
         <v>14.83424116</v>
       </c>
       <c r="E214" t="n">
@@ -5029,10 +5134,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C215" s="5" t="n">
+      <c r="C215" s="2" t="n">
         <v>251573.15</v>
       </c>
-      <c r="D215" s="6" t="n">
+      <c r="D215" s="3" t="n">
         <v>68.32514322</v>
       </c>
       <c r="E215" t="n">
@@ -5050,10 +5155,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C216" s="5" t="n">
+      <c r="C216" s="2" t="n">
         <v>892</v>
       </c>
-      <c r="D216" s="6" t="n">
+      <c r="D216" s="3" t="n">
         <v>0.30548187</v>
       </c>
       <c r="E216" t="n">
@@ -5071,10 +5176,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C217" s="5" t="n">
+      <c r="C217" s="2" t="n">
         <v>7918.09</v>
       </c>
-      <c r="D217" s="6" t="n">
+      <c r="D217" s="3" t="n">
         <v>2.71169611</v>
       </c>
       <c r="E217" t="n">
@@ -5092,10 +5197,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C218" s="5" t="n">
+      <c r="C218" s="2" t="n">
         <v>37.66</v>
       </c>
-      <c r="D218" s="6" t="n">
+      <c r="D218" s="3" t="n">
         <v>0.01289736</v>
       </c>
       <c r="E218" t="n">
@@ -5113,10 +5218,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C219" s="5" t="n">
+      <c r="C219" s="2" t="n">
         <v>14209.15</v>
       </c>
-      <c r="D219" s="6" t="n">
+      <c r="D219" s="3" t="n">
         <v>4.86618576</v>
       </c>
       <c r="E219" t="n">
@@ -5134,10 +5239,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C220" s="5" t="n">
+      <c r="C220" s="2" t="n">
         <v>268940.79</v>
       </c>
-      <c r="D220" s="6" t="n">
+      <c r="D220" s="3" t="n">
         <v>92.1037389</v>
       </c>
       <c r="E220" t="n">
@@ -5155,10 +5260,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C221" s="5" t="n">
+      <c r="C221" s="2" t="n">
         <v>287</v>
       </c>
-      <c r="D221" s="6" t="n">
+      <c r="D221" s="3" t="n">
         <v>0.07919683</v>
       </c>
       <c r="E221" t="n">
@@ -5176,10 +5281,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C222" s="5" t="n">
+      <c r="C222" s="2" t="n">
         <v>17982.75</v>
       </c>
-      <c r="D222" s="6" t="n">
+      <c r="D222" s="3" t="n">
         <v>4.96228879</v>
       </c>
       <c r="E222" t="n">
@@ -5197,10 +5302,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C223" s="5" t="n">
+      <c r="C223" s="2" t="n">
         <v>2603.68</v>
       </c>
-      <c r="D223" s="6" t="n">
+      <c r="D223" s="3" t="n">
         <v>0.7184781</v>
       </c>
       <c r="E223" t="n">
@@ -5218,10 +5323,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C224" s="5" t="n">
+      <c r="C224" s="2" t="n">
         <v>34911.64</v>
       </c>
-      <c r="D224" s="6" t="n">
+      <c r="D224" s="3" t="n">
         <v>9.6337679</v>
       </c>
       <c r="E224" t="n">
@@ -5239,10 +5344,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C225" s="5" t="n">
+      <c r="C225" s="2" t="n">
         <v>306603.15</v>
       </c>
-      <c r="D225" s="6" t="n">
+      <c r="D225" s="3" t="n">
         <v>84.60626838</v>
       </c>
       <c r="E225" t="n">
@@ -5260,10 +5365,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C226" s="5" t="n">
+      <c r="C226" s="2" t="n">
         <v>1099.13</v>
       </c>
-      <c r="D226" s="6" t="n">
+      <c r="D226" s="3" t="n">
         <v>0.35003695</v>
       </c>
       <c r="E226" t="n">
@@ -5281,10 +5386,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C227" s="5" t="n">
+      <c r="C227" s="2" t="n">
         <v>1908.13</v>
       </c>
-      <c r="D227" s="6" t="n">
+      <c r="D227" s="3" t="n">
         <v>0.60767699</v>
       </c>
       <c r="E227" t="n">
@@ -5302,10 +5407,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C228" s="5" t="n">
+      <c r="C228" s="2" t="n">
         <v>1788.1</v>
       </c>
-      <c r="D228" s="6" t="n">
+      <c r="D228" s="3" t="n">
         <v>0.56945136</v>
       </c>
       <c r="E228" t="n">
@@ -5323,10 +5428,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C229" s="5" t="n">
+      <c r="C229" s="2" t="n">
         <v>54065.52</v>
       </c>
-      <c r="D229" s="6" t="n">
+      <c r="D229" s="3" t="n">
         <v>17.21809968</v>
       </c>
       <c r="E229" t="n">
@@ -5344,10 +5449,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C230" s="5" t="n">
+      <c r="C230" s="2" t="n">
         <v>255143.11</v>
       </c>
-      <c r="D230" s="6" t="n">
+      <c r="D230" s="3" t="n">
         <v>81.25473501</v>
       </c>
       <c r="E230" t="n">
@@ -5365,10 +5470,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C231" s="5" t="n">
+      <c r="C231" s="2" t="n">
         <v>2988.23</v>
       </c>
-      <c r="D231" s="6" t="n">
+      <c r="D231" s="3" t="n">
         <v>1.09502707</v>
       </c>
       <c r="E231" t="n">
@@ -5386,10 +5491,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C232" s="5" t="n">
+      <c r="C232" s="2" t="n">
         <v>89030.31</v>
       </c>
-      <c r="D232" s="6" t="n">
+      <c r="D232" s="3" t="n">
         <v>32.62486479</v>
       </c>
       <c r="E232" t="n">
@@ -5407,10 +5512,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C233" s="5" t="n">
+      <c r="C233" s="2" t="n">
         <v>180872.43</v>
       </c>
-      <c r="D233" s="6" t="n">
+      <c r="D233" s="3" t="n">
         <v>66.28010813</v>
       </c>
       <c r="E233" t="n">
@@ -5428,10 +5533,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C234" s="5" t="n">
+      <c r="C234" s="2" t="n">
         <v>232.92</v>
       </c>
-      <c r="D234" s="6" t="n">
+      <c r="D234" s="3" t="n">
         <v>0.10614272</v>
       </c>
       <c r="E234" t="n">
@@ -5449,10 +5554,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C235" s="5" t="n">
+      <c r="C235" s="2" t="n">
         <v>27443.48</v>
       </c>
-      <c r="D235" s="6" t="n">
+      <c r="D235" s="3" t="n">
         <v>12.50612011</v>
       </c>
       <c r="E235" t="n">
@@ -5470,10 +5575,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C236" s="5" t="n">
+      <c r="C236" s="2" t="n">
         <v>66453.41</v>
       </c>
-      <c r="D236" s="6" t="n">
+      <c r="D236" s="3" t="n">
         <v>30.28312471</v>
       </c>
       <c r="E236" t="n">
@@ -5491,10 +5596,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C237" s="5" t="n">
+      <c r="C237" s="2" t="n">
         <v>125310.59</v>
       </c>
-      <c r="D237" s="6" t="n">
+      <c r="D237" s="3" t="n">
         <v>57.10461246</v>
       </c>
       <c r="E237" t="n">
@@ -5512,10 +5617,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C238" s="5" t="n">
+      <c r="C238" s="2" t="n">
         <v>12206.63</v>
       </c>
-      <c r="D238" s="6" t="n">
+      <c r="D238" s="3" t="n">
         <v>2.80910278</v>
       </c>
       <c r="E238" t="n">
@@ -5533,10 +5638,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C239" s="5" t="n">
+      <c r="C239" s="2" t="n">
         <v>14439.81</v>
       </c>
-      <c r="D239" s="6" t="n">
+      <c r="D239" s="3" t="n">
         <v>3.32302285</v>
       </c>
       <c r="E239" t="n">
@@ -5554,10 +5659,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C240" s="5" t="n">
+      <c r="C240" s="2" t="n">
         <v>73404.17</v>
       </c>
-      <c r="D240" s="6" t="n">
+      <c r="D240" s="3" t="n">
         <v>16.89244764</v>
       </c>
       <c r="E240" t="n">
@@ -5575,10 +5680,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C241" s="5" t="n">
+      <c r="C241" s="2" t="n">
         <v>334487.78</v>
       </c>
-      <c r="D241" s="6" t="n">
+      <c r="D241" s="3" t="n">
         <v>76.97542673</v>
       </c>
       <c r="E241" t="n">
@@ -5596,10 +5701,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C242" s="5" t="n">
+      <c r="C242" s="2" t="n">
         <v>4414.12</v>
       </c>
-      <c r="D242" s="6" t="n">
+      <c r="D242" s="3" t="n">
         <v>2.02734127</v>
       </c>
       <c r="E242" t="n">
@@ -5617,10 +5722,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C243" s="5" t="n">
+      <c r="C243" s="2" t="n">
         <v>206.75</v>
       </c>
-      <c r="D243" s="6" t="n">
+      <c r="D243" s="3" t="n">
         <v>0.09495727</v>
       </c>
       <c r="E243" t="n">
@@ -5638,10 +5743,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C244" s="5" t="n">
+      <c r="C244" s="2" t="n">
         <v>6938.86</v>
       </c>
-      <c r="D244" s="6" t="n">
+      <c r="D244" s="3" t="n">
         <v>3.18691771</v>
       </c>
       <c r="E244" t="n">
@@ -5659,10 +5764,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C245" s="5" t="n">
+      <c r="C245" s="2" t="n">
         <v>206169.77</v>
       </c>
-      <c r="D245" s="6" t="n">
+      <c r="D245" s="3" t="n">
         <v>94.69078374999999</v>
       </c>
       <c r="E245" t="n">
@@ -5680,10 +5785,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C246" s="5" t="n">
+      <c r="C246" s="2" t="n">
         <v>45195.76</v>
       </c>
-      <c r="D246" s="6" t="n">
+      <c r="D246" s="3" t="n">
         <v>10.41762819</v>
       </c>
       <c r="E246" t="n">
@@ -5701,10 +5806,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C247" s="5" t="n">
+      <c r="C247" s="2" t="n">
         <v>9882.6</v>
       </c>
-      <c r="D247" s="6" t="n">
+      <c r="D247" s="3" t="n">
         <v>2.2779405</v>
       </c>
       <c r="E247" t="n">
@@ -5722,10 +5827,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C248" s="5" t="n">
+      <c r="C248" s="2" t="n">
         <v>305.19</v>
       </c>
-      <c r="D248" s="6" t="n">
+      <c r="D248" s="3" t="n">
         <v>0.07034633</v>
       </c>
       <c r="E248" t="n">
@@ -5743,10 +5848,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C249" s="5" t="n">
+      <c r="C249" s="2" t="n">
         <v>9384.76</v>
       </c>
-      <c r="D249" s="6" t="n">
+      <c r="D249" s="3" t="n">
         <v>2.16318832</v>
       </c>
       <c r="E249" t="n">
@@ -5764,10 +5869,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C250" s="5" t="n">
+      <c r="C250" s="2" t="n">
         <v>369070.94</v>
       </c>
-      <c r="D250" s="6" t="n">
+      <c r="D250" s="3" t="n">
         <v>85.07089664999999</v>
       </c>
       <c r="E250" t="n">
@@ -5785,10 +5890,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C251" s="5" t="n">
+      <c r="C251" s="2" t="n">
         <v>387.59</v>
       </c>
-      <c r="D251" s="6" t="n">
+      <c r="D251" s="3" t="n">
         <v>0.10977502</v>
       </c>
       <c r="E251" t="n">
@@ -5806,10 +5911,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C252" s="5" t="n">
+      <c r="C252" s="2" t="n">
         <v>3000</v>
       </c>
-      <c r="D252" s="6" t="n">
+      <c r="D252" s="3" t="n">
         <v>0.84967379</v>
       </c>
       <c r="E252" t="n">
@@ -5827,10 +5932,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C253" s="5" t="n">
+      <c r="C253" s="2" t="n">
         <v>114879.27</v>
       </c>
-      <c r="D253" s="6" t="n">
+      <c r="D253" s="3" t="n">
         <v>32.53663482</v>
       </c>
       <c r="E253" t="n">
@@ -5848,10 +5953,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C254" s="5" t="n">
+      <c r="C254" s="2" t="n">
         <v>234809.82</v>
       </c>
-      <c r="D254" s="6" t="n">
+      <c r="D254" s="3" t="n">
         <v>66.50391637</v>
       </c>
       <c r="E254" t="n">
@@ -5869,10 +5974,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C255" s="5" t="n">
+      <c r="C255" s="2" t="n">
         <v>8859.66</v>
       </c>
-      <c r="D255" s="6" t="n">
+      <c r="D255" s="3" t="n">
         <v>5.34081687</v>
       </c>
       <c r="E255" t="n">
@@ -5890,10 +5995,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C256" s="5" t="n">
+      <c r="C256" s="2" t="n">
         <v>1006.9</v>
       </c>
-      <c r="D256" s="6" t="n">
+      <c r="D256" s="3" t="n">
         <v>0.6069836199999999</v>
       </c>
       <c r="E256" t="n">
@@ -5911,10 +6016,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C257" s="5" t="n">
+      <c r="C257" s="2" t="n">
         <v>1000</v>
       </c>
-      <c r="D257" s="6" t="n">
+      <c r="D257" s="3" t="n">
         <v>0.60282413</v>
       </c>
       <c r="E257" t="n">
@@ -5932,10 +6037,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C258" s="5" t="n">
+      <c r="C258" s="2" t="n">
         <v>51121.7</v>
       </c>
-      <c r="D258" s="6" t="n">
+      <c r="D258" s="3" t="n">
         <v>30.81739456</v>
       </c>
       <c r="E258" t="n">
@@ -5953,10 +6058,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C259" s="5" t="n">
+      <c r="C259" s="2" t="n">
         <v>103897.6</v>
       </c>
-      <c r="D259" s="6" t="n">
+      <c r="D259" s="3" t="n">
         <v>62.63198081</v>
       </c>
       <c r="E259" t="n">
@@ -5974,10 +6079,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C260" s="5" t="n">
+      <c r="C260" s="2" t="n">
         <v>7692.3</v>
       </c>
-      <c r="D260" s="6" t="n">
+      <c r="D260" s="3" t="n">
         <v>6.29078176</v>
       </c>
       <c r="E260" t="n">
@@ -5995,10 +6100,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C261" s="5" t="n">
+      <c r="C261" s="2" t="n">
         <v>1882.73</v>
       </c>
-      <c r="D261" s="6" t="n">
+      <c r="D261" s="3" t="n">
         <v>1.5397012</v>
       </c>
       <c r="E261" t="n">
@@ -6016,10 +6121,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C262" s="5" t="n">
+      <c r="C262" s="2" t="n">
         <v>14869.63</v>
       </c>
-      <c r="D262" s="6" t="n">
+      <c r="D262" s="3" t="n">
         <v>12.1604198</v>
       </c>
       <c r="E262" t="n">
@@ -6037,10 +6142,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C263" s="5" t="n">
+      <c r="C263" s="2" t="n">
         <v>97834.25999999999</v>
       </c>
-      <c r="D263" s="6" t="n">
+      <c r="D263" s="3" t="n">
         <v>80.00909722999999</v>
       </c>
       <c r="E263" t="n">
@@ -6058,10 +6163,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C264" s="5" t="n">
+      <c r="C264" s="2" t="n">
         <v>3303.59</v>
       </c>
-      <c r="D264" s="6" t="n">
+      <c r="D264" s="3" t="n">
         <v>1.27093949</v>
       </c>
       <c r="E264" t="n">
@@ -6079,10 +6184,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C265" s="5" t="n">
+      <c r="C265" s="2" t="n">
         <v>18435.53</v>
       </c>
-      <c r="D265" s="6" t="n">
+      <c r="D265" s="3" t="n">
         <v>7.09241858</v>
       </c>
       <c r="E265" t="n">
@@ -6100,10 +6205,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C266" s="5" t="n">
+      <c r="C266" s="2" t="n">
         <v>2222.22</v>
       </c>
-      <c r="D266" s="6" t="n">
+      <c r="D266" s="3" t="n">
         <v>0.8549206</v>
       </c>
       <c r="E266" t="n">
@@ -6121,10 +6226,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C267" s="5" t="n">
+      <c r="C267" s="2" t="n">
         <v>50871.54</v>
       </c>
-      <c r="D267" s="6" t="n">
+      <c r="D267" s="3" t="n">
         <v>19.571027</v>
       </c>
       <c r="E267" t="n">
@@ -6142,10 +6247,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C268" s="5" t="n">
+      <c r="C268" s="2" t="n">
         <v>185100.03</v>
       </c>
-      <c r="D268" s="6" t="n">
+      <c r="D268" s="3" t="n">
         <v>71.21069433</v>
       </c>
       <c r="E268" t="n">
@@ -6163,10 +6268,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C269" s="5" t="n">
+      <c r="C269" s="2" t="n">
         <v>26854.86</v>
       </c>
-      <c r="D269" s="6" t="n">
+      <c r="D269" s="3" t="n">
         <v>6.60466391</v>
       </c>
       <c r="E269" t="n">
@@ -6184,10 +6289,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="C270" s="5" t="n">
+      <c r="C270" s="2" t="n">
         <v>554.28</v>
       </c>
-      <c r="D270" s="6" t="n">
+      <c r="D270" s="3" t="n">
         <v>0.1363192</v>
       </c>
       <c r="E270" t="n">
@@ -6205,10 +6310,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C271" s="5" t="n">
+      <c r="C271" s="2" t="n">
         <v>487.8</v>
       </c>
-      <c r="D271" s="6" t="n">
+      <c r="D271" s="3" t="n">
         <v>0.11996916</v>
       </c>
       <c r="E271" t="n">
@@ -6226,10 +6331,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C272" s="5" t="n">
+      <c r="C272" s="2" t="n">
         <v>12206.22</v>
       </c>
-      <c r="D272" s="6" t="n">
+      <c r="D272" s="3" t="n">
         <v>3.00198849</v>
       </c>
       <c r="E272" t="n">
@@ -6247,10 +6352,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C273" s="5" t="n">
+      <c r="C273" s="2" t="n">
         <v>28370.02</v>
       </c>
-      <c r="D273" s="6" t="n">
+      <c r="D273" s="3" t="n">
         <v>6.97730121</v>
       </c>
       <c r="E273" t="n">
@@ -6268,10 +6373,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C274" s="5" t="n">
+      <c r="C274" s="2" t="n">
         <v>338131.31</v>
       </c>
-      <c r="D274" s="6" t="n">
+      <c r="D274" s="3" t="n">
         <v>83.15975802</v>
       </c>
       <c r="E274" t="n">
@@ -6289,10 +6394,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C275" s="5" t="n">
+      <c r="C275" s="2" t="n">
         <v>19985.78</v>
       </c>
-      <c r="D275" s="6" t="n">
+      <c r="D275" s="3" t="n">
         <v>7.97052191</v>
       </c>
       <c r="E275" t="n">
@@ -6310,10 +6415,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="C276" s="5" t="n">
+      <c r="C276" s="2" t="n">
         <v>2222.22</v>
       </c>
-      <c r="D276" s="6" t="n">
+      <c r="D276" s="3" t="n">
         <v>0.88624278</v>
       </c>
       <c r="E276" t="n">
@@ -6331,10 +6436,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C277" s="5" t="n">
+      <c r="C277" s="2" t="n">
         <v>4445.7</v>
       </c>
-      <c r="D277" s="6" t="n">
+      <c r="D277" s="3" t="n">
         <v>1.77298806</v>
       </c>
       <c r="E277" t="n">
@@ -6352,10 +6457,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C278" s="5" t="n">
+      <c r="C278" s="2" t="n">
         <v>50514.02</v>
       </c>
-      <c r="D278" s="6" t="n">
+      <c r="D278" s="3" t="n">
         <v>20.14547858</v>
       </c>
       <c r="E278" t="n">
@@ -6373,10 +6478,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C279" s="5" t="n">
+      <c r="C279" s="2" t="n">
         <v>173578.47</v>
       </c>
-      <c r="D279" s="6" t="n">
+      <c r="D279" s="3" t="n">
         <v>69.22476868</v>
       </c>
       <c r="E279" t="n">
@@ -6394,10 +6499,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C280" s="5" t="n">
+      <c r="C280" s="2" t="n">
         <v>40560.99</v>
       </c>
-      <c r="D280" s="6" t="n">
+      <c r="D280" s="3" t="n">
         <v>8.644859670000001</v>
       </c>
       <c r="E280" t="n">
@@ -6415,10 +6520,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C281" s="5" t="n">
+      <c r="C281" s="2" t="n">
         <v>6836.42</v>
       </c>
-      <c r="D281" s="6" t="n">
+      <c r="D281" s="3" t="n">
         <v>1.45706235</v>
       </c>
       <c r="E281" t="n">
@@ -6436,10 +6541,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C282" s="5" t="n">
+      <c r="C282" s="2" t="n">
         <v>34873.15</v>
       </c>
-      <c r="D282" s="6" t="n">
+      <c r="D282" s="3" t="n">
         <v>7.43259689</v>
       </c>
       <c r="E282" t="n">
@@ -6457,10 +6562,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C283" s="5" t="n">
+      <c r="C283" s="2" t="n">
         <v>386921.44</v>
       </c>
-      <c r="D283" s="6" t="n">
+      <c r="D283" s="3" t="n">
         <v>82.46548108</v>
       </c>
       <c r="E283" t="n">
@@ -6478,10 +6583,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="C284" s="5" t="n">
+      <c r="C284" s="2" t="n">
         <v>2062.08</v>
       </c>
-      <c r="D284" s="6" t="n">
+      <c r="D284" s="3" t="n">
         <v>0.67843969</v>
       </c>
       <c r="E284" t="n">
@@ -6499,10 +6604,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C285" s="5" t="n">
+      <c r="C285" s="2" t="n">
         <v>67302.87</v>
       </c>
-      <c r="D285" s="6" t="n">
+      <c r="D285" s="3" t="n">
         <v>22.14314601</v>
       </c>
       <c r="E285" t="n">
@@ -6520,10 +6625,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C286" s="5" t="n">
+      <c r="C286" s="2" t="n">
         <v>37.83</v>
       </c>
-      <c r="D286" s="6" t="n">
+      <c r="D286" s="3" t="n">
         <v>0.01244635</v>
       </c>
       <c r="E286" t="n">
@@ -6541,10 +6646,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C287" s="5" t="n">
+      <c r="C287" s="2" t="n">
         <v>82048.36</v>
       </c>
-      <c r="D287" s="6" t="n">
+      <c r="D287" s="3" t="n">
         <v>26.99452216</v>
       </c>
       <c r="E287" t="n">
@@ -6562,10 +6667,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C288" s="5" t="n">
+      <c r="C288" s="2" t="n">
         <v>152493.34</v>
       </c>
-      <c r="D288" s="6" t="n">
+      <c r="D288" s="3" t="n">
         <v>50.17144579</v>
       </c>
       <c r="E288" t="n">
@@ -6583,10 +6688,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C289" s="5" t="n">
+      <c r="C289" s="2" t="n">
         <v>16850.05</v>
       </c>
-      <c r="D289" s="6" t="n">
+      <c r="D289" s="3" t="n">
         <v>8.3557591</v>
       </c>
       <c r="E289" t="n">
@@ -6604,10 +6709,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C290" s="5" t="n">
+      <c r="C290" s="2" t="n">
         <v>1221.31</v>
       </c>
-      <c r="D290" s="6" t="n">
+      <c r="D290" s="3" t="n">
         <v>0.60563453</v>
       </c>
       <c r="E290" t="n">
@@ -6625,10 +6730,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C291" s="5" t="n">
+      <c r="C291" s="2" t="n">
         <v>542.72</v>
       </c>
-      <c r="D291" s="6" t="n">
+      <c r="D291" s="3" t="n">
         <v>0.26912903</v>
       </c>
       <c r="E291" t="n">
@@ -6646,10 +6751,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C292" s="5" t="n">
+      <c r="C292" s="2" t="n">
         <v>1989.87</v>
       </c>
-      <c r="D292" s="6" t="n">
+      <c r="D292" s="3" t="n">
         <v>0.98675519</v>
       </c>
       <c r="E292" t="n">
@@ -6667,10 +6772,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C293" s="5" t="n">
+      <c r="C293" s="2" t="n">
         <v>181053.97</v>
       </c>
-      <c r="D293" s="6" t="n">
+      <c r="D293" s="3" t="n">
         <v>89.78272215</v>
       </c>
       <c r="E293" t="n">
@@ -6688,10 +6793,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C294" s="5" t="n">
+      <c r="C294" s="2" t="n">
         <v>2791.46</v>
       </c>
-      <c r="D294" s="6" t="n">
+      <c r="D294" s="3" t="n">
         <v>1.6215349</v>
       </c>
       <c r="E294" t="n">
@@ -6709,10 +6814,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C295" s="5" t="n">
+      <c r="C295" s="2" t="n">
         <v>6752.82</v>
       </c>
-      <c r="D295" s="6" t="n">
+      <c r="D295" s="3" t="n">
         <v>3.92265455</v>
       </c>
       <c r="E295" t="n">
@@ -6730,10 +6835,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C296" s="5" t="n">
+      <c r="C296" s="2" t="n">
         <v>42038.15</v>
       </c>
-      <c r="D296" s="6" t="n">
+      <c r="D296" s="3" t="n">
         <v>24.41959662</v>
       </c>
       <c r="E296" t="n">
@@ -6751,10 +6856,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C297" s="5" t="n">
+      <c r="C297" s="2" t="n">
         <v>120566.81</v>
       </c>
-      <c r="D297" s="6" t="n">
+      <c r="D297" s="3" t="n">
         <v>70.03621393</v>
       </c>
       <c r="E297" t="n">
@@ -6772,10 +6877,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C298" s="5" t="n">
+      <c r="C298" s="2" t="n">
         <v>360</v>
       </c>
-      <c r="D298" s="6" t="n">
+      <c r="D298" s="3" t="n">
         <v>0.13798773</v>
       </c>
       <c r="E298" t="n">
@@ -6793,10 +6898,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C299" s="5" t="n">
+      <c r="C299" s="2" t="n">
         <v>9364.209999999999</v>
       </c>
-      <c r="D299" s="6" t="n">
+      <c r="D299" s="3" t="n">
         <v>3.58929456</v>
       </c>
       <c r="E299" t="n">
@@ -6814,10 +6919,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C300" s="5" t="n">
+      <c r="C300" s="2" t="n">
         <v>4780.88</v>
       </c>
-      <c r="D300" s="6" t="n">
+      <c r="D300" s="3" t="n">
         <v>1.83250766</v>
       </c>
       <c r="E300" t="n">
@@ -6835,10 +6940,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C301" s="5" t="n">
+      <c r="C301" s="2" t="n">
         <v>246387.68</v>
       </c>
-      <c r="D301" s="6" t="n">
+      <c r="D301" s="3" t="n">
         <v>94.44021005</v>
       </c>
       <c r="E301" t="n">
@@ -6856,10 +6961,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C302" s="5" t="n">
+      <c r="C302" s="2" t="n">
         <v>6057.75</v>
       </c>
-      <c r="D302" s="6" t="n">
+      <c r="D302" s="3" t="n">
         <v>2.33727832</v>
       </c>
       <c r="E302" t="n">
@@ -6877,10 +6982,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C303" s="5" t="n">
+      <c r="C303" s="2" t="n">
         <v>48766.63</v>
       </c>
-      <c r="D303" s="6" t="n">
+      <c r="D303" s="3" t="n">
         <v>18.81576278</v>
       </c>
       <c r="E303" t="n">
@@ -6898,10 +7003,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C304" s="5" t="n">
+      <c r="C304" s="2" t="n">
         <v>204355.28</v>
       </c>
-      <c r="D304" s="6" t="n">
+      <c r="D304" s="3" t="n">
         <v>78.8469589</v>
       </c>
       <c r="E304" t="n">
@@ -6919,10 +7024,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C305" s="5" t="n">
+      <c r="C305" s="2" t="n">
         <v>16523.23</v>
       </c>
-      <c r="D305" s="6" t="n">
+      <c r="D305" s="3" t="n">
         <v>6.18627246</v>
       </c>
       <c r="E305" t="n">
@@ -6940,10 +7045,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="C306" s="5" t="n">
+      <c r="C306" s="2" t="n">
         <v>1000</v>
       </c>
-      <c r="D306" s="6" t="n">
+      <c r="D306" s="3" t="n">
         <v>0.3743985</v>
       </c>
       <c r="E306" t="n">
@@ -6961,10 +7066,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C307" s="5" t="n">
+      <c r="C307" s="2" t="n">
         <v>19175.48</v>
       </c>
-      <c r="D307" s="6" t="n">
+      <c r="D307" s="3" t="n">
         <v>7.17927087</v>
       </c>
       <c r="E307" t="n">
@@ -6982,10 +7087,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C308" s="5" t="n">
+      <c r="C308" s="2" t="n">
         <v>22548.18</v>
       </c>
-      <c r="D308" s="6" t="n">
+      <c r="D308" s="3" t="n">
         <v>8.44200468</v>
       </c>
       <c r="E308" t="n">
@@ -7003,10 +7108,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C309" s="5" t="n">
+      <c r="C309" s="2" t="n">
         <v>3105.38</v>
       </c>
-      <c r="D309" s="6" t="n">
+      <c r="D309" s="3" t="n">
         <v>1.1626496</v>
       </c>
       <c r="E309" t="n">
@@ -7024,10 +7129,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C310" s="5" t="n">
+      <c r="C310" s="2" t="n">
         <v>9171.51</v>
       </c>
-      <c r="D310" s="6" t="n">
+      <c r="D310" s="3" t="n">
         <v>3.43379955</v>
       </c>
       <c r="E310" t="n">
@@ -7045,10 +7150,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C311" s="5" t="n">
+      <c r="C311" s="2" t="n">
         <v>195571.31</v>
       </c>
-      <c r="D311" s="6" t="n">
+      <c r="D311" s="3" t="n">
         <v>73.22160434</v>
       </c>
       <c r="E311" t="n">
@@ -7066,10 +7171,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C312" s="5" t="n">
+      <c r="C312" s="2" t="n">
         <v>27350.51</v>
       </c>
-      <c r="D312" s="6" t="n">
+      <c r="D312" s="3" t="n">
         <v>9.8197723</v>
       </c>
       <c r="E312" t="n">
@@ -7087,10 +7192,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C313" s="5" t="n">
+      <c r="C313" s="2" t="n">
         <v>21653.68</v>
       </c>
-      <c r="D313" s="6" t="n">
+      <c r="D313" s="3" t="n">
         <v>7.7744147</v>
       </c>
       <c r="E313" t="n">
@@ -7108,10 +7213,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C314" s="5" t="n">
+      <c r="C314" s="2" t="n">
         <v>30092.08</v>
       </c>
-      <c r="D314" s="6" t="n">
+      <c r="D314" s="3" t="n">
         <v>10.80409008</v>
       </c>
       <c r="E314" t="n">
@@ -7129,10 +7234,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C315" s="5" t="n">
+      <c r="C315" s="2" t="n">
         <v>199428.62</v>
       </c>
-      <c r="D315" s="6" t="n">
+      <c r="D315" s="3" t="n">
         <v>71.60172292</v>
       </c>
       <c r="E315" t="n">
@@ -7150,10 +7255,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C316" s="5" t="n">
+      <c r="C316" s="2" t="n">
         <v>18403.89</v>
       </c>
-      <c r="D316" s="6" t="n">
+      <c r="D316" s="3" t="n">
         <v>5.9503914</v>
       </c>
       <c r="E316" t="n">
@@ -7171,10 +7276,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C317" s="5" t="n">
+      <c r="C317" s="2" t="n">
         <v>88.88</v>
       </c>
-      <c r="D317" s="6" t="n">
+      <c r="D317" s="3" t="n">
         <v>0.0287369</v>
       </c>
       <c r="E317" t="n">
@@ -7192,10 +7297,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C318" s="5" t="n">
+      <c r="C318" s="2" t="n">
         <v>72445.86</v>
       </c>
-      <c r="D318" s="6" t="n">
+      <c r="D318" s="3" t="n">
         <v>23.4233753</v>
       </c>
       <c r="E318" t="n">
@@ -7213,10 +7318,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C319" s="5" t="n">
+      <c r="C319" s="2" t="n">
         <v>1021.81</v>
       </c>
-      <c r="D319" s="6" t="n">
+      <c r="D319" s="3" t="n">
         <v>0.33037415</v>
       </c>
       <c r="E319" t="n">
@@ -7234,10 +7339,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C320" s="5" t="n">
+      <c r="C320" s="2" t="n">
         <v>23146.75</v>
       </c>
-      <c r="D320" s="6" t="n">
+      <c r="D320" s="3" t="n">
         <v>7.48386467</v>
       </c>
       <c r="E320" t="n">
@@ -7255,10 +7360,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C321" s="5" t="n">
+      <c r="C321" s="2" t="n">
         <v>194181.54</v>
       </c>
-      <c r="D321" s="6" t="n">
+      <c r="D321" s="3" t="n">
         <v>62.78325757</v>
       </c>
       <c r="E321" t="n">
@@ -7276,10 +7381,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C322" s="5" t="n">
+      <c r="C322" s="2" t="n">
         <v>3620.25</v>
       </c>
-      <c r="D322" s="6" t="n">
+      <c r="D322" s="3" t="n">
         <v>1.23604851</v>
       </c>
       <c r="E322" t="n">
@@ -7297,10 +7402,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C323" s="5" t="n">
+      <c r="C323" s="2" t="n">
         <v>19747.53</v>
       </c>
-      <c r="D323" s="6" t="n">
+      <c r="D323" s="3" t="n">
         <v>6.74232582</v>
       </c>
       <c r="E323" t="n">
@@ -7318,10 +7423,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C324" s="5" t="n">
+      <c r="C324" s="2" t="n">
         <v>148.8</v>
       </c>
-      <c r="D324" s="6" t="n">
+      <c r="D324" s="3" t="n">
         <v>0.05080423</v>
       </c>
       <c r="E324" t="n">
@@ -7339,10 +7444,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C325" s="5" t="n">
+      <c r="C325" s="2" t="n">
         <v>59465.09</v>
       </c>
-      <c r="D325" s="6" t="n">
+      <c r="D325" s="3" t="n">
         <v>20.30294481</v>
       </c>
       <c r="E325" t="n">
@@ -7360,10 +7465,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C326" s="5" t="n">
+      <c r="C326" s="2" t="n">
         <v>209907.32</v>
       </c>
-      <c r="D326" s="6" t="n">
+      <c r="D326" s="3" t="n">
         <v>71.66787662</v>
       </c>
       <c r="E326" t="n">
@@ -7381,10 +7486,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C327" s="5" t="n">
+      <c r="C327" s="2" t="n">
         <v>6884.07</v>
       </c>
-      <c r="D327" s="6" t="n">
+      <c r="D327" s="3" t="n">
         <v>2.33908458</v>
       </c>
       <c r="E327" t="n">
@@ -7402,10 +7507,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C328" s="5" t="n">
+      <c r="C328" s="2" t="n">
         <v>1851.18</v>
       </c>
-      <c r="D328" s="6" t="n">
+      <c r="D328" s="3" t="n">
         <v>0.62899805</v>
       </c>
       <c r="E328" t="n">
@@ -7423,10 +7528,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C329" s="5" t="n">
+      <c r="C329" s="2" t="n">
         <v>27.27</v>
       </c>
-      <c r="D329" s="6" t="n">
+      <c r="D329" s="3" t="n">
         <v>0.009265860000000001</v>
       </c>
       <c r="E329" t="n">
@@ -7444,10 +7549,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C330" s="5" t="n">
+      <c r="C330" s="2" t="n">
         <v>48724.48</v>
       </c>
-      <c r="D330" s="6" t="n">
+      <c r="D330" s="3" t="n">
         <v>16.55571192</v>
       </c>
       <c r="E330" t="n">
@@ -7465,10 +7570,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C331" s="5" t="n">
+      <c r="C331" s="2" t="n">
         <v>236819.16</v>
       </c>
-      <c r="D331" s="6" t="n">
+      <c r="D331" s="3" t="n">
         <v>80.4669396</v>
       </c>
       <c r="E331" t="n">
@@ -7486,10 +7591,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C332" s="5" t="n">
+      <c r="C332" s="2" t="n">
         <v>1121.22</v>
       </c>
-      <c r="D332" s="6" t="n">
+      <c r="D332" s="3" t="n">
         <v>0.3654631</v>
       </c>
       <c r="E332" t="n">
@@ -7507,10 +7612,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C333" s="5" t="n">
+      <c r="C333" s="2" t="n">
         <v>44200.33</v>
       </c>
-      <c r="D333" s="6" t="n">
+      <c r="D333" s="3" t="n">
         <v>14.40715442</v>
       </c>
       <c r="E333" t="n">
@@ -7528,10 +7633,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C334" s="5" t="n">
+      <c r="C334" s="2" t="n">
         <v>1029.79</v>
       </c>
-      <c r="D334" s="6" t="n">
+      <c r="D334" s="3" t="n">
         <v>0.33566138</v>
       </c>
       <c r="E334" t="n">
@@ -7549,10 +7654,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C335" s="5" t="n">
+      <c r="C335" s="2" t="n">
         <v>47810.16</v>
       </c>
-      <c r="D335" s="6" t="n">
+      <c r="D335" s="3" t="n">
         <v>15.58378315</v>
       </c>
       <c r="E335" t="n">
@@ -7570,10 +7675,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C336" s="5" t="n">
+      <c r="C336" s="2" t="n">
         <v>212632.81</v>
       </c>
-      <c r="D336" s="6" t="n">
+      <c r="D336" s="3" t="n">
         <v>69.30793795</v>
       </c>
       <c r="E336" t="n">
@@ -7591,10 +7696,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C337" s="5" t="n">
+      <c r="C337" s="2" t="n">
         <v>6174.11</v>
       </c>
-      <c r="D337" s="6" t="n">
+      <c r="D337" s="3" t="n">
         <v>2.21572231</v>
       </c>
       <c r="E337" t="n">
@@ -7612,10 +7717,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C338" s="5" t="n">
+      <c r="C338" s="2" t="n">
         <v>41944.2</v>
       </c>
-      <c r="D338" s="6" t="n">
+      <c r="D338" s="3" t="n">
         <v>15.05264723</v>
       </c>
       <c r="E338" t="n">
@@ -7633,10 +7738,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C339" s="5" t="n">
+      <c r="C339" s="2" t="n">
         <v>77569.86</v>
       </c>
-      <c r="D339" s="6" t="n">
+      <c r="D339" s="3" t="n">
         <v>27.8377401</v>
       </c>
       <c r="E339" t="n">
@@ -7654,10 +7759,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C340" s="5" t="n">
+      <c r="C340" s="2" t="n">
         <v>152961.82</v>
       </c>
-      <c r="D340" s="6" t="n">
+      <c r="D340" s="3" t="n">
         <v>54.89389036</v>
       </c>
       <c r="E340" t="n">
@@ -7675,10 +7780,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C341" s="5" t="n">
+      <c r="C341" s="2" t="n">
         <v>4327.58</v>
       </c>
-      <c r="D341" s="6" t="n">
+      <c r="D341" s="3" t="n">
         <v>1.21146897</v>
       </c>
       <c r="E341" t="n">
@@ -7696,10 +7801,10 @@
           <t>Culture</t>
         </is>
       </c>
-      <c r="C342" s="5" t="n">
+      <c r="C342" s="2" t="n">
         <v>28414.86</v>
       </c>
-      <c r="D342" s="6" t="n">
+      <c r="D342" s="3" t="n">
         <v>7.95449675</v>
       </c>
       <c r="E342" t="n">
@@ -7717,10 +7822,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C343" s="5" t="n">
+      <c r="C343" s="2" t="n">
         <v>57985.61</v>
       </c>
-      <c r="D343" s="6" t="n">
+      <c r="D343" s="3" t="n">
         <v>16.23257501</v>
       </c>
       <c r="E343" t="n">
@@ -7738,10 +7843,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C344" s="5" t="n">
+      <c r="C344" s="2" t="n">
         <v>164042.55</v>
       </c>
-      <c r="D344" s="6" t="n">
+      <c r="D344" s="3" t="n">
         <v>45.92230724</v>
       </c>
       <c r="E344" t="n">
@@ -7759,10 +7864,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C345" s="5" t="n">
+      <c r="C345" s="2" t="n">
         <v>102446.97</v>
       </c>
-      <c r="D345" s="6" t="n">
+      <c r="D345" s="3" t="n">
         <v>28.67915204</v>
       </c>
       <c r="E345" t="n">
@@ -7780,10 +7885,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C346" s="5" t="n">
+      <c r="C346" s="2" t="n">
         <v>6549.34</v>
       </c>
-      <c r="D346" s="6" t="n">
+      <c r="D346" s="3" t="n">
         <v>1.3658538</v>
       </c>
       <c r="E346" t="n">
@@ -7801,10 +7906,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C347" s="5" t="n">
+      <c r="C347" s="2" t="n">
         <v>70012.2</v>
       </c>
-      <c r="D347" s="6" t="n">
+      <c r="D347" s="3" t="n">
         <v>14.60092612</v>
       </c>
       <c r="E347" t="n">
@@ -7822,10 +7927,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C348" s="5" t="n">
+      <c r="C348" s="2" t="n">
         <v>131512.85</v>
       </c>
-      <c r="D348" s="6" t="n">
+      <c r="D348" s="3" t="n">
         <v>27.42678286</v>
       </c>
       <c r="E348" t="n">
@@ -7843,10 +7948,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C349" s="5" t="n">
+      <c r="C349" s="2" t="n">
         <v>271430.81</v>
       </c>
-      <c r="D349" s="6" t="n">
+      <c r="D349" s="3" t="n">
         <v>56.60643722</v>
       </c>
       <c r="E349" t="n">
@@ -7864,10 +7969,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C350" s="5" t="n">
+      <c r="C350" s="2" t="n">
         <v>15339.66</v>
       </c>
-      <c r="D350" s="6" t="n">
+      <c r="D350" s="3" t="n">
         <v>4.55580253</v>
       </c>
       <c r="E350" t="n">
@@ -7885,10 +7990,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C351" s="5" t="n">
+      <c r="C351" s="2" t="n">
         <v>24900.55</v>
       </c>
-      <c r="D351" s="6" t="n">
+      <c r="D351" s="3" t="n">
         <v>7.39533918</v>
       </c>
       <c r="E351" t="n">
@@ -7906,10 +8011,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C352" s="5" t="n">
+      <c r="C352" s="2" t="n">
         <v>7486.19</v>
       </c>
-      <c r="D352" s="6" t="n">
+      <c r="D352" s="3" t="n">
         <v>2.2233611</v>
       </c>
       <c r="E352" t="n">
@@ -7927,10 +8032,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C353" s="5" t="n">
+      <c r="C353" s="2" t="n">
         <v>75899.28</v>
       </c>
-      <c r="D353" s="6" t="n">
+      <c r="D353" s="3" t="n">
         <v>22.54170768</v>
       </c>
       <c r="E353" t="n">
@@ -7948,10 +8053,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C354" s="5" t="n">
+      <c r="C354" s="2" t="n">
         <v>213080.31</v>
       </c>
-      <c r="D354" s="6" t="n">
+      <c r="D354" s="3" t="n">
         <v>63.28378952</v>
       </c>
       <c r="E354" t="n">
@@ -7969,10 +8074,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C355" s="5" t="n">
+      <c r="C355" s="2" t="n">
         <v>99.05</v>
       </c>
-      <c r="D355" s="6" t="n">
+      <c r="D355" s="3" t="n">
         <v>0.05450467</v>
       </c>
       <c r="E355" t="n">
@@ -7990,10 +8095,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C356" s="5" t="n">
+      <c r="C356" s="2" t="n">
         <v>40317.43</v>
       </c>
-      <c r="D356" s="6" t="n">
+      <c r="D356" s="3" t="n">
         <v>22.18564427</v>
       </c>
       <c r="E356" t="n">
@@ -8011,10 +8116,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C357" s="5" t="n">
+      <c r="C357" s="2" t="n">
         <v>441.17</v>
       </c>
-      <c r="D357" s="6" t="n">
+      <c r="D357" s="3" t="n">
         <v>0.2427645</v>
       </c>
       <c r="E357" t="n">
@@ -8032,10 +8137,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C358" s="5" t="n">
+      <c r="C358" s="2" t="n">
         <v>15478.5</v>
       </c>
-      <c r="D358" s="6" t="n">
+      <c r="D358" s="3" t="n">
         <v>8.517420250000001</v>
       </c>
       <c r="E358" t="n">
@@ -8053,10 +8158,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C359" s="5" t="n">
+      <c r="C359" s="2" t="n">
         <v>125391.41</v>
       </c>
-      <c r="D359" s="6" t="n">
+      <c r="D359" s="3" t="n">
         <v>68.99966630999999</v>
       </c>
       <c r="E359" t="n">
@@ -8074,10 +8179,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C360" s="5" t="n">
+      <c r="C360" s="2" t="n">
         <v>1078.53</v>
       </c>
-      <c r="D360" s="6" t="n">
+      <c r="D360" s="3" t="n">
         <v>0.2616409</v>
       </c>
       <c r="E360" t="n">
@@ -8095,10 +8200,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C361" s="5" t="n">
+      <c r="C361" s="2" t="n">
         <v>18773.2</v>
       </c>
-      <c r="D361" s="6" t="n">
+      <c r="D361" s="3" t="n">
         <v>4.55419596</v>
       </c>
       <c r="E361" t="n">
@@ -8116,10 +8221,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C362" s="5" t="n">
+      <c r="C362" s="2" t="n">
         <v>131529.74</v>
       </c>
-      <c r="D362" s="6" t="n">
+      <c r="D362" s="3" t="n">
         <v>31.90783723</v>
       </c>
       <c r="E362" t="n">
@@ -8137,10 +8242,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C363" s="5" t="n">
+      <c r="C363" s="2" t="n">
         <v>260836.19</v>
       </c>
-      <c r="D363" s="6" t="n">
+      <c r="D363" s="3" t="n">
         <v>63.27632591</v>
       </c>
       <c r="E363" t="n">
@@ -8158,10 +8263,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C364" s="5" t="n">
+      <c r="C364" s="2" t="n">
         <v>101597</v>
       </c>
-      <c r="D364" s="6" t="n">
+      <c r="D364" s="3" t="n">
         <v>23.3811176</v>
       </c>
       <c r="E364" t="n">
@@ -8179,10 +8284,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C365" s="5" t="n">
+      <c r="C365" s="2" t="n">
         <v>28150.66</v>
       </c>
-      <c r="D365" s="6" t="n">
+      <c r="D365" s="3" t="n">
         <v>6.47847763</v>
       </c>
       <c r="E365" t="n">
@@ -8200,10 +8305,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C366" s="5" t="n">
+      <c r="C366" s="2" t="n">
         <v>40.94</v>
       </c>
-      <c r="D366" s="6" t="n">
+      <c r="D366" s="3" t="n">
         <v>0.00942176</v>
       </c>
       <c r="E366" t="n">
@@ -8221,10 +8326,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C367" s="5" t="n">
+      <c r="C367" s="2" t="n">
         <v>39974.48</v>
       </c>
-      <c r="D367" s="6" t="n">
+      <c r="D367" s="3" t="n">
         <v>9.19956316</v>
       </c>
       <c r="E367" t="n">
@@ -8242,10 +8347,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C368" s="5" t="n">
+      <c r="C368" s="2" t="n">
         <v>264762.77</v>
       </c>
-      <c r="D368" s="6" t="n">
+      <c r="D368" s="3" t="n">
         <v>60.93141985</v>
       </c>
       <c r="E368" t="n">
@@ -8263,10 +8368,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C369" s="5" t="n">
+      <c r="C369" s="2" t="n">
         <v>4391.2</v>
       </c>
-      <c r="D369" s="6" t="n">
+      <c r="D369" s="3" t="n">
         <v>1.20491459</v>
       </c>
       <c r="E369" t="n">
@@ -8284,10 +8389,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C370" s="5" t="n">
+      <c r="C370" s="2" t="n">
         <v>65068.55</v>
       </c>
-      <c r="D370" s="6" t="n">
+      <c r="D370" s="3" t="n">
         <v>17.85435532</v>
       </c>
       <c r="E370" t="n">
@@ -8305,10 +8410,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C371" s="5" t="n">
+      <c r="C371" s="2" t="n">
         <v>121692.04</v>
       </c>
-      <c r="D371" s="6" t="n">
+      <c r="D371" s="3" t="n">
         <v>33.3914452</v>
       </c>
       <c r="E371" t="n">
@@ -8326,10 +8431,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C372" s="5" t="n">
+      <c r="C372" s="2" t="n">
         <v>173288.98</v>
       </c>
-      <c r="D372" s="6" t="n">
+      <c r="D372" s="3" t="n">
         <v>47.54928489</v>
       </c>
       <c r="E372" t="n">
@@ -8347,10 +8452,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C373" s="5" t="n">
+      <c r="C373" s="2" t="n">
         <v>17775.38</v>
       </c>
-      <c r="D373" s="6" t="n">
+      <c r="D373" s="3" t="n">
         <v>7.37116189</v>
       </c>
       <c r="E373" t="n">
@@ -8368,10 +8473,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C374" s="5" t="n">
+      <c r="C374" s="2" t="n">
         <v>29163.77</v>
       </c>
-      <c r="D374" s="6" t="n">
+      <c r="D374" s="3" t="n">
         <v>12.09374259</v>
       </c>
       <c r="E374" t="n">
@@ -8389,10 +8494,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C375" s="5" t="n">
+      <c r="C375" s="2" t="n">
         <v>52107.99</v>
       </c>
-      <c r="D375" s="6" t="n">
+      <c r="D375" s="3" t="n">
         <v>21.60833863</v>
       </c>
       <c r="E375" t="n">
@@ -8410,10 +8515,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C376" s="5" t="n">
+      <c r="C376" s="2" t="n">
         <v>142100.46</v>
       </c>
-      <c r="D376" s="6" t="n">
+      <c r="D376" s="3" t="n">
         <v>58.92675689</v>
       </c>
       <c r="E376" t="n">
@@ -8431,10 +8536,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C377" s="5" t="n">
+      <c r="C377" s="2" t="n">
         <v>10000</v>
       </c>
-      <c r="D377" s="6" t="n">
+      <c r="D377" s="3" t="n">
         <v>3.50118517</v>
       </c>
       <c r="E377" t="n">
@@ -8452,10 +8557,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C378" s="5" t="n">
+      <c r="C378" s="2" t="n">
         <v>4643.79</v>
       </c>
-      <c r="D378" s="6" t="n">
+      <c r="D378" s="3" t="n">
         <v>1.62587687</v>
       </c>
       <c r="E378" t="n">
@@ -8473,10 +8578,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C379" s="5" t="n">
+      <c r="C379" s="2" t="n">
         <v>520.28</v>
       </c>
-      <c r="D379" s="6" t="n">
+      <c r="D379" s="3" t="n">
         <v>0.18215966</v>
       </c>
       <c r="E379" t="n">
@@ -8494,10 +8599,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C380" s="5" t="n">
+      <c r="C380" s="2" t="n">
         <v>19199.2</v>
       </c>
-      <c r="D380" s="6" t="n">
+      <c r="D380" s="3" t="n">
         <v>6.72199543</v>
       </c>
       <c r="E380" t="n">
@@ -8515,10 +8620,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C381" s="5" t="n">
+      <c r="C381" s="2" t="n">
         <v>251254.3</v>
       </c>
-      <c r="D381" s="6" t="n">
+      <c r="D381" s="3" t="n">
         <v>87.96878287</v>
       </c>
       <c r="E381" t="n">
@@ -8536,10 +8641,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C382" s="5" t="n">
+      <c r="C382" s="2" t="n">
         <v>2713.17</v>
       </c>
-      <c r="D382" s="6" t="n">
+      <c r="D382" s="3" t="n">
         <v>1.2942759</v>
       </c>
       <c r="E382" t="n">
@@ -8557,10 +8662,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C383" s="5" t="n">
+      <c r="C383" s="2" t="n">
         <v>3564.2</v>
       </c>
-      <c r="D383" s="6" t="n">
+      <c r="D383" s="3" t="n">
         <v>1.70024664</v>
       </c>
       <c r="E383" t="n">
@@ -8578,10 +8683,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C384" s="5" t="n">
+      <c r="C384" s="2" t="n">
         <v>41002.83</v>
       </c>
-      <c r="D384" s="6" t="n">
+      <c r="D384" s="3" t="n">
         <v>19.55976769</v>
       </c>
       <c r="E384" t="n">
@@ -8599,10 +8704,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C385" s="5" t="n">
+      <c r="C385" s="2" t="n">
         <v>162348.21</v>
       </c>
-      <c r="D385" s="6" t="n">
+      <c r="D385" s="3" t="n">
         <v>77.44570976999999</v>
       </c>
       <c r="E385" t="n">
@@ -8620,10 +8725,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C386" s="5" t="n">
+      <c r="C386" s="2" t="n">
         <v>1485.87</v>
       </c>
-      <c r="D386" s="6" t="n">
+      <c r="D386" s="3" t="n">
         <v>0.73523958</v>
       </c>
       <c r="E386" t="n">
@@ -8641,10 +8746,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C387" s="5" t="n">
+      <c r="C387" s="2" t="n">
         <v>42513.88</v>
       </c>
-      <c r="D387" s="6" t="n">
+      <c r="D387" s="3" t="n">
         <v>21.03675772</v>
       </c>
       <c r="E387" t="n">
@@ -8662,10 +8767,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C388" s="5" t="n">
+      <c r="C388" s="2" t="n">
         <v>450.45</v>
       </c>
-      <c r="D388" s="6" t="n">
+      <c r="D388" s="3" t="n">
         <v>0.22289209</v>
       </c>
       <c r="E388" t="n">
@@ -8683,10 +8788,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C389" s="5" t="n">
+      <c r="C389" s="2" t="n">
         <v>15613.89</v>
       </c>
-      <c r="D389" s="6" t="n">
+      <c r="D389" s="3" t="n">
         <v>7.7260796</v>
       </c>
       <c r="E389" t="n">
@@ -8704,10 +8809,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C390" s="5" t="n">
+      <c r="C390" s="2" t="n">
         <v>142029.22</v>
       </c>
-      <c r="D390" s="6" t="n">
+      <c r="D390" s="3" t="n">
         <v>70.27903101</v>
       </c>
       <c r="E390" t="n">
@@ -8725,10 +8830,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C391" s="5" t="n">
+      <c r="C391" s="2" t="n">
         <v>35429.86</v>
       </c>
-      <c r="D391" s="6" t="n">
+      <c r="D391" s="3" t="n">
         <v>13.31062066</v>
       </c>
       <c r="E391" t="n">
@@ -8746,10 +8851,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C392" s="5" t="n">
+      <c r="C392" s="2" t="n">
         <v>32122.79</v>
       </c>
-      <c r="D392" s="6" t="n">
+      <c r="D392" s="3" t="n">
         <v>12.06818972</v>
       </c>
       <c r="E392" t="n">
@@ -8767,10 +8872,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C393" s="5" t="n">
+      <c r="C393" s="2" t="n">
         <v>40536.38</v>
       </c>
-      <c r="D393" s="6" t="n">
+      <c r="D393" s="3" t="n">
         <v>15.22908578</v>
       </c>
       <c r="E393" t="n">
@@ -8788,10 +8893,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C394" s="5" t="n">
+      <c r="C394" s="2" t="n">
         <v>158088.34</v>
       </c>
-      <c r="D394" s="6" t="n">
+      <c r="D394" s="3" t="n">
         <v>59.39210384</v>
       </c>
       <c r="E394" t="n">
@@ -8809,10 +8914,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C395" s="5" t="n">
+      <c r="C395" s="2" t="n">
         <v>18675.56</v>
       </c>
-      <c r="D395" s="6" t="n">
+      <c r="D395" s="3" t="n">
         <v>5.96308598</v>
       </c>
       <c r="E395" t="n">
@@ -8830,10 +8935,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C396" s="5" t="n">
+      <c r="C396" s="2" t="n">
         <v>15011.7</v>
       </c>
-      <c r="D396" s="6" t="n">
+      <c r="D396" s="3" t="n">
         <v>4.79321947</v>
       </c>
       <c r="E396" t="n">
@@ -8851,10 +8956,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C397" s="5" t="n">
+      <c r="C397" s="2" t="n">
         <v>158704.71</v>
       </c>
-      <c r="D397" s="6" t="n">
+      <c r="D397" s="3" t="n">
         <v>50.67424116</v>
       </c>
       <c r="E397" t="n">
@@ -8872,10 +8977,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C398" s="5" t="n">
+      <c r="C398" s="2" t="n">
         <v>120794.19</v>
       </c>
-      <c r="D398" s="6" t="n">
+      <c r="D398" s="3" t="n">
         <v>38.56945339</v>
       </c>
       <c r="E398" t="n">
@@ -8893,10 +8998,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C399" s="5" t="n">
+      <c r="C399" s="2" t="n">
         <v>925.92</v>
       </c>
-      <c r="D399" s="6" t="n">
+      <c r="D399" s="3" t="n">
         <v>0.29872596</v>
       </c>
       <c r="E399" t="n">
@@ -8914,10 +9019,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C400" s="5" t="n">
+      <c r="C400" s="2" t="n">
         <v>2850.15</v>
       </c>
-      <c r="D400" s="6" t="n">
+      <c r="D400" s="3" t="n">
         <v>0.91953279</v>
       </c>
       <c r="E400" t="n">
@@ -8935,10 +9040,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C401" s="5" t="n">
+      <c r="C401" s="2" t="n">
         <v>6.62</v>
       </c>
-      <c r="D401" s="6" t="n">
+      <c r="D401" s="3" t="n">
         <v>0.00213578</v>
       </c>
       <c r="E401" t="n">
@@ -8956,10 +9061,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C402" s="5" t="n">
+      <c r="C402" s="2" t="n">
         <v>97008.50999999999</v>
       </c>
-      <c r="D402" s="6" t="n">
+      <c r="D402" s="3" t="n">
         <v>31.29747766</v>
       </c>
       <c r="E402" t="n">
@@ -8977,10 +9082,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C403" s="5" t="n">
+      <c r="C403" s="2" t="n">
         <v>209165.12</v>
       </c>
-      <c r="D403" s="6" t="n">
+      <c r="D403" s="3" t="n">
         <v>67.4821278</v>
       </c>
       <c r="E403" t="n">
@@ -8998,10 +9103,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C404" s="5" t="n">
+      <c r="C404" s="2" t="n">
         <v>1554.4</v>
       </c>
-      <c r="D404" s="6" t="n">
+      <c r="D404" s="3" t="n">
         <v>0.2805159</v>
       </c>
       <c r="E404" t="n">
@@ -9019,10 +9124,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C405" s="5" t="n">
+      <c r="C405" s="2" t="n">
         <v>13257.43</v>
       </c>
-      <c r="D405" s="6" t="n">
+      <c r="D405" s="3" t="n">
         <v>2.39251151</v>
       </c>
       <c r="E405" t="n">
@@ -9040,10 +9145,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C406" s="5" t="n">
+      <c r="C406" s="2" t="n">
         <v>68317.38</v>
       </c>
-      <c r="D406" s="6" t="n">
+      <c r="D406" s="3" t="n">
         <v>12.32894445</v>
       </c>
       <c r="E406" t="n">
@@ -9061,10 +9166,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C407" s="5" t="n">
+      <c r="C407" s="2" t="n">
         <v>36483.28</v>
       </c>
-      <c r="D407" s="6" t="n">
+      <c r="D407" s="3" t="n">
         <v>6.58398101</v>
       </c>
       <c r="E407" t="n">
@@ -9082,10 +9187,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C408" s="5" t="n">
+      <c r="C408" s="2" t="n">
         <v>434509.4</v>
       </c>
-      <c r="D408" s="6" t="n">
+      <c r="D408" s="3" t="n">
         <v>78.41404713</v>
       </c>
       <c r="E408" t="n">
@@ -9103,10 +9208,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C409" s="5" t="n">
+      <c r="C409" s="2" t="n">
         <v>84045.97</v>
       </c>
-      <c r="D409" s="6" t="n">
+      <c r="D409" s="3" t="n">
         <v>25.37763076</v>
       </c>
       <c r="E409" t="n">
@@ -9124,10 +9229,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C410" s="5" t="n">
+      <c r="C410" s="2" t="n">
         <v>3679.54</v>
       </c>
-      <c r="D410" s="6" t="n">
+      <c r="D410" s="3" t="n">
         <v>1.11103492</v>
       </c>
       <c r="E410" t="n">
@@ -9145,10 +9250,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C411" s="5" t="n">
+      <c r="C411" s="2" t="n">
         <v>1538.46</v>
       </c>
-      <c r="D411" s="6" t="n">
+      <c r="D411" s="3" t="n">
         <v>0.46453708</v>
       </c>
       <c r="E411" t="n">
@@ -9166,10 +9271,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C412" s="5" t="n">
+      <c r="C412" s="2" t="n">
         <v>26688.17</v>
       </c>
-      <c r="D412" s="6" t="n">
+      <c r="D412" s="3" t="n">
         <v>8.05847709</v>
       </c>
       <c r="E412" t="n">
@@ -9187,10 +9292,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C413" s="5" t="n">
+      <c r="C413" s="2" t="n">
         <v>215229.17</v>
       </c>
-      <c r="D413" s="6" t="n">
+      <c r="D413" s="3" t="n">
         <v>64.98832014</v>
       </c>
       <c r="E413" t="n">
@@ -9208,10 +9313,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C414" s="5" t="n">
+      <c r="C414" s="2" t="n">
         <v>6028.33</v>
       </c>
-      <c r="D414" s="6" t="n">
+      <c r="D414" s="3" t="n">
         <v>2.51184038</v>
       </c>
       <c r="E414" t="n">
@@ -9229,10 +9334,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="C415" s="5" t="n">
+      <c r="C415" s="2" t="n">
         <v>3112.84</v>
       </c>
-      <c r="D415" s="6" t="n">
+      <c r="D415" s="3" t="n">
         <v>1.29703537</v>
       </c>
       <c r="E415" t="n">
@@ -9250,10 +9355,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C416" s="5" t="n">
+      <c r="C416" s="2" t="n">
         <v>467.28</v>
       </c>
-      <c r="D416" s="6" t="n">
+      <c r="D416" s="3" t="n">
         <v>0.19470281</v>
       </c>
       <c r="E416" t="n">
@@ -9271,10 +9376,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C417" s="5" t="n">
+      <c r="C417" s="2" t="n">
         <v>2022.83</v>
       </c>
-      <c r="D417" s="6" t="n">
+      <c r="D417" s="3" t="n">
         <v>0.84285798</v>
       </c>
       <c r="E417" t="n">
@@ -9292,10 +9397,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C418" s="5" t="n">
+      <c r="C418" s="2" t="n">
         <v>25240.28</v>
       </c>
-      <c r="D418" s="6" t="n">
+      <c r="D418" s="3" t="n">
         <v>10.51693495</v>
       </c>
       <c r="E418" t="n">
@@ -9313,10 +9418,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C419" s="5" t="n">
+      <c r="C419" s="2" t="n">
         <v>203124.98</v>
       </c>
-      <c r="D419" s="6" t="n">
+      <c r="D419" s="3" t="n">
         <v>84.63662850999999</v>
       </c>
       <c r="E419" t="n">
@@ -9334,10 +9439,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C420" s="5" t="n">
+      <c r="C420" s="2" t="n">
         <v>4052.09</v>
       </c>
-      <c r="D420" s="6" t="n">
+      <c r="D420" s="3" t="n">
         <v>1.92281922</v>
       </c>
       <c r="E420" t="n">
@@ -9355,10 +9460,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="C421" s="5" t="n">
+      <c r="C421" s="2" t="n">
         <v>4783.33</v>
       </c>
-      <c r="D421" s="6" t="n">
+      <c r="D421" s="3" t="n">
         <v>2.2698111</v>
       </c>
       <c r="E421" t="n">
@@ -9376,10 +9481,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C422" s="5" t="n">
+      <c r="C422" s="2" t="n">
         <v>3694.66</v>
       </c>
-      <c r="D422" s="6" t="n">
+      <c r="D422" s="3" t="n">
         <v>1.75320964</v>
       </c>
       <c r="E422" t="n">
@@ -9397,10 +9502,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C423" s="5" t="n">
+      <c r="C423" s="2" t="n">
         <v>784.2</v>
       </c>
-      <c r="D423" s="6" t="n">
+      <c r="D423" s="3" t="n">
         <v>0.37212274</v>
       </c>
       <c r="E423" t="n">
@@ -9418,10 +9523,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C424" s="5" t="n">
+      <c r="C424" s="2" t="n">
         <v>36763.78</v>
       </c>
-      <c r="D424" s="6" t="n">
+      <c r="D424" s="3" t="n">
         <v>17.4453437</v>
       </c>
       <c r="E424" t="n">
@@ -9439,10 +9544,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C425" s="5" t="n">
+      <c r="C425" s="2" t="n">
         <v>160658.86</v>
       </c>
-      <c r="D425" s="6" t="n">
+      <c r="D425" s="3" t="n">
         <v>76.2366936</v>
       </c>
       <c r="E425" t="n">
@@ -9460,10 +9565,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C426" s="5" t="n">
+      <c r="C426" s="2" t="n">
         <v>632.91</v>
       </c>
-      <c r="D426" s="6" t="n">
+      <c r="D426" s="3" t="n">
         <v>0.28103066</v>
       </c>
       <c r="E426" t="n">
@@ -9481,10 +9586,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C427" s="5" t="n">
+      <c r="C427" s="2" t="n">
         <v>31634.55</v>
       </c>
-      <c r="D427" s="6" t="n">
+      <c r="D427" s="3" t="n">
         <v>14.04667104</v>
       </c>
       <c r="E427" t="n">
@@ -9502,10 +9607,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C428" s="5" t="n">
+      <c r="C428" s="2" t="n">
         <v>51.07</v>
       </c>
-      <c r="D428" s="6" t="n">
+      <c r="D428" s="3" t="n">
         <v>0.02267658</v>
       </c>
       <c r="E428" t="n">
@@ -9523,10 +9628,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C429" s="5" t="n">
+      <c r="C429" s="2" t="n">
         <v>8138.08</v>
       </c>
-      <c r="D429" s="6" t="n">
+      <c r="D429" s="3" t="n">
         <v>3.61354698</v>
       </c>
       <c r="E429" t="n">
@@ -9544,10 +9649,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C430" s="5" t="n">
+      <c r="C430" s="2" t="n">
         <v>184753.69</v>
       </c>
-      <c r="D430" s="6" t="n">
+      <c r="D430" s="3" t="n">
         <v>82.03607473</v>
       </c>
       <c r="E430" t="n">
@@ -9565,10 +9670,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C431" s="5" t="n">
+      <c r="C431" s="2" t="n">
         <v>370.37</v>
       </c>
-      <c r="D431" s="6" t="n">
+      <c r="D431" s="3" t="n">
         <v>0.12318944</v>
       </c>
       <c r="E431" t="n">
@@ -9586,10 +9691,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C432" s="5" t="n">
+      <c r="C432" s="2" t="n">
         <v>13374.33</v>
       </c>
-      <c r="D432" s="6" t="n">
+      <c r="D432" s="3" t="n">
         <v>4.44846025</v>
       </c>
       <c r="E432" t="n">
@@ -9607,10 +9712,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C433" s="5" t="n">
+      <c r="C433" s="2" t="n">
         <v>90262.50999999999</v>
       </c>
-      <c r="D433" s="6" t="n">
+      <c r="D433" s="3" t="n">
         <v>30.02237779</v>
       </c>
       <c r="E433" t="n">
@@ -9628,10 +9733,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C434" s="5" t="n">
+      <c r="C434" s="2" t="n">
         <v>196643.56</v>
       </c>
-      <c r="D434" s="6" t="n">
+      <c r="D434" s="3" t="n">
         <v>65.40597252000001</v>
       </c>
       <c r="E434" t="n">
@@ -9649,10 +9754,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C435" s="5" t="n">
+      <c r="C435" s="2" t="n">
         <v>24.5</v>
       </c>
-      <c r="D435" s="6" t="n">
+      <c r="D435" s="3" t="n">
         <v>0.00775989</v>
       </c>
       <c r="E435" t="n">
@@ -9670,10 +9775,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C436" s="5" t="n">
+      <c r="C436" s="2" t="n">
         <v>5137.53</v>
       </c>
-      <c r="D436" s="6" t="n">
+      <c r="D436" s="3" t="n">
         <v>1.62721069</v>
       </c>
       <c r="E436" t="n">
@@ -9691,10 +9796,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C437" s="5" t="n">
+      <c r="C437" s="2" t="n">
         <v>387.7</v>
       </c>
-      <c r="D437" s="6" t="n">
+      <c r="D437" s="3" t="n">
         <v>0.12279628</v>
       </c>
       <c r="E437" t="n">
@@ -9712,10 +9817,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C438" s="5" t="n">
+      <c r="C438" s="2" t="n">
         <v>69638.25999999999</v>
       </c>
-      <c r="D438" s="6" t="n">
+      <c r="D438" s="3" t="n">
         <v>22.05653716</v>
       </c>
       <c r="E438" t="n">
@@ -9733,10 +9838,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C439" s="5" t="n">
+      <c r="C439" s="2" t="n">
         <v>240538.18</v>
       </c>
-      <c r="D439" s="6" t="n">
+      <c r="D439" s="3" t="n">
         <v>76.18569598000001</v>
       </c>
       <c r="E439" t="n">
@@ -9754,10 +9859,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C440" s="5" t="n">
+      <c r="C440" s="2" t="n">
         <v>11292.41</v>
       </c>
-      <c r="D440" s="6" t="n">
+      <c r="D440" s="3" t="n">
         <v>5.00321928</v>
       </c>
       <c r="E440" t="n">
@@ -9775,10 +9880,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C441" s="5" t="n">
+      <c r="C441" s="2" t="n">
         <v>5806.79</v>
       </c>
-      <c r="D441" s="6" t="n">
+      <c r="D441" s="3" t="n">
         <v>2.57275849</v>
       </c>
       <c r="E441" t="n">
@@ -9796,10 +9901,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C442" s="5" t="n">
+      <c r="C442" s="2" t="n">
         <v>5227.27</v>
       </c>
-      <c r="D442" s="6" t="n">
+      <c r="D442" s="3" t="n">
         <v>2.31599615</v>
       </c>
       <c r="E442" t="n">
@@ -9817,10 +9922,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C443" s="5" t="n">
+      <c r="C443" s="2" t="n">
         <v>44798.68</v>
       </c>
-      <c r="D443" s="6" t="n">
+      <c r="D443" s="3" t="n">
         <v>19.84851943</v>
       </c>
       <c r="E443" t="n">
@@ -9838,10 +9943,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C444" s="5" t="n">
+      <c r="C444" s="2" t="n">
         <v>158577.73</v>
       </c>
-      <c r="D444" s="6" t="n">
+      <c r="D444" s="3" t="n">
         <v>70.25950666</v>
       </c>
       <c r="E444" t="n">
@@ -9859,10 +9964,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C445" s="5" t="n">
+      <c r="C445" s="2" t="n">
         <v>4.65</v>
       </c>
-      <c r="D445" s="6" t="n">
+      <c r="D445" s="3" t="n">
         <v>0.00087428</v>
       </c>
       <c r="E445" t="n">
@@ -9880,10 +9985,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C446" s="5" t="n">
+      <c r="C446" s="2" t="n">
         <v>27501.45</v>
       </c>
-      <c r="D446" s="6" t="n">
+      <c r="D446" s="3" t="n">
         <v>5.17072427</v>
       </c>
       <c r="E446" t="n">
@@ -9901,10 +10006,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C447" s="5" t="n">
+      <c r="C447" s="2" t="n">
         <v>162.95</v>
       </c>
-      <c r="D447" s="6" t="n">
+      <c r="D447" s="3" t="n">
         <v>0.03063728</v>
       </c>
       <c r="E447" t="n">
@@ -9922,10 +10027,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C448" s="5" t="n">
+      <c r="C448" s="2" t="n">
         <v>27839.02</v>
       </c>
-      <c r="D448" s="6" t="n">
+      <c r="D448" s="3" t="n">
         <v>5.23419298</v>
       </c>
       <c r="E448" t="n">
@@ -9943,10 +10048,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C449" s="5" t="n">
+      <c r="C449" s="2" t="n">
         <v>476360.36</v>
       </c>
-      <c r="D449" s="6" t="n">
+      <c r="D449" s="3" t="n">
         <v>89.5635712</v>
       </c>
       <c r="E449" t="n">
@@ -9964,10 +10069,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C450" s="5" t="n">
+      <c r="C450" s="2" t="n">
         <v>822.03</v>
       </c>
-      <c r="D450" s="6" t="n">
+      <c r="D450" s="3" t="n">
         <v>0.77226073</v>
       </c>
       <c r="E450" t="n">
@@ -9985,10 +10090,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C451" s="5" t="n">
+      <c r="C451" s="2" t="n">
         <v>1928.09</v>
       </c>
-      <c r="D451" s="6" t="n">
+      <c r="D451" s="3" t="n">
         <v>1.81135505</v>
       </c>
       <c r="E451" t="n">
@@ -10006,10 +10111,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C452" s="5" t="n">
+      <c r="C452" s="2" t="n">
         <v>19728.18</v>
       </c>
-      <c r="D452" s="6" t="n">
+      <c r="D452" s="3" t="n">
         <v>18.53375023</v>
       </c>
       <c r="E452" t="n">
@@ -10027,10 +10132,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C453" s="5" t="n">
+      <c r="C453" s="2" t="n">
         <v>83966.32000000001</v>
       </c>
-      <c r="D453" s="6" t="n">
+      <c r="D453" s="3" t="n">
         <v>78.88263399</v>
       </c>
       <c r="E453" t="n">
@@ -10048,10 +10153,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C454" s="5" t="n">
+      <c r="C454" s="2" t="n">
         <v>11929.86</v>
       </c>
-      <c r="D454" s="6" t="n">
+      <c r="D454" s="3" t="n">
         <v>17.33404491</v>
       </c>
       <c r="E454" t="n">
@@ -10069,10 +10174,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C455" s="5" t="n">
+      <c r="C455" s="2" t="n">
         <v>9020.1</v>
       </c>
-      <c r="D455" s="6" t="n">
+      <c r="D455" s="3" t="n">
         <v>13.1061738</v>
       </c>
       <c r="E455" t="n">
@@ -10090,10 +10195,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C456" s="5" t="n">
+      <c r="C456" s="2" t="n">
         <v>47873.33</v>
       </c>
-      <c r="D456" s="6" t="n">
+      <c r="D456" s="3" t="n">
         <v>69.55978129</v>
       </c>
       <c r="E456" t="n">
@@ -10111,10 +10216,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C457" s="5" t="n">
+      <c r="C457" s="2" t="n">
         <v>22.76</v>
       </c>
-      <c r="D457" s="6" t="n">
+      <c r="D457" s="3" t="n">
         <v>0.01502378</v>
       </c>
       <c r="E457" t="n">
@@ -10132,10 +10237,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C458" s="5" t="n">
+      <c r="C458" s="2" t="n">
         <v>9530.34</v>
       </c>
-      <c r="D458" s="6" t="n">
+      <c r="D458" s="3" t="n">
         <v>6.29093708</v>
       </c>
       <c r="E458" t="n">
@@ -10153,10 +10258,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C459" s="5" t="n">
+      <c r="C459" s="2" t="n">
         <v>10214.3</v>
       </c>
-      <c r="D459" s="6" t="n">
+      <c r="D459" s="3" t="n">
         <v>6.74241618</v>
       </c>
       <c r="E459" t="n">
@@ -10174,10 +10279,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C460" s="5" t="n">
+      <c r="C460" s="2" t="n">
         <v>27605.06</v>
       </c>
-      <c r="D460" s="6" t="n">
+      <c r="D460" s="3" t="n">
         <v>18.22198321</v>
       </c>
       <c r="E460" t="n">
@@ -10195,10 +10300,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C461" s="5" t="n">
+      <c r="C461" s="2" t="n">
         <v>104120.71</v>
       </c>
-      <c r="D461" s="6" t="n">
+      <c r="D461" s="3" t="n">
         <v>68.72963976</v>
       </c>
       <c r="E461" t="n">
@@ -10216,10 +10321,10 @@
           <t>Crypto</t>
         </is>
       </c>
-      <c r="C462" s="5" t="n">
+      <c r="C462" s="2" t="n">
         <v>769.23</v>
       </c>
-      <c r="D462" s="6" t="n">
+      <c r="D462" s="3" t="n">
         <v>0.38771701</v>
       </c>
       <c r="E462" t="n">
@@ -10237,10 +10342,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C463" s="5" t="n">
+      <c r="C463" s="2" t="n">
         <v>521.15</v>
       </c>
-      <c r="D463" s="6" t="n">
+      <c r="D463" s="3" t="n">
         <v>0.2626766</v>
       </c>
       <c r="E463" t="n">
@@ -10258,10 +10363,10 @@
           <t>Sports</t>
         </is>
       </c>
-      <c r="C464" s="5" t="n">
+      <c r="C464" s="2" t="n">
         <v>701.92</v>
       </c>
-      <c r="D464" s="6" t="n">
+      <c r="D464" s="3" t="n">
         <v>0.35379057</v>
       </c>
       <c r="E464" t="n">
@@ -10279,10 +10384,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C465" s="5" t="n">
+      <c r="C465" s="2" t="n">
         <v>45400.43</v>
       </c>
-      <c r="D465" s="6" t="n">
+      <c r="D465" s="3" t="n">
         <v>22.8832974</v>
       </c>
       <c r="E465" t="n">
@@ -10300,10 +10405,10 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C466" s="5" t="n">
+      <c r="C466" s="2" t="n">
         <v>151007.13</v>
       </c>
-      <c r="D466" s="6" t="n">
+      <c r="D466" s="3" t="n">
         <v>76.11251842999999</v>
       </c>
       <c r="E466" t="n">
@@ -10321,10 +10426,10 @@
           <t>Business/Economy</t>
         </is>
       </c>
-      <c r="C467" s="5" t="n">
+      <c r="C467" s="2" t="n">
         <v>16710.66</v>
       </c>
-      <c r="D467" s="6" t="n">
+      <c r="D467" s="3" t="n">
         <v>9.58302746</v>
       </c>
       <c r="E467" t="n">
@@ -10342,10 +10447,10 @@
           <t>Geopolitics</t>
         </is>
       </c>
-      <c r="C468" s="5" t="n">
+      <c r="C468" s="2" t="n">
         <v>294.11</v>
       </c>
-      <c r="D468" s="6" t="n">
+      <c r="D468" s="3" t="n">
         <v>0.16866265</v>
       </c>
       <c r="E468" t="n">
@@ -10363,10 +10468,10 @@
           <t>Tech &amp; Science</t>
         </is>
       </c>
-      <c r="C469" s="5" t="n">
+      <c r="C469" s="2" t="n">
         <v>45149.15</v>
       </c>
-      <c r="D469" s="6" t="n">
+      <c r="D469" s="3" t="n">
         <v>25.89158922</v>
       </c>
       <c r="E469" t="n">
@@ -10384,14 +10489,119 @@
           <t>Unclassified</t>
         </is>
       </c>
-      <c r="C470" s="5" t="n">
+      <c r="C470" s="2" t="n">
         <v>112223.75</v>
       </c>
-      <c r="D470" s="6" t="n">
+      <c r="D470" s="3" t="n">
         <v>64.35672067</v>
       </c>
       <c r="E470" t="n">
         <v>120</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>Business/Economy</t>
+        </is>
+      </c>
+      <c r="C471" s="2" t="n">
+        <v>2631.57</v>
+      </c>
+      <c r="D471" s="3" t="n">
+        <v>1.49459218</v>
+      </c>
+      <c r="E471" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="C472" s="2" t="n">
+        <v>75.34999999999999</v>
+      </c>
+      <c r="D472" s="3" t="n">
+        <v>0.0427948</v>
+      </c>
+      <c r="E472" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C473" s="2" t="n">
+        <v>2884.61</v>
+      </c>
+      <c r="D473" s="3" t="n">
+        <v>1.63830548</v>
+      </c>
+      <c r="E473" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C474" s="2" t="n">
+        <v>29126.64</v>
+      </c>
+      <c r="D474" s="3" t="n">
+        <v>16.54238662</v>
+      </c>
+      <c r="E474" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C475" s="2" t="n">
+        <v>141354.61</v>
+      </c>
+      <c r="D475" s="3" t="n">
+        <v>80.28192092</v>
+      </c>
+      <c r="E475" t="n">
+        <v>143</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/kalshi_cumulative_topic_share.xlsx
+++ b/docs/data/kalshi_cumulative_topic_share.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -479,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -488,19 +488,19 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>141354.61</v>
+        <v>174195.15</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>80.28192092</v>
+        <v>72.46717971</v>
       </c>
       <c r="E2" t="n">
-        <v>143</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>29126.64</v>
+        <v>44381</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>16.54238662</v>
+        <v>18.46300487</v>
       </c>
       <c r="E3" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-31</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,76 +530,34 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>2884.61</v>
+        <v>21801.84</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1.63830548</v>
+        <v>9.069815419999999</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Business/Economy</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>2631.57</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>1.49459218</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Crypto</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>75.34999999999999</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0.0427948</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="C7" s="5" t="n">
-        <v>176072.78</v>
-      </c>
-      <c r="D7" s="6" t="n">
+      <c r="C5" s="5" t="n">
+        <v>240377.99</v>
+      </c>
+      <c r="D5" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="E7" s="4" t="n">
-        <v>178</v>
+      <c r="E5" s="4" t="n">
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -613,7 +571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E475"/>
+  <dimension ref="A1:E478"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10604,6 +10562,69 @@
         <v>143</v>
       </c>
     </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>Geopolitics</t>
+        </is>
+      </c>
+      <c r="C476" s="2" t="n">
+        <v>21801.84</v>
+      </c>
+      <c r="D476" s="3" t="n">
+        <v>9.069815419999999</v>
+      </c>
+      <c r="E476" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>Tech &amp; Science</t>
+        </is>
+      </c>
+      <c r="C477" s="2" t="n">
+        <v>44381</v>
+      </c>
+      <c r="D477" s="3" t="n">
+        <v>18.46300487</v>
+      </c>
+      <c r="E477" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
+        </is>
+      </c>
+      <c r="C478" s="2" t="n">
+        <v>174195.15</v>
+      </c>
+      <c r="D478" s="3" t="n">
+        <v>72.46717971</v>
+      </c>
+      <c r="E478" t="n">
+        <v>110</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
